--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -6382,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X101" s="1" t="n">
         <v>46285</v>
@@ -7947,7 +7947,7 @@
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X128" s="1" t="n">
         <v>46285</v>
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="T193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U193" t="n">
         <v>0</v>
@@ -11766,7 +11766,7 @@
         <v>0</v>
       </c>
       <c r="W193" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="X193" s="1" t="n">
         <v>46283</v>
@@ -12233,13 +12233,13 @@
         </is>
       </c>
       <c r="T201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U201" t="n">
-        <v>120.97</v>
+        <v>153.6</v>
       </c>
       <c r="V201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W201" t="n">
         <v>0</v>
@@ -12836,7 +12836,7 @@
         <v>0</v>
       </c>
       <c r="W211" t="n">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="X211" s="1" t="n">
         <v>46242</v>
@@ -15821,7 +15821,7 @@
         <v>0</v>
       </c>
       <c r="W262" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X262" s="1" t="n">
         <v>46282</v>
@@ -16515,13 +16515,13 @@
         <v>1</v>
       </c>
       <c r="U274" t="n">
-        <v>9.99</v>
+        <v>19.98</v>
       </c>
       <c r="V274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W274" t="n">
-        <v>88</v>
+        <v>224</v>
       </c>
       <c r="X274" s="1" t="n">
         <v>46285</v>
@@ -16997,7 +16997,7 @@
         <v>0</v>
       </c>
       <c r="W282" t="n">
-        <v>15876</v>
+        <v>19150</v>
       </c>
       <c r="X282" s="1" t="n">
         <v>46282</v>
@@ -19164,7 +19164,7 @@
         <v>0</v>
       </c>
       <c r="W319" t="n">
-        <v>214</v>
+        <v>314</v>
       </c>
       <c r="X319" s="1" t="n">
         <v>46285</v>
@@ -24276,7 +24276,7 @@
         <v>2</v>
       </c>
       <c r="W407" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="X407" s="1" t="n">
         <v>46281</v>
@@ -28758,15 +28758,27 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T484" t="inlineStr"/>
-      <c r="U484" t="inlineStr"/>
-      <c r="V484" t="inlineStr"/>
-      <c r="W484" t="inlineStr"/>
-      <c r="X484" t="inlineStr"/>
-      <c r="Y484" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T484" t="n">
+        <v>1</v>
+      </c>
+      <c r="U484" t="n">
+        <v>0</v>
+      </c>
+      <c r="V484" t="n">
+        <v>0</v>
+      </c>
+      <c r="W484" t="n">
+        <v>4</v>
+      </c>
+      <c r="X484" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="Y484" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -29117,7 +29129,7 @@
         <v>0</v>
       </c>
       <c r="W490" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="X490" s="1" t="n">
         <v>46282</v>
@@ -33616,7 +33628,7 @@
         <v>1</v>
       </c>
       <c r="W567" t="n">
-        <v>3824</v>
+        <v>3855</v>
       </c>
       <c r="X567" s="1" t="n">
         <v>46278</v>
@@ -33843,15 +33855,27 @@
       </c>
       <c r="S571" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T571" t="inlineStr"/>
-      <c r="U571" t="inlineStr"/>
-      <c r="V571" t="inlineStr"/>
-      <c r="W571" t="inlineStr"/>
-      <c r="X571" t="inlineStr"/>
-      <c r="Y571" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T571" t="n">
+        <v>1</v>
+      </c>
+      <c r="U571" t="n">
+        <v>0</v>
+      </c>
+      <c r="V571" t="n">
+        <v>0</v>
+      </c>
+      <c r="W571" t="n">
+        <v>54</v>
+      </c>
+      <c r="X571" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="Y571" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -35598,7 +35622,7 @@
         <v>0</v>
       </c>
       <c r="W601" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X601" s="1" t="n">
         <v>46284</v>
@@ -36994,7 +37018,7 @@
         <v>0</v>
       </c>
       <c r="W625" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X625" s="1" t="n">
         <v>46271</v>
@@ -41556,7 +41580,7 @@
         <v>1</v>
       </c>
       <c r="W703" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="X703" s="1" t="n">
         <v>46283</v>
@@ -48345,13 +48369,13 @@
         <v>1</v>
       </c>
       <c r="U820" t="n">
-        <v>2799.51</v>
+        <v>3135.27</v>
       </c>
       <c r="V820" t="n">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="W820" t="n">
-        <v>222517</v>
+        <v>255066</v>
       </c>
       <c r="X820" s="1" t="n">
         <v>46279</v>
@@ -48994,13 +49018,13 @@
         <v>4</v>
       </c>
       <c r="U831" t="n">
-        <v>0</v>
+        <v>42.89</v>
       </c>
       <c r="V831" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W831" t="n">
-        <v>202</v>
+        <v>499</v>
       </c>
       <c r="X831" s="1" t="n">
         <v>46283</v>
@@ -49932,7 +49956,7 @@
         <v>0</v>
       </c>
       <c r="W847" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X847" s="1" t="n">
         <v>46282</v>
@@ -50707,7 +50731,7 @@
         <v>0</v>
       </c>
       <c r="W860" t="n">
-        <v>124</v>
+        <v>260</v>
       </c>
       <c r="X860" s="1" t="n">
         <v>46285</v>
@@ -53742,15 +53766,27 @@
       </c>
       <c r="S912" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T912" t="inlineStr"/>
-      <c r="U912" t="inlineStr"/>
-      <c r="V912" t="inlineStr"/>
-      <c r="W912" t="inlineStr"/>
-      <c r="X912" t="inlineStr"/>
-      <c r="Y912" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T912" t="n">
+        <v>1</v>
+      </c>
+      <c r="U912" t="n">
+        <v>0</v>
+      </c>
+      <c r="V912" t="n">
+        <v>0</v>
+      </c>
+      <c r="W912" t="n">
+        <v>271</v>
+      </c>
+      <c r="X912" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="Y912" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -53979,7 +54015,7 @@
         <v>0</v>
       </c>
       <c r="W916" t="n">
-        <v>295</v>
+        <v>407</v>
       </c>
       <c r="X916" s="1" t="n">
         <v>46284</v>
@@ -54337,13 +54373,13 @@
         <v>0</v>
       </c>
       <c r="W922" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="X922" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="Y922" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="923">
@@ -55980,16 +56016,16 @@
         </is>
       </c>
       <c r="T950" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U950" t="n">
-        <v>59.94</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="V950" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W950" t="n">
-        <v>1873</v>
+        <v>2777</v>
       </c>
       <c r="X950" s="1" t="n">
         <v>46281</v>
@@ -56448,15 +56484,27 @@
       </c>
       <c r="S958" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T958" t="inlineStr"/>
-      <c r="U958" t="inlineStr"/>
-      <c r="V958" t="inlineStr"/>
-      <c r="W958" t="inlineStr"/>
-      <c r="X958" t="inlineStr"/>
-      <c r="Y958" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T958" t="n">
+        <v>1</v>
+      </c>
+      <c r="U958" t="n">
+        <v>0</v>
+      </c>
+      <c r="V958" t="n">
+        <v>0</v>
+      </c>
+      <c r="W958" t="n">
+        <v>19</v>
+      </c>
+      <c r="X958" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="Y958" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -12379,13 +12379,13 @@
         <v>0</v>
       </c>
       <c r="W204" t="n">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="X204" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="Y204" t="n">
-        <v>-38</v>
+        <v>-37</v>
       </c>
     </row>
     <row r="205">
@@ -17203,15 +17203,27 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T287" t="inlineStr"/>
-      <c r="U287" t="inlineStr"/>
-      <c r="V287" t="inlineStr"/>
-      <c r="W287" t="inlineStr"/>
-      <c r="X287" t="inlineStr"/>
-      <c r="Y287" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T287" t="n">
+        <v>3</v>
+      </c>
+      <c r="U287" t="n">
+        <v>0</v>
+      </c>
+      <c r="V287" t="n">
+        <v>0</v>
+      </c>
+      <c r="W287" t="n">
+        <v>24</v>
+      </c>
+      <c r="X287" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -63619,15 +63631,27 @@
       </c>
       <c r="S1087" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T1087" t="inlineStr"/>
-      <c r="U1087" t="inlineStr"/>
-      <c r="V1087" t="inlineStr"/>
-      <c r="W1087" t="inlineStr"/>
-      <c r="X1087" t="inlineStr"/>
-      <c r="Y1087" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T1087" t="n">
+        <v>2</v>
+      </c>
+      <c r="U1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1087" t="n">
+        <v>237</v>
+      </c>
+      <c r="X1087" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="Y1087" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
@@ -66875,27 +66899,15 @@
       </c>
       <c r="S1143" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T1143" t="n">
-        <v>1</v>
-      </c>
-      <c r="U1143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V1143" t="n">
-        <v>0</v>
-      </c>
-      <c r="W1143" t="n">
-        <v>1</v>
-      </c>
-      <c r="X1143" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="Y1143" t="n">
-        <v>21</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T1143" t="inlineStr"/>
+      <c r="U1143" t="inlineStr"/>
+      <c r="V1143" t="inlineStr"/>
+      <c r="W1143" t="inlineStr"/>
+      <c r="X1143" t="inlineStr"/>
+      <c r="Y1143" t="inlineStr"/>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="312">
   <si>
     <t>handle</t>
   </si>
@@ -91,57 +91,24 @@
     <t>days_to_first_video</t>
   </si>
   <si>
-    <t>_life_of_dc</t>
-  </si>
-  <si>
-    <t>a.williamsonx</t>
-  </si>
-  <si>
     <t>adwoafrimpong7</t>
   </si>
   <si>
     <t>ak786786786786786fk</t>
   </si>
   <si>
-    <t>angelagrove5</t>
-  </si>
-  <si>
     <t>annredfearn1</t>
   </si>
   <si>
-    <t>approvedvault</t>
-  </si>
-  <si>
-    <t>balogundamilola8</t>
-  </si>
-  <si>
-    <t>bargain.hunter.mum.2</t>
-  </si>
-  <si>
     <t>beauty.baddie.444</t>
   </si>
   <si>
-    <t>begumasma75</t>
-  </si>
-  <si>
-    <t>brookeleighofficial</t>
-  </si>
-  <si>
-    <t>brumgirllibby</t>
-  </si>
-  <si>
     <t>brunozpage</t>
   </si>
   <si>
     <t>celaniklozet</t>
   </si>
   <si>
-    <t>celestialcreations1981</t>
-  </si>
-  <si>
-    <t>chelsea..gallagherxox</t>
-  </si>
-  <si>
     <t>chivequeen5</t>
   </si>
   <si>
@@ -151,27 +118,18 @@
     <t>clarasdiary28</t>
   </si>
   <si>
-    <t>coolestinfluencer1</t>
-  </si>
-  <si>
     <t>craigkennethmccal</t>
   </si>
   <si>
     <t>dad_nails_tiktok</t>
   </si>
   <si>
-    <t>dealchefshops</t>
-  </si>
-  <si>
     <t>debsline.co</t>
   </si>
   <si>
     <t>deenreminders0786</t>
   </si>
   <si>
-    <t>earnwithtrisjay</t>
-  </si>
-  <si>
     <t>elizabeth.haigh3</t>
   </si>
   <si>
@@ -238,15 +196,9 @@
     <t>homeandlifefinds2</t>
   </si>
   <si>
-    <t>hunbea91</t>
-  </si>
-  <si>
     <t>huzair329</t>
   </si>
   <si>
-    <t>itsh1yk</t>
-  </si>
-  <si>
     <t>jadexoxo93</t>
   </si>
   <si>
@@ -289,60 +241,30 @@
     <t>krfindsuk</t>
   </si>
   <si>
-    <t>lauu2tiktokshop</t>
-  </si>
-  <si>
     <t>lesliepeckback1</t>
   </si>
   <si>
-    <t>lifeassamantha</t>
-  </si>
-  <si>
-    <t>lifewithsabz</t>
-  </si>
-  <si>
     <t>lindastubbs88</t>
   </si>
   <si>
-    <t>lisaugccreator2</t>
-  </si>
-  <si>
-    <t>lorentviralcart</t>
-  </si>
-  <si>
     <t>mah70178</t>
   </si>
   <si>
     <t>mairashopuk0</t>
   </si>
   <si>
-    <t>makesenseadhd</t>
-  </si>
-  <si>
-    <t>maria_london7</t>
-  </si>
-  <si>
     <t>marjorie.binks</t>
   </si>
   <si>
-    <t>mart_jireh</t>
-  </si>
-  <si>
     <t>martinsmissen</t>
   </si>
   <si>
-    <t>marvel_ola21</t>
-  </si>
-  <si>
     <t>may506162</t>
   </si>
   <si>
     <t>melissavanzan236</t>
   </si>
   <si>
-    <t>mo1reviews</t>
-  </si>
-  <si>
     <t>mrs.a.saim</t>
   </si>
   <si>
@@ -355,18 +277,12 @@
     <t>nadiabeeh1</t>
   </si>
   <si>
-    <t>nailajinam</t>
-  </si>
-  <si>
     <t>nanaeruramadoris</t>
   </si>
   <si>
     <t>nazobasket</t>
   </si>
   <si>
-    <t>ngvic.lifestyle</t>
-  </si>
-  <si>
     <t>nicki.sayce</t>
   </si>
   <si>
@@ -388,9 +304,6 @@
     <t>peachyfindsuk</t>
   </si>
   <si>
-    <t>philomema12</t>
-  </si>
-  <si>
     <t>pickandmix1</t>
   </si>
   <si>
@@ -406,9 +319,6 @@
     <t>rainydaysdeals</t>
   </si>
   <si>
-    <t>ranilifestylehub</t>
-  </si>
-  <si>
     <t>realbeautylondon</t>
   </si>
   <si>
@@ -418,9 +328,6 @@
     <t>rileys.gallery</t>
   </si>
   <si>
-    <t>ritaotv1</t>
-  </si>
-  <si>
     <t>s.asif11</t>
   </si>
   <si>
@@ -454,9 +361,6 @@
     <t>silentforever92</t>
   </si>
   <si>
-    <t>simonaba</t>
-  </si>
-  <si>
     <t>smartukfinds_</t>
   </si>
   <si>
@@ -508,9 +412,6 @@
     <t>tiktokshopbestbuys4</t>
   </si>
   <si>
-    <t>tiktopshopuk</t>
-  </si>
-  <si>
     <t>tinae38</t>
   </si>
   <si>
@@ -526,12 +427,6 @@
     <t>user8008669545474</t>
   </si>
   <si>
-    <t>uzmaashfaq</t>
-  </si>
-  <si>
-    <t>verasfinds</t>
-  </si>
-  <si>
     <t>vision.rift</t>
   </si>
   <si>
@@ -571,57 +466,24 @@
     <t>zynislam2</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@_life_of_dc</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@a.williamsonx</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@adwoafrimpong7</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@ak786786786786786fk</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@angelagrove5</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@annredfearn1</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@approvedvault</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@balogundamilola8</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@bargain.hunter.mum.2</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@beauty.baddie.444</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@begumasma75</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@brookeleighofficial</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@brumgirllibby</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@brunozpage</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@celaniklozet</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@celestialcreations1981</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@chelsea..gallagherxox</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@chivequeen5</t>
   </si>
   <si>
@@ -631,27 +493,18 @@
     <t>https://www.tiktok.com/@clarasdiary28</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@coolestinfluencer1</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@craigkennethmccal</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@dad_nails_tiktok</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@dealchefshops</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@debsline.co</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@deenreminders0786</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@earnwithtrisjay</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@elizabeth.haigh3</t>
   </si>
   <si>
@@ -718,15 +571,9 @@
     <t>https://www.tiktok.com/@homeandlifefinds2</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@hunbea91</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@huzair329</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@itsh1yk</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@jadexoxo93</t>
   </si>
   <si>
@@ -769,60 +616,30 @@
     <t>https://www.tiktok.com/@krfindsuk</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@lauu2tiktokshop</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@lesliepeckback1</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@lifeassamantha</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@lifewithsabz</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@lindastubbs88</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@lisaugccreator2</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@lorentviralcart</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@mah70178</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@mairashopuk0</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@makesenseadhd</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@maria_london7</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@marjorie.binks</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@mart_jireh</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@martinsmissen</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@marvel_ola21</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@may506162</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@melissavanzan236</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@mo1reviews</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@mrs.a.saim</t>
   </si>
   <si>
@@ -835,18 +652,12 @@
     <t>https://www.tiktok.com/@nadiabeeh1</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@nailajinam</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@nanaeruramadoris</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@nazobasket</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@ngvic.lifestyle</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@nicki.sayce</t>
   </si>
   <si>
@@ -868,9 +679,6 @@
     <t>https://www.tiktok.com/@peachyfindsuk</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@philomema12</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@pickandmix1</t>
   </si>
   <si>
@@ -886,9 +694,6 @@
     <t>https://www.tiktok.com/@rainydaysdeals</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@ranilifestylehub</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@realbeautylondon</t>
   </si>
   <si>
@@ -898,9 +703,6 @@
     <t>https://www.tiktok.com/@rileys.gallery</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@ritaotv1</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@s.asif11</t>
   </si>
   <si>
@@ -934,9 +736,6 @@
     <t>https://www.tiktok.com/@silentforever92</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@simonaba</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@smartukfinds_</t>
   </si>
   <si>
@@ -988,9 +787,6 @@
     <t>https://www.tiktok.com/@tiktokshopbestbuys4</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@tiktopshopuk</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@tinae38</t>
   </si>
   <si>
@@ -1006,12 +802,6 @@
     <t>https://www.tiktok.com/@user8008669545474</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@uzmaashfaq</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@verasfinds</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@vision.rift</t>
   </si>
   <si>
@@ -1063,12 +853,12 @@
     <t>35-44</t>
   </si>
   <si>
+    <t>Not found</t>
+  </si>
+  <si>
     <t>White/European</t>
   </si>
   <si>
-    <t>Not found</t>
-  </si>
-  <si>
     <t>Black/African</t>
   </si>
   <si>
@@ -1093,33 +883,27 @@
     <t>Household Appliances, Kitchenware, Toys &amp; Hobbies</t>
   </si>
   <si>
+    <t>Green Burner</t>
+  </si>
+  <si>
     <t>Ashwagandha Coffee</t>
   </si>
   <si>
-    <t>Green Burner</t>
-  </si>
-  <si>
     <t>Ashwagandha Coffee, Green Burner, Gut Shift, Skin Radiance, Turmeric Curcumin</t>
   </si>
   <si>
-    <t>Spearmint</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Green Burner, Gut Shift</t>
-  </si>
-  <si>
     <t>Ashwagandha Coffee, Green Burner, Turmeric Curcumin</t>
   </si>
   <si>
+    <t>Ashwagandha Coffee, Shatavari</t>
+  </si>
+  <si>
+    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Turmeric Curcumin</t>
+  </si>
+  <si>
     <t>Ashwagandha Coffee, Green Burner</t>
   </si>
   <si>
-    <t>Ashwagandha Coffee, Shatavari</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Turmeric Curcumin</t>
-  </si>
-  <si>
     <t>Ashwagandha Capsules, Ashwagandha Coffee, Green Burner, Gut Shift, Hibiscus, Spearmint, Turmeric Curcumin</t>
   </si>
   <si>
@@ -1132,34 +916,34 @@
     <t>Ashwagandha Coffee, Skin Radiance, Turmeric Curcumin</t>
   </si>
   <si>
+    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Skin Radiance</t>
+  </si>
+  <si>
+    <t>Advent Teas of Joy</t>
+  </si>
+  <si>
+    <t>Gut Shift, Skin Radiance</t>
+  </si>
+  <si>
+    <t>Ashwagandha Coffee, Green Burner, Skin Radiance</t>
+  </si>
+  <si>
+    <t>Green Burner, Gut Shift, Skin Radiance, Turmeric Curcumin</t>
+  </si>
+  <si>
     <t>Hibiscus</t>
   </si>
   <si>
-    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Skin Radiance</t>
-  </si>
-  <si>
-    <t>Advent Teas of Joy</t>
-  </si>
-  <si>
-    <t>Gut Shift, Skin Radiance</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Green Burner, Skin Radiance</t>
-  </si>
-  <si>
-    <t>Green Burner, Gut Shift, Skin Radiance, Turmeric Curcumin</t>
-  </si>
-  <si>
     <t>Turmeric Curcumin</t>
   </si>
   <si>
     <t>TikTok Shop (FBT)</t>
   </si>
   <si>
+    <t>TikTok Shop (FBT), seller</t>
+  </si>
+  <si>
     <t>seller</t>
-  </si>
-  <si>
-    <t>TikTok Shop (FBT), seller</t>
   </si>
   <si>
     <t>No</t>
@@ -1540,7 +1324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y161"/>
+  <dimension ref="A1:Y126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1625,28 +1409,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>185</v>
+        <v>150</v>
+      </c>
+      <c r="I2" t="s">
+        <v>279</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>359</v>
+        <v>289</v>
       </c>
       <c r="O2" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P2" s="3">
-        <v>46314.39734953704</v>
+        <v>46028.62637731482</v>
       </c>
       <c r="Q2" s="3">
-        <v>46314.39734953704</v>
+        <v>46028.62637731482</v>
       </c>
       <c r="R2">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="S2" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1654,31 +1441,31 @@
         <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="I3" t="s">
-        <v>349</v>
+        <v>279</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O3" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P3" s="3">
-        <v>46221.58803240741</v>
+        <v>45998.88378472222</v>
       </c>
       <c r="Q3" s="3">
-        <v>46221.58803240741</v>
+        <v>45998.88378472222</v>
       </c>
       <c r="R3">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S3" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1686,31 +1473,31 @@
         <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="I4" t="s">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="O4" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P4" s="3">
-        <v>46028.62637731482</v>
+        <v>45986.77690972222</v>
       </c>
       <c r="Q4" s="3">
-        <v>46028.62637731482</v>
+        <v>45986.77690972222</v>
       </c>
       <c r="R4">
-        <v>5.64</v>
+        <v>5.69</v>
       </c>
       <c r="S4" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1718,31 +1505,31 @@
         <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="I5" t="s">
-        <v>350</v>
+        <v>281</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O5" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P5" s="3">
-        <v>45998.88378472222</v>
+        <v>45911.17809027778</v>
       </c>
       <c r="Q5" s="3">
-        <v>45998.88378472222</v>
+        <v>45911.17809027778</v>
       </c>
       <c r="R5">
         <v>9.31</v>
       </c>
       <c r="S5" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1750,31 +1537,46 @@
         <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I6" t="s">
-        <v>349</v>
+        <v>154</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N6" t="s">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="O6" t="s">
-        <v>380</v>
+        <v>308</v>
       </c>
       <c r="P6" s="3">
-        <v>46241.50561342593</v>
+        <v>46312.05796296296</v>
       </c>
       <c r="Q6" s="3">
-        <v>46241.50561342593</v>
+        <v>46314.78833333333</v>
       </c>
       <c r="R6">
-        <v>8.58</v>
+        <v>36.63</v>
       </c>
       <c r="S6" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6" s="3">
+        <v>46316</v>
+      </c>
+      <c r="Y6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1782,31 +1584,52 @@
         <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>190</v>
+        <v>155</v>
+      </c>
+      <c r="E7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F7" t="s">
+        <v>276</v>
+      </c>
+      <c r="G7" t="s">
+        <v>277</v>
+      </c>
+      <c r="H7" t="s">
+        <v>278</v>
       </c>
       <c r="I7" t="s">
-        <v>349</v>
+        <v>281</v>
+      </c>
+      <c r="J7" t="s">
+        <v>287</v>
+      </c>
+      <c r="K7" t="s">
+        <v>288</v>
+      </c>
+      <c r="L7" t="s">
+        <v>287</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O7" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P7" s="3">
-        <v>45986.77690972222</v>
+        <v>45989.98658564815</v>
       </c>
       <c r="Q7" s="3">
-        <v>45986.77690972222</v>
+        <v>45989.98658564815</v>
       </c>
       <c r="R7">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S7" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1814,28 +1637,28 @@
         <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O8" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P8" s="3">
-        <v>46314.39738425926</v>
+        <v>46316.98170138889</v>
       </c>
       <c r="Q8" s="3">
-        <v>46314.39738425926</v>
+        <v>46316.98170138889</v>
       </c>
       <c r="R8">
         <v>5.69</v>
       </c>
       <c r="S8" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1843,31 +1666,31 @@
         <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="I9" t="s">
-        <v>351</v>
+        <v>279</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="O9" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P9" s="3">
-        <v>46241.505625</v>
+        <v>45974.46635416667</v>
       </c>
       <c r="Q9" s="3">
-        <v>46241.505625</v>
+        <v>45974.46635416667</v>
       </c>
       <c r="R9">
-        <v>5.64</v>
+        <v>9.31</v>
       </c>
       <c r="S9" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1875,28 +1698,28 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N10" t="s">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="O10" t="s">
-        <v>380</v>
+        <v>308</v>
       </c>
       <c r="P10" s="3">
-        <v>46311.73292824074</v>
+        <v>46311.70082175926</v>
       </c>
       <c r="Q10" s="3">
-        <v>46311.73292824074</v>
+        <v>46314.79664351852</v>
       </c>
       <c r="R10">
-        <v>8.58</v>
+        <v>17.86</v>
       </c>
       <c r="S10" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1904,31 +1727,31 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="I11" t="s">
-        <v>351</v>
+        <v>280</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O11" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P11" s="3">
-        <v>45911.17809027778</v>
+        <v>45967.48326388889</v>
       </c>
       <c r="Q11" s="3">
-        <v>45911.17809027778</v>
+        <v>45967.48326388889</v>
       </c>
       <c r="R11">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S11" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1936,31 +1759,46 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I12" t="s">
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O12" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P12" s="3">
-        <v>46221.47042824074</v>
+        <v>46311.84297453704</v>
       </c>
       <c r="Q12" s="3">
-        <v>46221.47042824074</v>
+        <v>46311.84297453704</v>
       </c>
       <c r="R12">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S12" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>7</v>
+      </c>
+      <c r="X12" s="3">
+        <v>46316</v>
+      </c>
+      <c r="Y12">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1968,31 +1806,31 @@
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="I13" t="s">
-        <v>349</v>
+        <v>282</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O13" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P13" s="3">
-        <v>46221.67496527778</v>
+        <v>46176.59099537037</v>
       </c>
       <c r="Q13" s="3">
-        <v>46221.67496527778</v>
+        <v>46176.59099537037</v>
       </c>
       <c r="R13">
         <v>5.69</v>
       </c>
       <c r="S13" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2000,31 +1838,28 @@
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I14" t="s">
-        <v>349</v>
+        <v>162</v>
       </c>
       <c r="M14">
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>359</v>
+        <v>293</v>
       </c>
       <c r="O14" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P14" s="3">
-        <v>46206.37920138889</v>
+        <v>46314.47375</v>
       </c>
       <c r="Q14" s="3">
-        <v>46206.37920138889</v>
+        <v>46314.47375</v>
       </c>
       <c r="R14">
         <v>5.69</v>
       </c>
       <c r="S14" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2032,46 +1867,31 @@
         <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>198</v>
+        <v>163</v>
+      </c>
+      <c r="I15" t="s">
+        <v>279</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>361</v>
+        <v>290</v>
       </c>
       <c r="O15" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P15" s="3">
-        <v>46312.05796296296</v>
+        <v>45996.23743055556</v>
       </c>
       <c r="Q15" s="3">
-        <v>46314.78833333333</v>
+        <v>45996.23743055556</v>
       </c>
       <c r="R15">
-        <v>36.63</v>
+        <v>12.46</v>
       </c>
       <c r="S15" t="s">
-        <v>383</v>
-      </c>
-      <c r="T15">
-        <v>1</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>3</v>
-      </c>
-      <c r="X15" s="3">
-        <v>46316</v>
-      </c>
-      <c r="Y15">
-        <v>3</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2079,52 +1899,28 @@
         <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E16" t="s">
-        <v>345</v>
-      </c>
-      <c r="F16" t="s">
-        <v>346</v>
-      </c>
-      <c r="G16" t="s">
-        <v>347</v>
-      </c>
-      <c r="H16" t="s">
-        <v>348</v>
-      </c>
-      <c r="I16" t="s">
-        <v>351</v>
-      </c>
-      <c r="J16" t="s">
-        <v>357</v>
-      </c>
-      <c r="K16" t="s">
-        <v>358</v>
-      </c>
-      <c r="L16" t="s">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O16" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P16" s="3">
-        <v>45989.98658564815</v>
+        <v>46314.79108796296</v>
       </c>
       <c r="Q16" s="3">
-        <v>45989.98658564815</v>
+        <v>46314.79108796296</v>
       </c>
       <c r="R16">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S16" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2132,31 +1928,31 @@
         <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="I17" t="s">
-        <v>349</v>
+        <v>280</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>362</v>
+        <v>290</v>
       </c>
       <c r="O17" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P17" s="3">
-        <v>46239.48800925926</v>
+        <v>46209.78530092593</v>
       </c>
       <c r="Q17" s="3">
-        <v>46239.48800925926</v>
+        <v>46209.78530092593</v>
       </c>
       <c r="R17">
-        <v>4.86</v>
+        <v>5.69</v>
       </c>
       <c r="S17" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2164,28 +1960,31 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>201</v>
+        <v>166</v>
+      </c>
+      <c r="I18" t="s">
+        <v>281</v>
       </c>
       <c r="M18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>363</v>
+        <v>290</v>
       </c>
       <c r="O18" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P18" s="3">
-        <v>45989.93555555555</v>
+        <v>46092.52502314815</v>
       </c>
       <c r="Q18" s="3">
-        <v>46251.5021412037</v>
+        <v>46092.52502314815</v>
       </c>
       <c r="R18">
-        <v>34.57</v>
+        <v>5.69</v>
       </c>
       <c r="S18" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2193,28 +1992,46 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" t="s">
-        <v>359</v>
+        <v>294</v>
       </c>
       <c r="O19" t="s">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="P19" s="3">
-        <v>46316.98170138889</v>
+        <v>46296.61392361111</v>
       </c>
       <c r="Q19" s="3">
-        <v>46316.98170138889</v>
+        <v>46296.61392361111</v>
       </c>
       <c r="R19">
-        <v>5.69</v>
+        <v>26.83</v>
       </c>
       <c r="S19" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T19">
+        <v>4</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>219</v>
+      </c>
+      <c r="X19" s="3">
+        <v>46303</v>
+      </c>
+      <c r="Y19">
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2222,31 +2039,28 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I20" t="s">
-        <v>350</v>
+        <v>168</v>
       </c>
       <c r="M20">
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O20" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P20" s="3">
-        <v>45974.46635416667</v>
+        <v>46196.83574074074</v>
       </c>
       <c r="Q20" s="3">
-        <v>45974.46635416667</v>
+        <v>46196.83574074074</v>
       </c>
       <c r="R20">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S20" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2254,28 +2068,28 @@
         <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="M21">
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>364</v>
+        <v>292</v>
       </c>
       <c r="O21" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="P21" s="3">
-        <v>46311.70082175926</v>
+        <v>46314.47582175926</v>
       </c>
       <c r="Q21" s="3">
-        <v>46314.79664351852</v>
+        <v>46314.80358796296</v>
       </c>
       <c r="R21">
-        <v>17.86</v>
+        <v>20.75</v>
       </c>
       <c r="S21" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2283,31 +2097,31 @@
         <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="I22" t="s">
-        <v>351</v>
+        <v>283</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O22" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P22" s="3">
-        <v>46240.65908564815</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="Q22" s="3">
-        <v>46240.65908564815</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="R22">
         <v>5.69</v>
       </c>
       <c r="S22" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2315,31 +2129,31 @@
         <v>46</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="I23" t="s">
-        <v>349</v>
+        <v>280</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N23" t="s">
-        <v>359</v>
+        <v>295</v>
       </c>
       <c r="O23" t="s">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="P23" s="3">
-        <v>45967.48326388889</v>
+        <v>45840.45584490741</v>
       </c>
       <c r="Q23" s="3">
-        <v>45967.48326388889</v>
+        <v>46170.61114583333</v>
       </c>
       <c r="R23">
-        <v>5.69</v>
+        <v>17.02</v>
       </c>
       <c r="S23" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2347,46 +2161,31 @@
         <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>207</v>
+        <v>172</v>
+      </c>
+      <c r="I24" t="s">
+        <v>281</v>
       </c>
       <c r="M24">
         <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O24" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P24" s="3">
-        <v>46311.84297453704</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="Q24" s="3">
-        <v>46311.84297453704</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="R24">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S24" t="s">
-        <v>383</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>7</v>
-      </c>
-      <c r="X24" s="3">
-        <v>46316</v>
-      </c>
-      <c r="Y24">
-        <v>4</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2394,31 +2193,46 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="I25" t="s">
-        <v>350</v>
+        <v>173</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>365</v>
+        <v>290</v>
       </c>
       <c r="O25" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P25" s="3">
-        <v>46027.41738425926</v>
+        <v>46309.55629629629</v>
       </c>
       <c r="Q25" s="3">
-        <v>46169.4778125</v>
+        <v>46309.55629629629</v>
       </c>
       <c r="R25">
-        <v>11.33</v>
+        <v>5.69</v>
       </c>
       <c r="S25" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>10</v>
+      </c>
+      <c r="X25" s="3">
+        <v>46311</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2426,31 +2240,28 @@
         <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I26" t="s">
-        <v>352</v>
+        <v>174</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O26" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P26" s="3">
-        <v>46176.59099537037</v>
+        <v>46252.93552083334</v>
       </c>
       <c r="Q26" s="3">
-        <v>46176.59099537037</v>
+        <v>46252.93552083334</v>
       </c>
       <c r="R26">
         <v>5.69</v>
       </c>
       <c r="S26" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2458,28 +2269,31 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>210</v>
+        <v>175</v>
+      </c>
+      <c r="I27" t="s">
+        <v>284</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>366</v>
+        <v>290</v>
       </c>
       <c r="O27" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P27" s="3">
-        <v>46314.47375</v>
+        <v>46062.02391203704</v>
       </c>
       <c r="Q27" s="3">
-        <v>46314.47375</v>
+        <v>46062.02391203704</v>
       </c>
       <c r="R27">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S27" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2487,46 +2301,31 @@
         <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>211</v>
+        <v>176</v>
+      </c>
+      <c r="I28" t="s">
+        <v>281</v>
       </c>
       <c r="M28">
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="O28" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P28" s="3">
-        <v>46256.77996527778</v>
+        <v>45903.0252662037</v>
       </c>
       <c r="Q28" s="3">
-        <v>46256.77996527778</v>
+        <v>45903.0252662037</v>
       </c>
       <c r="R28">
-        <v>5.64</v>
+        <v>9.31</v>
       </c>
       <c r="S28" t="s">
-        <v>383</v>
-      </c>
-      <c r="T28">
-        <v>1</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>402</v>
-      </c>
-      <c r="X28" s="3">
-        <v>46273</v>
-      </c>
-      <c r="Y28">
-        <v>16</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2534,31 +2333,31 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="I29" t="s">
-        <v>350</v>
+        <v>281</v>
       </c>
       <c r="M29">
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O29" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P29" s="3">
-        <v>45996.23743055556</v>
+        <v>46178.95283564815</v>
       </c>
       <c r="Q29" s="3">
-        <v>45996.23743055556</v>
+        <v>46178.95283564815</v>
       </c>
       <c r="R29">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S29" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2566,28 +2365,31 @@
         <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>213</v>
+        <v>178</v>
+      </c>
+      <c r="I30" t="s">
+        <v>283</v>
       </c>
       <c r="M30">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N30" t="s">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="O30" t="s">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="P30" s="3">
-        <v>46314.79108796296</v>
+        <v>46181.5243287037</v>
       </c>
       <c r="Q30" s="3">
-        <v>46314.79108796296</v>
+        <v>46253.65496527778</v>
       </c>
       <c r="R30">
-        <v>5.69</v>
+        <v>60.34</v>
       </c>
       <c r="S30" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2595,31 +2397,28 @@
         <v>54</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I31" t="s">
-        <v>349</v>
+        <v>179</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O31" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P31" s="3">
-        <v>46209.78530092593</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="Q31" s="3">
-        <v>46209.78530092593</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="R31">
         <v>5.69</v>
       </c>
       <c r="S31" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2627,31 +2426,31 @@
         <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="I32" t="s">
-        <v>351</v>
+        <v>279</v>
       </c>
       <c r="M32">
         <v>1</v>
       </c>
       <c r="N32" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O32" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P32" s="3">
-        <v>46092.52502314815</v>
+        <v>46008.62306712963</v>
       </c>
       <c r="Q32" s="3">
-        <v>46092.52502314815</v>
+        <v>46008.62306712963</v>
       </c>
       <c r="R32">
         <v>5.69</v>
       </c>
       <c r="S32" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2659,46 +2458,31 @@
         <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>216</v>
+        <v>181</v>
+      </c>
+      <c r="I33" t="s">
+        <v>284</v>
       </c>
       <c r="M33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" t="s">
-        <v>367</v>
+        <v>290</v>
       </c>
       <c r="O33" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P33" s="3">
-        <v>46296.61392361111</v>
+        <v>46152.90292824074</v>
       </c>
       <c r="Q33" s="3">
-        <v>46296.61392361111</v>
+        <v>46152.90292824074</v>
       </c>
       <c r="R33">
-        <v>26.83</v>
+        <v>5.69</v>
       </c>
       <c r="S33" t="s">
-        <v>383</v>
-      </c>
-      <c r="T33">
-        <v>4</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>219</v>
-      </c>
-      <c r="X33" s="3">
-        <v>46303</v>
-      </c>
-      <c r="Y33">
-        <v>6</v>
+        <v>310</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -2706,28 +2490,46 @@
         <v>57</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O34" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P34" s="3">
-        <v>46196.83574074074</v>
+        <v>46307.41046296297</v>
       </c>
       <c r="Q34" s="3">
-        <v>46196.83574074074</v>
+        <v>46307.41046296297</v>
       </c>
       <c r="R34">
         <v>5.69</v>
       </c>
       <c r="S34" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T34">
+        <v>1</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>18</v>
+      </c>
+      <c r="X34" s="3">
+        <v>46312</v>
+      </c>
+      <c r="Y34">
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -2735,28 +2537,31 @@
         <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>218</v>
+        <v>183</v>
+      </c>
+      <c r="I35" t="s">
+        <v>280</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N35" t="s">
-        <v>364</v>
+        <v>290</v>
       </c>
       <c r="O35" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P35" s="3">
-        <v>46314.47582175926</v>
+        <v>45953.84554398148</v>
       </c>
       <c r="Q35" s="3">
-        <v>46314.80358796296</v>
+        <v>45953.84554398148</v>
       </c>
       <c r="R35">
-        <v>20.75</v>
+        <v>12.46</v>
       </c>
       <c r="S35" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -2764,31 +2569,46 @@
         <v>59</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I36" t="s">
-        <v>353</v>
+        <v>184</v>
       </c>
       <c r="M36">
         <v>1</v>
       </c>
       <c r="N36" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O36" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P36" s="3">
-        <v>46198.6271412037</v>
+        <v>46310.5215625</v>
       </c>
       <c r="Q36" s="3">
-        <v>46198.6271412037</v>
+        <v>46310.5215625</v>
       </c>
       <c r="R36">
         <v>5.69</v>
       </c>
       <c r="S36" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T36">
+        <v>6</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>185</v>
+      </c>
+      <c r="X36" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y36">
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -2796,31 +2616,31 @@
         <v>60</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="I37" t="s">
-        <v>349</v>
+        <v>279</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N37" t="s">
-        <v>365</v>
+        <v>290</v>
       </c>
       <c r="O37" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P37" s="3">
-        <v>45840.45584490741</v>
+        <v>46111.64181712963</v>
       </c>
       <c r="Q37" s="3">
-        <v>46170.61114583333</v>
+        <v>46111.64181712963</v>
       </c>
       <c r="R37">
-        <v>17.02</v>
+        <v>12.46</v>
       </c>
       <c r="S37" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -2828,31 +2648,46 @@
         <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="I38" t="s">
-        <v>351</v>
+        <v>186</v>
       </c>
       <c r="M38">
         <v>1</v>
       </c>
       <c r="N38" t="s">
-        <v>359</v>
+        <v>289</v>
       </c>
       <c r="O38" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P38" s="3">
-        <v>46198.6271412037</v>
+        <v>46296.45141203704</v>
       </c>
       <c r="Q38" s="3">
-        <v>46198.6271412037</v>
+        <v>46296.45141203704</v>
       </c>
       <c r="R38">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="S38" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>9</v>
+      </c>
+      <c r="X38" s="3">
+        <v>46298</v>
+      </c>
+      <c r="Y38">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -2860,46 +2695,31 @@
         <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>222</v>
+        <v>187</v>
+      </c>
+      <c r="I39" t="s">
+        <v>280</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O39" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P39" s="3">
-        <v>46309.55629629629</v>
+        <v>46210.48171296297</v>
       </c>
       <c r="Q39" s="3">
-        <v>46309.55629629629</v>
+        <v>46210.48171296297</v>
       </c>
       <c r="R39">
         <v>5.69</v>
       </c>
       <c r="S39" t="s">
-        <v>383</v>
-      </c>
-      <c r="T39">
-        <v>1</v>
-      </c>
-      <c r="U39">
-        <v>0</v>
-      </c>
-      <c r="V39">
-        <v>0</v>
-      </c>
-      <c r="W39">
-        <v>10</v>
-      </c>
-      <c r="X39" s="3">
-        <v>46311</v>
-      </c>
-      <c r="Y39">
-        <v>1</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -2907,28 +2727,46 @@
         <v>63</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="M40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N40" t="s">
-        <v>359</v>
+        <v>297</v>
       </c>
       <c r="O40" t="s">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="P40" s="3">
-        <v>46252.93552083334</v>
+        <v>46280.49378472222</v>
       </c>
       <c r="Q40" s="3">
-        <v>46252.93552083334</v>
+        <v>46280.49379629629</v>
       </c>
       <c r="R40">
-        <v>5.69</v>
+        <v>10.55</v>
       </c>
       <c r="S40" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T40">
+        <v>4</v>
+      </c>
+      <c r="U40">
+        <v>19.91</v>
+      </c>
+      <c r="V40">
+        <v>2</v>
+      </c>
+      <c r="W40">
+        <v>689</v>
+      </c>
+      <c r="X40" s="3">
+        <v>46281</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -2936,31 +2774,31 @@
         <v>64</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="I41" t="s">
-        <v>354</v>
+        <v>285</v>
       </c>
       <c r="M41">
         <v>1</v>
       </c>
       <c r="N41" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O41" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P41" s="3">
-        <v>46062.02391203704</v>
+        <v>46225.98408564815</v>
       </c>
       <c r="Q41" s="3">
-        <v>46062.02391203704</v>
+        <v>46225.98408564815</v>
       </c>
       <c r="R41">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S41" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -2968,31 +2806,31 @@
         <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="I42" t="s">
-        <v>351</v>
+        <v>280</v>
       </c>
       <c r="M42">
         <v>1</v>
       </c>
       <c r="N42" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O42" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P42" s="3">
-        <v>45903.0252662037</v>
+        <v>46106.56184027778</v>
       </c>
       <c r="Q42" s="3">
-        <v>45903.0252662037</v>
+        <v>46106.56184027778</v>
       </c>
       <c r="R42">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S42" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3000,31 +2838,28 @@
         <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I43" t="s">
-        <v>351</v>
+        <v>191</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O43" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P43" s="3">
-        <v>46178.95283564815</v>
+        <v>46313.79324074074</v>
       </c>
       <c r="Q43" s="3">
-        <v>46178.95283564815</v>
+        <v>46313.79324074074</v>
       </c>
       <c r="R43">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S43" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3032,31 +2867,31 @@
         <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="I44" t="s">
-        <v>353</v>
+        <v>284</v>
       </c>
       <c r="M44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N44" t="s">
-        <v>368</v>
+        <v>290</v>
       </c>
       <c r="O44" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P44" s="3">
-        <v>46181.5243287037</v>
+        <v>46196.84141203704</v>
       </c>
       <c r="Q44" s="3">
-        <v>46253.65496527778</v>
+        <v>46196.84141203704</v>
       </c>
       <c r="R44">
-        <v>60.34</v>
+        <v>5.69</v>
       </c>
       <c r="S44" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -3064,28 +2899,28 @@
         <v>68</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="M45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N45" t="s">
-        <v>359</v>
+        <v>298</v>
       </c>
       <c r="O45" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P45" s="3">
-        <v>46053.63612268519</v>
+        <v>46312.81608796296</v>
       </c>
       <c r="Q45" s="3">
-        <v>46053.63612268519</v>
+        <v>46313.7452662037</v>
       </c>
       <c r="R45">
-        <v>5.69</v>
+        <v>14.62</v>
       </c>
       <c r="S45" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -3093,31 +2928,28 @@
         <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I46" t="s">
-        <v>350</v>
+        <v>194</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
       <c r="N46" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O46" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P46" s="3">
-        <v>46008.62306712963</v>
+        <v>46316.59872685185</v>
       </c>
       <c r="Q46" s="3">
-        <v>46008.62306712963</v>
+        <v>46316.59872685185</v>
       </c>
       <c r="R46">
         <v>5.69</v>
       </c>
       <c r="S46" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -3125,31 +2957,31 @@
         <v>70</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="I47" t="s">
-        <v>354</v>
+        <v>283</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O47" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P47" s="3">
-        <v>46152.90292824074</v>
+        <v>46073.66815972222</v>
       </c>
       <c r="Q47" s="3">
-        <v>46152.90292824074</v>
+        <v>46073.66815972222</v>
       </c>
       <c r="R47">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S47" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:25">
@@ -3157,28 +2989,31 @@
         <v>71</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>231</v>
+        <v>196</v>
+      </c>
+      <c r="I48" t="s">
+        <v>284</v>
       </c>
       <c r="M48">
         <v>1</v>
       </c>
       <c r="N48" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O48" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P48" s="3">
-        <v>46307.41046296297</v>
+        <v>46245.82854166667</v>
       </c>
       <c r="Q48" s="3">
-        <v>46307.41046296297</v>
+        <v>46245.82854166667</v>
       </c>
       <c r="R48">
         <v>5.69</v>
       </c>
       <c r="S48" t="s">
-        <v>383</v>
+        <v>311</v>
       </c>
       <c r="T48">
         <v>1</v>
@@ -3190,13 +3025,13 @@
         <v>0</v>
       </c>
       <c r="W48">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X48" s="3">
-        <v>46312</v>
+        <v>46261</v>
       </c>
       <c r="Y48">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:25">
@@ -3204,31 +3039,28 @@
         <v>72</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="I49" t="s">
-        <v>349</v>
+        <v>197</v>
       </c>
       <c r="M49">
         <v>1</v>
       </c>
       <c r="N49" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O49" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P49" s="3">
-        <v>45953.84554398148</v>
+        <v>46314.79525462963</v>
       </c>
       <c r="Q49" s="3">
-        <v>45953.84554398148</v>
+        <v>46314.79525462963</v>
       </c>
       <c r="R49">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S49" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:25">
@@ -3236,46 +3068,28 @@
         <v>73</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="M50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N50" t="s">
-        <v>359</v>
+        <v>299</v>
       </c>
       <c r="O50" t="s">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="P50" s="3">
-        <v>46310.5215625</v>
+        <v>46313.77442129629</v>
       </c>
       <c r="Q50" s="3">
-        <v>46310.5215625</v>
+        <v>46314.79109953704</v>
       </c>
       <c r="R50">
-        <v>5.69</v>
+        <v>27.71</v>
       </c>
       <c r="S50" t="s">
-        <v>383</v>
-      </c>
-      <c r="T50">
-        <v>6</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>185</v>
-      </c>
-      <c r="X50" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y50">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:25">
@@ -3283,31 +3097,28 @@
         <v>74</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I51" t="s">
-        <v>349</v>
+        <v>199</v>
       </c>
       <c r="M51">
         <v>1</v>
       </c>
       <c r="N51" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O51" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P51" s="3">
-        <v>46241.50561342593</v>
+        <v>46316.43623842593</v>
       </c>
       <c r="Q51" s="3">
-        <v>46241.50561342593</v>
+        <v>46316.43623842593</v>
       </c>
       <c r="R51">
         <v>5.69</v>
       </c>
       <c r="S51" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:25">
@@ -3315,31 +3126,46 @@
         <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I52" t="s">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="M52">
         <v>1</v>
       </c>
       <c r="N52" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O52" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P52" s="3">
-        <v>46111.64181712963</v>
+        <v>46281.49586805556</v>
       </c>
       <c r="Q52" s="3">
-        <v>46111.64181712963</v>
+        <v>46281.49586805556</v>
       </c>
       <c r="R52">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S52" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T52">
+        <v>7</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>119</v>
+      </c>
+      <c r="X52" s="3">
+        <v>46282</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:25">
@@ -3347,49 +3173,31 @@
         <v>76</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="I53" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O53" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P53" s="3">
-        <v>46248.24103009259</v>
+        <v>46050.93159722222</v>
       </c>
       <c r="Q53" s="3">
-        <v>46248.24103009259</v>
+        <v>46050.93159722222</v>
       </c>
       <c r="R53">
-        <v>8.58</v>
+        <v>12.46</v>
       </c>
       <c r="S53" t="s">
-        <v>383</v>
-      </c>
-      <c r="T53">
-        <v>1</v>
-      </c>
-      <c r="U53">
-        <v>0</v>
-      </c>
-      <c r="V53">
-        <v>0</v>
-      </c>
-      <c r="W53">
-        <v>65</v>
-      </c>
-      <c r="X53" s="3">
-        <v>46259</v>
-      </c>
-      <c r="Y53">
-        <v>10</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:25">
@@ -3397,31 +3205,31 @@
         <v>77</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="M54">
         <v>1</v>
       </c>
       <c r="N54" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="O54" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P54" s="3">
-        <v>46296.45141203704</v>
+        <v>46310.34238425926</v>
       </c>
       <c r="Q54" s="3">
-        <v>46296.45141203704</v>
+        <v>46310.34238425926</v>
       </c>
       <c r="R54">
-        <v>5.64</v>
+        <v>5.69</v>
       </c>
       <c r="S54" t="s">
-        <v>383</v>
+        <v>311</v>
       </c>
       <c r="T54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U54">
         <v>0</v>
@@ -3430,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="W54">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="X54" s="3">
-        <v>46298</v>
+        <v>46313</v>
       </c>
       <c r="Y54">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:25">
@@ -3444,31 +3252,28 @@
         <v>78</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="I55" t="s">
-        <v>349</v>
+        <v>203</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O55" t="s">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="P55" s="3">
-        <v>46210.48171296297</v>
+        <v>46314.07822916667</v>
       </c>
       <c r="Q55" s="3">
-        <v>46210.48171296297</v>
+        <v>46314.07822916667</v>
       </c>
       <c r="R55">
-        <v>5.69</v>
+        <v>14.27</v>
       </c>
       <c r="S55" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" spans="1:25">
@@ -3476,46 +3281,31 @@
         <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>239</v>
+        <v>204</v>
+      </c>
+      <c r="I56" t="s">
+        <v>284</v>
       </c>
       <c r="M56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N56" t="s">
-        <v>369</v>
+        <v>290</v>
       </c>
       <c r="O56" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P56" s="3">
-        <v>46280.49378472222</v>
+        <v>45965.93854166667</v>
       </c>
       <c r="Q56" s="3">
-        <v>46280.49379629629</v>
+        <v>45965.93854166667</v>
       </c>
       <c r="R56">
-        <v>10.55</v>
+        <v>5.69</v>
       </c>
       <c r="S56" t="s">
-        <v>383</v>
-      </c>
-      <c r="T56">
-        <v>4</v>
-      </c>
-      <c r="U56">
-        <v>19.91</v>
-      </c>
-      <c r="V56">
-        <v>2</v>
-      </c>
-      <c r="W56">
-        <v>689</v>
-      </c>
-      <c r="X56" s="3">
-        <v>46281</v>
-      </c>
-      <c r="Y56">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="57" spans="1:25">
@@ -3523,31 +3313,31 @@
         <v>80</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="I57" t="s">
-        <v>355</v>
+        <v>280</v>
       </c>
       <c r="M57">
         <v>1</v>
       </c>
       <c r="N57" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O57" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P57" s="3">
-        <v>46225.98408564815</v>
+        <v>45992.89240740741</v>
       </c>
       <c r="Q57" s="3">
-        <v>46225.98408564815</v>
+        <v>45992.89240740741</v>
       </c>
       <c r="R57">
         <v>5.69</v>
       </c>
       <c r="S57" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:25">
@@ -3555,31 +3345,31 @@
         <v>81</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="I58" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="M58">
         <v>1</v>
       </c>
       <c r="N58" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O58" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P58" s="3">
-        <v>46106.56184027778</v>
+        <v>45944.90217592593</v>
       </c>
       <c r="Q58" s="3">
-        <v>46106.56184027778</v>
+        <v>45944.90217592593</v>
       </c>
       <c r="R58">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S58" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="59" spans="1:25">
@@ -3587,28 +3377,31 @@
         <v>82</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>242</v>
+        <v>207</v>
+      </c>
+      <c r="I59" t="s">
+        <v>280</v>
       </c>
       <c r="M59">
         <v>1</v>
       </c>
       <c r="N59" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O59" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P59" s="3">
-        <v>46313.79324074074</v>
+        <v>46105.47987268519</v>
       </c>
       <c r="Q59" s="3">
-        <v>46313.79324074074</v>
+        <v>46105.47987268519</v>
       </c>
       <c r="R59">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S59" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60" spans="1:25">
@@ -3616,31 +3409,28 @@
         <v>83</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="I60" t="s">
-        <v>354</v>
+        <v>208</v>
       </c>
       <c r="M60">
         <v>1</v>
       </c>
       <c r="N60" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O60" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P60" s="3">
-        <v>46196.84141203704</v>
+        <v>46314.78832175926</v>
       </c>
       <c r="Q60" s="3">
-        <v>46196.84141203704</v>
+        <v>46314.78832175926</v>
       </c>
       <c r="R60">
         <v>5.69</v>
       </c>
       <c r="S60" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="61" spans="1:25">
@@ -3648,28 +3438,31 @@
         <v>84</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>244</v>
+        <v>209</v>
+      </c>
+      <c r="I61" t="s">
+        <v>284</v>
       </c>
       <c r="M61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N61" t="s">
-        <v>370</v>
+        <v>290</v>
       </c>
       <c r="O61" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P61" s="3">
-        <v>46312.81608796296</v>
+        <v>46210.50420138889</v>
       </c>
       <c r="Q61" s="3">
-        <v>46313.7452662037</v>
+        <v>46210.50420138889</v>
       </c>
       <c r="R61">
-        <v>14.62</v>
+        <v>5.69</v>
       </c>
       <c r="S61" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="62" spans="1:25">
@@ -3677,28 +3470,28 @@
         <v>85</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="M62">
         <v>1</v>
       </c>
       <c r="N62" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O62" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P62" s="3">
-        <v>46316.59872685185</v>
+        <v>46052.56390046296</v>
       </c>
       <c r="Q62" s="3">
-        <v>46316.59872685185</v>
+        <v>46052.56390046296</v>
       </c>
       <c r="R62">
         <v>5.69</v>
       </c>
       <c r="S62" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="63" spans="1:25">
@@ -3706,31 +3499,31 @@
         <v>86</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="I63" t="s">
-        <v>353</v>
+        <v>281</v>
       </c>
       <c r="M63">
         <v>1</v>
       </c>
       <c r="N63" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O63" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P63" s="3">
-        <v>46073.66815972222</v>
+        <v>46091.88748842593</v>
       </c>
       <c r="Q63" s="3">
-        <v>46073.66815972222</v>
+        <v>46091.88748842593</v>
       </c>
       <c r="R63">
-        <v>12.46</v>
+        <v>9.31</v>
       </c>
       <c r="S63" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="64" spans="1:25">
@@ -3738,49 +3531,31 @@
         <v>87</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="I64" t="s">
-        <v>354</v>
+        <v>281</v>
       </c>
       <c r="M64">
         <v>1</v>
       </c>
       <c r="N64" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O64" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P64" s="3">
-        <v>46245.82854166667</v>
+        <v>45978.69265046297</v>
       </c>
       <c r="Q64" s="3">
-        <v>46245.82854166667</v>
+        <v>45978.69265046297</v>
       </c>
       <c r="R64">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S64" t="s">
-        <v>383</v>
-      </c>
-      <c r="T64">
-        <v>1</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-      <c r="V64">
-        <v>0</v>
-      </c>
-      <c r="W64">
-        <v>23</v>
-      </c>
-      <c r="X64" s="3">
-        <v>46261</v>
-      </c>
-      <c r="Y64">
-        <v>15</v>
+        <v>310</v>
       </c>
     </row>
     <row r="65" spans="1:25">
@@ -3788,28 +3563,28 @@
         <v>88</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="M65">
         <v>1</v>
       </c>
       <c r="N65" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O65" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P65" s="3">
-        <v>46314.79525462963</v>
+        <v>46314.79108796296</v>
       </c>
       <c r="Q65" s="3">
-        <v>46314.79525462963</v>
+        <v>46314.79108796296</v>
       </c>
       <c r="R65">
         <v>5.69</v>
       </c>
       <c r="S65" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="66" spans="1:25">
@@ -3817,28 +3592,31 @@
         <v>89</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>249</v>
+        <v>214</v>
+      </c>
+      <c r="I66" t="s">
+        <v>280</v>
       </c>
       <c r="M66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N66" t="s">
-        <v>371</v>
+        <v>290</v>
       </c>
       <c r="O66" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P66" s="3">
-        <v>46313.77442129629</v>
+        <v>45919.81163194445</v>
       </c>
       <c r="Q66" s="3">
-        <v>46314.79109953704</v>
+        <v>45919.81163194445</v>
       </c>
       <c r="R66">
-        <v>27.71</v>
+        <v>5.69</v>
       </c>
       <c r="S66" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="67" spans="1:25">
@@ -3846,28 +3624,28 @@
         <v>90</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="M67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N67" t="s">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="O67" t="s">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="P67" s="3">
-        <v>46316.43623842593</v>
+        <v>46313.77442129629</v>
       </c>
       <c r="Q67" s="3">
-        <v>46316.43623842593</v>
+        <v>46314.78831018518</v>
       </c>
       <c r="R67">
-        <v>5.69</v>
+        <v>30.1</v>
       </c>
       <c r="S67" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="1:25">
@@ -3875,46 +3653,46 @@
         <v>91</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68" t="s">
+        <v>301</v>
+      </c>
+      <c r="O68" t="s">
+        <v>309</v>
+      </c>
+      <c r="P68" s="3">
+        <v>46314.50759259259</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>46314.50759259259</v>
+      </c>
+      <c r="R68">
+        <v>6.04</v>
+      </c>
+      <c r="S68" t="s">
+        <v>311</v>
+      </c>
+      <c r="T68">
         <v>2</v>
       </c>
-      <c r="N68" t="s">
-        <v>365</v>
-      </c>
-      <c r="O68" t="s">
-        <v>381</v>
-      </c>
-      <c r="P68" s="3">
-        <v>46253.01677083333</v>
-      </c>
-      <c r="Q68" s="3">
-        <v>46253.01677083333</v>
-      </c>
-      <c r="R68">
-        <v>14.22</v>
-      </c>
-      <c r="S68" t="s">
-        <v>383</v>
-      </c>
-      <c r="T68">
-        <v>3</v>
-      </c>
       <c r="U68">
-        <v>19.99</v>
+        <v>20.03</v>
       </c>
       <c r="V68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68">
-        <v>7</v>
+        <v>473</v>
       </c>
       <c r="X68" s="3">
-        <v>46259</v>
+        <v>46313</v>
       </c>
       <c r="Y68">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="69" spans="1:25">
@@ -3922,46 +3700,31 @@
         <v>92</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>252</v>
+        <v>217</v>
+      </c>
+      <c r="I69" t="s">
+        <v>279</v>
       </c>
       <c r="M69">
         <v>1</v>
       </c>
       <c r="N69" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O69" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P69" s="3">
-        <v>46281.49586805556</v>
+        <v>46051.04447916667</v>
       </c>
       <c r="Q69" s="3">
-        <v>46281.49586805556</v>
+        <v>46051.04447916667</v>
       </c>
       <c r="R69">
         <v>5.69</v>
       </c>
       <c r="S69" t="s">
-        <v>383</v>
-      </c>
-      <c r="T69">
-        <v>7</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>119</v>
-      </c>
-      <c r="X69" s="3">
-        <v>46282</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:25">
@@ -3969,31 +3732,28 @@
         <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I70" t="s">
-        <v>350</v>
+        <v>218</v>
       </c>
       <c r="M70">
         <v>1</v>
       </c>
       <c r="N70" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O70" t="s">
-        <v>380</v>
+        <v>309</v>
       </c>
       <c r="P70" s="3">
-        <v>46243.94936342593</v>
+        <v>46314.40084490741</v>
       </c>
       <c r="Q70" s="3">
-        <v>46243.94936342593</v>
+        <v>46314.40084490741</v>
       </c>
       <c r="R70">
         <v>8.58</v>
       </c>
       <c r="S70" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="71" spans="1:25">
@@ -4001,31 +3761,31 @@
         <v>94</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="I71" t="s">
-        <v>354</v>
+        <v>279</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O71" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P71" s="3">
-        <v>46251.59519675926</v>
+        <v>45891.71650462963</v>
       </c>
       <c r="Q71" s="3">
-        <v>46251.59519675926</v>
+        <v>45891.71650462963</v>
       </c>
       <c r="R71">
-        <v>8.58</v>
+        <v>9.31</v>
       </c>
       <c r="S71" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="72" spans="1:25">
@@ -4033,31 +3793,31 @@
         <v>95</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="I72" t="s">
-        <v>349</v>
+        <v>279</v>
       </c>
       <c r="M72">
         <v>1</v>
       </c>
       <c r="N72" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O72" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P72" s="3">
-        <v>46050.93159722222</v>
+        <v>46211.60210648148</v>
       </c>
       <c r="Q72" s="3">
-        <v>46050.93159722222</v>
+        <v>46211.60210648148</v>
       </c>
       <c r="R72">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S72" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="73" spans="1:25">
@@ -4065,31 +3825,28 @@
         <v>96</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I73" t="s">
-        <v>349</v>
+        <v>221</v>
       </c>
       <c r="M73">
         <v>1</v>
       </c>
       <c r="N73" t="s">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="O73" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P73" s="3">
-        <v>46225.91961805556</v>
+        <v>46314.35015046296</v>
       </c>
       <c r="Q73" s="3">
-        <v>46225.91961805556</v>
+        <v>46314.35015046296</v>
       </c>
       <c r="R73">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S73" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="74" spans="1:25">
@@ -4097,31 +3854,31 @@
         <v>97</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="I74" t="s">
-        <v>349</v>
+        <v>281</v>
       </c>
       <c r="M74">
         <v>1</v>
       </c>
       <c r="N74" t="s">
-        <v>372</v>
+        <v>290</v>
       </c>
       <c r="O74" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P74" s="3">
-        <v>46238.46950231482</v>
+        <v>46167.36722222222</v>
       </c>
       <c r="Q74" s="3">
-        <v>46238.46950231482</v>
+        <v>46167.36722222222</v>
       </c>
       <c r="R74">
-        <v>4.73</v>
+        <v>5.69</v>
       </c>
       <c r="S74" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="1:25">
@@ -4129,46 +3886,28 @@
         <v>98</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="M75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N75" t="s">
-        <v>359</v>
+        <v>298</v>
       </c>
       <c r="O75" t="s">
-        <v>380</v>
+        <v>308</v>
       </c>
       <c r="P75" s="3">
-        <v>46310.34238425926</v>
+        <v>46313.73414351852</v>
       </c>
       <c r="Q75" s="3">
-        <v>46310.34238425926</v>
+        <v>46313.73415509259</v>
       </c>
       <c r="R75">
-        <v>5.69</v>
+        <v>11.73</v>
       </c>
       <c r="S75" t="s">
-        <v>383</v>
-      </c>
-      <c r="T75">
-        <v>3</v>
-      </c>
-      <c r="U75">
-        <v>0</v>
-      </c>
-      <c r="V75">
-        <v>0</v>
-      </c>
-      <c r="W75">
-        <v>93</v>
-      </c>
-      <c r="X75" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y75">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="76" spans="1:25">
@@ -4176,28 +3915,49 @@
         <v>99</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>259</v>
+        <v>224</v>
+      </c>
+      <c r="I76" t="s">
+        <v>281</v>
       </c>
       <c r="M76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N76" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O76" t="s">
-        <v>381</v>
+        <v>309</v>
       </c>
       <c r="P76" s="3">
-        <v>46314.07822916667</v>
+        <v>46309.5507175926</v>
       </c>
       <c r="Q76" s="3">
-        <v>46314.07822916667</v>
+        <v>46309.5507175926</v>
       </c>
       <c r="R76">
-        <v>14.27</v>
+        <v>5.69</v>
       </c>
       <c r="S76" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T76">
+        <v>1</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>12</v>
+      </c>
+      <c r="X76" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y76">
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:25">
@@ -4205,31 +3965,28 @@
         <v>100</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="I77" t="s">
-        <v>354</v>
+        <v>225</v>
       </c>
       <c r="M77">
         <v>1</v>
       </c>
       <c r="N77" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O77" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P77" s="3">
-        <v>46210.7556712963</v>
+        <v>46312.0579050926</v>
       </c>
       <c r="Q77" s="3">
-        <v>46210.7556712963</v>
+        <v>46312.0579050926</v>
       </c>
       <c r="R77">
         <v>5.69</v>
       </c>
       <c r="S77" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="78" spans="1:25">
@@ -4237,46 +3994,31 @@
         <v>101</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>261</v>
+        <v>226</v>
+      </c>
+      <c r="I78" t="s">
+        <v>284</v>
       </c>
       <c r="M78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N78" t="s">
-        <v>363</v>
+        <v>290</v>
       </c>
       <c r="O78" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P78" s="3">
-        <v>46256.87302083334</v>
+        <v>46050.54237268519</v>
       </c>
       <c r="Q78" s="3">
-        <v>46256.87302083334</v>
+        <v>46050.54237268519</v>
       </c>
       <c r="R78">
-        <v>23.19</v>
+        <v>5.69</v>
       </c>
       <c r="S78" t="s">
-        <v>383</v>
-      </c>
-      <c r="T78">
-        <v>2</v>
-      </c>
-      <c r="U78">
-        <v>0</v>
-      </c>
-      <c r="V78">
-        <v>0</v>
-      </c>
-      <c r="W78">
-        <v>271</v>
-      </c>
-      <c r="X78" s="3">
-        <v>46279</v>
-      </c>
-      <c r="Y78">
-        <v>22</v>
+        <v>310</v>
       </c>
     </row>
     <row r="79" spans="1:25">
@@ -4284,31 +4026,31 @@
         <v>102</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="I79" t="s">
-        <v>354</v>
+        <v>283</v>
       </c>
       <c r="M79">
         <v>1</v>
       </c>
       <c r="N79" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O79" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P79" s="3">
-        <v>45965.93854166667</v>
+        <v>45957.49894675926</v>
       </c>
       <c r="Q79" s="3">
-        <v>45965.93854166667</v>
+        <v>45957.49894675926</v>
       </c>
       <c r="R79">
         <v>5.69</v>
       </c>
       <c r="S79" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="1:25">
@@ -4316,31 +4058,46 @@
         <v>103</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I80" t="s">
-        <v>351</v>
+        <v>228</v>
       </c>
       <c r="M80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N80" t="s">
-        <v>359</v>
+        <v>302</v>
       </c>
       <c r="O80" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P80" s="3">
-        <v>46221.58542824074</v>
+        <v>46316.49146990741</v>
       </c>
       <c r="Q80" s="3">
-        <v>46221.58542824074</v>
+        <v>46316.49152777778</v>
       </c>
       <c r="R80">
-        <v>5.69</v>
+        <v>15.88</v>
       </c>
       <c r="S80" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T80">
+        <v>15</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>226</v>
+      </c>
+      <c r="X80" s="3">
+        <v>46298</v>
+      </c>
+      <c r="Y80">
+        <v>-19</v>
       </c>
     </row>
     <row r="81" spans="1:25">
@@ -4348,31 +4105,31 @@
         <v>104</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="I81" t="s">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="M81">
         <v>1</v>
       </c>
       <c r="N81" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O81" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P81" s="3">
-        <v>45992.89240740741</v>
+        <v>46196.62574074074</v>
       </c>
       <c r="Q81" s="3">
-        <v>45992.89240740741</v>
+        <v>46196.62574074074</v>
       </c>
       <c r="R81">
         <v>5.69</v>
       </c>
       <c r="S81" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="82" spans="1:25">
@@ -4380,31 +4137,31 @@
         <v>105</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="I82" t="s">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="M82">
         <v>1</v>
       </c>
       <c r="N82" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="O82" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P82" s="3">
-        <v>46241.505625</v>
+        <v>45959.6512037037</v>
       </c>
       <c r="Q82" s="3">
-        <v>46241.505625</v>
+        <v>45959.6512037037</v>
       </c>
       <c r="R82">
-        <v>5.64</v>
+        <v>9.31</v>
       </c>
       <c r="S82" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="83" spans="1:25">
@@ -4412,31 +4169,31 @@
         <v>106</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="I83" t="s">
-        <v>356</v>
+        <v>279</v>
       </c>
       <c r="M83">
         <v>1</v>
       </c>
       <c r="N83" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O83" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P83" s="3">
-        <v>45944.90217592593</v>
+        <v>45973.56506944444</v>
       </c>
       <c r="Q83" s="3">
-        <v>45944.90217592593</v>
+        <v>45973.56506944444</v>
       </c>
       <c r="R83">
         <v>9.31</v>
       </c>
       <c r="S83" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="84" spans="1:25">
@@ -4444,31 +4201,28 @@
         <v>107</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I84" t="s">
-        <v>349</v>
+        <v>232</v>
       </c>
       <c r="M84">
         <v>1</v>
       </c>
       <c r="N84" t="s">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="O84" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P84" s="3">
-        <v>46105.47987268519</v>
+        <v>46313.49944444445</v>
       </c>
       <c r="Q84" s="3">
-        <v>46105.47987268519</v>
+        <v>46313.49944444445</v>
       </c>
       <c r="R84">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S84" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="85" spans="1:25">
@@ -4476,31 +4230,28 @@
         <v>108</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I85" t="s">
-        <v>356</v>
+        <v>233</v>
       </c>
       <c r="M85">
         <v>1</v>
       </c>
       <c r="N85" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O85" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P85" s="3">
-        <v>46218.74396990741</v>
+        <v>46316.43068287037</v>
       </c>
       <c r="Q85" s="3">
-        <v>46218.74396990741</v>
+        <v>46316.43068287037</v>
       </c>
       <c r="R85">
         <v>5.69</v>
       </c>
       <c r="S85" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="86" spans="1:25">
@@ -4508,28 +4259,28 @@
         <v>109</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="M86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N86" t="s">
-        <v>359</v>
+        <v>303</v>
       </c>
       <c r="O86" t="s">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="P86" s="3">
-        <v>46314.78832175926</v>
+        <v>46313.73415509259</v>
       </c>
       <c r="Q86" s="3">
-        <v>46314.78832175926</v>
+        <v>46316.43625</v>
       </c>
       <c r="R86">
-        <v>5.69</v>
+        <v>26.82</v>
       </c>
       <c r="S86" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="87" spans="1:25">
@@ -4537,31 +4288,31 @@
         <v>110</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="I87" t="s">
-        <v>354</v>
+        <v>280</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
       <c r="N87" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O87" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P87" s="3">
-        <v>46210.50420138889</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="Q87" s="3">
-        <v>46210.50420138889</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="R87">
         <v>5.69</v>
       </c>
       <c r="S87" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="88" spans="1:25">
@@ -4569,28 +4320,46 @@
         <v>111</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="M88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N88" t="s">
-        <v>359</v>
+        <v>295</v>
       </c>
       <c r="O88" t="s">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="P88" s="3">
-        <v>46052.56390046296</v>
+        <v>46286.62572916667</v>
       </c>
       <c r="Q88" s="3">
-        <v>46052.56390046296</v>
+        <v>46306.5500462963</v>
       </c>
       <c r="R88">
-        <v>5.69</v>
+        <v>14.22</v>
       </c>
       <c r="S88" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T88">
+        <v>2</v>
+      </c>
+      <c r="U88">
+        <v>0</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>32</v>
+      </c>
+      <c r="X88" s="3">
+        <v>46297</v>
+      </c>
+      <c r="Y88">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:25">
@@ -4598,31 +4367,28 @@
         <v>112</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I89" t="s">
-        <v>351</v>
+        <v>237</v>
       </c>
       <c r="M89">
         <v>1</v>
       </c>
       <c r="N89" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O89" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P89" s="3">
-        <v>46091.88748842593</v>
+        <v>46304.50560185185</v>
       </c>
       <c r="Q89" s="3">
-        <v>46091.88748842593</v>
+        <v>46304.50560185185</v>
       </c>
       <c r="R89">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S89" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="90" spans="1:25">
@@ -4630,46 +4396,28 @@
         <v>113</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="M90">
         <v>1</v>
       </c>
       <c r="N90" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O90" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P90" s="3">
-        <v>46259.6521875</v>
+        <v>46314.40085648148</v>
       </c>
       <c r="Q90" s="3">
-        <v>46259.6521875</v>
+        <v>46314.40085648148</v>
       </c>
       <c r="R90">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S90" t="s">
-        <v>383</v>
-      </c>
-      <c r="T90">
-        <v>1</v>
-      </c>
-      <c r="U90">
-        <v>0</v>
-      </c>
-      <c r="V90">
-        <v>0</v>
-      </c>
-      <c r="W90">
-        <v>29</v>
-      </c>
-      <c r="X90" s="3">
-        <v>46267</v>
-      </c>
-      <c r="Y90">
-        <v>7</v>
+        <v>310</v>
       </c>
     </row>
     <row r="91" spans="1:25">
@@ -4677,31 +4425,28 @@
         <v>114</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I91" t="s">
-        <v>351</v>
+        <v>239</v>
       </c>
       <c r="M91">
         <v>1</v>
       </c>
       <c r="N91" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O91" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P91" s="3">
-        <v>45978.69265046297</v>
+        <v>46027.60903935185</v>
       </c>
       <c r="Q91" s="3">
-        <v>45978.69265046297</v>
+        <v>46027.60903935185</v>
       </c>
       <c r="R91">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S91" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" spans="1:25">
@@ -4709,28 +4454,46 @@
         <v>115</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="M92">
         <v>1</v>
       </c>
       <c r="N92" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O92" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P92" s="3">
-        <v>46314.79108796296</v>
+        <v>46280.49518518519</v>
       </c>
       <c r="Q92" s="3">
-        <v>46314.79108796296</v>
+        <v>46280.49518518519</v>
       </c>
       <c r="R92">
         <v>5.69</v>
       </c>
       <c r="S92" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T92">
+        <v>1</v>
+      </c>
+      <c r="U92">
+        <v>0</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>17</v>
+      </c>
+      <c r="X92" s="3">
+        <v>46283</v>
+      </c>
+      <c r="Y92">
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:25">
@@ -4738,46 +4501,28 @@
         <v>116</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="M93">
         <v>1</v>
       </c>
       <c r="N93" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="O93" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P93" s="3">
-        <v>46256.2834375</v>
+        <v>46311.94667824074</v>
       </c>
       <c r="Q93" s="3">
-        <v>46256.2834375</v>
+        <v>46311.94667824074</v>
       </c>
       <c r="R93">
-        <v>5.64</v>
+        <v>5.69</v>
       </c>
       <c r="S93" t="s">
-        <v>383</v>
-      </c>
-      <c r="T93">
-        <v>1</v>
-      </c>
-      <c r="U93">
-        <v>0</v>
-      </c>
-      <c r="V93">
-        <v>0</v>
-      </c>
-      <c r="W93">
-        <v>164</v>
-      </c>
-      <c r="X93" s="3">
-        <v>46263</v>
-      </c>
-      <c r="Y93">
-        <v>6</v>
+        <v>310</v>
       </c>
     </row>
     <row r="94" spans="1:25">
@@ -4785,31 +4530,28 @@
         <v>117</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I94" t="s">
-        <v>349</v>
+        <v>242</v>
       </c>
       <c r="M94">
         <v>1</v>
       </c>
       <c r="N94" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O94" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P94" s="3">
-        <v>45919.81163194445</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="Q94" s="3">
-        <v>45919.81163194445</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="R94">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S94" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="95" spans="1:25">
@@ -4817,28 +4559,31 @@
         <v>118</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>278</v>
+        <v>243</v>
+      </c>
+      <c r="I95" t="s">
+        <v>286</v>
       </c>
       <c r="M95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N95" t="s">
-        <v>373</v>
+        <v>290</v>
       </c>
       <c r="O95" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P95" s="3">
-        <v>46313.77442129629</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q95" s="3">
-        <v>46314.78831018518</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R95">
-        <v>30.1</v>
+        <v>5.69</v>
       </c>
       <c r="S95" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="96" spans="1:25">
@@ -4846,46 +4591,31 @@
         <v>119</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>279</v>
+        <v>244</v>
+      </c>
+      <c r="I96" t="s">
+        <v>283</v>
       </c>
       <c r="M96">
         <v>1</v>
       </c>
       <c r="N96" t="s">
-        <v>374</v>
+        <v>290</v>
       </c>
       <c r="O96" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P96" s="3">
-        <v>46314.50759259259</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="Q96" s="3">
-        <v>46314.50759259259</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="R96">
-        <v>6.04</v>
+        <v>5.69</v>
       </c>
       <c r="S96" t="s">
-        <v>383</v>
-      </c>
-      <c r="T96">
-        <v>2</v>
-      </c>
-      <c r="U96">
-        <v>19.98</v>
-      </c>
-      <c r="V96">
-        <v>2</v>
-      </c>
-      <c r="W96">
-        <v>473</v>
-      </c>
-      <c r="X96" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y96">
-        <v>-2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="97" spans="1:25">
@@ -4893,31 +4623,28 @@
         <v>120</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I97" t="s">
-        <v>350</v>
+        <v>245</v>
       </c>
       <c r="M97">
         <v>1</v>
       </c>
       <c r="N97" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O97" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P97" s="3">
-        <v>46051.04447916667</v>
+        <v>46199.43622685185</v>
       </c>
       <c r="Q97" s="3">
-        <v>46051.04447916667</v>
+        <v>46199.43622685185</v>
       </c>
       <c r="R97">
         <v>5.69</v>
       </c>
       <c r="S97" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="98" spans="1:25">
@@ -4925,28 +4652,31 @@
         <v>121</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>281</v>
+        <v>246</v>
+      </c>
+      <c r="I98" t="s">
+        <v>279</v>
       </c>
       <c r="M98">
         <v>1</v>
       </c>
       <c r="N98" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O98" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P98" s="3">
-        <v>46314.40084490741</v>
+        <v>46211.60422453703</v>
       </c>
       <c r="Q98" s="3">
-        <v>46314.40084490741</v>
+        <v>46211.60422453703</v>
       </c>
       <c r="R98">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S98" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="99" spans="1:25">
@@ -4954,31 +4684,28 @@
         <v>122</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="I99" t="s">
-        <v>350</v>
+        <v>247</v>
       </c>
       <c r="M99">
         <v>1</v>
       </c>
       <c r="N99" t="s">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="O99" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P99" s="3">
-        <v>45891.71650462963</v>
+        <v>46314.39943287037</v>
       </c>
       <c r="Q99" s="3">
-        <v>45891.71650462963</v>
+        <v>46314.39943287037</v>
       </c>
       <c r="R99">
-        <v>9.31</v>
+        <v>6.04</v>
       </c>
       <c r="S99" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="100" spans="1:25">
@@ -4986,31 +4713,31 @@
         <v>123</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="I100" t="s">
-        <v>350</v>
+        <v>279</v>
       </c>
       <c r="M100">
         <v>1</v>
       </c>
       <c r="N100" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O100" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P100" s="3">
-        <v>46211.60210648148</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="Q100" s="3">
-        <v>46211.60210648148</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="R100">
         <v>5.69</v>
       </c>
       <c r="S100" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="101" spans="1:25">
@@ -5018,49 +4745,28 @@
         <v>124</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="I101" t="s">
-        <v>351</v>
+        <v>249</v>
       </c>
       <c r="M101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N101" t="s">
-        <v>365</v>
+        <v>290</v>
       </c>
       <c r="O101" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P101" s="3">
-        <v>46251.03130787037</v>
+        <v>46316.43622685185</v>
       </c>
       <c r="Q101" s="3">
-        <v>46251.03130787037</v>
+        <v>46316.43622685185</v>
       </c>
       <c r="R101">
-        <v>14.22</v>
+        <v>5.69</v>
       </c>
       <c r="S101" t="s">
-        <v>383</v>
-      </c>
-      <c r="T101">
-        <v>1</v>
-      </c>
-      <c r="U101">
-        <v>0</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>2</v>
-      </c>
-      <c r="X101" s="3">
-        <v>46257</v>
-      </c>
-      <c r="Y101">
-        <v>5</v>
+        <v>310</v>
       </c>
     </row>
     <row r="102" spans="1:25">
@@ -5068,28 +4774,28 @@
         <v>125</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="M102">
         <v>1</v>
       </c>
       <c r="N102" t="s">
-        <v>374</v>
+        <v>290</v>
       </c>
       <c r="O102" t="s">
-        <v>380</v>
+        <v>309</v>
       </c>
       <c r="P102" s="3">
-        <v>46314.35015046296</v>
+        <v>46314.45354166667</v>
       </c>
       <c r="Q102" s="3">
-        <v>46314.35015046296</v>
+        <v>46314.45354166667</v>
       </c>
       <c r="R102">
-        <v>6.04</v>
+        <v>8.58</v>
       </c>
       <c r="S102" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="103" spans="1:25">
@@ -5097,31 +4803,28 @@
         <v>126</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I103" t="s">
-        <v>351</v>
+        <v>251</v>
       </c>
       <c r="M103">
         <v>1</v>
       </c>
       <c r="N103" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O103" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P103" s="3">
-        <v>46167.36722222222</v>
+        <v>46316.43068287037</v>
       </c>
       <c r="Q103" s="3">
-        <v>46167.36722222222</v>
+        <v>46316.43068287037</v>
       </c>
       <c r="R103">
         <v>5.69</v>
       </c>
       <c r="S103" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="104" spans="1:25">
@@ -5129,28 +4832,31 @@
         <v>127</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>287</v>
+        <v>252</v>
+      </c>
+      <c r="I104" t="s">
+        <v>280</v>
       </c>
       <c r="M104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N104" t="s">
-        <v>370</v>
+        <v>290</v>
       </c>
       <c r="O104" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P104" s="3">
-        <v>46313.73414351852</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="Q104" s="3">
-        <v>46313.73415509259</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="R104">
-        <v>11.73</v>
+        <v>5.69</v>
       </c>
       <c r="S104" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="105" spans="1:25">
@@ -5158,49 +4864,28 @@
         <v>128</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I105" t="s">
-        <v>351</v>
+        <v>253</v>
       </c>
       <c r="M105">
         <v>1</v>
       </c>
       <c r="N105" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O105" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P105" s="3">
-        <v>46309.5507175926</v>
+        <v>46313.72997685185</v>
       </c>
       <c r="Q105" s="3">
-        <v>46309.5507175926</v>
+        <v>46313.72997685185</v>
       </c>
       <c r="R105">
         <v>5.69</v>
       </c>
       <c r="S105" t="s">
-        <v>383</v>
-      </c>
-      <c r="T105">
-        <v>1</v>
-      </c>
-      <c r="U105">
-        <v>0</v>
-      </c>
-      <c r="V105">
-        <v>0</v>
-      </c>
-      <c r="W105">
-        <v>12</v>
-      </c>
-      <c r="X105" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y105">
-        <v>3</v>
+        <v>310</v>
       </c>
     </row>
     <row r="106" spans="1:25">
@@ -5208,28 +4893,28 @@
         <v>129</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="M106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N106" t="s">
-        <v>359</v>
+        <v>304</v>
       </c>
       <c r="O106" t="s">
-        <v>379</v>
+        <v>308</v>
       </c>
       <c r="P106" s="3">
-        <v>46312.0579050926</v>
+        <v>46296.45002314815</v>
       </c>
       <c r="Q106" s="3">
-        <v>46312.0579050926</v>
+        <v>46296.45003472222</v>
       </c>
       <c r="R106">
-        <v>5.69</v>
+        <v>26.25</v>
       </c>
       <c r="S106" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="107" spans="1:25">
@@ -5237,31 +4922,31 @@
         <v>130</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>290</v>
+        <v>255</v>
       </c>
       <c r="I107" t="s">
-        <v>353</v>
+        <v>281</v>
       </c>
       <c r="M107">
         <v>1</v>
       </c>
       <c r="N107" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O107" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P107" s="3">
-        <v>46221.49940972222</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="Q107" s="3">
-        <v>46221.49940972222</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="R107">
         <v>5.69</v>
       </c>
       <c r="S107" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="108" spans="1:25">
@@ -5269,31 +4954,46 @@
         <v>131</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="I108" t="s">
-        <v>354</v>
+        <v>256</v>
       </c>
       <c r="M108">
         <v>1</v>
       </c>
       <c r="N108" t="s">
-        <v>359</v>
+        <v>305</v>
       </c>
       <c r="O108" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P108" s="3">
-        <v>46050.54237268519</v>
+        <v>46303.44568287037</v>
       </c>
       <c r="Q108" s="3">
-        <v>46050.54237268519</v>
+        <v>46303.44568287037</v>
       </c>
       <c r="R108">
-        <v>5.69</v>
+        <v>4.73</v>
       </c>
       <c r="S108" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T108">
+        <v>2</v>
+      </c>
+      <c r="U108">
+        <v>0</v>
+      </c>
+      <c r="V108">
+        <v>0</v>
+      </c>
+      <c r="W108">
+        <v>111</v>
+      </c>
+      <c r="X108" s="3">
+        <v>46308</v>
+      </c>
+      <c r="Y108">
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:25">
@@ -5301,31 +5001,28 @@
         <v>132</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I109" t="s">
-        <v>353</v>
+        <v>257</v>
       </c>
       <c r="M109">
         <v>1</v>
       </c>
       <c r="N109" t="s">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="O109" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P109" s="3">
-        <v>45957.49894675926</v>
+        <v>46301.52780092593</v>
       </c>
       <c r="Q109" s="3">
-        <v>45957.49894675926</v>
+        <v>46301.52780092593</v>
       </c>
       <c r="R109">
-        <v>5.69</v>
+        <v>6.53</v>
       </c>
       <c r="S109" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="110" spans="1:25">
@@ -5333,46 +5030,31 @@
         <v>133</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>293</v>
+        <v>258</v>
+      </c>
+      <c r="I110" t="s">
+        <v>280</v>
       </c>
       <c r="M110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N110" t="s">
-        <v>375</v>
+        <v>290</v>
       </c>
       <c r="O110" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P110" s="3">
-        <v>46316.49146990741</v>
+        <v>46221.54171296296</v>
       </c>
       <c r="Q110" s="3">
-        <v>46316.49152777778</v>
+        <v>46221.54171296296</v>
       </c>
       <c r="R110">
-        <v>15.88</v>
+        <v>5.69</v>
       </c>
       <c r="S110" t="s">
-        <v>383</v>
-      </c>
-      <c r="T110">
-        <v>15</v>
-      </c>
-      <c r="U110">
-        <v>0</v>
-      </c>
-      <c r="V110">
-        <v>0</v>
-      </c>
-      <c r="W110">
-        <v>226</v>
-      </c>
-      <c r="X110" s="3">
-        <v>46298</v>
-      </c>
-      <c r="Y110">
-        <v>-19</v>
+        <v>310</v>
       </c>
     </row>
     <row r="111" spans="1:25">
@@ -5380,31 +5062,31 @@
         <v>134</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>294</v>
+        <v>259</v>
       </c>
       <c r="I111" t="s">
-        <v>351</v>
+        <v>284</v>
       </c>
       <c r="M111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N111" t="s">
-        <v>365</v>
+        <v>290</v>
       </c>
       <c r="O111" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P111" s="3">
-        <v>46241.505625</v>
+        <v>45993.6759375</v>
       </c>
       <c r="Q111" s="3">
-        <v>46241.505625</v>
+        <v>45993.6759375</v>
       </c>
       <c r="R111">
-        <v>11.33</v>
+        <v>9.31</v>
       </c>
       <c r="S111" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="112" spans="1:25">
@@ -5412,31 +5094,31 @@
         <v>135</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="I112" t="s">
-        <v>353</v>
+        <v>284</v>
       </c>
       <c r="M112">
         <v>1</v>
       </c>
       <c r="N112" t="s">
-        <v>359</v>
+        <v>289</v>
       </c>
       <c r="O112" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P112" s="3">
-        <v>46196.62574074074</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="Q112" s="3">
-        <v>46196.62574074074</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="R112">
-        <v>5.69</v>
+        <v>12.41</v>
       </c>
       <c r="S112" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="113" spans="1:25">
@@ -5444,31 +5126,31 @@
         <v>136</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="I113" t="s">
-        <v>351</v>
+        <v>279</v>
       </c>
       <c r="M113">
         <v>1</v>
       </c>
       <c r="N113" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O113" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P113" s="3">
-        <v>45959.6512037037</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="Q113" s="3">
-        <v>45959.6512037037</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="R113">
         <v>9.31</v>
       </c>
       <c r="S113" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="114" spans="1:25">
@@ -5476,31 +5158,31 @@
         <v>137</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="I114" t="s">
-        <v>350</v>
+        <v>281</v>
       </c>
       <c r="M114">
         <v>1</v>
       </c>
       <c r="N114" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O114" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P114" s="3">
-        <v>45973.56506944444</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="Q114" s="3">
-        <v>45973.56506944444</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="R114">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S114" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="115" spans="1:25">
@@ -5508,28 +5190,31 @@
         <v>138</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>298</v>
+        <v>263</v>
+      </c>
+      <c r="I115" t="s">
+        <v>284</v>
       </c>
       <c r="M115">
         <v>1</v>
       </c>
       <c r="N115" t="s">
-        <v>374</v>
+        <v>290</v>
       </c>
       <c r="O115" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P115" s="3">
-        <v>46313.49944444445</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="Q115" s="3">
-        <v>46313.49944444445</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="R115">
-        <v>6.04</v>
+        <v>5.69</v>
       </c>
       <c r="S115" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="116" spans="1:25">
@@ -5537,28 +5222,31 @@
         <v>139</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>299</v>
+        <v>264</v>
+      </c>
+      <c r="I116" t="s">
+        <v>283</v>
       </c>
       <c r="M116">
         <v>1</v>
       </c>
       <c r="N116" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O116" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P116" s="3">
-        <v>46316.43068287037</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="Q116" s="3">
-        <v>46316.43068287037</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="R116">
         <v>5.69</v>
       </c>
       <c r="S116" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="117" spans="1:25">
@@ -5566,28 +5254,46 @@
         <v>140</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="M117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N117" t="s">
-        <v>376</v>
+        <v>290</v>
       </c>
       <c r="O117" t="s">
-        <v>381</v>
+        <v>309</v>
       </c>
       <c r="P117" s="3">
-        <v>46313.73415509259</v>
+        <v>46306.55003472222</v>
       </c>
       <c r="Q117" s="3">
-        <v>46316.43625</v>
+        <v>46306.55003472222</v>
       </c>
       <c r="R117">
-        <v>26.82</v>
+        <v>8.58</v>
       </c>
       <c r="S117" t="s">
-        <v>382</v>
+        <v>311</v>
+      </c>
+      <c r="T117">
+        <v>2</v>
+      </c>
+      <c r="U117">
+        <v>59.99</v>
+      </c>
+      <c r="V117">
+        <v>1</v>
+      </c>
+      <c r="W117">
+        <v>946</v>
+      </c>
+      <c r="X117" s="3">
+        <v>46294</v>
+      </c>
+      <c r="Y117">
+        <v>-13</v>
       </c>
     </row>
     <row r="118" spans="1:25">
@@ -5595,31 +5301,28 @@
         <v>141</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="I118" t="s">
-        <v>349</v>
+        <v>266</v>
       </c>
       <c r="M118">
         <v>1</v>
       </c>
       <c r="N118" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O118" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P118" s="3">
-        <v>46191.82362268519</v>
+        <v>46312.95512731482</v>
       </c>
       <c r="Q118" s="3">
-        <v>46191.82362268519</v>
+        <v>46312.95512731482</v>
       </c>
       <c r="R118">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S118" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="119" spans="1:25">
@@ -5627,46 +5330,31 @@
         <v>142</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>302</v>
+        <v>267</v>
+      </c>
+      <c r="I119" t="s">
+        <v>279</v>
       </c>
       <c r="M119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N119" t="s">
-        <v>365</v>
+        <v>290</v>
       </c>
       <c r="O119" t="s">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="P119" s="3">
-        <v>46286.62572916667</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="Q119" s="3">
-        <v>46306.5500462963</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="R119">
-        <v>14.22</v>
+        <v>9.31</v>
       </c>
       <c r="S119" t="s">
-        <v>383</v>
-      </c>
-      <c r="T119">
-        <v>2</v>
-      </c>
-      <c r="U119">
-        <v>0</v>
-      </c>
-      <c r="V119">
-        <v>0</v>
-      </c>
-      <c r="W119">
-        <v>32</v>
-      </c>
-      <c r="X119" s="3">
-        <v>46297</v>
-      </c>
-      <c r="Y119">
-        <v>10</v>
+        <v>310</v>
       </c>
     </row>
     <row r="120" spans="1:25">
@@ -5674,28 +5362,31 @@
         <v>143</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>303</v>
+        <v>268</v>
+      </c>
+      <c r="I120" t="s">
+        <v>280</v>
       </c>
       <c r="M120">
         <v>1</v>
       </c>
       <c r="N120" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O120" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P120" s="3">
-        <v>46304.50560185185</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q120" s="3">
-        <v>46304.50560185185</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R120">
         <v>5.69</v>
       </c>
       <c r="S120" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="121" spans="1:25">
@@ -5703,28 +5394,31 @@
         <v>144</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>304</v>
+        <v>269</v>
+      </c>
+      <c r="I121" t="s">
+        <v>284</v>
       </c>
       <c r="M121">
         <v>1</v>
       </c>
       <c r="N121" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O121" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P121" s="3">
-        <v>46314.40085648148</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="Q121" s="3">
-        <v>46314.40085648148</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="R121">
         <v>5.69</v>
       </c>
       <c r="S121" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="122" spans="1:25">
@@ -5732,28 +5426,31 @@
         <v>145</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>305</v>
+        <v>270</v>
+      </c>
+      <c r="I122" t="s">
+        <v>283</v>
       </c>
       <c r="M122">
         <v>1</v>
       </c>
       <c r="N122" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O122" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P122" s="3">
-        <v>46027.60903935185</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="Q122" s="3">
-        <v>46027.60903935185</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="R122">
         <v>5.69</v>
       </c>
       <c r="S122" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="123" spans="1:25">
@@ -5761,31 +5458,28 @@
         <v>146</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I123" t="s">
-        <v>354</v>
+        <v>271</v>
       </c>
       <c r="M123">
         <v>1</v>
       </c>
       <c r="N123" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O123" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="P123" s="3">
-        <v>46215.75961805556</v>
+        <v>46314.78832175926</v>
       </c>
       <c r="Q123" s="3">
-        <v>46215.75961805556</v>
+        <v>46314.78832175926</v>
       </c>
       <c r="R123">
         <v>5.69</v>
       </c>
       <c r="S123" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="124" spans="1:25">
@@ -5793,46 +5487,28 @@
         <v>147</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="M124">
         <v>1</v>
       </c>
       <c r="N124" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O124" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P124" s="3">
-        <v>46280.49518518519</v>
+        <v>46314.79108796296</v>
       </c>
       <c r="Q124" s="3">
-        <v>46280.49518518519</v>
+        <v>46314.79108796296</v>
       </c>
       <c r="R124">
         <v>5.69</v>
       </c>
       <c r="S124" t="s">
-        <v>383</v>
-      </c>
-      <c r="T124">
-        <v>1</v>
-      </c>
-      <c r="U124">
-        <v>0</v>
-      </c>
-      <c r="V124">
-        <v>0</v>
-      </c>
-      <c r="W124">
-        <v>17</v>
-      </c>
-      <c r="X124" s="3">
-        <v>46283</v>
-      </c>
-      <c r="Y124">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="125" spans="1:25">
@@ -5840,28 +5516,31 @@
         <v>148</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>308</v>
+        <v>273</v>
+      </c>
+      <c r="I125" t="s">
+        <v>281</v>
       </c>
       <c r="M125">
         <v>1</v>
       </c>
       <c r="N125" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O125" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="P125" s="3">
-        <v>46311.94667824074</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="Q125" s="3">
-        <v>46311.94667824074</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="R125">
         <v>5.69</v>
       </c>
       <c r="S125" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="126" spans="1:25">
@@ -5869,1145 +5548,31 @@
         <v>149</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>309</v>
+        <v>274</v>
+      </c>
+      <c r="I126" t="s">
+        <v>283</v>
       </c>
       <c r="M126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N126" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="O126" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="P126" s="3">
-        <v>46313.79785879629</v>
+        <v>46196.65561342592</v>
       </c>
       <c r="Q126" s="3">
-        <v>46313.79785879629</v>
+        <v>46224.32857638889</v>
       </c>
       <c r="R126">
-        <v>8.58</v>
+        <v>11.38</v>
       </c>
       <c r="S126" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="127" spans="1:25">
-      <c r="A127" t="s">
-        <v>150</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="I127" t="s">
-        <v>356</v>
-      </c>
-      <c r="M127">
-        <v>1</v>
-      </c>
-      <c r="N127" t="s">
-        <v>359</v>
-      </c>
-      <c r="O127" t="s">
-        <v>379</v>
-      </c>
-      <c r="P127" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="Q127" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="R127">
-        <v>5.69</v>
-      </c>
-      <c r="S127" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="128" spans="1:25">
-      <c r="A128" t="s">
-        <v>151</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="I128" t="s">
-        <v>353</v>
-      </c>
-      <c r="M128">
-        <v>1</v>
-      </c>
-      <c r="N128" t="s">
-        <v>359</v>
-      </c>
-      <c r="O128" t="s">
-        <v>379</v>
-      </c>
-      <c r="P128" s="3">
-        <v>46212.55766203703</v>
-      </c>
-      <c r="Q128" s="3">
-        <v>46212.55766203703</v>
-      </c>
-      <c r="R128">
-        <v>5.69</v>
-      </c>
-      <c r="S128" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="129" spans="1:25">
-      <c r="A129" t="s">
-        <v>152</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="M129">
-        <v>1</v>
-      </c>
-      <c r="N129" t="s">
-        <v>359</v>
-      </c>
-      <c r="O129" t="s">
-        <v>379</v>
-      </c>
-      <c r="P129" s="3">
-        <v>46199.43622685185</v>
-      </c>
-      <c r="Q129" s="3">
-        <v>46199.43622685185</v>
-      </c>
-      <c r="R129">
-        <v>5.69</v>
-      </c>
-      <c r="S129" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="130" spans="1:25">
-      <c r="A130" t="s">
-        <v>153</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="I130" t="s">
-        <v>350</v>
-      </c>
-      <c r="M130">
-        <v>1</v>
-      </c>
-      <c r="N130" t="s">
-        <v>359</v>
-      </c>
-      <c r="O130" t="s">
-        <v>379</v>
-      </c>
-      <c r="P130" s="3">
-        <v>46211.60422453703</v>
-      </c>
-      <c r="Q130" s="3">
-        <v>46211.60422453703</v>
-      </c>
-      <c r="R130">
-        <v>5.69</v>
-      </c>
-      <c r="S130" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="131" spans="1:25">
-      <c r="A131" t="s">
-        <v>154</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="M131">
-        <v>1</v>
-      </c>
-      <c r="N131" t="s">
-        <v>374</v>
-      </c>
-      <c r="O131" t="s">
-        <v>380</v>
-      </c>
-      <c r="P131" s="3">
-        <v>46314.39943287037</v>
-      </c>
-      <c r="Q131" s="3">
-        <v>46314.39943287037</v>
-      </c>
-      <c r="R131">
-        <v>6.04</v>
-      </c>
-      <c r="S131" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="132" spans="1:25">
-      <c r="A132" t="s">
-        <v>155</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="I132" t="s">
-        <v>350</v>
-      </c>
-      <c r="M132">
-        <v>1</v>
-      </c>
-      <c r="N132" t="s">
-        <v>359</v>
-      </c>
-      <c r="O132" t="s">
-        <v>379</v>
-      </c>
-      <c r="P132" s="3">
-        <v>46196.76916666667</v>
-      </c>
-      <c r="Q132" s="3">
-        <v>46196.76916666667</v>
-      </c>
-      <c r="R132">
-        <v>5.69</v>
-      </c>
-      <c r="S132" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="133" spans="1:25">
-      <c r="A133" t="s">
-        <v>156</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="M133">
-        <v>1</v>
-      </c>
-      <c r="N133" t="s">
-        <v>359</v>
-      </c>
-      <c r="O133" t="s">
-        <v>379</v>
-      </c>
-      <c r="P133" s="3">
-        <v>46316.43622685185</v>
-      </c>
-      <c r="Q133" s="3">
-        <v>46316.43622685185</v>
-      </c>
-      <c r="R133">
-        <v>5.69</v>
-      </c>
-      <c r="S133" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="134" spans="1:25">
-      <c r="A134" t="s">
-        <v>157</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="M134">
-        <v>1</v>
-      </c>
-      <c r="N134" t="s">
-        <v>359</v>
-      </c>
-      <c r="O134" t="s">
-        <v>380</v>
-      </c>
-      <c r="P134" s="3">
-        <v>46314.45354166667</v>
-      </c>
-      <c r="Q134" s="3">
-        <v>46314.45354166667</v>
-      </c>
-      <c r="R134">
-        <v>8.58</v>
-      </c>
-      <c r="S134" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="135" spans="1:25">
-      <c r="A135" t="s">
-        <v>158</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="M135">
-        <v>1</v>
-      </c>
-      <c r="N135" t="s">
-        <v>359</v>
-      </c>
-      <c r="O135" t="s">
-        <v>379</v>
-      </c>
-      <c r="P135" s="3">
-        <v>46316.43068287037</v>
-      </c>
-      <c r="Q135" s="3">
-        <v>46316.43068287037</v>
-      </c>
-      <c r="R135">
-        <v>5.69</v>
-      </c>
-      <c r="S135" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="136" spans="1:25">
-      <c r="A136" t="s">
-        <v>159</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="I136" t="s">
-        <v>349</v>
-      </c>
-      <c r="M136">
-        <v>1</v>
-      </c>
-      <c r="N136" t="s">
-        <v>359</v>
-      </c>
-      <c r="O136" t="s">
-        <v>379</v>
-      </c>
-      <c r="P136" s="3">
-        <v>46198.62644675926</v>
-      </c>
-      <c r="Q136" s="3">
-        <v>46198.62644675926</v>
-      </c>
-      <c r="R136">
-        <v>5.69</v>
-      </c>
-      <c r="S136" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="137" spans="1:25">
-      <c r="A137" t="s">
-        <v>160</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="M137">
-        <v>1</v>
-      </c>
-      <c r="N137" t="s">
-        <v>359</v>
-      </c>
-      <c r="O137" t="s">
-        <v>379</v>
-      </c>
-      <c r="P137" s="3">
-        <v>46313.72997685185</v>
-      </c>
-      <c r="Q137" s="3">
-        <v>46313.72997685185</v>
-      </c>
-      <c r="R137">
-        <v>5.69</v>
-      </c>
-      <c r="S137" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="138" spans="1:25">
-      <c r="A138" t="s">
-        <v>161</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="M138">
-        <v>2</v>
-      </c>
-      <c r="N138" t="s">
-        <v>377</v>
-      </c>
-      <c r="O138" t="s">
-        <v>381</v>
-      </c>
-      <c r="P138" s="3">
-        <v>46296.45002314815</v>
-      </c>
-      <c r="Q138" s="3">
-        <v>46296.45003472222</v>
-      </c>
-      <c r="R138">
-        <v>26.25</v>
-      </c>
-      <c r="S138" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="139" spans="1:25">
-      <c r="A139" t="s">
-        <v>162</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="I139" t="s">
-        <v>351</v>
-      </c>
-      <c r="M139">
-        <v>1</v>
-      </c>
-      <c r="N139" t="s">
-        <v>359</v>
-      </c>
-      <c r="O139" t="s">
-        <v>379</v>
-      </c>
-      <c r="P139" s="3">
-        <v>46220.44594907408</v>
-      </c>
-      <c r="Q139" s="3">
-        <v>46220.44594907408</v>
-      </c>
-      <c r="R139">
-        <v>5.69</v>
-      </c>
-      <c r="S139" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="140" spans="1:25">
-      <c r="A140" t="s">
-        <v>163</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="M140">
-        <v>1</v>
-      </c>
-      <c r="N140" t="s">
-        <v>372</v>
-      </c>
-      <c r="O140" t="s">
-        <v>380</v>
-      </c>
-      <c r="P140" s="3">
-        <v>46303.44568287037</v>
-      </c>
-      <c r="Q140" s="3">
-        <v>46303.44568287037</v>
-      </c>
-      <c r="R140">
-        <v>4.73</v>
-      </c>
-      <c r="S140" t="s">
-        <v>383</v>
-      </c>
-      <c r="T140">
-        <v>2</v>
-      </c>
-      <c r="U140">
-        <v>0</v>
-      </c>
-      <c r="V140">
-        <v>0</v>
-      </c>
-      <c r="W140">
-        <v>112</v>
-      </c>
-      <c r="X140" s="3">
-        <v>46308</v>
-      </c>
-      <c r="Y140">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="141" spans="1:25">
-      <c r="A141" t="s">
-        <v>164</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="I141" t="s">
-        <v>354</v>
-      </c>
-      <c r="M141">
-        <v>1</v>
-      </c>
-      <c r="N141" t="s">
-        <v>362</v>
-      </c>
-      <c r="O141" t="s">
-        <v>380</v>
-      </c>
-      <c r="P141" s="3">
-        <v>46241.50563657407</v>
-      </c>
-      <c r="Q141" s="3">
-        <v>46241.50563657407</v>
-      </c>
-      <c r="R141">
-        <v>4.86</v>
-      </c>
-      <c r="S141" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="142" spans="1:25">
-      <c r="A142" t="s">
-        <v>165</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="M142">
-        <v>1</v>
-      </c>
-      <c r="N142" t="s">
-        <v>378</v>
-      </c>
-      <c r="O142" t="s">
-        <v>380</v>
-      </c>
-      <c r="P142" s="3">
-        <v>46301.52780092593</v>
-      </c>
-      <c r="Q142" s="3">
-        <v>46301.52780092593</v>
-      </c>
-      <c r="R142">
-        <v>6.53</v>
-      </c>
-      <c r="S142" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="143" spans="1:25">
-      <c r="A143" t="s">
-        <v>166</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="I143" t="s">
-        <v>349</v>
-      </c>
-      <c r="M143">
-        <v>1</v>
-      </c>
-      <c r="N143" t="s">
-        <v>359</v>
-      </c>
-      <c r="O143" t="s">
-        <v>379</v>
-      </c>
-      <c r="P143" s="3">
-        <v>46221.54171296296</v>
-      </c>
-      <c r="Q143" s="3">
-        <v>46221.54171296296</v>
-      </c>
-      <c r="R143">
-        <v>5.69</v>
-      </c>
-      <c r="S143" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="144" spans="1:25">
-      <c r="A144" t="s">
-        <v>167</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="I144" t="s">
-        <v>354</v>
-      </c>
-      <c r="M144">
-        <v>1</v>
-      </c>
-      <c r="N144" t="s">
-        <v>359</v>
-      </c>
-      <c r="O144" t="s">
-        <v>379</v>
-      </c>
-      <c r="P144" s="3">
-        <v>45993.6759375</v>
-      </c>
-      <c r="Q144" s="3">
-        <v>45993.6759375</v>
-      </c>
-      <c r="R144">
-        <v>9.31</v>
-      </c>
-      <c r="S144" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="145" spans="1:25">
-      <c r="A145" t="s">
-        <v>168</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="I145" t="s">
-        <v>354</v>
-      </c>
-      <c r="M145">
-        <v>1</v>
-      </c>
-      <c r="N145" t="s">
-        <v>360</v>
-      </c>
-      <c r="O145" t="s">
-        <v>380</v>
-      </c>
-      <c r="P145" s="3">
-        <v>46178.61515046296</v>
-      </c>
-      <c r="Q145" s="3">
-        <v>46178.61515046296</v>
-      </c>
-      <c r="R145">
-        <v>12.41</v>
-      </c>
-      <c r="S145" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="146" spans="1:25">
-      <c r="A146" t="s">
-        <v>169</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="I146" t="s">
-        <v>350</v>
-      </c>
-      <c r="M146">
-        <v>1</v>
-      </c>
-      <c r="N146" t="s">
-        <v>359</v>
-      </c>
-      <c r="O146" t="s">
-        <v>379</v>
-      </c>
-      <c r="P146" s="3">
-        <v>45981.84152777777</v>
-      </c>
-      <c r="Q146" s="3">
-        <v>45981.84152777777</v>
-      </c>
-      <c r="R146">
-        <v>9.31</v>
-      </c>
-      <c r="S146" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="147" spans="1:25">
-      <c r="A147" t="s">
-        <v>170</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="I147" t="s">
-        <v>353</v>
-      </c>
-      <c r="M147">
-        <v>1</v>
-      </c>
-      <c r="N147" t="s">
-        <v>359</v>
-      </c>
-      <c r="O147" t="s">
-        <v>380</v>
-      </c>
-      <c r="P147" s="3">
-        <v>46252.04450231481</v>
-      </c>
-      <c r="Q147" s="3">
-        <v>46252.04450231481</v>
-      </c>
-      <c r="R147">
-        <v>8.58</v>
-      </c>
-      <c r="S147" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="148" spans="1:25">
-      <c r="A148" t="s">
-        <v>171</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="I148" t="s">
-        <v>349</v>
-      </c>
-      <c r="M148">
-        <v>1</v>
-      </c>
-      <c r="N148" t="s">
-        <v>359</v>
-      </c>
-      <c r="O148" t="s">
-        <v>379</v>
-      </c>
-      <c r="P148" s="3">
-        <v>46209.7618287037</v>
-      </c>
-      <c r="Q148" s="3">
-        <v>46209.7618287037</v>
-      </c>
-      <c r="R148">
-        <v>5.69</v>
-      </c>
-      <c r="S148" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="149" spans="1:25">
-      <c r="A149" t="s">
-        <v>172</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="I149" t="s">
-        <v>351</v>
-      </c>
-      <c r="M149">
-        <v>1</v>
-      </c>
-      <c r="N149" t="s">
-        <v>359</v>
-      </c>
-      <c r="O149" t="s">
-        <v>379</v>
-      </c>
-      <c r="P149" s="3">
-        <v>45965.5908449074</v>
-      </c>
-      <c r="Q149" s="3">
-        <v>45965.5908449074</v>
-      </c>
-      <c r="R149">
-        <v>5.69</v>
-      </c>
-      <c r="S149" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="150" spans="1:25">
-      <c r="A150" t="s">
-        <v>173</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="I150" t="s">
-        <v>354</v>
-      </c>
-      <c r="M150">
-        <v>1</v>
-      </c>
-      <c r="N150" t="s">
-        <v>359</v>
-      </c>
-      <c r="O150" t="s">
-        <v>379</v>
-      </c>
-      <c r="P150" s="3">
-        <v>46206.37778935185</v>
-      </c>
-      <c r="Q150" s="3">
-        <v>46206.37778935185</v>
-      </c>
-      <c r="R150">
-        <v>5.69</v>
-      </c>
-      <c r="S150" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="151" spans="1:25">
-      <c r="A151" t="s">
-        <v>174</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="I151" t="s">
-        <v>353</v>
-      </c>
-      <c r="M151">
-        <v>1</v>
-      </c>
-      <c r="N151" t="s">
-        <v>359</v>
-      </c>
-      <c r="O151" t="s">
-        <v>379</v>
-      </c>
-      <c r="P151" s="3">
-        <v>46220.91548611111</v>
-      </c>
-      <c r="Q151" s="3">
-        <v>46220.91548611111</v>
-      </c>
-      <c r="R151">
-        <v>5.69</v>
-      </c>
-      <c r="S151" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="152" spans="1:25">
-      <c r="A152" t="s">
-        <v>175</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="M152">
-        <v>1</v>
-      </c>
-      <c r="N152" t="s">
-        <v>359</v>
-      </c>
-      <c r="O152" t="s">
-        <v>380</v>
-      </c>
-      <c r="P152" s="3">
-        <v>46306.55003472222</v>
-      </c>
-      <c r="Q152" s="3">
-        <v>46306.55003472222</v>
-      </c>
-      <c r="R152">
-        <v>8.58</v>
-      </c>
-      <c r="S152" t="s">
-        <v>383</v>
-      </c>
-      <c r="T152">
-        <v>2</v>
-      </c>
-      <c r="U152">
-        <v>59.99</v>
-      </c>
-      <c r="V152">
-        <v>1</v>
-      </c>
-      <c r="W152">
-        <v>946</v>
-      </c>
-      <c r="X152" s="3">
-        <v>46294</v>
-      </c>
-      <c r="Y152">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="153" spans="1:25">
-      <c r="A153" t="s">
-        <v>176</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="M153">
-        <v>1</v>
-      </c>
-      <c r="N153" t="s">
-        <v>359</v>
-      </c>
-      <c r="O153" t="s">
-        <v>380</v>
-      </c>
-      <c r="P153" s="3">
-        <v>46312.95512731482</v>
-      </c>
-      <c r="Q153" s="3">
-        <v>46312.95512731482</v>
-      </c>
-      <c r="R153">
-        <v>8.58</v>
-      </c>
-      <c r="S153" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="154" spans="1:25">
-      <c r="A154" t="s">
-        <v>177</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="I154" t="s">
-        <v>350</v>
-      </c>
-      <c r="M154">
-        <v>1</v>
-      </c>
-      <c r="N154" t="s">
-        <v>359</v>
-      </c>
-      <c r="O154" t="s">
-        <v>379</v>
-      </c>
-      <c r="P154" s="3">
-        <v>45939.98240740741</v>
-      </c>
-      <c r="Q154" s="3">
-        <v>45939.98240740741</v>
-      </c>
-      <c r="R154">
-        <v>9.31</v>
-      </c>
-      <c r="S154" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="155" spans="1:25">
-      <c r="A155" t="s">
-        <v>178</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="I155" t="s">
-        <v>349</v>
-      </c>
-      <c r="M155">
-        <v>1</v>
-      </c>
-      <c r="N155" t="s">
-        <v>359</v>
-      </c>
-      <c r="O155" t="s">
-        <v>379</v>
-      </c>
-      <c r="P155" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="Q155" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="R155">
-        <v>5.69</v>
-      </c>
-      <c r="S155" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="156" spans="1:25">
-      <c r="A156" t="s">
-        <v>179</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="I156" t="s">
-        <v>354</v>
-      </c>
-      <c r="M156">
-        <v>1</v>
-      </c>
-      <c r="N156" t="s">
-        <v>359</v>
-      </c>
-      <c r="O156" t="s">
-        <v>379</v>
-      </c>
-      <c r="P156" s="3">
-        <v>45990.94167824074</v>
-      </c>
-      <c r="Q156" s="3">
-        <v>45990.94167824074</v>
-      </c>
-      <c r="R156">
-        <v>5.69</v>
-      </c>
-      <c r="S156" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="157" spans="1:25">
-      <c r="A157" t="s">
-        <v>180</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="I157" t="s">
-        <v>353</v>
-      </c>
-      <c r="M157">
-        <v>1</v>
-      </c>
-      <c r="N157" t="s">
-        <v>359</v>
-      </c>
-      <c r="O157" t="s">
-        <v>379</v>
-      </c>
-      <c r="P157" s="3">
-        <v>45913.74726851852</v>
-      </c>
-      <c r="Q157" s="3">
-        <v>45913.74726851852</v>
-      </c>
-      <c r="R157">
-        <v>5.69</v>
-      </c>
-      <c r="S157" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="158" spans="1:25">
-      <c r="A158" t="s">
-        <v>181</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="M158">
-        <v>1</v>
-      </c>
-      <c r="N158" t="s">
-        <v>359</v>
-      </c>
-      <c r="O158" t="s">
-        <v>380</v>
-      </c>
-      <c r="P158" s="3">
-        <v>46314.78832175926</v>
-      </c>
-      <c r="Q158" s="3">
-        <v>46314.78832175926</v>
-      </c>
-      <c r="R158">
-        <v>5.69</v>
-      </c>
-      <c r="S158" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="159" spans="1:25">
-      <c r="A159" t="s">
-        <v>182</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="M159">
-        <v>1</v>
-      </c>
-      <c r="N159" t="s">
-        <v>359</v>
-      </c>
-      <c r="O159" t="s">
-        <v>379</v>
-      </c>
-      <c r="P159" s="3">
-        <v>46314.79108796296</v>
-      </c>
-      <c r="Q159" s="3">
-        <v>46314.79108796296</v>
-      </c>
-      <c r="R159">
-        <v>5.69</v>
-      </c>
-      <c r="S159" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="160" spans="1:25">
-      <c r="A160" t="s">
-        <v>183</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="I160" t="s">
-        <v>351</v>
-      </c>
-      <c r="M160">
-        <v>1</v>
-      </c>
-      <c r="N160" t="s">
-        <v>359</v>
-      </c>
-      <c r="O160" t="s">
-        <v>379</v>
-      </c>
-      <c r="P160" s="3">
-        <v>46221.60350694445</v>
-      </c>
-      <c r="Q160" s="3">
-        <v>46221.60350694445</v>
-      </c>
-      <c r="R160">
-        <v>5.69</v>
-      </c>
-      <c r="S160" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="161" spans="1:19">
-      <c r="A161" t="s">
-        <v>184</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="I161" t="s">
-        <v>353</v>
-      </c>
-      <c r="M161">
-        <v>2</v>
-      </c>
-      <c r="N161" t="s">
-        <v>359</v>
-      </c>
-      <c r="O161" t="s">
-        <v>379</v>
-      </c>
-      <c r="P161" s="3">
-        <v>46196.65561342592</v>
-      </c>
-      <c r="Q161" s="3">
-        <v>46224.32857638889</v>
-      </c>
-      <c r="R161">
-        <v>11.38</v>
-      </c>
-      <c r="S161" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -7137,41 +5702,6 @@
     <hyperlink ref="B124" r:id="rId123"/>
     <hyperlink ref="B125" r:id="rId124"/>
     <hyperlink ref="B126" r:id="rId125"/>
-    <hyperlink ref="B127" r:id="rId126"/>
-    <hyperlink ref="B128" r:id="rId127"/>
-    <hyperlink ref="B129" r:id="rId128"/>
-    <hyperlink ref="B130" r:id="rId129"/>
-    <hyperlink ref="B131" r:id="rId130"/>
-    <hyperlink ref="B132" r:id="rId131"/>
-    <hyperlink ref="B133" r:id="rId132"/>
-    <hyperlink ref="B134" r:id="rId133"/>
-    <hyperlink ref="B135" r:id="rId134"/>
-    <hyperlink ref="B136" r:id="rId135"/>
-    <hyperlink ref="B137" r:id="rId136"/>
-    <hyperlink ref="B138" r:id="rId137"/>
-    <hyperlink ref="B139" r:id="rId138"/>
-    <hyperlink ref="B140" r:id="rId139"/>
-    <hyperlink ref="B141" r:id="rId140"/>
-    <hyperlink ref="B142" r:id="rId141"/>
-    <hyperlink ref="B143" r:id="rId142"/>
-    <hyperlink ref="B144" r:id="rId143"/>
-    <hyperlink ref="B145" r:id="rId144"/>
-    <hyperlink ref="B146" r:id="rId145"/>
-    <hyperlink ref="B147" r:id="rId146"/>
-    <hyperlink ref="B148" r:id="rId147"/>
-    <hyperlink ref="B149" r:id="rId148"/>
-    <hyperlink ref="B150" r:id="rId149"/>
-    <hyperlink ref="B151" r:id="rId150"/>
-    <hyperlink ref="B152" r:id="rId151"/>
-    <hyperlink ref="B153" r:id="rId152"/>
-    <hyperlink ref="B154" r:id="rId153"/>
-    <hyperlink ref="B155" r:id="rId154"/>
-    <hyperlink ref="B156" r:id="rId155"/>
-    <hyperlink ref="B157" r:id="rId156"/>
-    <hyperlink ref="B158" r:id="rId157"/>
-    <hyperlink ref="B159" r:id="rId158"/>
-    <hyperlink ref="B160" r:id="rId159"/>
-    <hyperlink ref="B161" r:id="rId160"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="287">
   <si>
     <t>handle</t>
   </si>
@@ -103,39 +103,21 @@
     <t>beauty.baddie.444</t>
   </si>
   <si>
-    <t>brunozpage</t>
-  </si>
-  <si>
     <t>celaniklozet</t>
   </si>
   <si>
-    <t>chivequeen5</t>
-  </si>
-  <si>
     <t>christopherreidy7</t>
   </si>
   <si>
-    <t>clarasdiary28</t>
-  </si>
-  <si>
     <t>craigkennethmccal</t>
   </si>
   <si>
-    <t>dad_nails_tiktok</t>
-  </si>
-  <si>
     <t>debsline.co</t>
   </si>
   <si>
-    <t>deenreminders0786</t>
-  </si>
-  <si>
     <t>elizabeth.haigh3</t>
   </si>
   <si>
-    <t>ellaoxborough</t>
-  </si>
-  <si>
     <t>emandpete_vanlife</t>
   </si>
   <si>
@@ -148,9 +130,6 @@
     <t>eyeofrahhhhh</t>
   </si>
   <si>
-    <t>fancyfinds81</t>
-  </si>
-  <si>
     <t>fariwala66</t>
   </si>
   <si>
@@ -223,18 +202,12 @@
     <t>katie.the.reader</t>
   </si>
   <si>
-    <t>kerry_thompson83</t>
-  </si>
-  <si>
     <t>khadeeja088</t>
   </si>
   <si>
     <t>kingmxn</t>
   </si>
   <si>
-    <t>kiyanitiktokshop</t>
-  </si>
-  <si>
     <t>knic_26</t>
   </si>
   <si>
@@ -250,9 +223,6 @@
     <t>mah70178</t>
   </si>
   <si>
-    <t>mairashopuk0</t>
-  </si>
-  <si>
     <t>marjorie.binks</t>
   </si>
   <si>
@@ -265,9 +235,6 @@
     <t>melissavanzan236</t>
   </si>
   <si>
-    <t>mrs.a.saim</t>
-  </si>
-  <si>
     <t>mssushi26</t>
   </si>
   <si>
@@ -478,39 +445,21 @@
     <t>https://www.tiktok.com/@beauty.baddie.444</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@brunozpage</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@celaniklozet</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@chivequeen5</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@christopherreidy7</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@clarasdiary28</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@craigkennethmccal</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@dad_nails_tiktok</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@debsline.co</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@deenreminders0786</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@elizabeth.haigh3</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@ellaoxborough</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@emandpete_vanlife</t>
   </si>
   <si>
@@ -523,9 +472,6 @@
     <t>https://www.tiktok.com/@eyeofrahhhhh</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@fancyfinds81</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@fariwala66</t>
   </si>
   <si>
@@ -598,18 +544,12 @@
     <t>https://www.tiktok.com/@katie.the.reader</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@kerry_thompson83</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@khadeeja088</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@kingmxn</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@kiyanitiktokshop</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@knic_26</t>
   </si>
   <si>
@@ -625,9 +565,6 @@
     <t>https://www.tiktok.com/@mah70178</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@mairashopuk0</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@marjorie.binks</t>
   </si>
   <si>
@@ -640,9 +577,6 @@
     <t>https://www.tiktok.com/@melissavanzan236</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@mrs.a.saim</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@mssushi26</t>
   </si>
   <si>
@@ -887,15 +821,6 @@
   </si>
   <si>
     <t>Ashwagandha Coffee</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Skin Radiance, Turmeric Curcumin</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Green Burner, Turmeric Curcumin</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Shatavari</t>
   </si>
   <si>
     <t>Ashwagandha Coffee, Green Burner, Gut Shift, Turmeric Curcumin</t>
@@ -1324,7 +1249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y126"/>
+  <dimension ref="A1:Y115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1409,19 +1334,19 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I2" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="O2" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P2" s="3">
         <v>46028.62637731482</v>
@@ -1433,7 +1358,7 @@
         <v>5.64</v>
       </c>
       <c r="S2" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1441,19 +1366,19 @@
         <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I3" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O3" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P3" s="3">
         <v>45998.88378472222</v>
@@ -1465,7 +1390,7 @@
         <v>9.31</v>
       </c>
       <c r="S3" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1473,19 +1398,19 @@
         <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I4" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O4" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P4" s="3">
         <v>45986.77690972222</v>
@@ -1497,7 +1422,7 @@
         <v>5.69</v>
       </c>
       <c r="S4" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1505,19 +1430,19 @@
         <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="I5" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O5" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P5" s="3">
         <v>45911.17809027778</v>
@@ -1529,7 +1454,7 @@
         <v>9.31</v>
       </c>
       <c r="S5" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1537,46 +1462,52 @@
         <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>154</v>
+        <v>143</v>
+      </c>
+      <c r="E6" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" t="s">
+        <v>254</v>
+      </c>
+      <c r="G6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I6" t="s">
+        <v>259</v>
+      </c>
+      <c r="J6" t="s">
+        <v>265</v>
+      </c>
+      <c r="K6" t="s">
+        <v>266</v>
+      </c>
+      <c r="L6" t="s">
+        <v>265</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="O6" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="P6" s="3">
-        <v>46312.05796296296</v>
+        <v>45989.98658564815</v>
       </c>
       <c r="Q6" s="3">
-        <v>46314.78833333333</v>
+        <v>45989.98658564815</v>
       </c>
       <c r="R6">
-        <v>36.63</v>
+        <v>9.31</v>
       </c>
       <c r="S6" t="s">
-        <v>311</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>3</v>
-      </c>
-      <c r="X6" s="3">
-        <v>46316</v>
-      </c>
-      <c r="Y6">
-        <v>3</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1584,52 +1515,31 @@
         <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" t="s">
-        <v>275</v>
-      </c>
-      <c r="F7" t="s">
-        <v>276</v>
-      </c>
-      <c r="G7" t="s">
-        <v>277</v>
-      </c>
-      <c r="H7" t="s">
-        <v>278</v>
+        <v>144</v>
       </c>
       <c r="I7" t="s">
-        <v>281</v>
-      </c>
-      <c r="J7" t="s">
-        <v>287</v>
-      </c>
-      <c r="K7" t="s">
-        <v>288</v>
-      </c>
-      <c r="L7" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O7" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P7" s="3">
-        <v>45989.98658564815</v>
+        <v>45974.46635416667</v>
       </c>
       <c r="Q7" s="3">
-        <v>45989.98658564815</v>
+        <v>45974.46635416667</v>
       </c>
       <c r="R7">
         <v>9.31</v>
       </c>
       <c r="S7" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1637,28 +1547,31 @@
         <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>156</v>
+        <v>145</v>
+      </c>
+      <c r="I8" t="s">
+        <v>258</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O8" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P8" s="3">
-        <v>46316.98170138889</v>
+        <v>45967.48326388889</v>
       </c>
       <c r="Q8" s="3">
-        <v>46316.98170138889</v>
+        <v>45967.48326388889</v>
       </c>
       <c r="R8">
         <v>5.69</v>
       </c>
       <c r="S8" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1666,31 +1579,31 @@
         <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="I9" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O9" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P9" s="3">
-        <v>45974.46635416667</v>
+        <v>46176.59099537037</v>
       </c>
       <c r="Q9" s="3">
-        <v>45974.46635416667</v>
+        <v>46176.59099537037</v>
       </c>
       <c r="R9">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S9" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1698,28 +1611,31 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
+      </c>
+      <c r="I10" t="s">
+        <v>257</v>
       </c>
       <c r="M10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="O10" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="P10" s="3">
-        <v>46311.70082175926</v>
+        <v>45996.23743055556</v>
       </c>
       <c r="Q10" s="3">
-        <v>46314.79664351852</v>
+        <v>45996.23743055556</v>
       </c>
       <c r="R10">
-        <v>17.86</v>
+        <v>12.46</v>
       </c>
       <c r="S10" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1727,31 +1643,31 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="I11" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O11" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P11" s="3">
-        <v>45967.48326388889</v>
+        <v>46209.78530092593</v>
       </c>
       <c r="Q11" s="3">
-        <v>45967.48326388889</v>
+        <v>46209.78530092593</v>
       </c>
       <c r="R11">
         <v>5.69</v>
       </c>
       <c r="S11" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1759,46 +1675,31 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>160</v>
+        <v>149</v>
+      </c>
+      <c r="I12" t="s">
+        <v>259</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O12" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P12" s="3">
-        <v>46311.84297453704</v>
+        <v>46092.52502314815</v>
       </c>
       <c r="Q12" s="3">
-        <v>46311.84297453704</v>
+        <v>46092.52502314815</v>
       </c>
       <c r="R12">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S12" t="s">
-        <v>311</v>
-      </c>
-      <c r="T12">
-        <v>1</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>7</v>
-      </c>
-      <c r="X12" s="3">
-        <v>46316</v>
-      </c>
-      <c r="Y12">
-        <v>4</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1806,31 +1707,46 @@
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I13" t="s">
-        <v>282</v>
+        <v>150</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="O13" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="P13" s="3">
-        <v>46176.59099537037</v>
+        <v>46296.61392361111</v>
       </c>
       <c r="Q13" s="3">
-        <v>46176.59099537037</v>
+        <v>46296.61392361111</v>
       </c>
       <c r="R13">
-        <v>5.69</v>
+        <v>26.83</v>
       </c>
       <c r="S13" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T13">
+        <v>4</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>219</v>
+      </c>
+      <c r="X13" s="3">
+        <v>46303</v>
+      </c>
+      <c r="Y13">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1838,28 +1754,28 @@
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="M14">
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="O14" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P14" s="3">
-        <v>46314.47375</v>
+        <v>46196.83574074074</v>
       </c>
       <c r="Q14" s="3">
-        <v>46314.47375</v>
+        <v>46196.83574074074</v>
       </c>
       <c r="R14">
         <v>5.69</v>
       </c>
       <c r="S14" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1867,31 +1783,31 @@
         <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="I15" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="M15">
         <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O15" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P15" s="3">
-        <v>45996.23743055556</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="Q15" s="3">
-        <v>45996.23743055556</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="R15">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S15" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1899,28 +1815,31 @@
         <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
+      </c>
+      <c r="I16" t="s">
+        <v>258</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="O16" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="P16" s="3">
-        <v>46314.79108796296</v>
+        <v>45840.45584490741</v>
       </c>
       <c r="Q16" s="3">
-        <v>46314.79108796296</v>
+        <v>46170.61114583333</v>
       </c>
       <c r="R16">
-        <v>5.69</v>
+        <v>17.02</v>
       </c>
       <c r="S16" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1928,31 +1847,31 @@
         <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="I17" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O17" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P17" s="3">
-        <v>46209.78530092593</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="Q17" s="3">
-        <v>46209.78530092593</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="R17">
         <v>5.69</v>
       </c>
       <c r="S17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1960,31 +1879,46 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="I18" t="s">
-        <v>281</v>
+        <v>155</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O18" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P18" s="3">
-        <v>46092.52502314815</v>
+        <v>46309.55629629629</v>
       </c>
       <c r="Q18" s="3">
-        <v>46092.52502314815</v>
+        <v>46309.55629629629</v>
       </c>
       <c r="R18">
         <v>5.69</v>
       </c>
       <c r="S18" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>10</v>
+      </c>
+      <c r="X18" s="3">
+        <v>46311</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1992,46 +1926,28 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="M19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="O19" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="P19" s="3">
-        <v>46296.61392361111</v>
+        <v>46252.93552083334</v>
       </c>
       <c r="Q19" s="3">
-        <v>46296.61392361111</v>
+        <v>46252.93552083334</v>
       </c>
       <c r="R19">
-        <v>26.83</v>
+        <v>5.69</v>
       </c>
       <c r="S19" t="s">
-        <v>311</v>
-      </c>
-      <c r="T19">
-        <v>4</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>219</v>
-      </c>
-      <c r="X19" s="3">
-        <v>46303</v>
-      </c>
-      <c r="Y19">
-        <v>6</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2039,28 +1955,31 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
+      </c>
+      <c r="I20" t="s">
+        <v>262</v>
       </c>
       <c r="M20">
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O20" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P20" s="3">
-        <v>46196.83574074074</v>
+        <v>46062.02391203704</v>
       </c>
       <c r="Q20" s="3">
-        <v>46196.83574074074</v>
+        <v>46062.02391203704</v>
       </c>
       <c r="R20">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S20" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2068,28 +1987,31 @@
         <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
+      </c>
+      <c r="I21" t="s">
+        <v>259</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="O21" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="P21" s="3">
-        <v>46314.47582175926</v>
+        <v>45903.0252662037</v>
       </c>
       <c r="Q21" s="3">
-        <v>46314.80358796296</v>
+        <v>45903.0252662037</v>
       </c>
       <c r="R21">
-        <v>20.75</v>
+        <v>9.31</v>
       </c>
       <c r="S21" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2097,31 +2019,31 @@
         <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="I22" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O22" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P22" s="3">
-        <v>46198.6271412037</v>
+        <v>46178.95283564815</v>
       </c>
       <c r="Q22" s="3">
-        <v>46198.6271412037</v>
+        <v>46178.95283564815</v>
       </c>
       <c r="R22">
         <v>5.69</v>
       </c>
       <c r="S22" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2129,31 +2051,31 @@
         <v>46</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="I23" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="M23">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N23" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="O23" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="P23" s="3">
-        <v>45840.45584490741</v>
+        <v>46181.5243287037</v>
       </c>
       <c r="Q23" s="3">
-        <v>46170.61114583333</v>
+        <v>46253.65496527778</v>
       </c>
       <c r="R23">
-        <v>17.02</v>
+        <v>60.34</v>
       </c>
       <c r="S23" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2161,31 +2083,28 @@
         <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I24" t="s">
-        <v>281</v>
+        <v>161</v>
       </c>
       <c r="M24">
         <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O24" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P24" s="3">
-        <v>46198.6271412037</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="Q24" s="3">
-        <v>46198.6271412037</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="R24">
         <v>5.69</v>
       </c>
       <c r="S24" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2193,46 +2112,31 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
+      </c>
+      <c r="I25" t="s">
+        <v>257</v>
       </c>
       <c r="M25">
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O25" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P25" s="3">
-        <v>46309.55629629629</v>
+        <v>46008.62306712963</v>
       </c>
       <c r="Q25" s="3">
-        <v>46309.55629629629</v>
+        <v>46008.62306712963</v>
       </c>
       <c r="R25">
         <v>5.69</v>
       </c>
       <c r="S25" t="s">
-        <v>311</v>
-      </c>
-      <c r="T25">
-        <v>1</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>10</v>
-      </c>
-      <c r="X25" s="3">
-        <v>46311</v>
-      </c>
-      <c r="Y25">
-        <v>1</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2240,28 +2144,31 @@
         <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
+      </c>
+      <c r="I26" t="s">
+        <v>262</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O26" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P26" s="3">
-        <v>46252.93552083334</v>
+        <v>46152.90292824074</v>
       </c>
       <c r="Q26" s="3">
-        <v>46252.93552083334</v>
+        <v>46152.90292824074</v>
       </c>
       <c r="R26">
         <v>5.69</v>
       </c>
       <c r="S26" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2269,31 +2176,46 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I27" t="s">
-        <v>284</v>
+        <v>164</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O27" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P27" s="3">
-        <v>46062.02391203704</v>
+        <v>46307.41046296297</v>
       </c>
       <c r="Q27" s="3">
-        <v>46062.02391203704</v>
+        <v>46307.41046296297</v>
       </c>
       <c r="R27">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S27" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>18</v>
+      </c>
+      <c r="X27" s="3">
+        <v>46312</v>
+      </c>
+      <c r="Y27">
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2301,31 +2223,31 @@
         <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="I28" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="M28">
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O28" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P28" s="3">
-        <v>45903.0252662037</v>
+        <v>45953.84554398148</v>
       </c>
       <c r="Q28" s="3">
-        <v>45903.0252662037</v>
+        <v>45953.84554398148</v>
       </c>
       <c r="R28">
-        <v>9.31</v>
+        <v>12.46</v>
       </c>
       <c r="S28" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2333,31 +2255,46 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I29" t="s">
-        <v>281</v>
+        <v>166</v>
       </c>
       <c r="M29">
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O29" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P29" s="3">
-        <v>46178.95283564815</v>
+        <v>46310.5215625</v>
       </c>
       <c r="Q29" s="3">
-        <v>46178.95283564815</v>
+        <v>46310.5215625</v>
       </c>
       <c r="R29">
         <v>5.69</v>
       </c>
       <c r="S29" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T29">
+        <v>6</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>185</v>
+      </c>
+      <c r="X29" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y29">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2365,31 +2302,31 @@
         <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="I30" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="M30">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N30" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="O30" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="P30" s="3">
-        <v>46181.5243287037</v>
+        <v>46111.64181712963</v>
       </c>
       <c r="Q30" s="3">
-        <v>46253.65496527778</v>
+        <v>46111.64181712963</v>
       </c>
       <c r="R30">
-        <v>60.34</v>
+        <v>12.46</v>
       </c>
       <c r="S30" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2397,28 +2334,46 @@
         <v>54</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="O31" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P31" s="3">
-        <v>46053.63612268519</v>
+        <v>46296.45141203704</v>
       </c>
       <c r="Q31" s="3">
-        <v>46053.63612268519</v>
+        <v>46296.45141203704</v>
       </c>
       <c r="R31">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="S31" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>9</v>
+      </c>
+      <c r="X31" s="3">
+        <v>46298</v>
+      </c>
+      <c r="Y31">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2426,31 +2381,31 @@
         <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="I32" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="M32">
         <v>1</v>
       </c>
       <c r="N32" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O32" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P32" s="3">
-        <v>46008.62306712963</v>
+        <v>46210.48171296297</v>
       </c>
       <c r="Q32" s="3">
-        <v>46008.62306712963</v>
+        <v>46210.48171296297</v>
       </c>
       <c r="R32">
         <v>5.69</v>
       </c>
       <c r="S32" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2458,31 +2413,46 @@
         <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I33" t="s">
-        <v>284</v>
+        <v>170</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N33" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="O33" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="P33" s="3">
-        <v>46152.90292824074</v>
+        <v>46280.49378472222</v>
       </c>
       <c r="Q33" s="3">
-        <v>46152.90292824074</v>
+        <v>46280.49379629629</v>
       </c>
       <c r="R33">
-        <v>5.69</v>
+        <v>10.55</v>
       </c>
       <c r="S33" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T33">
+        <v>4</v>
+      </c>
+      <c r="U33">
+        <v>19.91</v>
+      </c>
+      <c r="V33">
+        <v>2</v>
+      </c>
+      <c r="W33">
+        <v>689</v>
+      </c>
+      <c r="X33" s="3">
+        <v>46281</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -2490,46 +2460,31 @@
         <v>57</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
+      </c>
+      <c r="I34" t="s">
+        <v>263</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O34" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P34" s="3">
-        <v>46307.41046296297</v>
+        <v>46225.98408564815</v>
       </c>
       <c r="Q34" s="3">
-        <v>46307.41046296297</v>
+        <v>46225.98408564815</v>
       </c>
       <c r="R34">
         <v>5.69</v>
       </c>
       <c r="S34" t="s">
-        <v>311</v>
-      </c>
-      <c r="T34">
-        <v>1</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>18</v>
-      </c>
-      <c r="X34" s="3">
-        <v>46312</v>
-      </c>
-      <c r="Y34">
-        <v>4</v>
+        <v>285</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -2537,31 +2492,31 @@
         <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="I35" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="M35">
         <v>1</v>
       </c>
       <c r="N35" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O35" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P35" s="3">
-        <v>45953.84554398148</v>
+        <v>46106.56184027778</v>
       </c>
       <c r="Q35" s="3">
-        <v>45953.84554398148</v>
+        <v>46106.56184027778</v>
       </c>
       <c r="R35">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S35" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -2569,46 +2524,28 @@
         <v>59</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="M36">
         <v>1</v>
       </c>
       <c r="N36" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O36" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P36" s="3">
-        <v>46310.5215625</v>
+        <v>46313.79324074074</v>
       </c>
       <c r="Q36" s="3">
-        <v>46310.5215625</v>
+        <v>46313.79324074074</v>
       </c>
       <c r="R36">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S36" t="s">
-        <v>311</v>
-      </c>
-      <c r="T36">
-        <v>6</v>
-      </c>
-      <c r="U36">
-        <v>0</v>
-      </c>
-      <c r="V36">
-        <v>0</v>
-      </c>
-      <c r="W36">
-        <v>185</v>
-      </c>
-      <c r="X36" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y36">
-        <v>2</v>
+        <v>285</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -2616,31 +2553,31 @@
         <v>60</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="I37" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="M37">
         <v>1</v>
       </c>
       <c r="N37" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O37" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P37" s="3">
-        <v>46111.64181712963</v>
+        <v>46196.84141203704</v>
       </c>
       <c r="Q37" s="3">
-        <v>46111.64181712963</v>
+        <v>46196.84141203704</v>
       </c>
       <c r="R37">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S37" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -2648,46 +2585,28 @@
         <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="M38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N38" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="O38" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P38" s="3">
-        <v>46296.45141203704</v>
+        <v>46312.81608796296</v>
       </c>
       <c r="Q38" s="3">
-        <v>46296.45141203704</v>
+        <v>46313.7452662037</v>
       </c>
       <c r="R38">
-        <v>5.64</v>
+        <v>14.62</v>
       </c>
       <c r="S38" t="s">
-        <v>311</v>
-      </c>
-      <c r="T38">
-        <v>1</v>
-      </c>
-      <c r="U38">
-        <v>0</v>
-      </c>
-      <c r="V38">
-        <v>0</v>
-      </c>
-      <c r="W38">
-        <v>9</v>
-      </c>
-      <c r="X38" s="3">
-        <v>46298</v>
-      </c>
-      <c r="Y38">
-        <v>1</v>
+        <v>285</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -2695,31 +2614,31 @@
         <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="I39" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O39" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P39" s="3">
-        <v>46210.48171296297</v>
+        <v>46073.66815972222</v>
       </c>
       <c r="Q39" s="3">
-        <v>46210.48171296297</v>
+        <v>46073.66815972222</v>
       </c>
       <c r="R39">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S39" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -2727,46 +2646,49 @@
         <v>63</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
+      </c>
+      <c r="I40" t="s">
+        <v>262</v>
       </c>
       <c r="M40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N40" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="O40" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="P40" s="3">
-        <v>46280.49378472222</v>
+        <v>46245.82854166667</v>
       </c>
       <c r="Q40" s="3">
-        <v>46280.49379629629</v>
+        <v>46245.82854166667</v>
       </c>
       <c r="R40">
-        <v>10.55</v>
+        <v>5.69</v>
       </c>
       <c r="S40" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U40">
-        <v>19.91</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>689</v>
+        <v>23</v>
       </c>
       <c r="X40" s="3">
-        <v>46281</v>
+        <v>46261</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -2774,31 +2696,28 @@
         <v>64</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I41" t="s">
-        <v>285</v>
+        <v>178</v>
       </c>
       <c r="M41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N41" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="O41" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="P41" s="3">
-        <v>46225.98408564815</v>
+        <v>46313.77442129629</v>
       </c>
       <c r="Q41" s="3">
-        <v>46225.98408564815</v>
+        <v>46314.79109953704</v>
       </c>
       <c r="R41">
-        <v>5.69</v>
+        <v>27.71</v>
       </c>
       <c r="S41" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -2806,31 +2725,28 @@
         <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I42" t="s">
-        <v>280</v>
+        <v>179</v>
       </c>
       <c r="M42">
         <v>1</v>
       </c>
       <c r="N42" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O42" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P42" s="3">
-        <v>46106.56184027778</v>
+        <v>46316.43623842593</v>
       </c>
       <c r="Q42" s="3">
-        <v>46106.56184027778</v>
+        <v>46316.43623842593</v>
       </c>
       <c r="R42">
         <v>5.69</v>
       </c>
       <c r="S42" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -2838,28 +2754,46 @@
         <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O43" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P43" s="3">
-        <v>46313.79324074074</v>
+        <v>46281.49586805556</v>
       </c>
       <c r="Q43" s="3">
-        <v>46313.79324074074</v>
+        <v>46281.49586805556</v>
       </c>
       <c r="R43">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S43" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T43">
+        <v>7</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>119</v>
+      </c>
+      <c r="X43" s="3">
+        <v>46282</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -2867,31 +2801,31 @@
         <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="I44" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="M44">
         <v>1</v>
       </c>
       <c r="N44" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O44" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P44" s="3">
-        <v>46196.84141203704</v>
+        <v>46050.93159722222</v>
       </c>
       <c r="Q44" s="3">
-        <v>46196.84141203704</v>
+        <v>46050.93159722222</v>
       </c>
       <c r="R44">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S44" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -2899,28 +2833,46 @@
         <v>68</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45" t="s">
+        <v>268</v>
+      </c>
+      <c r="O45" t="s">
+        <v>284</v>
+      </c>
+      <c r="P45" s="3">
+        <v>46310.34238425926</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>46310.34238425926</v>
+      </c>
+      <c r="R45">
+        <v>5.69</v>
+      </c>
+      <c r="S45" t="s">
+        <v>286</v>
+      </c>
+      <c r="T45">
+        <v>3</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>92</v>
+      </c>
+      <c r="X45" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y45">
         <v>2</v>
-      </c>
-      <c r="N45" t="s">
-        <v>298</v>
-      </c>
-      <c r="O45" t="s">
-        <v>309</v>
-      </c>
-      <c r="P45" s="3">
-        <v>46312.81608796296</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>46313.7452662037</v>
-      </c>
-      <c r="R45">
-        <v>14.62</v>
-      </c>
-      <c r="S45" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -2928,28 +2880,31 @@
         <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
+      </c>
+      <c r="I46" t="s">
+        <v>262</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
       <c r="N46" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O46" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P46" s="3">
-        <v>46316.59872685185</v>
+        <v>45965.93854166667</v>
       </c>
       <c r="Q46" s="3">
-        <v>46316.59872685185</v>
+        <v>45965.93854166667</v>
       </c>
       <c r="R46">
         <v>5.69</v>
       </c>
       <c r="S46" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -2957,31 +2912,31 @@
         <v>70</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="I47" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O47" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P47" s="3">
-        <v>46073.66815972222</v>
+        <v>45992.89240740741</v>
       </c>
       <c r="Q47" s="3">
-        <v>46073.66815972222</v>
+        <v>45992.89240740741</v>
       </c>
       <c r="R47">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S47" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="48" spans="1:25">
@@ -2989,49 +2944,31 @@
         <v>71</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="I48" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="M48">
         <v>1</v>
       </c>
       <c r="N48" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O48" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P48" s="3">
-        <v>46245.82854166667</v>
+        <v>45944.90217592593</v>
       </c>
       <c r="Q48" s="3">
-        <v>46245.82854166667</v>
+        <v>45944.90217592593</v>
       </c>
       <c r="R48">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S48" t="s">
-        <v>311</v>
-      </c>
-      <c r="T48">
-        <v>1</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>23</v>
-      </c>
-      <c r="X48" s="3">
-        <v>46261</v>
-      </c>
-      <c r="Y48">
-        <v>15</v>
+        <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:25">
@@ -3039,28 +2976,31 @@
         <v>72</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
+      </c>
+      <c r="I49" t="s">
+        <v>258</v>
       </c>
       <c r="M49">
         <v>1</v>
       </c>
       <c r="N49" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O49" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P49" s="3">
-        <v>46314.79525462963</v>
+        <v>46105.47987268519</v>
       </c>
       <c r="Q49" s="3">
-        <v>46314.79525462963</v>
+        <v>46105.47987268519</v>
       </c>
       <c r="R49">
         <v>5.69</v>
       </c>
       <c r="S49" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="50" spans="1:25">
@@ -3068,28 +3008,31 @@
         <v>73</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
+      </c>
+      <c r="I50" t="s">
+        <v>262</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N50" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="O50" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="P50" s="3">
-        <v>46313.77442129629</v>
+        <v>46210.50420138889</v>
       </c>
       <c r="Q50" s="3">
-        <v>46314.79109953704</v>
+        <v>46210.50420138889</v>
       </c>
       <c r="R50">
-        <v>27.71</v>
+        <v>5.69</v>
       </c>
       <c r="S50" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="51" spans="1:25">
@@ -3097,28 +3040,28 @@
         <v>74</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="M51">
         <v>1</v>
       </c>
       <c r="N51" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O51" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P51" s="3">
-        <v>46316.43623842593</v>
+        <v>46052.56390046296</v>
       </c>
       <c r="Q51" s="3">
-        <v>46316.43623842593</v>
+        <v>46052.56390046296</v>
       </c>
       <c r="R51">
         <v>5.69</v>
       </c>
       <c r="S51" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="52" spans="1:25">
@@ -3126,46 +3069,31 @@
         <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
+      </c>
+      <c r="I52" t="s">
+        <v>259</v>
       </c>
       <c r="M52">
         <v>1</v>
       </c>
       <c r="N52" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O52" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P52" s="3">
-        <v>46281.49586805556</v>
+        <v>46091.88748842593</v>
       </c>
       <c r="Q52" s="3">
-        <v>46281.49586805556</v>
+        <v>46091.88748842593</v>
       </c>
       <c r="R52">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S52" t="s">
-        <v>311</v>
-      </c>
-      <c r="T52">
-        <v>7</v>
-      </c>
-      <c r="U52">
-        <v>0</v>
-      </c>
-      <c r="V52">
-        <v>0</v>
-      </c>
-      <c r="W52">
-        <v>119</v>
-      </c>
-      <c r="X52" s="3">
-        <v>46282</v>
-      </c>
-      <c r="Y52">
-        <v>0</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:25">
@@ -3173,31 +3101,31 @@
         <v>76</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="I53" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O53" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P53" s="3">
-        <v>46050.93159722222</v>
+        <v>45978.69265046297</v>
       </c>
       <c r="Q53" s="3">
-        <v>46050.93159722222</v>
+        <v>45978.69265046297</v>
       </c>
       <c r="R53">
         <v>12.46</v>
       </c>
       <c r="S53" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54" spans="1:25">
@@ -3205,46 +3133,28 @@
         <v>77</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="M54">
         <v>1</v>
       </c>
       <c r="N54" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O54" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P54" s="3">
-        <v>46310.34238425926</v>
+        <v>46314.79108796296</v>
       </c>
       <c r="Q54" s="3">
-        <v>46310.34238425926</v>
+        <v>46314.79108796296</v>
       </c>
       <c r="R54">
         <v>5.69</v>
       </c>
       <c r="S54" t="s">
-        <v>311</v>
-      </c>
-      <c r="T54">
-        <v>3</v>
-      </c>
-      <c r="U54">
-        <v>0</v>
-      </c>
-      <c r="V54">
-        <v>0</v>
-      </c>
-      <c r="W54">
-        <v>92</v>
-      </c>
-      <c r="X54" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y54">
-        <v>2</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" spans="1:25">
@@ -3252,28 +3162,31 @@
         <v>78</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
+      </c>
+      <c r="I55" t="s">
+        <v>258</v>
       </c>
       <c r="M55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N55" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O55" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="P55" s="3">
-        <v>46314.07822916667</v>
+        <v>45919.81163194445</v>
       </c>
       <c r="Q55" s="3">
-        <v>46314.07822916667</v>
+        <v>45919.81163194445</v>
       </c>
       <c r="R55">
-        <v>14.27</v>
+        <v>5.69</v>
       </c>
       <c r="S55" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="56" spans="1:25">
@@ -3281,31 +3194,28 @@
         <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="I56" t="s">
-        <v>284</v>
+        <v>193</v>
       </c>
       <c r="M56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N56" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="O56" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="P56" s="3">
-        <v>45965.93854166667</v>
+        <v>46313.77442129629</v>
       </c>
       <c r="Q56" s="3">
-        <v>45965.93854166667</v>
+        <v>46314.78831018518</v>
       </c>
       <c r="R56">
-        <v>5.69</v>
+        <v>30.1</v>
       </c>
       <c r="S56" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="57" spans="1:25">
@@ -3313,31 +3223,46 @@
         <v>80</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I57" t="s">
-        <v>280</v>
+        <v>194</v>
       </c>
       <c r="M57">
         <v>1</v>
       </c>
       <c r="N57" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="O57" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P57" s="3">
-        <v>45992.89240740741</v>
+        <v>46314.50759259259</v>
       </c>
       <c r="Q57" s="3">
-        <v>45992.89240740741</v>
+        <v>46314.50759259259</v>
       </c>
       <c r="R57">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S57" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T57">
+        <v>2</v>
+      </c>
+      <c r="U57">
+        <v>20.03</v>
+      </c>
+      <c r="V57">
+        <v>2</v>
+      </c>
+      <c r="W57">
+        <v>473</v>
+      </c>
+      <c r="X57" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y57">
+        <v>-2</v>
       </c>
     </row>
     <row r="58" spans="1:25">
@@ -3345,31 +3270,31 @@
         <v>81</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="I58" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="M58">
         <v>1</v>
       </c>
       <c r="N58" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O58" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P58" s="3">
-        <v>45944.90217592593</v>
+        <v>46051.04447916667</v>
       </c>
       <c r="Q58" s="3">
-        <v>45944.90217592593</v>
+        <v>46051.04447916667</v>
       </c>
       <c r="R58">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S58" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59" spans="1:25">
@@ -3377,31 +3302,28 @@
         <v>82</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I59" t="s">
-        <v>280</v>
+        <v>196</v>
       </c>
       <c r="M59">
         <v>1</v>
       </c>
       <c r="N59" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O59" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P59" s="3">
-        <v>46105.47987268519</v>
+        <v>46314.40084490741</v>
       </c>
       <c r="Q59" s="3">
-        <v>46105.47987268519</v>
+        <v>46314.40084490741</v>
       </c>
       <c r="R59">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S59" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60" spans="1:25">
@@ -3409,28 +3331,31 @@
         <v>83</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
+      </c>
+      <c r="I60" t="s">
+        <v>257</v>
       </c>
       <c r="M60">
         <v>1</v>
       </c>
       <c r="N60" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O60" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P60" s="3">
-        <v>46314.78832175926</v>
+        <v>45891.71650462963</v>
       </c>
       <c r="Q60" s="3">
-        <v>46314.78832175926</v>
+        <v>45891.71650462963</v>
       </c>
       <c r="R60">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S60" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="61" spans="1:25">
@@ -3438,31 +3363,31 @@
         <v>84</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="I61" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="M61">
         <v>1</v>
       </c>
       <c r="N61" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O61" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P61" s="3">
-        <v>46210.50420138889</v>
+        <v>46211.60210648148</v>
       </c>
       <c r="Q61" s="3">
-        <v>46210.50420138889</v>
+        <v>46211.60210648148</v>
       </c>
       <c r="R61">
         <v>5.69</v>
       </c>
       <c r="S61" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="62" spans="1:25">
@@ -3470,28 +3395,28 @@
         <v>85</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="M62">
         <v>1</v>
       </c>
       <c r="N62" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="O62" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P62" s="3">
-        <v>46052.56390046296</v>
+        <v>46314.35015046296</v>
       </c>
       <c r="Q62" s="3">
-        <v>46052.56390046296</v>
+        <v>46314.35015046296</v>
       </c>
       <c r="R62">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S62" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="63" spans="1:25">
@@ -3499,31 +3424,31 @@
         <v>86</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="I63" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="M63">
         <v>1</v>
       </c>
       <c r="N63" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O63" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P63" s="3">
-        <v>46091.88748842593</v>
+        <v>46167.36722222222</v>
       </c>
       <c r="Q63" s="3">
-        <v>46091.88748842593</v>
+        <v>46167.36722222222</v>
       </c>
       <c r="R63">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S63" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="64" spans="1:25">
@@ -3531,31 +3456,28 @@
         <v>87</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I64" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="M64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N64" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="O64" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="P64" s="3">
-        <v>45978.69265046297</v>
+        <v>46313.73414351852</v>
       </c>
       <c r="Q64" s="3">
-        <v>45978.69265046297</v>
+        <v>46313.73415509259</v>
       </c>
       <c r="R64">
-        <v>12.46</v>
+        <v>11.73</v>
       </c>
       <c r="S64" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="65" spans="1:25">
@@ -3563,28 +3485,49 @@
         <v>88</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
+      </c>
+      <c r="I65" t="s">
+        <v>259</v>
       </c>
       <c r="M65">
         <v>1</v>
       </c>
       <c r="N65" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O65" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P65" s="3">
-        <v>46314.79108796296</v>
+        <v>46309.5507175926</v>
       </c>
       <c r="Q65" s="3">
-        <v>46314.79108796296</v>
+        <v>46309.5507175926</v>
       </c>
       <c r="R65">
         <v>5.69</v>
       </c>
       <c r="S65" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T65">
+        <v>1</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>12</v>
+      </c>
+      <c r="X65" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y65">
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:25">
@@ -3592,31 +3535,28 @@
         <v>89</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I66" t="s">
-        <v>280</v>
+        <v>203</v>
       </c>
       <c r="M66">
         <v>1</v>
       </c>
       <c r="N66" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O66" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P66" s="3">
-        <v>45919.81163194445</v>
+        <v>46312.0579050926</v>
       </c>
       <c r="Q66" s="3">
-        <v>45919.81163194445</v>
+        <v>46312.0579050926</v>
       </c>
       <c r="R66">
         <v>5.69</v>
       </c>
       <c r="S66" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="67" spans="1:25">
@@ -3624,28 +3564,31 @@
         <v>90</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
+      </c>
+      <c r="I67" t="s">
+        <v>262</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N67" t="s">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c r="O67" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="P67" s="3">
-        <v>46313.77442129629</v>
+        <v>46050.54237268519</v>
       </c>
       <c r="Q67" s="3">
-        <v>46314.78831018518</v>
+        <v>46050.54237268519</v>
       </c>
       <c r="R67">
-        <v>30.1</v>
+        <v>5.69</v>
       </c>
       <c r="S67" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="68" spans="1:25">
@@ -3653,46 +3596,31 @@
         <v>91</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
+      </c>
+      <c r="I68" t="s">
+        <v>261</v>
       </c>
       <c r="M68">
         <v>1</v>
       </c>
       <c r="N68" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="O68" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P68" s="3">
-        <v>46314.50759259259</v>
+        <v>45957.49894675926</v>
       </c>
       <c r="Q68" s="3">
-        <v>46314.50759259259</v>
+        <v>45957.49894675926</v>
       </c>
       <c r="R68">
-        <v>6.04</v>
+        <v>5.69</v>
       </c>
       <c r="S68" t="s">
-        <v>311</v>
-      </c>
-      <c r="T68">
-        <v>2</v>
-      </c>
-      <c r="U68">
-        <v>20.03</v>
-      </c>
-      <c r="V68">
-        <v>2</v>
-      </c>
-      <c r="W68">
-        <v>473</v>
-      </c>
-      <c r="X68" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y68">
-        <v>-2</v>
+        <v>285</v>
       </c>
     </row>
     <row r="69" spans="1:25">
@@ -3700,31 +3628,46 @@
         <v>92</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I69" t="s">
-        <v>279</v>
+        <v>206</v>
       </c>
       <c r="M69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="O69" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P69" s="3">
-        <v>46051.04447916667</v>
+        <v>46316.49146990741</v>
       </c>
       <c r="Q69" s="3">
-        <v>46051.04447916667</v>
+        <v>46316.49152777778</v>
       </c>
       <c r="R69">
-        <v>5.69</v>
+        <v>15.88</v>
       </c>
       <c r="S69" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T69">
+        <v>15</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>226</v>
+      </c>
+      <c r="X69" s="3">
+        <v>46298</v>
+      </c>
+      <c r="Y69">
+        <v>-19</v>
       </c>
     </row>
     <row r="70" spans="1:25">
@@ -3732,28 +3675,31 @@
         <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
+      </c>
+      <c r="I70" t="s">
+        <v>261</v>
       </c>
       <c r="M70">
         <v>1</v>
       </c>
       <c r="N70" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O70" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P70" s="3">
-        <v>46314.40084490741</v>
+        <v>46196.62574074074</v>
       </c>
       <c r="Q70" s="3">
-        <v>46314.40084490741</v>
+        <v>46196.62574074074</v>
       </c>
       <c r="R70">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S70" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="71" spans="1:25">
@@ -3761,31 +3707,31 @@
         <v>94</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="I71" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O71" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P71" s="3">
-        <v>45891.71650462963</v>
+        <v>45959.6512037037</v>
       </c>
       <c r="Q71" s="3">
-        <v>45891.71650462963</v>
+        <v>45959.6512037037</v>
       </c>
       <c r="R71">
         <v>9.31</v>
       </c>
       <c r="S71" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="72" spans="1:25">
@@ -3793,31 +3739,31 @@
         <v>95</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="I72" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="M72">
         <v>1</v>
       </c>
       <c r="N72" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O72" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P72" s="3">
-        <v>46211.60210648148</v>
+        <v>45973.56506944444</v>
       </c>
       <c r="Q72" s="3">
-        <v>46211.60210648148</v>
+        <v>45973.56506944444</v>
       </c>
       <c r="R72">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S72" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="73" spans="1:25">
@@ -3825,28 +3771,28 @@
         <v>96</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="M73">
         <v>1</v>
       </c>
       <c r="N73" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="O73" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="P73" s="3">
-        <v>46314.35015046296</v>
+        <v>46313.49944444445</v>
       </c>
       <c r="Q73" s="3">
-        <v>46314.35015046296</v>
+        <v>46313.49944444445</v>
       </c>
       <c r="R73">
         <v>6.04</v>
       </c>
       <c r="S73" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="74" spans="1:25">
@@ -3854,31 +3800,28 @@
         <v>97</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I74" t="s">
-        <v>281</v>
+        <v>211</v>
       </c>
       <c r="M74">
         <v>1</v>
       </c>
       <c r="N74" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O74" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P74" s="3">
-        <v>46167.36722222222</v>
+        <v>46316.43068287037</v>
       </c>
       <c r="Q74" s="3">
-        <v>46167.36722222222</v>
+        <v>46316.43068287037</v>
       </c>
       <c r="R74">
         <v>5.69</v>
       </c>
       <c r="S74" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="75" spans="1:25">
@@ -3886,28 +3829,28 @@
         <v>98</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="M75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N75" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="O75" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="P75" s="3">
-        <v>46313.73414351852</v>
+        <v>46313.73415509259</v>
       </c>
       <c r="Q75" s="3">
-        <v>46313.73415509259</v>
+        <v>46316.43625</v>
       </c>
       <c r="R75">
-        <v>11.73</v>
+        <v>26.82</v>
       </c>
       <c r="S75" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="76" spans="1:25">
@@ -3915,49 +3858,31 @@
         <v>99</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="I76" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="M76">
         <v>1</v>
       </c>
       <c r="N76" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O76" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P76" s="3">
-        <v>46309.5507175926</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="Q76" s="3">
-        <v>46309.5507175926</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="R76">
         <v>5.69</v>
       </c>
       <c r="S76" t="s">
-        <v>311</v>
-      </c>
-      <c r="T76">
-        <v>1</v>
-      </c>
-      <c r="U76">
-        <v>0</v>
-      </c>
-      <c r="V76">
-        <v>0</v>
-      </c>
-      <c r="W76">
-        <v>12</v>
-      </c>
-      <c r="X76" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y76">
-        <v>3</v>
+        <v>285</v>
       </c>
     </row>
     <row r="77" spans="1:25">
@@ -3965,28 +3890,46 @@
         <v>100</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N77" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="O77" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="P77" s="3">
-        <v>46312.0579050926</v>
+        <v>46286.62572916667</v>
       </c>
       <c r="Q77" s="3">
-        <v>46312.0579050926</v>
+        <v>46306.5500462963</v>
       </c>
       <c r="R77">
-        <v>5.69</v>
+        <v>14.22</v>
       </c>
       <c r="S77" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T77">
+        <v>2</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>32</v>
+      </c>
+      <c r="X77" s="3">
+        <v>46297</v>
+      </c>
+      <c r="Y77">
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:25">
@@ -3994,31 +3937,28 @@
         <v>101</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I78" t="s">
-        <v>284</v>
+        <v>215</v>
       </c>
       <c r="M78">
         <v>1</v>
       </c>
       <c r="N78" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O78" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P78" s="3">
-        <v>46050.54237268519</v>
+        <v>46304.50560185185</v>
       </c>
       <c r="Q78" s="3">
-        <v>46050.54237268519</v>
+        <v>46304.50560185185</v>
       </c>
       <c r="R78">
         <v>5.69</v>
       </c>
       <c r="S78" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="79" spans="1:25">
@@ -4026,31 +3966,28 @@
         <v>102</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I79" t="s">
-        <v>283</v>
+        <v>216</v>
       </c>
       <c r="M79">
         <v>1</v>
       </c>
       <c r="N79" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O79" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P79" s="3">
-        <v>45957.49894675926</v>
+        <v>46314.40085648148</v>
       </c>
       <c r="Q79" s="3">
-        <v>45957.49894675926</v>
+        <v>46314.40085648148</v>
       </c>
       <c r="R79">
         <v>5.69</v>
       </c>
       <c r="S79" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="80" spans="1:25">
@@ -4058,46 +3995,28 @@
         <v>103</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="M80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N80" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="O80" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P80" s="3">
-        <v>46316.49146990741</v>
+        <v>46027.60903935185</v>
       </c>
       <c r="Q80" s="3">
-        <v>46316.49152777778</v>
+        <v>46027.60903935185</v>
       </c>
       <c r="R80">
-        <v>15.88</v>
+        <v>5.69</v>
       </c>
       <c r="S80" t="s">
-        <v>311</v>
-      </c>
-      <c r="T80">
-        <v>15</v>
-      </c>
-      <c r="U80">
-        <v>0</v>
-      </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
-      <c r="W80">
-        <v>226</v>
-      </c>
-      <c r="X80" s="3">
-        <v>46298</v>
-      </c>
-      <c r="Y80">
-        <v>-19</v>
+        <v>285</v>
       </c>
     </row>
     <row r="81" spans="1:25">
@@ -4105,31 +4024,46 @@
         <v>104</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I81" t="s">
-        <v>283</v>
+        <v>218</v>
       </c>
       <c r="M81">
         <v>1</v>
       </c>
       <c r="N81" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O81" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P81" s="3">
-        <v>46196.62574074074</v>
+        <v>46280.49518518519</v>
       </c>
       <c r="Q81" s="3">
-        <v>46196.62574074074</v>
+        <v>46280.49518518519</v>
       </c>
       <c r="R81">
         <v>5.69</v>
       </c>
       <c r="S81" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T81">
+        <v>1</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>17</v>
+      </c>
+      <c r="X81" s="3">
+        <v>46283</v>
+      </c>
+      <c r="Y81">
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:25">
@@ -4137,31 +4071,28 @@
         <v>105</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="I82" t="s">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="M82">
         <v>1</v>
       </c>
       <c r="N82" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O82" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P82" s="3">
-        <v>45959.6512037037</v>
+        <v>46311.94667824074</v>
       </c>
       <c r="Q82" s="3">
-        <v>45959.6512037037</v>
+        <v>46311.94667824074</v>
       </c>
       <c r="R82">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S82" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="83" spans="1:25">
@@ -4169,31 +4100,28 @@
         <v>106</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="I83" t="s">
-        <v>279</v>
+        <v>220</v>
       </c>
       <c r="M83">
         <v>1</v>
       </c>
       <c r="N83" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O83" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P83" s="3">
-        <v>45973.56506944444</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="Q83" s="3">
-        <v>45973.56506944444</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="R83">
-        <v>9.31</v>
+        <v>8.58</v>
       </c>
       <c r="S83" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="84" spans="1:25">
@@ -4201,28 +4129,31 @@
         <v>107</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
+      </c>
+      <c r="I84" t="s">
+        <v>264</v>
       </c>
       <c r="M84">
         <v>1</v>
       </c>
       <c r="N84" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="O84" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P84" s="3">
-        <v>46313.49944444445</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q84" s="3">
-        <v>46313.49944444445</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R84">
-        <v>6.04</v>
+        <v>5.69</v>
       </c>
       <c r="S84" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="85" spans="1:25">
@@ -4230,28 +4161,31 @@
         <v>108</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
+      </c>
+      <c r="I85" t="s">
+        <v>261</v>
       </c>
       <c r="M85">
         <v>1</v>
       </c>
       <c r="N85" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O85" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P85" s="3">
-        <v>46316.43068287037</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="Q85" s="3">
-        <v>46316.43068287037</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="R85">
         <v>5.69</v>
       </c>
       <c r="S85" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="1:25">
@@ -4259,28 +4193,28 @@
         <v>109</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="M86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N86" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="O86" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="P86" s="3">
-        <v>46313.73415509259</v>
+        <v>46199.43622685185</v>
       </c>
       <c r="Q86" s="3">
-        <v>46316.43625</v>
+        <v>46199.43622685185</v>
       </c>
       <c r="R86">
-        <v>26.82</v>
+        <v>5.69</v>
       </c>
       <c r="S86" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="87" spans="1:25">
@@ -4288,31 +4222,31 @@
         <v>110</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="I87" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
       <c r="N87" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O87" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P87" s="3">
-        <v>46191.82362268519</v>
+        <v>46211.60422453703</v>
       </c>
       <c r="Q87" s="3">
-        <v>46191.82362268519</v>
+        <v>46211.60422453703</v>
       </c>
       <c r="R87">
         <v>5.69</v>
       </c>
       <c r="S87" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="88" spans="1:25">
@@ -4320,46 +4254,28 @@
         <v>111</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="M88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N88" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="O88" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="P88" s="3">
-        <v>46286.62572916667</v>
+        <v>46314.39943287037</v>
       </c>
       <c r="Q88" s="3">
-        <v>46306.5500462963</v>
+        <v>46314.39943287037</v>
       </c>
       <c r="R88">
-        <v>14.22</v>
+        <v>6.04</v>
       </c>
       <c r="S88" t="s">
-        <v>311</v>
-      </c>
-      <c r="T88">
-        <v>2</v>
-      </c>
-      <c r="U88">
-        <v>0</v>
-      </c>
-      <c r="V88">
-        <v>0</v>
-      </c>
-      <c r="W88">
-        <v>32</v>
-      </c>
-      <c r="X88" s="3">
-        <v>46297</v>
-      </c>
-      <c r="Y88">
-        <v>10</v>
+        <v>285</v>
       </c>
     </row>
     <row r="89" spans="1:25">
@@ -4367,28 +4283,31 @@
         <v>112</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
+      </c>
+      <c r="I89" t="s">
+        <v>257</v>
       </c>
       <c r="M89">
         <v>1</v>
       </c>
       <c r="N89" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O89" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P89" s="3">
-        <v>46304.50560185185</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="Q89" s="3">
-        <v>46304.50560185185</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="R89">
         <v>5.69</v>
       </c>
       <c r="S89" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="90" spans="1:25">
@@ -4396,28 +4315,28 @@
         <v>113</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="M90">
         <v>1</v>
       </c>
       <c r="N90" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O90" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P90" s="3">
-        <v>46314.40085648148</v>
+        <v>46316.43622685185</v>
       </c>
       <c r="Q90" s="3">
-        <v>46314.40085648148</v>
+        <v>46316.43622685185</v>
       </c>
       <c r="R90">
         <v>5.69</v>
       </c>
       <c r="S90" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="91" spans="1:25">
@@ -4425,28 +4344,28 @@
         <v>114</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="M91">
         <v>1</v>
       </c>
       <c r="N91" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O91" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P91" s="3">
-        <v>46027.60903935185</v>
+        <v>46314.45354166667</v>
       </c>
       <c r="Q91" s="3">
-        <v>46027.60903935185</v>
+        <v>46314.45354166667</v>
       </c>
       <c r="R91">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S91" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="92" spans="1:25">
@@ -4454,46 +4373,28 @@
         <v>115</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M92">
         <v>1</v>
       </c>
       <c r="N92" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O92" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P92" s="3">
-        <v>46280.49518518519</v>
+        <v>46316.43068287037</v>
       </c>
       <c r="Q92" s="3">
-        <v>46280.49518518519</v>
+        <v>46316.43068287037</v>
       </c>
       <c r="R92">
         <v>5.69</v>
       </c>
       <c r="S92" t="s">
-        <v>311</v>
-      </c>
-      <c r="T92">
-        <v>1</v>
-      </c>
-      <c r="U92">
-        <v>0</v>
-      </c>
-      <c r="V92">
-        <v>0</v>
-      </c>
-      <c r="W92">
-        <v>17</v>
-      </c>
-      <c r="X92" s="3">
-        <v>46283</v>
-      </c>
-      <c r="Y92">
-        <v>2</v>
+        <v>285</v>
       </c>
     </row>
     <row r="93" spans="1:25">
@@ -4501,28 +4402,31 @@
         <v>116</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
+      </c>
+      <c r="I93" t="s">
+        <v>258</v>
       </c>
       <c r="M93">
         <v>1</v>
       </c>
       <c r="N93" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O93" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P93" s="3">
-        <v>46311.94667824074</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="Q93" s="3">
-        <v>46311.94667824074</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="R93">
         <v>5.69</v>
       </c>
       <c r="S93" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="94" spans="1:25">
@@ -4530,28 +4434,28 @@
         <v>117</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="M94">
         <v>1</v>
       </c>
       <c r="N94" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O94" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P94" s="3">
-        <v>46313.79785879629</v>
+        <v>46313.72997685185</v>
       </c>
       <c r="Q94" s="3">
-        <v>46313.79785879629</v>
+        <v>46313.72997685185</v>
       </c>
       <c r="R94">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S94" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="95" spans="1:25">
@@ -4559,31 +4463,28 @@
         <v>118</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="I95" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="M95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N95" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="O95" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="P95" s="3">
-        <v>46198.62712962963</v>
+        <v>46296.45002314815</v>
       </c>
       <c r="Q95" s="3">
-        <v>46198.62712962963</v>
+        <v>46296.45003472222</v>
       </c>
       <c r="R95">
-        <v>5.69</v>
+        <v>26.25</v>
       </c>
       <c r="S95" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="1:25">
@@ -4591,31 +4492,31 @@
         <v>119</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="I96" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="M96">
         <v>1</v>
       </c>
       <c r="N96" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O96" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P96" s="3">
-        <v>46212.55766203703</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="Q96" s="3">
-        <v>46212.55766203703</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="R96">
         <v>5.69</v>
       </c>
       <c r="S96" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="97" spans="1:25">
@@ -4623,28 +4524,46 @@
         <v>120</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="M97">
         <v>1</v>
       </c>
       <c r="N97" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="O97" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P97" s="3">
-        <v>46199.43622685185</v>
+        <v>46303.44568287037</v>
       </c>
       <c r="Q97" s="3">
-        <v>46199.43622685185</v>
+        <v>46303.44568287037</v>
       </c>
       <c r="R97">
-        <v>5.69</v>
+        <v>4.73</v>
       </c>
       <c r="S97" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="T97">
+        <v>2</v>
+      </c>
+      <c r="U97">
+        <v>0</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>111</v>
+      </c>
+      <c r="X97" s="3">
+        <v>46308</v>
+      </c>
+      <c r="Y97">
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:25">
@@ -4652,31 +4571,28 @@
         <v>121</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="I98" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="M98">
         <v>1</v>
       </c>
       <c r="N98" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="O98" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P98" s="3">
-        <v>46211.60422453703</v>
+        <v>46301.52780092593</v>
       </c>
       <c r="Q98" s="3">
-        <v>46211.60422453703</v>
+        <v>46301.52780092593</v>
       </c>
       <c r="R98">
-        <v>5.69</v>
+        <v>6.53</v>
       </c>
       <c r="S98" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="99" spans="1:25">
@@ -4684,28 +4600,31 @@
         <v>122</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
+      </c>
+      <c r="I99" t="s">
+        <v>258</v>
       </c>
       <c r="M99">
         <v>1</v>
       </c>
       <c r="N99" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="O99" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P99" s="3">
-        <v>46314.39943287037</v>
+        <v>46221.54171296296</v>
       </c>
       <c r="Q99" s="3">
-        <v>46314.39943287037</v>
+        <v>46221.54171296296</v>
       </c>
       <c r="R99">
-        <v>6.04</v>
+        <v>5.69</v>
       </c>
       <c r="S99" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="100" spans="1:25">
@@ -4713,31 +4632,31 @@
         <v>123</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="I100" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="M100">
         <v>1</v>
       </c>
       <c r="N100" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O100" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P100" s="3">
-        <v>46196.76916666667</v>
+        <v>45993.6759375</v>
       </c>
       <c r="Q100" s="3">
-        <v>46196.76916666667</v>
+        <v>45993.6759375</v>
       </c>
       <c r="R100">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S100" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="101" spans="1:25">
@@ -4745,28 +4664,31 @@
         <v>124</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
+      </c>
+      <c r="I101" t="s">
+        <v>262</v>
       </c>
       <c r="M101">
         <v>1</v>
       </c>
       <c r="N101" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="O101" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P101" s="3">
-        <v>46316.43622685185</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="Q101" s="3">
-        <v>46316.43622685185</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="R101">
-        <v>5.69</v>
+        <v>12.41</v>
       </c>
       <c r="S101" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="102" spans="1:25">
@@ -4774,28 +4696,31 @@
         <v>125</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>250</v>
+        <v>239</v>
+      </c>
+      <c r="I102" t="s">
+        <v>257</v>
       </c>
       <c r="M102">
         <v>1</v>
       </c>
       <c r="N102" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O102" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P102" s="3">
-        <v>46314.45354166667</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="Q102" s="3">
-        <v>46314.45354166667</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="R102">
-        <v>8.58</v>
+        <v>9.31</v>
       </c>
       <c r="S102" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="103" spans="1:25">
@@ -4803,28 +4728,31 @@
         <v>126</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>251</v>
+        <v>240</v>
+      </c>
+      <c r="I103" t="s">
+        <v>259</v>
       </c>
       <c r="M103">
         <v>1</v>
       </c>
       <c r="N103" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O103" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P103" s="3">
-        <v>46316.43068287037</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="Q103" s="3">
-        <v>46316.43068287037</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="R103">
         <v>5.69</v>
       </c>
       <c r="S103" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="104" spans="1:25">
@@ -4832,31 +4760,31 @@
         <v>127</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="I104" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="M104">
         <v>1</v>
       </c>
       <c r="N104" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O104" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P104" s="3">
-        <v>46198.62644675926</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="Q104" s="3">
-        <v>46198.62644675926</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="R104">
         <v>5.69</v>
       </c>
       <c r="S104" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="105" spans="1:25">
@@ -4864,28 +4792,31 @@
         <v>128</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>253</v>
+        <v>242</v>
+      </c>
+      <c r="I105" t="s">
+        <v>261</v>
       </c>
       <c r="M105">
         <v>1</v>
       </c>
       <c r="N105" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O105" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P105" s="3">
-        <v>46313.72997685185</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="Q105" s="3">
-        <v>46313.72997685185</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="R105">
         <v>5.69</v>
       </c>
       <c r="S105" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="106" spans="1:25">
@@ -4893,28 +4824,46 @@
         <v>129</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="N106" t="s">
+        <v>268</v>
+      </c>
+      <c r="O106" t="s">
+        <v>284</v>
+      </c>
+      <c r="P106" s="3">
+        <v>46306.55003472222</v>
+      </c>
+      <c r="Q106" s="3">
+        <v>46306.55003472222</v>
+      </c>
+      <c r="R106">
+        <v>8.58</v>
+      </c>
+      <c r="S106" t="s">
+        <v>286</v>
+      </c>
+      <c r="T106">
         <v>2</v>
       </c>
-      <c r="N106" t="s">
-        <v>304</v>
-      </c>
-      <c r="O106" t="s">
-        <v>308</v>
-      </c>
-      <c r="P106" s="3">
-        <v>46296.45002314815</v>
-      </c>
-      <c r="Q106" s="3">
-        <v>46296.45003472222</v>
-      </c>
-      <c r="R106">
-        <v>26.25</v>
-      </c>
-      <c r="S106" t="s">
-        <v>310</v>
+      <c r="U106">
+        <v>59.99</v>
+      </c>
+      <c r="V106">
+        <v>1</v>
+      </c>
+      <c r="W106">
+        <v>946</v>
+      </c>
+      <c r="X106" s="3">
+        <v>46294</v>
+      </c>
+      <c r="Y106">
+        <v>-13</v>
       </c>
     </row>
     <row r="107" spans="1:25">
@@ -4922,31 +4871,28 @@
         <v>130</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I107" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="M107">
         <v>1</v>
       </c>
       <c r="N107" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O107" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="P107" s="3">
-        <v>46220.44594907408</v>
+        <v>46312.95512731482</v>
       </c>
       <c r="Q107" s="3">
-        <v>46220.44594907408</v>
+        <v>46312.95512731482</v>
       </c>
       <c r="R107">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S107" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="108" spans="1:25">
@@ -4954,46 +4900,31 @@
         <v>131</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>256</v>
+        <v>245</v>
+      </c>
+      <c r="I108" t="s">
+        <v>257</v>
       </c>
       <c r="M108">
         <v>1</v>
       </c>
       <c r="N108" t="s">
-        <v>305</v>
+        <v>268</v>
       </c>
       <c r="O108" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P108" s="3">
-        <v>46303.44568287037</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="Q108" s="3">
-        <v>46303.44568287037</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="R108">
-        <v>4.73</v>
+        <v>9.31</v>
       </c>
       <c r="S108" t="s">
-        <v>311</v>
-      </c>
-      <c r="T108">
-        <v>2</v>
-      </c>
-      <c r="U108">
-        <v>0</v>
-      </c>
-      <c r="V108">
-        <v>0</v>
-      </c>
-      <c r="W108">
-        <v>111</v>
-      </c>
-      <c r="X108" s="3">
-        <v>46308</v>
-      </c>
-      <c r="Y108">
-        <v>4</v>
+        <v>285</v>
       </c>
     </row>
     <row r="109" spans="1:25">
@@ -5001,28 +4932,31 @@
         <v>132</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>257</v>
+        <v>246</v>
+      </c>
+      <c r="I109" t="s">
+        <v>258</v>
       </c>
       <c r="M109">
         <v>1</v>
       </c>
       <c r="N109" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="O109" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="P109" s="3">
-        <v>46301.52780092593</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q109" s="3">
-        <v>46301.52780092593</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R109">
-        <v>6.53</v>
+        <v>5.69</v>
       </c>
       <c r="S109" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="110" spans="1:25">
@@ -5030,31 +4964,31 @@
         <v>133</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="I110" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="M110">
         <v>1</v>
       </c>
       <c r="N110" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O110" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P110" s="3">
-        <v>46221.54171296296</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="Q110" s="3">
-        <v>46221.54171296296</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="R110">
         <v>5.69</v>
       </c>
       <c r="S110" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="111" spans="1:25">
@@ -5062,31 +4996,31 @@
         <v>134</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="I111" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="M111">
         <v>1</v>
       </c>
       <c r="N111" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O111" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P111" s="3">
-        <v>45993.6759375</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="Q111" s="3">
-        <v>45993.6759375</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="R111">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S111" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="112" spans="1:25">
@@ -5094,485 +5028,121 @@
         <v>135</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="I112" t="s">
+        <v>249</v>
+      </c>
+      <c r="M112">
+        <v>1</v>
+      </c>
+      <c r="N112" t="s">
+        <v>268</v>
+      </c>
+      <c r="O112" t="s">
         <v>284</v>
       </c>
-      <c r="M112">
-        <v>1</v>
-      </c>
-      <c r="N112" t="s">
-        <v>289</v>
-      </c>
-      <c r="O112" t="s">
-        <v>309</v>
-      </c>
       <c r="P112" s="3">
-        <v>46178.61515046296</v>
+        <v>46314.78832175926</v>
       </c>
       <c r="Q112" s="3">
-        <v>46178.61515046296</v>
+        <v>46314.78832175926</v>
       </c>
       <c r="R112">
-        <v>12.41</v>
+        <v>5.69</v>
       </c>
       <c r="S112" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="113" spans="1:25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19">
       <c r="A113" t="s">
         <v>136</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="I113" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="M113">
         <v>1</v>
       </c>
       <c r="N113" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O113" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P113" s="3">
-        <v>45981.84152777777</v>
+        <v>46314.79108796296</v>
       </c>
       <c r="Q113" s="3">
-        <v>45981.84152777777</v>
+        <v>46314.79108796296</v>
       </c>
       <c r="R113">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S113" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="114" spans="1:25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19">
       <c r="A114" t="s">
         <v>137</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="I114" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="M114">
         <v>1</v>
       </c>
       <c r="N114" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O114" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P114" s="3">
-        <v>45965.5908449074</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="Q114" s="3">
-        <v>45965.5908449074</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="R114">
         <v>5.69</v>
       </c>
       <c r="S114" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="115" spans="1:25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19">
       <c r="A115" t="s">
         <v>138</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="I115" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="M115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N115" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="O115" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="P115" s="3">
-        <v>46206.37778935185</v>
+        <v>46196.65561342592</v>
       </c>
       <c r="Q115" s="3">
-        <v>46206.37778935185</v>
+        <v>46224.32857638889</v>
       </c>
       <c r="R115">
-        <v>5.69</v>
+        <v>11.38</v>
       </c>
       <c r="S115" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="116" spans="1:25">
-      <c r="A116" t="s">
-        <v>139</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="I116" t="s">
-        <v>283</v>
-      </c>
-      <c r="M116">
-        <v>1</v>
-      </c>
-      <c r="N116" t="s">
-        <v>290</v>
-      </c>
-      <c r="O116" t="s">
-        <v>307</v>
-      </c>
-      <c r="P116" s="3">
-        <v>46220.91548611111</v>
-      </c>
-      <c r="Q116" s="3">
-        <v>46220.91548611111</v>
-      </c>
-      <c r="R116">
-        <v>5.69</v>
-      </c>
-      <c r="S116" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="117" spans="1:25">
-      <c r="A117" t="s">
-        <v>140</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="M117">
-        <v>1</v>
-      </c>
-      <c r="N117" t="s">
-        <v>290</v>
-      </c>
-      <c r="O117" t="s">
-        <v>309</v>
-      </c>
-      <c r="P117" s="3">
-        <v>46306.55003472222</v>
-      </c>
-      <c r="Q117" s="3">
-        <v>46306.55003472222</v>
-      </c>
-      <c r="R117">
-        <v>8.58</v>
-      </c>
-      <c r="S117" t="s">
-        <v>311</v>
-      </c>
-      <c r="T117">
-        <v>2</v>
-      </c>
-      <c r="U117">
-        <v>59.99</v>
-      </c>
-      <c r="V117">
-        <v>1</v>
-      </c>
-      <c r="W117">
-        <v>946</v>
-      </c>
-      <c r="X117" s="3">
-        <v>46294</v>
-      </c>
-      <c r="Y117">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="118" spans="1:25">
-      <c r="A118" t="s">
-        <v>141</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="M118">
-        <v>1</v>
-      </c>
-      <c r="N118" t="s">
-        <v>290</v>
-      </c>
-      <c r="O118" t="s">
-        <v>309</v>
-      </c>
-      <c r="P118" s="3">
-        <v>46312.95512731482</v>
-      </c>
-      <c r="Q118" s="3">
-        <v>46312.95512731482</v>
-      </c>
-      <c r="R118">
-        <v>8.58</v>
-      </c>
-      <c r="S118" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="119" spans="1:25">
-      <c r="A119" t="s">
-        <v>142</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I119" t="s">
-        <v>279</v>
-      </c>
-      <c r="M119">
-        <v>1</v>
-      </c>
-      <c r="N119" t="s">
-        <v>290</v>
-      </c>
-      <c r="O119" t="s">
-        <v>307</v>
-      </c>
-      <c r="P119" s="3">
-        <v>45939.98240740741</v>
-      </c>
-      <c r="Q119" s="3">
-        <v>45939.98240740741</v>
-      </c>
-      <c r="R119">
-        <v>9.31</v>
-      </c>
-      <c r="S119" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="120" spans="1:25">
-      <c r="A120" t="s">
-        <v>143</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I120" t="s">
-        <v>280</v>
-      </c>
-      <c r="M120">
-        <v>1</v>
-      </c>
-      <c r="N120" t="s">
-        <v>290</v>
-      </c>
-      <c r="O120" t="s">
-        <v>307</v>
-      </c>
-      <c r="P120" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="Q120" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="R120">
-        <v>5.69</v>
-      </c>
-      <c r="S120" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="121" spans="1:25">
-      <c r="A121" t="s">
-        <v>144</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I121" t="s">
-        <v>284</v>
-      </c>
-      <c r="M121">
-        <v>1</v>
-      </c>
-      <c r="N121" t="s">
-        <v>290</v>
-      </c>
-      <c r="O121" t="s">
-        <v>307</v>
-      </c>
-      <c r="P121" s="3">
-        <v>45990.94167824074</v>
-      </c>
-      <c r="Q121" s="3">
-        <v>45990.94167824074</v>
-      </c>
-      <c r="R121">
-        <v>5.69</v>
-      </c>
-      <c r="S121" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="122" spans="1:25">
-      <c r="A122" t="s">
-        <v>145</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I122" t="s">
-        <v>283</v>
-      </c>
-      <c r="M122">
-        <v>1</v>
-      </c>
-      <c r="N122" t="s">
-        <v>290</v>
-      </c>
-      <c r="O122" t="s">
-        <v>307</v>
-      </c>
-      <c r="P122" s="3">
-        <v>45913.74726851852</v>
-      </c>
-      <c r="Q122" s="3">
-        <v>45913.74726851852</v>
-      </c>
-      <c r="R122">
-        <v>5.69</v>
-      </c>
-      <c r="S122" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="123" spans="1:25">
-      <c r="A123" t="s">
-        <v>146</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="M123">
-        <v>1</v>
-      </c>
-      <c r="N123" t="s">
-        <v>290</v>
-      </c>
-      <c r="O123" t="s">
-        <v>309</v>
-      </c>
-      <c r="P123" s="3">
-        <v>46314.78832175926</v>
-      </c>
-      <c r="Q123" s="3">
-        <v>46314.78832175926</v>
-      </c>
-      <c r="R123">
-        <v>5.69</v>
-      </c>
-      <c r="S123" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="124" spans="1:25">
-      <c r="A124" t="s">
-        <v>147</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="M124">
-        <v>1</v>
-      </c>
-      <c r="N124" t="s">
-        <v>290</v>
-      </c>
-      <c r="O124" t="s">
-        <v>307</v>
-      </c>
-      <c r="P124" s="3">
-        <v>46314.79108796296</v>
-      </c>
-      <c r="Q124" s="3">
-        <v>46314.79108796296</v>
-      </c>
-      <c r="R124">
-        <v>5.69</v>
-      </c>
-      <c r="S124" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="125" spans="1:25">
-      <c r="A125" t="s">
-        <v>148</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I125" t="s">
-        <v>281</v>
-      </c>
-      <c r="M125">
-        <v>1</v>
-      </c>
-      <c r="N125" t="s">
-        <v>290</v>
-      </c>
-      <c r="O125" t="s">
-        <v>307</v>
-      </c>
-      <c r="P125" s="3">
-        <v>46221.60350694445</v>
-      </c>
-      <c r="Q125" s="3">
-        <v>46221.60350694445</v>
-      </c>
-      <c r="R125">
-        <v>5.69</v>
-      </c>
-      <c r="S125" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="126" spans="1:25">
-      <c r="A126" t="s">
-        <v>149</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I126" t="s">
-        <v>283</v>
-      </c>
-      <c r="M126">
-        <v>2</v>
-      </c>
-      <c r="N126" t="s">
-        <v>290</v>
-      </c>
-      <c r="O126" t="s">
-        <v>307</v>
-      </c>
-      <c r="P126" s="3">
-        <v>46196.65561342592</v>
-      </c>
-      <c r="Q126" s="3">
-        <v>46224.32857638889</v>
-      </c>
-      <c r="R126">
-        <v>11.38</v>
-      </c>
-      <c r="S126" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -5691,17 +5261,6 @@
     <hyperlink ref="B113" r:id="rId112"/>
     <hyperlink ref="B114" r:id="rId113"/>
     <hyperlink ref="B115" r:id="rId114"/>
-    <hyperlink ref="B116" r:id="rId115"/>
-    <hyperlink ref="B117" r:id="rId116"/>
-    <hyperlink ref="B118" r:id="rId117"/>
-    <hyperlink ref="B119" r:id="rId118"/>
-    <hyperlink ref="B120" r:id="rId119"/>
-    <hyperlink ref="B121" r:id="rId120"/>
-    <hyperlink ref="B122" r:id="rId121"/>
-    <hyperlink ref="B123" r:id="rId122"/>
-    <hyperlink ref="B124" r:id="rId123"/>
-    <hyperlink ref="B125" r:id="rId124"/>
-    <hyperlink ref="B126" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="261">
   <si>
     <t>handle</t>
   </si>
@@ -91,12 +91,6 @@
     <t>days_to_first_video</t>
   </si>
   <si>
-    <t>.smgb.digital</t>
-  </si>
-  <si>
-    <t>_k1mbles_</t>
-  </si>
-  <si>
     <t>adwoafrimpong7</t>
   </si>
   <si>
@@ -106,60 +100,27 @@
     <t>annredfearn1</t>
   </si>
   <si>
-    <t>ayesha.creator99</t>
-  </si>
-  <si>
     <t>beauty.baddie.444</t>
   </si>
   <si>
-    <t>beesmokes.4.2.0</t>
-  </si>
-  <si>
-    <t>blackwidow1194</t>
-  </si>
-  <si>
-    <t>burton_x</t>
-  </si>
-  <si>
     <t>celaniklozet</t>
   </si>
   <si>
-    <t>cherylker90</t>
-  </si>
-  <si>
     <t>christopherreidy7</t>
   </si>
   <si>
-    <t>cosylife4you</t>
-  </si>
-  <si>
     <t>craigkennethmccal</t>
   </si>
   <si>
-    <t>dagmawi_natty</t>
-  </si>
-  <si>
-    <t>dailysaver26</t>
-  </si>
-  <si>
     <t>debsline.co</t>
   </si>
   <si>
-    <t>donnaburton227</t>
-  </si>
-  <si>
-    <t>ehizofdgoodlife</t>
-  </si>
-  <si>
     <t>elizabeth.haigh3</t>
   </si>
   <si>
     <t>emandpete_vanlife</t>
   </si>
   <si>
-    <t>emerald..beauty</t>
-  </si>
-  <si>
     <t>exclusive_shop5</t>
   </si>
   <si>
@@ -172,9 +133,6 @@
     <t>fariwala66</t>
   </si>
   <si>
-    <t>featherbrinas</t>
-  </si>
-  <si>
     <t>feelinggoodafter50</t>
   </si>
   <si>
@@ -190,9 +148,6 @@
     <t>frankli2237</t>
   </si>
   <si>
-    <t>freshpickz3</t>
-  </si>
-  <si>
     <t>fxtimx20</t>
   </si>
   <si>
@@ -205,9 +160,6 @@
     <t>glotanning.myshopify.com</t>
   </si>
   <si>
-    <t>gmkbargains</t>
-  </si>
-  <si>
     <t>godisgoodoooo</t>
   </si>
   <si>
@@ -229,12 +181,6 @@
     <t>huzair329</t>
   </si>
   <si>
-    <t>iamteegirl15</t>
-  </si>
-  <si>
-    <t>infinitgrind</t>
-  </si>
-  <si>
     <t>jadexoxo93</t>
   </si>
   <si>
@@ -256,15 +202,9 @@
     <t>kailiaspuppies</t>
   </si>
   <si>
-    <t>karendickie0</t>
-  </si>
-  <si>
     <t>katie.the.reader</t>
   </si>
   <si>
-    <t>kellykp_uk</t>
-  </si>
-  <si>
     <t>khadeeja088</t>
   </si>
   <si>
@@ -277,24 +217,12 @@
     <t>krfindsuk</t>
   </si>
   <si>
-    <t>laurenwest6958</t>
-  </si>
-  <si>
-    <t>leahcrossxx</t>
-  </si>
-  <si>
     <t>lesliepeckback1</t>
   </si>
   <si>
     <t>lindastubbs88</t>
   </si>
   <si>
-    <t>little_misschatterbox</t>
-  </si>
-  <si>
-    <t>mabcfc</t>
-  </si>
-  <si>
     <t>mah70178</t>
   </si>
   <si>
@@ -328,15 +256,9 @@
     <t>nitaz10</t>
   </si>
   <si>
-    <t>no1dealz</t>
-  </si>
-  <si>
     <t>obsessique</t>
   </si>
   <si>
-    <t>obsessiverecessiveroots</t>
-  </si>
-  <si>
     <t>olufunkebakare84</t>
   </si>
   <si>
@@ -346,27 +268,15 @@
     <t>peachyfindsuk</t>
   </si>
   <si>
-    <t>peerose67</t>
-  </si>
-  <si>
     <t>precious.oghounu</t>
   </si>
   <si>
-    <t>queenkin380</t>
-  </si>
-  <si>
-    <t>queenshireen24</t>
-  </si>
-  <si>
     <t>rachieha</t>
   </si>
   <si>
     <t>rahman20182</t>
   </si>
   <si>
-    <t>ramzan.jami48</t>
-  </si>
-  <si>
     <t>realbeautylondon</t>
   </si>
   <si>
@@ -388,27 +298,18 @@
     <t>sarahs.daily.deal</t>
   </si>
   <si>
-    <t>shanor923</t>
-  </si>
-  <si>
     <t>shaz2uk</t>
   </si>
   <si>
     <t>sheluvslivx</t>
   </si>
   <si>
-    <t>shieldsyxoxo</t>
-  </si>
-  <si>
     <t>shopforfiver</t>
   </si>
   <si>
     <t>shopwithme082</t>
   </si>
   <si>
-    <t>side.hustle.shop69</t>
-  </si>
-  <si>
     <t>silentforever92</t>
   </si>
   <si>
@@ -418,24 +319,12 @@
     <t>softirontouches</t>
   </si>
   <si>
-    <t>sophia_d_first__</t>
-  </si>
-  <si>
     <t>stephanie.cameron4</t>
   </si>
   <si>
     <t>styled388</t>
   </si>
   <si>
-    <t>sum62118</t>
-  </si>
-  <si>
-    <t>sumbil.dar</t>
-  </si>
-  <si>
-    <t>sweetsoul2016</t>
-  </si>
-  <si>
     <t>sylhetimumukworld</t>
   </si>
   <si>
@@ -448,9 +337,6 @@
     <t>the.witchy.wander</t>
   </si>
   <si>
-    <t>thesheboss2</t>
-  </si>
-  <si>
     <t>thetripleteez</t>
   </si>
   <si>
@@ -460,15 +346,9 @@
     <t>theweebelfastman</t>
   </si>
   <si>
-    <t>tiajordan18</t>
-  </si>
-  <si>
     <t>tifeyhslash</t>
   </si>
   <si>
-    <t>tiktokmarket78</t>
-  </si>
-  <si>
     <t>tinae38</t>
   </si>
   <si>
@@ -478,9 +358,6 @@
     <t>tony03672</t>
   </si>
   <si>
-    <t>uk.tiny.cuisine</t>
-  </si>
-  <si>
     <t>user24484259047033</t>
   </si>
   <si>
@@ -508,30 +385,18 @@
     <t>xhollycolhounx</t>
   </si>
   <si>
-    <t>xunchashop</t>
-  </si>
-  <si>
     <t>yvette.chance8</t>
   </si>
   <si>
     <t>zaheersheikh786</t>
   </si>
   <si>
-    <t>zaman_7024</t>
-  </si>
-  <si>
     <t>zembii</t>
   </si>
   <si>
     <t>zynislam2</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@.smgb.digital</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@_k1mbles_</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@adwoafrimpong7</t>
   </si>
   <si>
@@ -541,60 +406,27 @@
     <t>https://www.tiktok.com/@annredfearn1</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@ayesha.creator99</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@beauty.baddie.444</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@beesmokes.4.2.0</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@blackwidow1194</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@burton_x</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@celaniklozet</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@cherylker90</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@christopherreidy7</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@cosylife4you</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@craigkennethmccal</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@dagmawi_natty</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@dailysaver26</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@debsline.co</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@donnaburton227</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@ehizofdgoodlife</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@elizabeth.haigh3</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@emandpete_vanlife</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@emerald..beauty</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@exclusive_shop5</t>
   </si>
   <si>
@@ -607,9 +439,6 @@
     <t>https://www.tiktok.com/@fariwala66</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@featherbrinas</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@feelinggoodafter50</t>
   </si>
   <si>
@@ -625,9 +454,6 @@
     <t>https://www.tiktok.com/@frankli2237</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@freshpickz3</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@fxtimx20</t>
   </si>
   <si>
@@ -640,9 +466,6 @@
     <t>https://www.tiktok.com/@glotanning.myshopify.com</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@gmkbargains</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@godisgoodoooo</t>
   </si>
   <si>
@@ -664,12 +487,6 @@
     <t>https://www.tiktok.com/@huzair329</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@iamteegirl15</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@infinitgrind</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@jadexoxo93</t>
   </si>
   <si>
@@ -691,15 +508,9 @@
     <t>https://www.tiktok.com/@kailiaspuppies</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@karendickie0</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@katie.the.reader</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@kellykp_uk</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@khadeeja088</t>
   </si>
   <si>
@@ -712,24 +523,12 @@
     <t>https://www.tiktok.com/@krfindsuk</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@laurenwest6958</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@leahcrossxx</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@lesliepeckback1</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@lindastubbs88</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@little_misschatterbox</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@mabcfc</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@mah70178</t>
   </si>
   <si>
@@ -763,15 +562,9 @@
     <t>https://www.tiktok.com/@nitaz10</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@no1dealz</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@obsessique</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@obsessiverecessiveroots</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@olufunkebakare84</t>
   </si>
   <si>
@@ -781,27 +574,15 @@
     <t>https://www.tiktok.com/@peachyfindsuk</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@peerose67</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@precious.oghounu</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@queenkin380</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@queenshireen24</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@rachieha</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@rahman20182</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@ramzan.jami48</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@realbeautylondon</t>
   </si>
   <si>
@@ -823,27 +604,18 @@
     <t>https://www.tiktok.com/@sarahs.daily.deal</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@shanor923</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@shaz2uk</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@sheluvslivx</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@shieldsyxoxo</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@shopforfiver</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@shopwithme082</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@side.hustle.shop69</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@silentforever92</t>
   </si>
   <si>
@@ -853,24 +625,12 @@
     <t>https://www.tiktok.com/@softirontouches</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@sophia_d_first__</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@stephanie.cameron4</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@styled388</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@sum62118</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@sumbil.dar</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@sweetsoul2016</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@sylhetimumukworld</t>
   </si>
   <si>
@@ -883,9 +643,6 @@
     <t>https://www.tiktok.com/@the.witchy.wander</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@thesheboss2</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@thetripleteez</t>
   </si>
   <si>
@@ -895,15 +652,9 @@
     <t>https://www.tiktok.com/@theweebelfastman</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@tiajordan18</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@tifeyhslash</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@tiktokmarket78</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@tinae38</t>
   </si>
   <si>
@@ -913,9 +664,6 @@
     <t>https://www.tiktok.com/@tony03672</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@uk.tiny.cuisine</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@user24484259047033</t>
   </si>
   <si>
@@ -943,18 +691,12 @@
     <t>https://www.tiktok.com/@xhollycolhounx</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@xunchashop</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@yvette.chance8</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@zaheersheikh786</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@zaman_7024</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@zembii</t>
   </si>
   <si>
@@ -1006,13 +748,34 @@
     <t>Green Burner</t>
   </si>
   <si>
+    <t>Ashwagandha Coffee</t>
+  </si>
+  <si>
+    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Turmeric Curcumin</t>
+  </si>
+  <si>
+    <t>Ashwagandha Coffee, Green Burner</t>
+  </si>
+  <si>
+    <t>Ashwagandha Capsules, Ashwagandha Coffee, Green Burner, Gut Shift, Hibiscus, Spearmint, Turmeric Curcumin</t>
+  </si>
+  <si>
+    <t>Ashwagandha Coffee, Spearmint</t>
+  </si>
+  <si>
+    <t>Advent Teas of Joy, Ashwagandha Coffee</t>
+  </si>
+  <si>
+    <t>Ashwagandha Coffee, Skin Radiance, Turmeric Curcumin</t>
+  </si>
+  <si>
+    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Skin Radiance</t>
+  </si>
+  <si>
     <t>Advent Teas of Joy</t>
   </si>
   <si>
-    <t>Ashwagandha Coffee</t>
-  </si>
-  <si>
-    <t>Green Burner, Turmeric Curcumin</t>
+    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Skin Radiance, Turmeric Curcumin</t>
   </si>
   <si>
     <t>Green Burner, Gut Shift, Skin Radiance, Turmeric Curcumin</t>
@@ -1021,52 +784,13 @@
     <t>Turmeric Curcumin</t>
   </si>
   <si>
-    <t>Spearmint</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Turmeric Curcumin</t>
-  </si>
-  <si>
-    <t>Gut Shift</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Green Burner</t>
-  </si>
-  <si>
-    <t>Ashwagandha Capsules, Ashwagandha Coffee, Green Burner, Gut Shift, Hibiscus, Spearmint, Turmeric Curcumin</t>
-  </si>
-  <si>
-    <t>Skin Radiance</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Spearmint</t>
-  </si>
-  <si>
-    <t>Advent Teas of Joy, Ashwagandha Coffee</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Skin Radiance, Turmeric Curcumin</t>
-  </si>
-  <si>
-    <t>Green Burner, Gut Shift, Skin Radiance</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Skin Radiance</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Green Burner, Skin Radiance, Turmeric Curcumin</t>
-  </si>
-  <si>
-    <t>Ashwagandha Coffee, Green Burner, Gut Shift, Skin Radiance, Turmeric Curcumin</t>
-  </si>
-  <si>
     <t>TikTok Shop (FBT)</t>
   </si>
   <si>
+    <t>TikTok Shop (FBT), seller</t>
+  </si>
+  <si>
     <t>seller</t>
-  </si>
-  <si>
-    <t>TikTok Shop (FBT), seller</t>
   </si>
   <si>
     <t>No</t>
@@ -1447,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y146"/>
+  <dimension ref="A1:Y103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1532,28 +1256,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>127</v>
+      </c>
+      <c r="I2" t="s">
+        <v>233</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>329</v>
+        <v>243</v>
       </c>
       <c r="O2" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P2" s="3">
-        <v>46317.34664351852</v>
+        <v>46028.62637731482</v>
       </c>
       <c r="Q2" s="3">
-        <v>46317.34664351852</v>
+        <v>46028.62637731482</v>
       </c>
       <c r="R2">
         <v>5.64</v>
       </c>
       <c r="S2" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1561,28 +1288,31 @@
         <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>171</v>
+        <v>128</v>
+      </c>
+      <c r="I3" t="s">
+        <v>233</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="O3" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P3" s="3">
-        <v>46317.53399305556</v>
+        <v>45998.88378472222</v>
       </c>
       <c r="Q3" s="3">
-        <v>46317.53399305556</v>
+        <v>45998.88378472222</v>
       </c>
       <c r="R3">
-        <v>6.04</v>
+        <v>9.31</v>
       </c>
       <c r="S3" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1590,31 +1320,31 @@
         <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="I4" t="s">
-        <v>319</v>
+        <v>234</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>329</v>
+        <v>244</v>
       </c>
       <c r="O4" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P4" s="3">
-        <v>46028.62637731482</v>
+        <v>45986.77690972222</v>
       </c>
       <c r="Q4" s="3">
-        <v>46028.62637731482</v>
+        <v>45986.77690972222</v>
       </c>
       <c r="R4">
-        <v>5.64</v>
+        <v>5.69</v>
       </c>
       <c r="S4" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1622,31 +1352,31 @@
         <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="I5" t="s">
-        <v>319</v>
+        <v>235</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O5" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P5" s="3">
-        <v>45998.88378472222</v>
+        <v>45911.17809027778</v>
       </c>
       <c r="Q5" s="3">
-        <v>45998.88378472222</v>
+        <v>45911.17809027778</v>
       </c>
       <c r="R5">
         <v>9.31</v>
       </c>
       <c r="S5" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1654,31 +1384,52 @@
         <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>174</v>
+        <v>131</v>
+      </c>
+      <c r="E6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H6" t="s">
+        <v>232</v>
       </c>
       <c r="I6" t="s">
-        <v>320</v>
+        <v>235</v>
+      </c>
+      <c r="J6" t="s">
+        <v>241</v>
+      </c>
+      <c r="K6" t="s">
+        <v>242</v>
+      </c>
+      <c r="L6" t="s">
+        <v>241</v>
       </c>
       <c r="M6">
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O6" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P6" s="3">
-        <v>45986.77690972222</v>
+        <v>45989.98658564815</v>
       </c>
       <c r="Q6" s="3">
-        <v>45986.77690972222</v>
+        <v>45989.98658564815</v>
       </c>
       <c r="R6">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S6" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1686,28 +1437,31 @@
         <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>175</v>
+        <v>132</v>
+      </c>
+      <c r="I7" t="s">
+        <v>233</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O7" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P7" s="3">
-        <v>46317.94641203704</v>
+        <v>45974.46635416667</v>
       </c>
       <c r="Q7" s="3">
-        <v>46317.94641203704</v>
+        <v>45974.46635416667</v>
       </c>
       <c r="R7">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S7" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1715,31 +1469,31 @@
         <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="I8" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O8" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P8" s="3">
-        <v>45911.17809027778</v>
+        <v>45967.48326388889</v>
       </c>
       <c r="Q8" s="3">
-        <v>45911.17809027778</v>
+        <v>45967.48326388889</v>
       </c>
       <c r="R8">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S8" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1747,28 +1501,31 @@
         <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>177</v>
+        <v>134</v>
+      </c>
+      <c r="I9" t="s">
+        <v>236</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O9" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P9" s="3">
-        <v>46317.5340162037</v>
+        <v>46176.59099537037</v>
       </c>
       <c r="Q9" s="3">
-        <v>46317.5340162037</v>
+        <v>46176.59099537037</v>
       </c>
       <c r="R9">
         <v>5.69</v>
       </c>
       <c r="S9" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1776,28 +1533,31 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>178</v>
+        <v>135</v>
+      </c>
+      <c r="I10" t="s">
+        <v>233</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="O10" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P10" s="3">
-        <v>46317.5654050926</v>
+        <v>45996.23743055556</v>
       </c>
       <c r="Q10" s="3">
-        <v>46317.5654050926</v>
+        <v>45996.23743055556</v>
       </c>
       <c r="R10">
-        <v>6.04</v>
+        <v>12.46</v>
       </c>
       <c r="S10" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1805,28 +1565,31 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>179</v>
+        <v>136</v>
+      </c>
+      <c r="I11" t="s">
+        <v>234</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O11" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P11" s="3">
-        <v>46317.94663194445</v>
+        <v>46209.78530092593</v>
       </c>
       <c r="Q11" s="3">
-        <v>46317.94663194445</v>
+        <v>46209.78530092593</v>
       </c>
       <c r="R11">
         <v>5.69</v>
       </c>
       <c r="S11" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1834,52 +1597,31 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E12" t="s">
-        <v>315</v>
-      </c>
-      <c r="F12" t="s">
-        <v>316</v>
-      </c>
-      <c r="G12" t="s">
-        <v>317</v>
-      </c>
-      <c r="H12" t="s">
-        <v>318</v>
+        <v>137</v>
       </c>
       <c r="I12" t="s">
-        <v>321</v>
-      </c>
-      <c r="J12" t="s">
-        <v>327</v>
-      </c>
-      <c r="K12" t="s">
-        <v>328</v>
-      </c>
-      <c r="L12" t="s">
-        <v>327</v>
+        <v>235</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O12" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P12" s="3">
-        <v>45989.98658564815</v>
+        <v>46092.52502314815</v>
       </c>
       <c r="Q12" s="3">
-        <v>45989.98658564815</v>
+        <v>46092.52502314815</v>
       </c>
       <c r="R12">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S12" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1887,28 +1629,46 @@
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="M13">
         <v>2</v>
       </c>
       <c r="N13" t="s">
-        <v>332</v>
+        <v>245</v>
       </c>
       <c r="O13" t="s">
-        <v>350</v>
+        <v>257</v>
       </c>
       <c r="P13" s="3">
-        <v>46317.53399305556</v>
+        <v>46296.61392361111</v>
       </c>
       <c r="Q13" s="3">
-        <v>46317.5340162037</v>
+        <v>46296.61392361111</v>
       </c>
       <c r="R13">
-        <v>12.17</v>
+        <v>26.83</v>
       </c>
       <c r="S13" t="s">
-        <v>351</v>
+        <v>260</v>
+      </c>
+      <c r="T13">
+        <v>4</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>219</v>
+      </c>
+      <c r="X13" s="3">
+        <v>46303</v>
+      </c>
+      <c r="Y13">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1916,31 +1676,28 @@
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I14" t="s">
-        <v>319</v>
+        <v>139</v>
       </c>
       <c r="M14">
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O14" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P14" s="3">
-        <v>45974.46635416667</v>
+        <v>46196.83574074074</v>
       </c>
       <c r="Q14" s="3">
-        <v>45974.46635416667</v>
+        <v>46196.83574074074</v>
       </c>
       <c r="R14">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S14" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1948,28 +1705,31 @@
         <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>183</v>
+        <v>140</v>
+      </c>
+      <c r="I15" t="s">
+        <v>237</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>333</v>
+        <v>244</v>
       </c>
       <c r="O15" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="P15" s="3">
-        <v>46317.34664351852</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="Q15" s="3">
-        <v>46317.3466550926</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="R15">
-        <v>28.05</v>
+        <v>5.69</v>
       </c>
       <c r="S15" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1977,31 +1737,31 @@
         <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="I16" t="s">
-        <v>320</v>
+        <v>234</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>331</v>
+        <v>246</v>
       </c>
       <c r="O16" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="P16" s="3">
-        <v>45967.48326388889</v>
+        <v>45840.45584490741</v>
       </c>
       <c r="Q16" s="3">
-        <v>45967.48326388889</v>
+        <v>46170.61114583333</v>
       </c>
       <c r="R16">
-        <v>5.69</v>
+        <v>17.02</v>
       </c>
       <c r="S16" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2009,28 +1769,31 @@
         <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>185</v>
+        <v>142</v>
+      </c>
+      <c r="I17" t="s">
+        <v>235</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O17" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P17" s="3">
-        <v>46317.3480324074</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="Q17" s="3">
-        <v>46317.3480324074</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="R17">
         <v>5.69</v>
       </c>
       <c r="S17" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2038,31 +1801,31 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>186</v>
+        <v>143</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>334</v>
+        <v>244</v>
       </c>
       <c r="O18" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P18" s="3">
-        <v>46317.53399305556</v>
+        <v>46309.55629629629</v>
       </c>
       <c r="Q18" s="3">
-        <v>46317.53399305556</v>
+        <v>46309.55629629629</v>
       </c>
       <c r="R18">
-        <v>6.53</v>
+        <v>5.69</v>
       </c>
       <c r="S18" t="s">
-        <v>352</v>
+        <v>260</v>
       </c>
       <c r="T18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18">
         <v>0</v>
@@ -2071,13 +1834,13 @@
         <v>0</v>
       </c>
       <c r="W18">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="X18" s="3">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="Y18">
-        <v>-9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2085,31 +1848,28 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I19" t="s">
-        <v>322</v>
+        <v>144</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O19" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P19" s="3">
-        <v>46176.59099537037</v>
+        <v>46252.93552083334</v>
       </c>
       <c r="Q19" s="3">
-        <v>46176.59099537037</v>
+        <v>46252.93552083334</v>
       </c>
       <c r="R19">
         <v>5.69</v>
       </c>
       <c r="S19" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2117,28 +1877,31 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>188</v>
+        <v>145</v>
+      </c>
+      <c r="I20" t="s">
+        <v>238</v>
       </c>
       <c r="M20">
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O20" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P20" s="3">
-        <v>46317.4325925926</v>
+        <v>46062.02391203704</v>
       </c>
       <c r="Q20" s="3">
-        <v>46317.4325925926</v>
+        <v>46062.02391203704</v>
       </c>
       <c r="R20">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S20" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2146,28 +1909,31 @@
         <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
+      </c>
+      <c r="I21" t="s">
+        <v>235</v>
       </c>
       <c r="M21">
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O21" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P21" s="3">
-        <v>46317.94638888889</v>
+        <v>45903.0252662037</v>
       </c>
       <c r="Q21" s="3">
-        <v>46317.94638888889</v>
+        <v>45903.0252662037</v>
       </c>
       <c r="R21">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S21" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2175,31 +1941,31 @@
         <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>190</v>
+        <v>147</v>
       </c>
       <c r="I22" t="s">
-        <v>319</v>
+        <v>235</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O22" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P22" s="3">
-        <v>45996.23743055556</v>
+        <v>46178.95283564815</v>
       </c>
       <c r="Q22" s="3">
-        <v>45996.23743055556</v>
+        <v>46178.95283564815</v>
       </c>
       <c r="R22">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S22" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2207,31 +1973,31 @@
         <v>46</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="I23" t="s">
-        <v>320</v>
+        <v>237</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N23" t="s">
-        <v>331</v>
+        <v>247</v>
       </c>
       <c r="O23" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="P23" s="3">
-        <v>46209.78530092593</v>
+        <v>46181.5243287037</v>
       </c>
       <c r="Q23" s="3">
-        <v>46209.78530092593</v>
+        <v>46253.65496527778</v>
       </c>
       <c r="R23">
-        <v>5.69</v>
+        <v>60.34</v>
       </c>
       <c r="S23" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2239,28 +2005,28 @@
         <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="M24">
         <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>335</v>
+        <v>244</v>
       </c>
       <c r="O24" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P24" s="3">
-        <v>46317.57966435186</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="Q24" s="3">
-        <v>46317.57966435186</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="R24">
-        <v>4.86</v>
+        <v>5.69</v>
       </c>
       <c r="S24" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2268,31 +2034,31 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="I25" t="s">
-        <v>321</v>
+        <v>233</v>
       </c>
       <c r="M25">
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O25" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P25" s="3">
-        <v>46092.52502314815</v>
+        <v>46008.62306712963</v>
       </c>
       <c r="Q25" s="3">
-        <v>46092.52502314815</v>
+        <v>46008.62306712963</v>
       </c>
       <c r="R25">
         <v>5.69</v>
       </c>
       <c r="S25" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2300,46 +2066,31 @@
         <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>194</v>
+        <v>151</v>
+      </c>
+      <c r="I26" t="s">
+        <v>238</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>336</v>
+        <v>244</v>
       </c>
       <c r="O26" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="P26" s="3">
-        <v>46296.61392361111</v>
+        <v>46152.90292824074</v>
       </c>
       <c r="Q26" s="3">
-        <v>46296.61392361111</v>
+        <v>46152.90292824074</v>
       </c>
       <c r="R26">
-        <v>26.83</v>
+        <v>5.69</v>
       </c>
       <c r="S26" t="s">
-        <v>352</v>
-      </c>
-      <c r="T26">
-        <v>4</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>219</v>
-      </c>
-      <c r="X26" s="3">
-        <v>46303</v>
-      </c>
-      <c r="Y26">
-        <v>6</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2347,28 +2098,46 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O27" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P27" s="3">
-        <v>46196.83574074074</v>
+        <v>46307.41046296297</v>
       </c>
       <c r="Q27" s="3">
-        <v>46196.83574074074</v>
+        <v>46307.41046296297</v>
       </c>
       <c r="R27">
         <v>5.69</v>
       </c>
       <c r="S27" t="s">
-        <v>351</v>
+        <v>260</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>18</v>
+      </c>
+      <c r="X27" s="3">
+        <v>46312</v>
+      </c>
+      <c r="Y27">
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2376,31 +2145,28 @@
         <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I28" t="s">
-        <v>323</v>
+        <v>153</v>
       </c>
       <c r="M28">
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O28" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P28" s="3">
-        <v>46198.6271412037</v>
+        <v>46317.94596064815</v>
       </c>
       <c r="Q28" s="3">
-        <v>46198.6271412037</v>
+        <v>46317.94596064815</v>
       </c>
       <c r="R28">
         <v>5.69</v>
       </c>
       <c r="S28" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2408,28 +2174,31 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>197</v>
+        <v>154</v>
+      </c>
+      <c r="I29" t="s">
+        <v>234</v>
       </c>
       <c r="M29">
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="O29" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P29" s="3">
-        <v>46317.5340625</v>
+        <v>45953.84554398148</v>
       </c>
       <c r="Q29" s="3">
-        <v>46317.5340625</v>
+        <v>45953.84554398148</v>
       </c>
       <c r="R29">
-        <v>8.970000000000001</v>
+        <v>12.46</v>
       </c>
       <c r="S29" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2437,31 +2206,46 @@
         <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I30" t="s">
-        <v>320</v>
+        <v>155</v>
       </c>
       <c r="M30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N30" t="s">
-        <v>338</v>
+        <v>244</v>
       </c>
       <c r="O30" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="P30" s="3">
-        <v>45840.45584490741</v>
+        <v>46310.5215625</v>
       </c>
       <c r="Q30" s="3">
-        <v>46170.61114583333</v>
+        <v>46310.5215625</v>
       </c>
       <c r="R30">
-        <v>17.02</v>
+        <v>5.69</v>
       </c>
       <c r="S30" t="s">
-        <v>351</v>
+        <v>260</v>
+      </c>
+      <c r="T30">
+        <v>6</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>185</v>
+      </c>
+      <c r="X30" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y30">
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2469,31 +2253,31 @@
         <v>54</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="I31" t="s">
-        <v>321</v>
+        <v>233</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O31" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P31" s="3">
-        <v>46198.6271412037</v>
+        <v>46111.64181712963</v>
       </c>
       <c r="Q31" s="3">
-        <v>46198.6271412037</v>
+        <v>46111.64181712963</v>
       </c>
       <c r="R31">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S31" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2501,28 +2285,28 @@
         <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="M32">
         <v>1</v>
       </c>
       <c r="N32" t="s">
-        <v>331</v>
+        <v>243</v>
       </c>
       <c r="O32" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P32" s="3">
-        <v>46309.55629629629</v>
+        <v>46296.45141203704</v>
       </c>
       <c r="Q32" s="3">
-        <v>46309.55629629629</v>
+        <v>46296.45141203704</v>
       </c>
       <c r="R32">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="S32" t="s">
-        <v>352</v>
+        <v>260</v>
       </c>
       <c r="T32">
         <v>1</v>
@@ -2534,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32" s="3">
-        <v>46311</v>
+        <v>46298</v>
       </c>
       <c r="Y32">
         <v>1</v>
@@ -2548,28 +2332,31 @@
         <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>201</v>
+        <v>158</v>
+      </c>
+      <c r="I33" t="s">
+        <v>234</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
       <c r="N33" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O33" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P33" s="3">
-        <v>46252.93552083334</v>
+        <v>46210.48171296297</v>
       </c>
       <c r="Q33" s="3">
-        <v>46252.93552083334</v>
+        <v>46210.48171296297</v>
       </c>
       <c r="R33">
         <v>5.69</v>
       </c>
       <c r="S33" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -2577,31 +2364,46 @@
         <v>57</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I34" t="s">
-        <v>324</v>
+        <v>159</v>
       </c>
       <c r="M34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N34" t="s">
-        <v>331</v>
+        <v>248</v>
       </c>
       <c r="O34" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="P34" s="3">
-        <v>46062.02391203704</v>
+        <v>46280.49378472222</v>
       </c>
       <c r="Q34" s="3">
-        <v>46062.02391203704</v>
+        <v>46280.49379629629</v>
       </c>
       <c r="R34">
-        <v>12.46</v>
+        <v>10.55</v>
       </c>
       <c r="S34" t="s">
-        <v>351</v>
+        <v>260</v>
+      </c>
+      <c r="T34">
+        <v>4</v>
+      </c>
+      <c r="U34">
+        <v>19.91</v>
+      </c>
+      <c r="V34">
+        <v>2</v>
+      </c>
+      <c r="W34">
+        <v>689</v>
+      </c>
+      <c r="X34" s="3">
+        <v>46281</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -2609,28 +2411,31 @@
         <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>203</v>
+        <v>160</v>
+      </c>
+      <c r="I35" t="s">
+        <v>239</v>
       </c>
       <c r="M35">
         <v>1</v>
       </c>
       <c r="N35" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O35" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P35" s="3">
-        <v>46317.26513888889</v>
+        <v>46225.98408564815</v>
       </c>
       <c r="Q35" s="3">
-        <v>46317.26513888889</v>
+        <v>46225.98408564815</v>
       </c>
       <c r="R35">
         <v>5.69</v>
       </c>
       <c r="S35" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -2638,31 +2443,31 @@
         <v>59</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="I36" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="M36">
         <v>1</v>
       </c>
       <c r="N36" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O36" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P36" s="3">
-        <v>45903.0252662037</v>
+        <v>46106.56184027778</v>
       </c>
       <c r="Q36" s="3">
-        <v>45903.0252662037</v>
+        <v>46106.56184027778</v>
       </c>
       <c r="R36">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S36" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -2670,31 +2475,28 @@
         <v>60</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I37" t="s">
-        <v>321</v>
+        <v>162</v>
       </c>
       <c r="M37">
         <v>1</v>
       </c>
       <c r="N37" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O37" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="P37" s="3">
-        <v>46178.95283564815</v>
+        <v>46313.79324074074</v>
       </c>
       <c r="Q37" s="3">
-        <v>46178.95283564815</v>
+        <v>46313.79324074074</v>
       </c>
       <c r="R37">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S37" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -2702,31 +2504,31 @@
         <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="I38" t="s">
-        <v>323</v>
+        <v>238</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N38" t="s">
-        <v>339</v>
+        <v>244</v>
       </c>
       <c r="O38" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="P38" s="3">
-        <v>46181.5243287037</v>
+        <v>46196.84141203704</v>
       </c>
       <c r="Q38" s="3">
-        <v>46253.65496527778</v>
+        <v>46196.84141203704</v>
       </c>
       <c r="R38">
-        <v>60.34</v>
+        <v>5.69</v>
       </c>
       <c r="S38" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -2734,28 +2536,28 @@
         <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="M39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N39" t="s">
-        <v>331</v>
+        <v>249</v>
       </c>
       <c r="O39" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="P39" s="3">
-        <v>46053.63612268519</v>
+        <v>46312.81608796296</v>
       </c>
       <c r="Q39" s="3">
-        <v>46053.63612268519</v>
+        <v>46313.7452662037</v>
       </c>
       <c r="R39">
-        <v>5.69</v>
+        <v>14.62</v>
       </c>
       <c r="S39" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -2763,28 +2565,31 @@
         <v>63</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>208</v>
+        <v>165</v>
+      </c>
+      <c r="I40" t="s">
+        <v>237</v>
       </c>
       <c r="M40">
         <v>1</v>
       </c>
       <c r="N40" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O40" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P40" s="3">
-        <v>46317.35082175926</v>
+        <v>46073.66815972222</v>
       </c>
       <c r="Q40" s="3">
-        <v>46317.35082175926</v>
+        <v>46073.66815972222</v>
       </c>
       <c r="R40">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S40" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -2792,31 +2597,49 @@
         <v>64</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>209</v>
+        <v>166</v>
       </c>
       <c r="I41" t="s">
-        <v>319</v>
+        <v>238</v>
       </c>
       <c r="M41">
         <v>1</v>
       </c>
       <c r="N41" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O41" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P41" s="3">
-        <v>46008.62306712963</v>
+        <v>46245.82854166667</v>
       </c>
       <c r="Q41" s="3">
-        <v>46008.62306712963</v>
+        <v>46245.82854166667</v>
       </c>
       <c r="R41">
         <v>5.69</v>
       </c>
       <c r="S41" t="s">
-        <v>351</v>
+        <v>260</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>23</v>
+      </c>
+      <c r="X41" s="3">
+        <v>46261</v>
+      </c>
+      <c r="Y41">
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -2824,31 +2647,28 @@
         <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="I42" t="s">
-        <v>324</v>
+        <v>167</v>
       </c>
       <c r="M42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N42" t="s">
-        <v>331</v>
+        <v>250</v>
       </c>
       <c r="O42" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="P42" s="3">
-        <v>46152.90292824074</v>
+        <v>46313.77442129629</v>
       </c>
       <c r="Q42" s="3">
-        <v>46152.90292824074</v>
+        <v>46314.79109953704</v>
       </c>
       <c r="R42">
-        <v>5.69</v>
+        <v>27.71</v>
       </c>
       <c r="S42" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -2856,46 +2676,28 @@
         <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O43" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P43" s="3">
-        <v>46307.41046296297</v>
+        <v>46316.43623842593</v>
       </c>
       <c r="Q43" s="3">
-        <v>46307.41046296297</v>
+        <v>46316.43623842593</v>
       </c>
       <c r="R43">
         <v>5.69</v>
       </c>
       <c r="S43" t="s">
-        <v>352</v>
-      </c>
-      <c r="T43">
-        <v>1</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-      <c r="W43">
-        <v>18</v>
-      </c>
-      <c r="X43" s="3">
-        <v>46312</v>
-      </c>
-      <c r="Y43">
-        <v>4</v>
+        <v>259</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -2903,28 +2705,46 @@
         <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="M44">
         <v>1</v>
       </c>
       <c r="N44" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O44" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P44" s="3">
-        <v>46317.94596064815</v>
+        <v>46281.49586805556</v>
       </c>
       <c r="Q44" s="3">
-        <v>46317.94596064815</v>
+        <v>46281.49586805556</v>
       </c>
       <c r="R44">
         <v>5.69</v>
       </c>
       <c r="S44" t="s">
-        <v>351</v>
+        <v>260</v>
+      </c>
+      <c r="T44">
+        <v>7</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>119</v>
+      </c>
+      <c r="X44" s="3">
+        <v>46282</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -2932,31 +2752,31 @@
         <v>68</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="I45" t="s">
-        <v>320</v>
+        <v>234</v>
       </c>
       <c r="M45">
         <v>1</v>
       </c>
       <c r="N45" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O45" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P45" s="3">
-        <v>45953.84554398148</v>
+        <v>46050.93159722222</v>
       </c>
       <c r="Q45" s="3">
-        <v>45953.84554398148</v>
+        <v>46050.93159722222</v>
       </c>
       <c r="R45">
         <v>12.46</v>
       </c>
       <c r="S45" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -2964,31 +2784,31 @@
         <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
       <c r="N46" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O46" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="P46" s="3">
-        <v>46310.5215625</v>
+        <v>46310.34238425926</v>
       </c>
       <c r="Q46" s="3">
-        <v>46310.5215625</v>
+        <v>46310.34238425926</v>
       </c>
       <c r="R46">
         <v>5.69</v>
       </c>
       <c r="S46" t="s">
-        <v>352</v>
+        <v>260</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -2997,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="W46">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="X46" s="3">
         <v>46313</v>
@@ -3011,31 +2831,31 @@
         <v>70</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="I47" t="s">
-        <v>319</v>
+        <v>238</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O47" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P47" s="3">
-        <v>46111.64181712963</v>
+        <v>45965.93854166667</v>
       </c>
       <c r="Q47" s="3">
-        <v>46111.64181712963</v>
+        <v>45965.93854166667</v>
       </c>
       <c r="R47">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S47" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="48" spans="1:25">
@@ -3043,28 +2863,31 @@
         <v>71</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>216</v>
+        <v>173</v>
+      </c>
+      <c r="I48" t="s">
+        <v>234</v>
       </c>
       <c r="M48">
         <v>1</v>
       </c>
       <c r="N48" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O48" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P48" s="3">
-        <v>46317.34734953703</v>
+        <v>45992.89240740741</v>
       </c>
       <c r="Q48" s="3">
-        <v>46317.34734953703</v>
+        <v>45992.89240740741</v>
       </c>
       <c r="R48">
         <v>5.69</v>
       </c>
       <c r="S48" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:25">
@@ -3072,28 +2895,31 @@
         <v>72</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>217</v>
+        <v>174</v>
+      </c>
+      <c r="I49" t="s">
+        <v>240</v>
       </c>
       <c r="M49">
         <v>1</v>
       </c>
       <c r="N49" t="s">
-        <v>340</v>
+        <v>244</v>
       </c>
       <c r="O49" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P49" s="3">
-        <v>46317.34734953703</v>
+        <v>45944.90217592593</v>
       </c>
       <c r="Q49" s="3">
-        <v>46317.34734953703</v>
+        <v>45944.90217592593</v>
       </c>
       <c r="R49">
-        <v>6.91</v>
+        <v>9.31</v>
       </c>
       <c r="S49" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="50" spans="1:25">
@@ -3101,46 +2927,31 @@
         <v>73</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>218</v>
+        <v>175</v>
+      </c>
+      <c r="I50" t="s">
+        <v>234</v>
       </c>
       <c r="M50">
         <v>1</v>
       </c>
       <c r="N50" t="s">
-        <v>329</v>
+        <v>244</v>
       </c>
       <c r="O50" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P50" s="3">
-        <v>46296.45141203704</v>
+        <v>46105.47987268519</v>
       </c>
       <c r="Q50" s="3">
-        <v>46296.45141203704</v>
+        <v>46105.47987268519</v>
       </c>
       <c r="R50">
-        <v>5.64</v>
+        <v>5.69</v>
       </c>
       <c r="S50" t="s">
-        <v>352</v>
-      </c>
-      <c r="T50">
-        <v>1</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>9</v>
-      </c>
-      <c r="X50" s="3">
-        <v>46298</v>
-      </c>
-      <c r="Y50">
-        <v>1</v>
+        <v>259</v>
       </c>
     </row>
     <row r="51" spans="1:25">
@@ -3148,31 +2959,31 @@
         <v>74</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="I51" t="s">
-        <v>320</v>
+        <v>238</v>
       </c>
       <c r="M51">
         <v>1</v>
       </c>
       <c r="N51" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O51" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P51" s="3">
-        <v>46210.48171296297</v>
+        <v>46210.50420138889</v>
       </c>
       <c r="Q51" s="3">
-        <v>46210.48171296297</v>
+        <v>46210.50420138889</v>
       </c>
       <c r="R51">
         <v>5.69</v>
       </c>
       <c r="S51" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="52" spans="1:25">
@@ -3180,46 +2991,28 @@
         <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>220</v>
+        <v>177</v>
       </c>
       <c r="M52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N52" t="s">
-        <v>341</v>
+        <v>244</v>
       </c>
       <c r="O52" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="P52" s="3">
-        <v>46280.49378472222</v>
+        <v>46052.56390046296</v>
       </c>
       <c r="Q52" s="3">
-        <v>46280.49379629629</v>
+        <v>46052.56390046296</v>
       </c>
       <c r="R52">
-        <v>10.55</v>
+        <v>5.69</v>
       </c>
       <c r="S52" t="s">
-        <v>352</v>
-      </c>
-      <c r="T52">
-        <v>4</v>
-      </c>
-      <c r="U52">
-        <v>19.91</v>
-      </c>
-      <c r="V52">
-        <v>2</v>
-      </c>
-      <c r="W52">
-        <v>689</v>
-      </c>
-      <c r="X52" s="3">
-        <v>46281</v>
-      </c>
-      <c r="Y52">
-        <v>0</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53" spans="1:25">
@@ -3227,31 +3020,31 @@
         <v>76</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="I53" t="s">
-        <v>325</v>
+        <v>235</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O53" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P53" s="3">
-        <v>46225.98408564815</v>
+        <v>46091.88748842593</v>
       </c>
       <c r="Q53" s="3">
-        <v>46225.98408564815</v>
+        <v>46091.88748842593</v>
       </c>
       <c r="R53">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S53" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="54" spans="1:25">
@@ -3259,31 +3052,31 @@
         <v>77</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="I54" t="s">
-        <v>320</v>
+        <v>235</v>
       </c>
       <c r="M54">
         <v>1</v>
       </c>
       <c r="N54" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O54" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P54" s="3">
-        <v>46106.56184027778</v>
+        <v>45978.69265046297</v>
       </c>
       <c r="Q54" s="3">
-        <v>46106.56184027778</v>
+        <v>45978.69265046297</v>
       </c>
       <c r="R54">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S54" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55" spans="1:25">
@@ -3291,28 +3084,31 @@
         <v>78</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>223</v>
+        <v>180</v>
+      </c>
+      <c r="I55" t="s">
+        <v>234</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O55" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P55" s="3">
-        <v>46313.79324074074</v>
+        <v>45919.81163194445</v>
       </c>
       <c r="Q55" s="3">
-        <v>46313.79324074074</v>
+        <v>45919.81163194445</v>
       </c>
       <c r="R55">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S55" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:25">
@@ -3320,31 +3116,28 @@
         <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="I56" t="s">
-        <v>324</v>
+        <v>181</v>
       </c>
       <c r="M56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N56" t="s">
-        <v>331</v>
+        <v>251</v>
       </c>
       <c r="O56" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="P56" s="3">
-        <v>46196.84141203704</v>
+        <v>46313.77442129629</v>
       </c>
       <c r="Q56" s="3">
-        <v>46196.84141203704</v>
+        <v>46314.78831018518</v>
       </c>
       <c r="R56">
-        <v>5.69</v>
+        <v>30.1</v>
       </c>
       <c r="S56" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" spans="1:25">
@@ -3352,28 +3145,46 @@
         <v>80</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="M57">
         <v>1</v>
       </c>
       <c r="N57" t="s">
-        <v>331</v>
+        <v>252</v>
       </c>
       <c r="O57" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="P57" s="3">
-        <v>46317.42579861111</v>
+        <v>46314.50759259259</v>
       </c>
       <c r="Q57" s="3">
-        <v>46317.42579861111</v>
+        <v>46314.50759259259</v>
       </c>
       <c r="R57">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S57" t="s">
-        <v>351</v>
+        <v>260</v>
+      </c>
+      <c r="T57">
+        <v>2</v>
+      </c>
+      <c r="U57">
+        <v>20.03</v>
+      </c>
+      <c r="V57">
+        <v>2</v>
+      </c>
+      <c r="W57">
+        <v>473</v>
+      </c>
+      <c r="X57" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y57">
+        <v>-2</v>
       </c>
     </row>
     <row r="58" spans="1:25">
@@ -3381,28 +3192,31 @@
         <v>81</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>226</v>
+        <v>183</v>
+      </c>
+      <c r="I58" t="s">
+        <v>233</v>
       </c>
       <c r="M58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N58" t="s">
-        <v>342</v>
+        <v>244</v>
       </c>
       <c r="O58" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P58" s="3">
-        <v>46312.81608796296</v>
+        <v>46051.04447916667</v>
       </c>
       <c r="Q58" s="3">
-        <v>46313.7452662037</v>
+        <v>46051.04447916667</v>
       </c>
       <c r="R58">
-        <v>14.62</v>
+        <v>5.69</v>
       </c>
       <c r="S58" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="59" spans="1:25">
@@ -3410,28 +3224,31 @@
         <v>82</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>227</v>
+        <v>184</v>
+      </c>
+      <c r="I59" t="s">
+        <v>233</v>
       </c>
       <c r="M59">
         <v>1</v>
       </c>
       <c r="N59" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="O59" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P59" s="3">
-        <v>46317.75636574074</v>
+        <v>45891.71650462963</v>
       </c>
       <c r="Q59" s="3">
-        <v>46317.75636574074</v>
+        <v>45891.71650462963</v>
       </c>
       <c r="R59">
-        <v>6.04</v>
+        <v>9.31</v>
       </c>
       <c r="S59" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="60" spans="1:25">
@@ -3439,31 +3256,31 @@
         <v>83</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="I60" t="s">
-        <v>323</v>
+        <v>233</v>
       </c>
       <c r="M60">
         <v>1</v>
       </c>
       <c r="N60" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O60" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P60" s="3">
-        <v>46073.66815972222</v>
+        <v>46211.60210648148</v>
       </c>
       <c r="Q60" s="3">
-        <v>46073.66815972222</v>
+        <v>46211.60210648148</v>
       </c>
       <c r="R60">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S60" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="61" spans="1:25">
@@ -3471,49 +3288,31 @@
         <v>84</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="I61" t="s">
-        <v>324</v>
+        <v>235</v>
       </c>
       <c r="M61">
         <v>1</v>
       </c>
       <c r="N61" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O61" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P61" s="3">
-        <v>46245.82854166667</v>
+        <v>46167.36722222222</v>
       </c>
       <c r="Q61" s="3">
-        <v>46245.82854166667</v>
+        <v>46167.36722222222</v>
       </c>
       <c r="R61">
         <v>5.69</v>
       </c>
       <c r="S61" t="s">
-        <v>352</v>
-      </c>
-      <c r="T61">
-        <v>1</v>
-      </c>
-      <c r="U61">
-        <v>0</v>
-      </c>
-      <c r="V61">
-        <v>0</v>
-      </c>
-      <c r="W61">
-        <v>23</v>
-      </c>
-      <c r="X61" s="3">
-        <v>46261</v>
-      </c>
-      <c r="Y61">
-        <v>15</v>
+        <v>259</v>
       </c>
     </row>
     <row r="62" spans="1:25">
@@ -3521,28 +3320,28 @@
         <v>85</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>230</v>
+        <v>187</v>
       </c>
       <c r="M62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N62" t="s">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="O62" t="s">
-        <v>350</v>
+        <v>257</v>
       </c>
       <c r="P62" s="3">
-        <v>46313.77442129629</v>
+        <v>46313.73414351852</v>
       </c>
       <c r="Q62" s="3">
-        <v>46314.79109953704</v>
+        <v>46313.73415509259</v>
       </c>
       <c r="R62">
-        <v>27.71</v>
+        <v>11.73</v>
       </c>
       <c r="S62" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="63" spans="1:25">
@@ -3550,28 +3349,49 @@
         <v>86</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>231</v>
+        <v>188</v>
+      </c>
+      <c r="I63" t="s">
+        <v>235</v>
       </c>
       <c r="M63">
         <v>1</v>
       </c>
       <c r="N63" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O63" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="P63" s="3">
-        <v>46316.43623842593</v>
+        <v>46309.5507175926</v>
       </c>
       <c r="Q63" s="3">
-        <v>46316.43623842593</v>
+        <v>46309.5507175926</v>
       </c>
       <c r="R63">
         <v>5.69</v>
       </c>
       <c r="S63" t="s">
-        <v>351</v>
+        <v>260</v>
+      </c>
+      <c r="T63">
+        <v>1</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>12</v>
+      </c>
+      <c r="X63" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y63">
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:25">
@@ -3579,28 +3399,31 @@
         <v>87</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>232</v>
+        <v>189</v>
+      </c>
+      <c r="I64" t="s">
+        <v>238</v>
       </c>
       <c r="M64">
         <v>1</v>
       </c>
       <c r="N64" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="O64" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P64" s="3">
-        <v>46317.56427083333</v>
+        <v>46050.54237268519</v>
       </c>
       <c r="Q64" s="3">
-        <v>46317.56427083333</v>
+        <v>46050.54237268519</v>
       </c>
       <c r="R64">
-        <v>8.970000000000001</v>
+        <v>5.69</v>
       </c>
       <c r="S64" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="65" spans="1:25">
@@ -3608,28 +3431,31 @@
         <v>88</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>233</v>
+        <v>190</v>
+      </c>
+      <c r="I65" t="s">
+        <v>237</v>
       </c>
       <c r="M65">
         <v>1</v>
       </c>
       <c r="N65" t="s">
-        <v>344</v>
+        <v>244</v>
       </c>
       <c r="O65" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P65" s="3">
-        <v>46317.34664351852</v>
+        <v>45957.49894675926</v>
       </c>
       <c r="Q65" s="3">
-        <v>46317.34664351852</v>
+        <v>45957.49894675926</v>
       </c>
       <c r="R65">
-        <v>21.52</v>
+        <v>5.69</v>
       </c>
       <c r="S65" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="66" spans="1:25">
@@ -3637,46 +3463,31 @@
         <v>89</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>234</v>
+        <v>191</v>
+      </c>
+      <c r="I66" t="s">
+        <v>237</v>
       </c>
       <c r="M66">
         <v>1</v>
       </c>
       <c r="N66" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O66" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P66" s="3">
-        <v>46281.49586805556</v>
+        <v>46196.62574074074</v>
       </c>
       <c r="Q66" s="3">
-        <v>46281.49586805556</v>
+        <v>46196.62574074074</v>
       </c>
       <c r="R66">
         <v>5.69</v>
       </c>
       <c r="S66" t="s">
-        <v>352</v>
-      </c>
-      <c r="T66">
-        <v>7</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>119</v>
-      </c>
-      <c r="X66" s="3">
-        <v>46282</v>
-      </c>
-      <c r="Y66">
-        <v>0</v>
+        <v>259</v>
       </c>
     </row>
     <row r="67" spans="1:25">
@@ -3684,31 +3495,31 @@
         <v>90</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I67" t="s">
         <v>235</v>
       </c>
-      <c r="I67" t="s">
-        <v>320</v>
-      </c>
       <c r="M67">
         <v>1</v>
       </c>
       <c r="N67" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O67" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P67" s="3">
-        <v>46050.93159722222</v>
+        <v>45959.6512037037</v>
       </c>
       <c r="Q67" s="3">
-        <v>46050.93159722222</v>
+        <v>45959.6512037037</v>
       </c>
       <c r="R67">
-        <v>12.46</v>
+        <v>9.31</v>
       </c>
       <c r="S67" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="68" spans="1:25">
@@ -3716,28 +3527,31 @@
         <v>91</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>236</v>
+        <v>193</v>
+      </c>
+      <c r="I68" t="s">
+        <v>233</v>
       </c>
       <c r="M68">
         <v>1</v>
       </c>
       <c r="N68" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="O68" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P68" s="3">
-        <v>46317.53399305556</v>
+        <v>45973.56506944444</v>
       </c>
       <c r="Q68" s="3">
-        <v>46317.53399305556</v>
+        <v>45973.56506944444</v>
       </c>
       <c r="R68">
-        <v>8.970000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="S68" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="69" spans="1:25">
@@ -3745,28 +3559,28 @@
         <v>92</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="M69">
         <v>1</v>
       </c>
       <c r="N69" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O69" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P69" s="3">
-        <v>46317.35081018518</v>
+        <v>46317.58319444444</v>
       </c>
       <c r="Q69" s="3">
-        <v>46317.35081018518</v>
+        <v>46317.58319444444</v>
       </c>
       <c r="R69">
         <v>5.69</v>
       </c>
       <c r="S69" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="70" spans="1:25">
@@ -3774,46 +3588,28 @@
         <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="M70">
         <v>1</v>
       </c>
       <c r="N70" t="s">
-        <v>331</v>
+        <v>252</v>
       </c>
       <c r="O70" t="s">
-        <v>349</v>
+        <v>258</v>
       </c>
       <c r="P70" s="3">
-        <v>46310.34238425926</v>
+        <v>46313.49944444445</v>
       </c>
       <c r="Q70" s="3">
-        <v>46310.34238425926</v>
+        <v>46313.49944444445</v>
       </c>
       <c r="R70">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S70" t="s">
-        <v>352</v>
-      </c>
-      <c r="T70">
-        <v>3</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-      <c r="V70">
-        <v>0</v>
-      </c>
-      <c r="W70">
-        <v>92</v>
-      </c>
-      <c r="X70" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y70">
-        <v>2</v>
+        <v>259</v>
       </c>
     </row>
     <row r="71" spans="1:25">
@@ -3821,31 +3617,28 @@
         <v>94</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I71" t="s">
-        <v>324</v>
+        <v>196</v>
       </c>
       <c r="M71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N71" t="s">
-        <v>331</v>
+        <v>253</v>
       </c>
       <c r="O71" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="P71" s="3">
-        <v>45965.93854166667</v>
+        <v>46313.73415509259</v>
       </c>
       <c r="Q71" s="3">
-        <v>45965.93854166667</v>
+        <v>46317.32998842592</v>
       </c>
       <c r="R71">
-        <v>5.69</v>
+        <v>42.32</v>
       </c>
       <c r="S71" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="72" spans="1:25">
@@ -3853,31 +3646,31 @@
         <v>95</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="I72" t="s">
-        <v>320</v>
+        <v>234</v>
       </c>
       <c r="M72">
         <v>1</v>
       </c>
       <c r="N72" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O72" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P72" s="3">
-        <v>45992.89240740741</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="Q72" s="3">
-        <v>45992.89240740741</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="R72">
         <v>5.69</v>
       </c>
       <c r="S72" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="73" spans="1:25">
@@ -3885,31 +3678,46 @@
         <v>96</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="I73" t="s">
-        <v>326</v>
+        <v>198</v>
       </c>
       <c r="M73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N73" t="s">
-        <v>331</v>
+        <v>246</v>
       </c>
       <c r="O73" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="P73" s="3">
-        <v>45944.90217592593</v>
+        <v>46286.62572916667</v>
       </c>
       <c r="Q73" s="3">
-        <v>45944.90217592593</v>
+        <v>46306.5500462963</v>
       </c>
       <c r="R73">
-        <v>9.31</v>
+        <v>14.22</v>
       </c>
       <c r="S73" t="s">
-        <v>351</v>
+        <v>260</v>
+      </c>
+      <c r="T73">
+        <v>2</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>32</v>
+      </c>
+      <c r="X73" s="3">
+        <v>46297</v>
+      </c>
+      <c r="Y73">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:25">
@@ -3917,31 +3725,28 @@
         <v>97</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="I74" t="s">
-        <v>320</v>
+        <v>199</v>
       </c>
       <c r="M74">
         <v>1</v>
       </c>
       <c r="N74" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O74" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P74" s="3">
-        <v>46105.47987268519</v>
+        <v>46304.50560185185</v>
       </c>
       <c r="Q74" s="3">
-        <v>46105.47987268519</v>
+        <v>46304.50560185185</v>
       </c>
       <c r="R74">
         <v>5.69</v>
       </c>
       <c r="S74" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="75" spans="1:25">
@@ -3949,31 +3754,28 @@
         <v>98</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="I75" t="s">
-        <v>324</v>
+        <v>200</v>
       </c>
       <c r="M75">
         <v>1</v>
       </c>
       <c r="N75" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O75" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P75" s="3">
-        <v>46210.50420138889</v>
+        <v>46027.60903935185</v>
       </c>
       <c r="Q75" s="3">
-        <v>46210.50420138889</v>
+        <v>46027.60903935185</v>
       </c>
       <c r="R75">
         <v>5.69</v>
       </c>
       <c r="S75" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" spans="1:25">
@@ -3981,28 +3783,46 @@
         <v>99</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="M76">
         <v>1</v>
       </c>
       <c r="N76" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O76" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P76" s="3">
-        <v>46052.56390046296</v>
+        <v>46280.49518518519</v>
       </c>
       <c r="Q76" s="3">
-        <v>46052.56390046296</v>
+        <v>46280.49518518519</v>
       </c>
       <c r="R76">
         <v>5.69</v>
       </c>
       <c r="S76" t="s">
-        <v>351</v>
+        <v>260</v>
+      </c>
+      <c r="T76">
+        <v>1</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>17</v>
+      </c>
+      <c r="X76" s="3">
+        <v>46283</v>
+      </c>
+      <c r="Y76">
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:25">
@@ -4010,31 +3830,28 @@
         <v>100</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="I77" t="s">
-        <v>321</v>
+        <v>202</v>
       </c>
       <c r="M77">
         <v>1</v>
       </c>
       <c r="N77" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O77" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P77" s="3">
-        <v>46091.88748842593</v>
+        <v>46311.94667824074</v>
       </c>
       <c r="Q77" s="3">
-        <v>46091.88748842593</v>
+        <v>46311.94667824074</v>
       </c>
       <c r="R77">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S77" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="78" spans="1:25">
@@ -4042,31 +3859,28 @@
         <v>101</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="I78" t="s">
-        <v>321</v>
+        <v>203</v>
       </c>
       <c r="M78">
         <v>1</v>
       </c>
       <c r="N78" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O78" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="P78" s="3">
-        <v>45978.69265046297</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="Q78" s="3">
-        <v>45978.69265046297</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="R78">
-        <v>12.46</v>
+        <v>8.58</v>
       </c>
       <c r="S78" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="79" spans="1:25">
@@ -4074,31 +3888,31 @@
         <v>102</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="I79" t="s">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="M79">
         <v>1</v>
       </c>
       <c r="N79" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O79" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P79" s="3">
-        <v>45919.81163194445</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q79" s="3">
-        <v>45919.81163194445</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R79">
         <v>5.69</v>
       </c>
       <c r="S79" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="80" spans="1:25">
@@ -4106,28 +3920,31 @@
         <v>103</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>248</v>
+        <v>205</v>
+      </c>
+      <c r="I80" t="s">
+        <v>237</v>
       </c>
       <c r="M80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N80" t="s">
-        <v>345</v>
+        <v>244</v>
       </c>
       <c r="O80" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="P80" s="3">
-        <v>46313.77442129629</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="Q80" s="3">
-        <v>46314.78831018518</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="R80">
-        <v>30.1</v>
+        <v>5.69</v>
       </c>
       <c r="S80" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" spans="1:25">
@@ -4135,28 +3952,28 @@
         <v>104</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>249</v>
+        <v>206</v>
       </c>
       <c r="M81">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N81" t="s">
-        <v>346</v>
+        <v>244</v>
       </c>
       <c r="O81" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="P81" s="3">
-        <v>46317.2653587963</v>
+        <v>46199.43622685185</v>
       </c>
       <c r="Q81" s="3">
-        <v>46317.2691087963</v>
+        <v>46199.43622685185</v>
       </c>
       <c r="R81">
-        <v>24.77</v>
+        <v>5.69</v>
       </c>
       <c r="S81" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82" spans="1:25">
@@ -4164,46 +3981,31 @@
         <v>105</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>250</v>
+        <v>207</v>
+      </c>
+      <c r="I82" t="s">
+        <v>233</v>
       </c>
       <c r="M82">
         <v>1</v>
       </c>
       <c r="N82" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="O82" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P82" s="3">
-        <v>46314.50759259259</v>
+        <v>46211.60422453703</v>
       </c>
       <c r="Q82" s="3">
-        <v>46314.50759259259</v>
+        <v>46211.60422453703</v>
       </c>
       <c r="R82">
-        <v>6.04</v>
+        <v>5.69</v>
       </c>
       <c r="S82" t="s">
-        <v>352</v>
-      </c>
-      <c r="T82">
-        <v>2</v>
-      </c>
-      <c r="U82">
-        <v>20.03</v>
-      </c>
-      <c r="V82">
-        <v>2</v>
-      </c>
-      <c r="W82">
-        <v>473</v>
-      </c>
-      <c r="X82" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y82">
-        <v>-2</v>
+        <v>259</v>
       </c>
     </row>
     <row r="83" spans="1:25">
@@ -4211,28 +4013,31 @@
         <v>106</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>251</v>
+        <v>208</v>
+      </c>
+      <c r="I83" t="s">
+        <v>233</v>
       </c>
       <c r="M83">
         <v>1</v>
       </c>
       <c r="N83" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O83" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P83" s="3">
-        <v>46317.35081018518</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="Q83" s="3">
-        <v>46317.35081018518</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="R83">
         <v>5.69</v>
       </c>
       <c r="S83" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="84" spans="1:25">
@@ -4240,31 +4045,31 @@
         <v>107</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>252</v>
+        <v>209</v>
       </c>
       <c r="I84" t="s">
-        <v>319</v>
+        <v>234</v>
       </c>
       <c r="M84">
         <v>1</v>
       </c>
       <c r="N84" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O84" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P84" s="3">
-        <v>46051.04447916667</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="Q84" s="3">
-        <v>46051.04447916667</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="R84">
         <v>5.69</v>
       </c>
       <c r="S84" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="85" spans="1:25">
@@ -4272,31 +4077,28 @@
         <v>108</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I85" t="s">
-        <v>319</v>
+        <v>210</v>
       </c>
       <c r="M85">
         <v>1</v>
       </c>
       <c r="N85" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O85" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P85" s="3">
-        <v>45891.71650462963</v>
+        <v>46313.72997685185</v>
       </c>
       <c r="Q85" s="3">
-        <v>45891.71650462963</v>
+        <v>46313.72997685185</v>
       </c>
       <c r="R85">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S85" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="86" spans="1:25">
@@ -4304,31 +4106,28 @@
         <v>109</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="M86">
+        <v>2</v>
+      </c>
+      <c r="N86" t="s">
         <v>254</v>
       </c>
-      <c r="I86" t="s">
-        <v>319</v>
-      </c>
-      <c r="M86">
-        <v>1</v>
-      </c>
-      <c r="N86" t="s">
-        <v>331</v>
-      </c>
       <c r="O86" t="s">
-        <v>348</v>
+        <v>257</v>
       </c>
       <c r="P86" s="3">
-        <v>46211.60210648148</v>
+        <v>46296.45002314815</v>
       </c>
       <c r="Q86" s="3">
-        <v>46211.60210648148</v>
+        <v>46296.45003472222</v>
       </c>
       <c r="R86">
-        <v>5.69</v>
+        <v>26.25</v>
       </c>
       <c r="S86" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="87" spans="1:25">
@@ -4336,28 +4135,31 @@
         <v>110</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>255</v>
+        <v>212</v>
+      </c>
+      <c r="I87" t="s">
+        <v>235</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
       <c r="N87" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O87" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P87" s="3">
-        <v>46317.3466550926</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="Q87" s="3">
-        <v>46317.3466550926</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="R87">
         <v>5.69</v>
       </c>
       <c r="S87" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="88" spans="1:25">
@@ -4365,31 +4167,28 @@
         <v>111</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I88" t="s">
-        <v>321</v>
+        <v>213</v>
       </c>
       <c r="M88">
         <v>1</v>
       </c>
       <c r="N88" t="s">
-        <v>331</v>
+        <v>255</v>
       </c>
       <c r="O88" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="P88" s="3">
-        <v>46167.36722222222</v>
+        <v>46301.52780092593</v>
       </c>
       <c r="Q88" s="3">
-        <v>46167.36722222222</v>
+        <v>46301.52780092593</v>
       </c>
       <c r="R88">
-        <v>5.69</v>
+        <v>6.53</v>
       </c>
       <c r="S88" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="89" spans="1:25">
@@ -4397,28 +4196,31 @@
         <v>112</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>257</v>
+        <v>214</v>
+      </c>
+      <c r="I89" t="s">
+        <v>234</v>
       </c>
       <c r="M89">
         <v>1</v>
       </c>
       <c r="N89" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O89" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P89" s="3">
-        <v>46317.34804398148</v>
+        <v>46221.54171296296</v>
       </c>
       <c r="Q89" s="3">
-        <v>46317.34804398148</v>
+        <v>46221.54171296296</v>
       </c>
       <c r="R89">
         <v>5.69</v>
       </c>
       <c r="S89" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="1:25">
@@ -4426,28 +4228,31 @@
         <v>113</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>258</v>
+        <v>215</v>
+      </c>
+      <c r="I90" t="s">
+        <v>238</v>
       </c>
       <c r="M90">
         <v>1</v>
       </c>
       <c r="N90" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="O90" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P90" s="3">
-        <v>46317.75636574074</v>
+        <v>45993.6759375</v>
       </c>
       <c r="Q90" s="3">
-        <v>46317.75636574074</v>
+        <v>45993.6759375</v>
       </c>
       <c r="R90">
-        <v>6.04</v>
+        <v>9.31</v>
       </c>
       <c r="S90" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="91" spans="1:25">
@@ -4455,28 +4260,31 @@
         <v>114</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>259</v>
+        <v>216</v>
+      </c>
+      <c r="I91" t="s">
+        <v>238</v>
       </c>
       <c r="M91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N91" t="s">
-        <v>342</v>
+        <v>243</v>
       </c>
       <c r="O91" t="s">
-        <v>350</v>
+        <v>258</v>
       </c>
       <c r="P91" s="3">
-        <v>46313.73414351852</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="Q91" s="3">
-        <v>46313.73415509259</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="R91">
-        <v>11.73</v>
+        <v>12.41</v>
       </c>
       <c r="S91" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" spans="1:25">
@@ -4484,49 +4292,31 @@
         <v>115</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>260</v>
+        <v>217</v>
       </c>
       <c r="I92" t="s">
-        <v>321</v>
+        <v>233</v>
       </c>
       <c r="M92">
         <v>1</v>
       </c>
       <c r="N92" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O92" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P92" s="3">
-        <v>46309.5507175926</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="Q92" s="3">
-        <v>46309.5507175926</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="R92">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S92" t="s">
-        <v>352</v>
-      </c>
-      <c r="T92">
-        <v>1</v>
-      </c>
-      <c r="U92">
-        <v>0</v>
-      </c>
-      <c r="V92">
-        <v>0</v>
-      </c>
-      <c r="W92">
-        <v>12</v>
-      </c>
-      <c r="X92" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y92">
-        <v>3</v>
+        <v>259</v>
       </c>
     </row>
     <row r="93" spans="1:25">
@@ -4534,28 +4324,31 @@
         <v>116</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>261</v>
+        <v>218</v>
+      </c>
+      <c r="I93" t="s">
+        <v>235</v>
       </c>
       <c r="M93">
         <v>1</v>
       </c>
       <c r="N93" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O93" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P93" s="3">
-        <v>46317.94633101852</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="Q93" s="3">
-        <v>46317.94633101852</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="R93">
         <v>5.69</v>
       </c>
       <c r="S93" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="94" spans="1:25">
@@ -4563,31 +4356,31 @@
         <v>117</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="I94" t="s">
-        <v>324</v>
+        <v>238</v>
       </c>
       <c r="M94">
         <v>1</v>
       </c>
       <c r="N94" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O94" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P94" s="3">
-        <v>46050.54237268519</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="Q94" s="3">
-        <v>46050.54237268519</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="R94">
         <v>5.69</v>
       </c>
       <c r="S94" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="95" spans="1:25">
@@ -4595,31 +4388,31 @@
         <v>118</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="I95" t="s">
-        <v>323</v>
+        <v>237</v>
       </c>
       <c r="M95">
         <v>1</v>
       </c>
       <c r="N95" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O95" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P95" s="3">
-        <v>45957.49894675926</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="Q95" s="3">
-        <v>45957.49894675926</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="R95">
         <v>5.69</v>
       </c>
       <c r="S95" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
     <row r="96" spans="1:25">
@@ -4627,1601 +4420,267 @@
         <v>119</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="I96" t="s">
-        <v>323</v>
+        <v>221</v>
       </c>
       <c r="M96">
         <v>1</v>
       </c>
       <c r="N96" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O96" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="P96" s="3">
-        <v>46196.62574074074</v>
+        <v>46306.55003472222</v>
       </c>
       <c r="Q96" s="3">
-        <v>46196.62574074074</v>
+        <v>46306.55003472222</v>
       </c>
       <c r="R96">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S96" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="97" spans="1:25">
+        <v>260</v>
+      </c>
+      <c r="T96">
+        <v>2</v>
+      </c>
+      <c r="U96">
+        <v>59.99</v>
+      </c>
+      <c r="V96">
+        <v>1</v>
+      </c>
+      <c r="W96">
+        <v>946</v>
+      </c>
+      <c r="X96" s="3">
+        <v>46294</v>
+      </c>
+      <c r="Y96">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19">
       <c r="A97" t="s">
         <v>120</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="I97" t="s">
-        <v>321</v>
+        <v>222</v>
       </c>
       <c r="M97">
         <v>1</v>
       </c>
       <c r="N97" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O97" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="P97" s="3">
-        <v>45959.6512037037</v>
+        <v>46312.95512731482</v>
       </c>
       <c r="Q97" s="3">
-        <v>45959.6512037037</v>
+        <v>46312.95512731482</v>
       </c>
       <c r="R97">
-        <v>9.31</v>
+        <v>8.58</v>
       </c>
       <c r="S97" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="98" spans="1:25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19">
       <c r="A98" t="s">
         <v>121</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="I98" t="s">
-        <v>319</v>
+        <v>233</v>
       </c>
       <c r="M98">
         <v>1</v>
       </c>
       <c r="N98" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O98" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P98" s="3">
-        <v>45973.56506944444</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="Q98" s="3">
-        <v>45973.56506944444</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="R98">
         <v>9.31</v>
       </c>
       <c r="S98" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="99" spans="1:25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19">
       <c r="A99" t="s">
         <v>122</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>267</v>
+        <v>224</v>
+      </c>
+      <c r="I99" t="s">
+        <v>234</v>
       </c>
       <c r="M99">
         <v>1</v>
       </c>
       <c r="N99" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O99" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P99" s="3">
-        <v>46317.58319444444</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q99" s="3">
-        <v>46317.58319444444</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R99">
         <v>5.69</v>
       </c>
       <c r="S99" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="100" spans="1:25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19">
       <c r="A100" t="s">
         <v>123</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>268</v>
+        <v>225</v>
+      </c>
+      <c r="I100" t="s">
+        <v>238</v>
       </c>
       <c r="M100">
         <v>1</v>
       </c>
       <c r="N100" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="O100" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P100" s="3">
-        <v>46313.49944444445</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="Q100" s="3">
-        <v>46313.49944444445</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="R100">
-        <v>6.04</v>
+        <v>5.69</v>
       </c>
       <c r="S100" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="101" spans="1:25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19">
       <c r="A101" t="s">
         <v>124</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>269</v>
+        <v>226</v>
+      </c>
+      <c r="I101" t="s">
+        <v>237</v>
       </c>
       <c r="M101">
         <v>1</v>
       </c>
       <c r="N101" t="s">
-        <v>334</v>
+        <v>244</v>
       </c>
       <c r="O101" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="P101" s="3">
-        <v>46317.34666666666</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="Q101" s="3">
-        <v>46317.34666666666</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="R101">
-        <v>6.53</v>
+        <v>5.69</v>
       </c>
       <c r="S101" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="102" spans="1:25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19">
       <c r="A102" t="s">
         <v>125</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>270</v>
+        <v>227</v>
+      </c>
+      <c r="I102" t="s">
+        <v>235</v>
       </c>
       <c r="M102">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N102" t="s">
-        <v>347</v>
+        <v>244</v>
       </c>
       <c r="O102" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="P102" s="3">
-        <v>46313.73415509259</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="Q102" s="3">
-        <v>46317.32998842592</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="R102">
-        <v>42.32</v>
+        <v>5.69</v>
       </c>
       <c r="S102" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="103" spans="1:25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19">
       <c r="A103" t="s">
         <v>126</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="I103" t="s">
-        <v>320</v>
+        <v>237</v>
       </c>
       <c r="M103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N103" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="O103" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="P103" s="3">
-        <v>46191.82362268519</v>
+        <v>46196.65561342592</v>
       </c>
       <c r="Q103" s="3">
-        <v>46191.82362268519</v>
+        <v>46224.32857638889</v>
       </c>
       <c r="R103">
-        <v>5.69</v>
+        <v>11.38</v>
       </c>
       <c r="S103" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="104" spans="1:25">
-      <c r="A104" t="s">
-        <v>127</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="M104">
-        <v>1</v>
-      </c>
-      <c r="N104" t="s">
-        <v>337</v>
-      </c>
-      <c r="O104" t="s">
-        <v>348</v>
-      </c>
-      <c r="P104" s="3">
-        <v>46317.5340625</v>
-      </c>
-      <c r="Q104" s="3">
-        <v>46317.5340625</v>
-      </c>
-      <c r="R104">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="S104" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="105" spans="1:25">
-      <c r="A105" t="s">
-        <v>128</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="M105">
-        <v>2</v>
-      </c>
-      <c r="N105" t="s">
-        <v>338</v>
-      </c>
-      <c r="O105" t="s">
-        <v>350</v>
-      </c>
-      <c r="P105" s="3">
-        <v>46286.62572916667</v>
-      </c>
-      <c r="Q105" s="3">
-        <v>46306.5500462963</v>
-      </c>
-      <c r="R105">
-        <v>14.22</v>
-      </c>
-      <c r="S105" t="s">
-        <v>352</v>
-      </c>
-      <c r="T105">
-        <v>2</v>
-      </c>
-      <c r="U105">
-        <v>0</v>
-      </c>
-      <c r="V105">
-        <v>0</v>
-      </c>
-      <c r="W105">
-        <v>32</v>
-      </c>
-      <c r="X105" s="3">
-        <v>46297</v>
-      </c>
-      <c r="Y105">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106" spans="1:25">
-      <c r="A106" t="s">
-        <v>129</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="M106">
-        <v>1</v>
-      </c>
-      <c r="N106" t="s">
-        <v>331</v>
-      </c>
-      <c r="O106" t="s">
-        <v>348</v>
-      </c>
-      <c r="P106" s="3">
-        <v>46304.50560185185</v>
-      </c>
-      <c r="Q106" s="3">
-        <v>46304.50560185185</v>
-      </c>
-      <c r="R106">
-        <v>5.69</v>
-      </c>
-      <c r="S106" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="107" spans="1:25">
-      <c r="A107" t="s">
-        <v>130</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="M107">
-        <v>5</v>
-      </c>
-      <c r="N107" t="s">
-        <v>347</v>
-      </c>
-      <c r="O107" t="s">
-        <v>350</v>
-      </c>
-      <c r="P107" s="3">
-        <v>46317.26458333333</v>
-      </c>
-      <c r="Q107" s="3">
-        <v>46317.2650462963</v>
-      </c>
-      <c r="R107">
-        <v>33.74</v>
-      </c>
-      <c r="S107" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="108" spans="1:25">
-      <c r="A108" t="s">
-        <v>131</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M108">
-        <v>1</v>
-      </c>
-      <c r="N108" t="s">
-        <v>331</v>
-      </c>
-      <c r="O108" t="s">
-        <v>348</v>
-      </c>
-      <c r="P108" s="3">
-        <v>46027.60903935185</v>
-      </c>
-      <c r="Q108" s="3">
-        <v>46027.60903935185</v>
-      </c>
-      <c r="R108">
-        <v>5.69</v>
-      </c>
-      <c r="S108" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="109" spans="1:25">
-      <c r="A109" t="s">
-        <v>132</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="M109">
-        <v>1</v>
-      </c>
-      <c r="N109" t="s">
-        <v>331</v>
-      </c>
-      <c r="O109" t="s">
-        <v>348</v>
-      </c>
-      <c r="P109" s="3">
-        <v>46280.49518518519</v>
-      </c>
-      <c r="Q109" s="3">
-        <v>46280.49518518519</v>
-      </c>
-      <c r="R109">
-        <v>5.69</v>
-      </c>
-      <c r="S109" t="s">
-        <v>352</v>
-      </c>
-      <c r="T109">
-        <v>1</v>
-      </c>
-      <c r="U109">
-        <v>0</v>
-      </c>
-      <c r="V109">
-        <v>0</v>
-      </c>
-      <c r="W109">
-        <v>17</v>
-      </c>
-      <c r="X109" s="3">
-        <v>46283</v>
-      </c>
-      <c r="Y109">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:25">
-      <c r="A110" t="s">
-        <v>133</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="M110">
-        <v>1</v>
-      </c>
-      <c r="N110" t="s">
-        <v>331</v>
-      </c>
-      <c r="O110" t="s">
-        <v>348</v>
-      </c>
-      <c r="P110" s="3">
-        <v>46311.94667824074</v>
-      </c>
-      <c r="Q110" s="3">
-        <v>46311.94667824074</v>
-      </c>
-      <c r="R110">
-        <v>5.69</v>
-      </c>
-      <c r="S110" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="111" spans="1:25">
-      <c r="A111" t="s">
-        <v>134</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="M111">
-        <v>1</v>
-      </c>
-      <c r="N111" t="s">
-        <v>331</v>
-      </c>
-      <c r="O111" t="s">
-        <v>349</v>
-      </c>
-      <c r="P111" s="3">
-        <v>46317.32998842592</v>
-      </c>
-      <c r="Q111" s="3">
-        <v>46317.32998842592</v>
-      </c>
-      <c r="R111">
-        <v>5.69</v>
-      </c>
-      <c r="S111" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="112" spans="1:25">
-      <c r="A112" t="s">
-        <v>135</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="M112">
-        <v>1</v>
-      </c>
-      <c r="N112" t="s">
-        <v>331</v>
-      </c>
-      <c r="O112" t="s">
-        <v>349</v>
-      </c>
-      <c r="P112" s="3">
-        <v>46313.79785879629</v>
-      </c>
-      <c r="Q112" s="3">
-        <v>46313.79785879629</v>
-      </c>
-      <c r="R112">
-        <v>8.58</v>
-      </c>
-      <c r="S112" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="113" spans="1:19">
-      <c r="A113" t="s">
-        <v>136</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I113" t="s">
-        <v>326</v>
-      </c>
-      <c r="M113">
-        <v>1</v>
-      </c>
-      <c r="N113" t="s">
-        <v>331</v>
-      </c>
-      <c r="O113" t="s">
-        <v>348</v>
-      </c>
-      <c r="P113" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="Q113" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="R113">
-        <v>5.69</v>
-      </c>
-      <c r="S113" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="114" spans="1:19">
-      <c r="A114" t="s">
-        <v>137</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="M114">
-        <v>1</v>
-      </c>
-      <c r="N114" t="s">
-        <v>331</v>
-      </c>
-      <c r="O114" t="s">
-        <v>348</v>
-      </c>
-      <c r="P114" s="3">
-        <v>46317.44239583334</v>
-      </c>
-      <c r="Q114" s="3">
-        <v>46317.44239583334</v>
-      </c>
-      <c r="R114">
-        <v>5.69</v>
-      </c>
-      <c r="S114" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="115" spans="1:19">
-      <c r="A115" t="s">
-        <v>138</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="M115">
-        <v>1</v>
-      </c>
-      <c r="N115" t="s">
-        <v>334</v>
-      </c>
-      <c r="O115" t="s">
-        <v>349</v>
-      </c>
-      <c r="P115" s="3">
-        <v>46317.3466550926</v>
-      </c>
-      <c r="Q115" s="3">
-        <v>46317.3466550926</v>
-      </c>
-      <c r="R115">
-        <v>6.53</v>
-      </c>
-      <c r="S115" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="116" spans="1:19">
-      <c r="A116" t="s">
-        <v>139</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="M116">
-        <v>1</v>
-      </c>
-      <c r="N116" t="s">
-        <v>331</v>
-      </c>
-      <c r="O116" t="s">
-        <v>348</v>
-      </c>
-      <c r="P116" s="3">
-        <v>46317.3466550926</v>
-      </c>
-      <c r="Q116" s="3">
-        <v>46317.3466550926</v>
-      </c>
-      <c r="R116">
-        <v>5.69</v>
-      </c>
-      <c r="S116" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19">
-      <c r="A117" t="s">
-        <v>140</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I117" t="s">
-        <v>323</v>
-      </c>
-      <c r="M117">
-        <v>1</v>
-      </c>
-      <c r="N117" t="s">
-        <v>331</v>
-      </c>
-      <c r="O117" t="s">
-        <v>348</v>
-      </c>
-      <c r="P117" s="3">
-        <v>46212.55766203703</v>
-      </c>
-      <c r="Q117" s="3">
-        <v>46212.55766203703</v>
-      </c>
-      <c r="R117">
-        <v>5.69</v>
-      </c>
-      <c r="S117" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="118" spans="1:19">
-      <c r="A118" t="s">
-        <v>141</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="M118">
-        <v>1</v>
-      </c>
-      <c r="N118" t="s">
-        <v>331</v>
-      </c>
-      <c r="O118" t="s">
-        <v>348</v>
-      </c>
-      <c r="P118" s="3">
-        <v>46199.43622685185</v>
-      </c>
-      <c r="Q118" s="3">
-        <v>46199.43622685185</v>
-      </c>
-      <c r="R118">
-        <v>5.69</v>
-      </c>
-      <c r="S118" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="119" spans="1:19">
-      <c r="A119" t="s">
-        <v>142</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I119" t="s">
-        <v>319</v>
-      </c>
-      <c r="M119">
-        <v>1</v>
-      </c>
-      <c r="N119" t="s">
-        <v>331</v>
-      </c>
-      <c r="O119" t="s">
-        <v>348</v>
-      </c>
-      <c r="P119" s="3">
-        <v>46211.60422453703</v>
-      </c>
-      <c r="Q119" s="3">
-        <v>46211.60422453703</v>
-      </c>
-      <c r="R119">
-        <v>5.69</v>
-      </c>
-      <c r="S119" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19">
-      <c r="A120" t="s">
-        <v>143</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I120" t="s">
-        <v>319</v>
-      </c>
-      <c r="M120">
-        <v>1</v>
-      </c>
-      <c r="N120" t="s">
-        <v>331</v>
-      </c>
-      <c r="O120" t="s">
-        <v>348</v>
-      </c>
-      <c r="P120" s="3">
-        <v>46196.76916666667</v>
-      </c>
-      <c r="Q120" s="3">
-        <v>46196.76916666667</v>
-      </c>
-      <c r="R120">
-        <v>5.69</v>
-      </c>
-      <c r="S120" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19">
-      <c r="A121" t="s">
-        <v>144</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="M121">
-        <v>1</v>
-      </c>
-      <c r="N121" t="s">
-        <v>331</v>
-      </c>
-      <c r="O121" t="s">
-        <v>348</v>
-      </c>
-      <c r="P121" s="3">
-        <v>46317.34804398148</v>
-      </c>
-      <c r="Q121" s="3">
-        <v>46317.34804398148</v>
-      </c>
-      <c r="R121">
-        <v>5.69</v>
-      </c>
-      <c r="S121" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="122" spans="1:19">
-      <c r="A122" t="s">
-        <v>145</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="I122" t="s">
-        <v>320</v>
-      </c>
-      <c r="M122">
-        <v>1</v>
-      </c>
-      <c r="N122" t="s">
-        <v>331</v>
-      </c>
-      <c r="O122" t="s">
-        <v>348</v>
-      </c>
-      <c r="P122" s="3">
-        <v>46198.62644675926</v>
-      </c>
-      <c r="Q122" s="3">
-        <v>46198.62644675926</v>
-      </c>
-      <c r="R122">
-        <v>5.69</v>
-      </c>
-      <c r="S122" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="123" spans="1:19">
-      <c r="A123" t="s">
-        <v>146</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="M123">
-        <v>1</v>
-      </c>
-      <c r="N123" t="s">
-        <v>331</v>
-      </c>
-      <c r="O123" t="s">
-        <v>348</v>
-      </c>
-      <c r="P123" s="3">
-        <v>46313.72997685185</v>
-      </c>
-      <c r="Q123" s="3">
-        <v>46313.72997685185</v>
-      </c>
-      <c r="R123">
-        <v>5.69</v>
-      </c>
-      <c r="S123" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="124" spans="1:19">
-      <c r="A124" t="s">
-        <v>147</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="M124">
-        <v>2</v>
-      </c>
-      <c r="N124" t="s">
-        <v>333</v>
-      </c>
-      <c r="O124" t="s">
-        <v>350</v>
-      </c>
-      <c r="P124" s="3">
-        <v>46296.45002314815</v>
-      </c>
-      <c r="Q124" s="3">
-        <v>46296.45003472222</v>
-      </c>
-      <c r="R124">
-        <v>26.25</v>
-      </c>
-      <c r="S124" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="125" spans="1:19">
-      <c r="A125" t="s">
-        <v>148</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="M125">
-        <v>1</v>
-      </c>
-      <c r="N125" t="s">
-        <v>330</v>
-      </c>
-      <c r="O125" t="s">
-        <v>349</v>
-      </c>
-      <c r="P125" s="3">
-        <v>46317.5340625</v>
-      </c>
-      <c r="Q125" s="3">
-        <v>46317.5340625</v>
-      </c>
-      <c r="R125">
-        <v>6.04</v>
-      </c>
-      <c r="S125" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="126" spans="1:19">
-      <c r="A126" t="s">
-        <v>149</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I126" t="s">
-        <v>321</v>
-      </c>
-      <c r="M126">
-        <v>1</v>
-      </c>
-      <c r="N126" t="s">
-        <v>331</v>
-      </c>
-      <c r="O126" t="s">
-        <v>348</v>
-      </c>
-      <c r="P126" s="3">
-        <v>46220.44594907408</v>
-      </c>
-      <c r="Q126" s="3">
-        <v>46220.44594907408</v>
-      </c>
-      <c r="R126">
-        <v>5.69</v>
-      </c>
-      <c r="S126" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="127" spans="1:19">
-      <c r="A127" t="s">
-        <v>150</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="M127">
-        <v>1</v>
-      </c>
-      <c r="N127" t="s">
-        <v>329</v>
-      </c>
-      <c r="O127" t="s">
-        <v>348</v>
-      </c>
-      <c r="P127" s="3">
-        <v>46317.34804398148</v>
-      </c>
-      <c r="Q127" s="3">
-        <v>46317.34804398148</v>
-      </c>
-      <c r="R127">
-        <v>5.64</v>
-      </c>
-      <c r="S127" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="128" spans="1:19">
-      <c r="A128" t="s">
-        <v>151</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="M128">
-        <v>1</v>
-      </c>
-      <c r="N128" t="s">
-        <v>334</v>
-      </c>
-      <c r="O128" t="s">
-        <v>349</v>
-      </c>
-      <c r="P128" s="3">
-        <v>46301.52780092593</v>
-      </c>
-      <c r="Q128" s="3">
-        <v>46301.52780092593</v>
-      </c>
-      <c r="R128">
-        <v>6.53</v>
-      </c>
-      <c r="S128" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="129" spans="1:25">
-      <c r="A129" t="s">
-        <v>152</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="I129" t="s">
-        <v>320</v>
-      </c>
-      <c r="M129">
-        <v>1</v>
-      </c>
-      <c r="N129" t="s">
-        <v>331</v>
-      </c>
-      <c r="O129" t="s">
-        <v>348</v>
-      </c>
-      <c r="P129" s="3">
-        <v>46221.54171296296</v>
-      </c>
-      <c r="Q129" s="3">
-        <v>46221.54171296296</v>
-      </c>
-      <c r="R129">
-        <v>5.69</v>
-      </c>
-      <c r="S129" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="130" spans="1:25">
-      <c r="A130" t="s">
-        <v>153</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I130" t="s">
-        <v>324</v>
-      </c>
-      <c r="M130">
-        <v>1</v>
-      </c>
-      <c r="N130" t="s">
-        <v>331</v>
-      </c>
-      <c r="O130" t="s">
-        <v>348</v>
-      </c>
-      <c r="P130" s="3">
-        <v>45993.6759375</v>
-      </c>
-      <c r="Q130" s="3">
-        <v>45993.6759375</v>
-      </c>
-      <c r="R130">
-        <v>9.31</v>
-      </c>
-      <c r="S130" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="131" spans="1:25">
-      <c r="A131" t="s">
-        <v>154</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="M131">
-        <v>1</v>
-      </c>
-      <c r="N131" t="s">
-        <v>331</v>
-      </c>
-      <c r="O131" t="s">
-        <v>349</v>
-      </c>
-      <c r="P131" s="3">
-        <v>46317.6072337963</v>
-      </c>
-      <c r="Q131" s="3">
-        <v>46317.6072337963</v>
-      </c>
-      <c r="R131">
-        <v>5.69</v>
-      </c>
-      <c r="S131" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="132" spans="1:25">
-      <c r="A132" t="s">
-        <v>155</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I132" t="s">
-        <v>324</v>
-      </c>
-      <c r="M132">
-        <v>1</v>
-      </c>
-      <c r="N132" t="s">
-        <v>329</v>
-      </c>
-      <c r="O132" t="s">
-        <v>349</v>
-      </c>
-      <c r="P132" s="3">
-        <v>46178.61515046296</v>
-      </c>
-      <c r="Q132" s="3">
-        <v>46178.61515046296</v>
-      </c>
-      <c r="R132">
-        <v>12.41</v>
-      </c>
-      <c r="S132" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="133" spans="1:25">
-      <c r="A133" t="s">
-        <v>156</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="I133" t="s">
-        <v>319</v>
-      </c>
-      <c r="M133">
-        <v>1</v>
-      </c>
-      <c r="N133" t="s">
-        <v>331</v>
-      </c>
-      <c r="O133" t="s">
-        <v>348</v>
-      </c>
-      <c r="P133" s="3">
-        <v>45981.84152777777</v>
-      </c>
-      <c r="Q133" s="3">
-        <v>45981.84152777777</v>
-      </c>
-      <c r="R133">
-        <v>9.31</v>
-      </c>
-      <c r="S133" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="134" spans="1:25">
-      <c r="A134" t="s">
-        <v>157</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="I134" t="s">
-        <v>321</v>
-      </c>
-      <c r="M134">
-        <v>1</v>
-      </c>
-      <c r="N134" t="s">
-        <v>331</v>
-      </c>
-      <c r="O134" t="s">
-        <v>348</v>
-      </c>
-      <c r="P134" s="3">
-        <v>45965.5908449074</v>
-      </c>
-      <c r="Q134" s="3">
-        <v>45965.5908449074</v>
-      </c>
-      <c r="R134">
-        <v>5.69</v>
-      </c>
-      <c r="S134" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="135" spans="1:25">
-      <c r="A135" t="s">
-        <v>158</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="I135" t="s">
-        <v>324</v>
-      </c>
-      <c r="M135">
-        <v>1</v>
-      </c>
-      <c r="N135" t="s">
-        <v>331</v>
-      </c>
-      <c r="O135" t="s">
-        <v>348</v>
-      </c>
-      <c r="P135" s="3">
-        <v>46206.37778935185</v>
-      </c>
-      <c r="Q135" s="3">
-        <v>46206.37778935185</v>
-      </c>
-      <c r="R135">
-        <v>5.69</v>
-      </c>
-      <c r="S135" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="136" spans="1:25">
-      <c r="A136" t="s">
-        <v>159</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I136" t="s">
-        <v>323</v>
-      </c>
-      <c r="M136">
-        <v>1</v>
-      </c>
-      <c r="N136" t="s">
-        <v>331</v>
-      </c>
-      <c r="O136" t="s">
-        <v>348</v>
-      </c>
-      <c r="P136" s="3">
-        <v>46220.91548611111</v>
-      </c>
-      <c r="Q136" s="3">
-        <v>46220.91548611111</v>
-      </c>
-      <c r="R136">
-        <v>5.69</v>
-      </c>
-      <c r="S136" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="137" spans="1:25">
-      <c r="A137" t="s">
-        <v>160</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="M137">
-        <v>1</v>
-      </c>
-      <c r="N137" t="s">
-        <v>331</v>
-      </c>
-      <c r="O137" t="s">
-        <v>349</v>
-      </c>
-      <c r="P137" s="3">
-        <v>46306.55003472222</v>
-      </c>
-      <c r="Q137" s="3">
-        <v>46306.55003472222</v>
-      </c>
-      <c r="R137">
-        <v>8.58</v>
-      </c>
-      <c r="S137" t="s">
-        <v>352</v>
-      </c>
-      <c r="T137">
-        <v>2</v>
-      </c>
-      <c r="U137">
-        <v>59.99</v>
-      </c>
-      <c r="V137">
-        <v>1</v>
-      </c>
-      <c r="W137">
-        <v>946</v>
-      </c>
-      <c r="X137" s="3">
-        <v>46294</v>
-      </c>
-      <c r="Y137">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="138" spans="1:25">
-      <c r="A138" t="s">
-        <v>161</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M138">
-        <v>1</v>
-      </c>
-      <c r="N138" t="s">
-        <v>331</v>
-      </c>
-      <c r="O138" t="s">
-        <v>349</v>
-      </c>
-      <c r="P138" s="3">
-        <v>46312.95512731482</v>
-      </c>
-      <c r="Q138" s="3">
-        <v>46312.95512731482</v>
-      </c>
-      <c r="R138">
-        <v>8.58</v>
-      </c>
-      <c r="S138" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="139" spans="1:25">
-      <c r="A139" t="s">
-        <v>162</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="I139" t="s">
-        <v>319</v>
-      </c>
-      <c r="M139">
-        <v>1</v>
-      </c>
-      <c r="N139" t="s">
-        <v>331</v>
-      </c>
-      <c r="O139" t="s">
-        <v>348</v>
-      </c>
-      <c r="P139" s="3">
-        <v>45939.98240740741</v>
-      </c>
-      <c r="Q139" s="3">
-        <v>45939.98240740741</v>
-      </c>
-      <c r="R139">
-        <v>9.31</v>
-      </c>
-      <c r="S139" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="140" spans="1:25">
-      <c r="A140" t="s">
-        <v>163</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="I140" t="s">
-        <v>320</v>
-      </c>
-      <c r="M140">
-        <v>1</v>
-      </c>
-      <c r="N140" t="s">
-        <v>331</v>
-      </c>
-      <c r="O140" t="s">
-        <v>348</v>
-      </c>
-      <c r="P140" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="Q140" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="R140">
-        <v>5.69</v>
-      </c>
-      <c r="S140" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="141" spans="1:25">
-      <c r="A141" t="s">
-        <v>164</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="M141">
-        <v>1</v>
-      </c>
-      <c r="N141" t="s">
-        <v>331</v>
-      </c>
-      <c r="O141" t="s">
-        <v>348</v>
-      </c>
-      <c r="P141" s="3">
-        <v>46317.35082175926</v>
-      </c>
-      <c r="Q141" s="3">
-        <v>46317.35082175926</v>
-      </c>
-      <c r="R141">
-        <v>5.69</v>
-      </c>
-      <c r="S141" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="142" spans="1:25">
-      <c r="A142" t="s">
-        <v>165</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="I142" t="s">
-        <v>324</v>
-      </c>
-      <c r="M142">
-        <v>1</v>
-      </c>
-      <c r="N142" t="s">
-        <v>331</v>
-      </c>
-      <c r="O142" t="s">
-        <v>348</v>
-      </c>
-      <c r="P142" s="3">
-        <v>45990.94167824074</v>
-      </c>
-      <c r="Q142" s="3">
-        <v>45990.94167824074</v>
-      </c>
-      <c r="R142">
-        <v>5.69</v>
-      </c>
-      <c r="S142" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="143" spans="1:25">
-      <c r="A143" t="s">
-        <v>166</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="I143" t="s">
-        <v>323</v>
-      </c>
-      <c r="M143">
-        <v>1</v>
-      </c>
-      <c r="N143" t="s">
-        <v>331</v>
-      </c>
-      <c r="O143" t="s">
-        <v>348</v>
-      </c>
-      <c r="P143" s="3">
-        <v>45913.74726851852</v>
-      </c>
-      <c r="Q143" s="3">
-        <v>45913.74726851852</v>
-      </c>
-      <c r="R143">
-        <v>5.69</v>
-      </c>
-      <c r="S143" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="144" spans="1:25">
-      <c r="A144" t="s">
-        <v>167</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="M144">
-        <v>1</v>
-      </c>
-      <c r="N144" t="s">
-        <v>331</v>
-      </c>
-      <c r="O144" t="s">
-        <v>348</v>
-      </c>
-      <c r="P144" s="3">
-        <v>46314.79108796296</v>
-      </c>
-      <c r="Q144" s="3">
-        <v>46314.79108796296</v>
-      </c>
-      <c r="R144">
-        <v>5.69</v>
-      </c>
-      <c r="S144" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="145" spans="1:19">
-      <c r="A145" t="s">
-        <v>168</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="I145" t="s">
-        <v>321</v>
-      </c>
-      <c r="M145">
-        <v>1</v>
-      </c>
-      <c r="N145" t="s">
-        <v>331</v>
-      </c>
-      <c r="O145" t="s">
-        <v>348</v>
-      </c>
-      <c r="P145" s="3">
-        <v>46221.60350694445</v>
-      </c>
-      <c r="Q145" s="3">
-        <v>46221.60350694445</v>
-      </c>
-      <c r="R145">
-        <v>5.69</v>
-      </c>
-      <c r="S145" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="146" spans="1:19">
-      <c r="A146" t="s">
-        <v>169</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="I146" t="s">
-        <v>323</v>
-      </c>
-      <c r="M146">
-        <v>2</v>
-      </c>
-      <c r="N146" t="s">
-        <v>331</v>
-      </c>
-      <c r="O146" t="s">
-        <v>348</v>
-      </c>
-      <c r="P146" s="3">
-        <v>46196.65561342592</v>
-      </c>
-      <c r="Q146" s="3">
-        <v>46224.32857638889</v>
-      </c>
-      <c r="R146">
-        <v>11.38</v>
-      </c>
-      <c r="S146" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -6328,49 +4787,6 @@
     <hyperlink ref="B101" r:id="rId100"/>
     <hyperlink ref="B102" r:id="rId101"/>
     <hyperlink ref="B103" r:id="rId102"/>
-    <hyperlink ref="B104" r:id="rId103"/>
-    <hyperlink ref="B105" r:id="rId104"/>
-    <hyperlink ref="B106" r:id="rId105"/>
-    <hyperlink ref="B107" r:id="rId106"/>
-    <hyperlink ref="B108" r:id="rId107"/>
-    <hyperlink ref="B109" r:id="rId108"/>
-    <hyperlink ref="B110" r:id="rId109"/>
-    <hyperlink ref="B111" r:id="rId110"/>
-    <hyperlink ref="B112" r:id="rId111"/>
-    <hyperlink ref="B113" r:id="rId112"/>
-    <hyperlink ref="B114" r:id="rId113"/>
-    <hyperlink ref="B115" r:id="rId114"/>
-    <hyperlink ref="B116" r:id="rId115"/>
-    <hyperlink ref="B117" r:id="rId116"/>
-    <hyperlink ref="B118" r:id="rId117"/>
-    <hyperlink ref="B119" r:id="rId118"/>
-    <hyperlink ref="B120" r:id="rId119"/>
-    <hyperlink ref="B121" r:id="rId120"/>
-    <hyperlink ref="B122" r:id="rId121"/>
-    <hyperlink ref="B123" r:id="rId122"/>
-    <hyperlink ref="B124" r:id="rId123"/>
-    <hyperlink ref="B125" r:id="rId124"/>
-    <hyperlink ref="B126" r:id="rId125"/>
-    <hyperlink ref="B127" r:id="rId126"/>
-    <hyperlink ref="B128" r:id="rId127"/>
-    <hyperlink ref="B129" r:id="rId128"/>
-    <hyperlink ref="B130" r:id="rId129"/>
-    <hyperlink ref="B131" r:id="rId130"/>
-    <hyperlink ref="B132" r:id="rId131"/>
-    <hyperlink ref="B133" r:id="rId132"/>
-    <hyperlink ref="B134" r:id="rId133"/>
-    <hyperlink ref="B135" r:id="rId134"/>
-    <hyperlink ref="B136" r:id="rId135"/>
-    <hyperlink ref="B137" r:id="rId136"/>
-    <hyperlink ref="B138" r:id="rId137"/>
-    <hyperlink ref="B139" r:id="rId138"/>
-    <hyperlink ref="B140" r:id="rId139"/>
-    <hyperlink ref="B141" r:id="rId140"/>
-    <hyperlink ref="B142" r:id="rId141"/>
-    <hyperlink ref="B143" r:id="rId142"/>
-    <hyperlink ref="B144" r:id="rId143"/>
-    <hyperlink ref="B145" r:id="rId144"/>
-    <hyperlink ref="B146" r:id="rId145"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="234">
   <si>
     <t>handle</t>
   </si>
@@ -289,9 +289,6 @@
     <t>softirontouches</t>
   </si>
   <si>
-    <t>sophiealicemumoffour</t>
-  </si>
-  <si>
     <t>stephanie.cameron4</t>
   </si>
   <si>
@@ -307,9 +304,6 @@
     <t>tantantiktokshop</t>
   </si>
   <si>
-    <t>tanyasbargainfinds</t>
-  </si>
-  <si>
     <t>the.witchy.wander</t>
   </si>
   <si>
@@ -361,9 +355,6 @@
     <t>zaheersheikh786</t>
   </si>
   <si>
-    <t>zahra39220</t>
-  </si>
-  <si>
     <t>zembii</t>
   </si>
   <si>
@@ -568,9 +559,6 @@
     <t>https://www.tiktok.com/@softirontouches</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@sophiealicemumoffour</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@stephanie.cameron4</t>
   </si>
   <si>
@@ -586,9 +574,6 @@
     <t>https://www.tiktok.com/@tantantiktokshop</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@tanyasbargainfinds</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@the.witchy.wander</t>
   </si>
   <si>
@@ -638,9 +623,6 @@
   </si>
   <si>
     <t>https://www.tiktok.com/@zaheersheikh786</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@zahra39220</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@zembii</t>
@@ -1108,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y94"/>
+  <dimension ref="A1:Y91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1193,19 +1175,19 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="O2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P2" s="3">
         <v>46028.62637731482</v>
@@ -1217,7 +1199,7 @@
         <v>5.64</v>
       </c>
       <c r="S2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1225,19 +1207,19 @@
         <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P3" s="3">
         <v>45998.88378472222</v>
@@ -1249,7 +1231,7 @@
         <v>9.31</v>
       </c>
       <c r="S3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1257,19 +1239,19 @@
         <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P4" s="3">
         <v>45986.77690972222</v>
@@ -1281,7 +1263,7 @@
         <v>5.69</v>
       </c>
       <c r="S4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1289,19 +1271,19 @@
         <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I5" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O5" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P5" s="3">
         <v>45911.17809027778</v>
@@ -1313,7 +1295,7 @@
         <v>9.31</v>
       </c>
       <c r="S5" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1321,40 +1303,40 @@
         <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H6" t="s">
+        <v>208</v>
+      </c>
+      <c r="I6" t="s">
         <v>211</v>
       </c>
-      <c r="F6" t="s">
-        <v>212</v>
-      </c>
-      <c r="G6" t="s">
-        <v>213</v>
-      </c>
-      <c r="H6" t="s">
-        <v>214</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>217</v>
       </c>
-      <c r="J6" t="s">
-        <v>223</v>
-      </c>
       <c r="K6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="L6" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="M6">
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O6" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P6" s="3">
         <v>45989.98658564815</v>
@@ -1366,7 +1348,7 @@
         <v>9.31</v>
       </c>
       <c r="S6" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1374,19 +1356,19 @@
         <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I7" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O7" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P7" s="3">
         <v>45974.46635416667</v>
@@ -1398,7 +1380,7 @@
         <v>9.31</v>
       </c>
       <c r="S7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1406,19 +1388,19 @@
         <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I8" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O8" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P8" s="3">
         <v>45967.48326388889</v>
@@ -1430,7 +1412,7 @@
         <v>5.69</v>
       </c>
       <c r="S8" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1438,19 +1420,19 @@
         <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I9" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O9" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P9" s="3">
         <v>46176.59099537037</v>
@@ -1462,7 +1444,7 @@
         <v>5.69</v>
       </c>
       <c r="S9" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1470,19 +1452,19 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I10" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O10" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P10" s="3">
         <v>45996.23743055556</v>
@@ -1494,7 +1476,7 @@
         <v>12.46</v>
       </c>
       <c r="S10" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1502,19 +1484,19 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I11" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O11" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P11" s="3">
         <v>46209.78530092593</v>
@@ -1526,7 +1508,7 @@
         <v>5.69</v>
       </c>
       <c r="S11" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1534,19 +1516,19 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I12" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O12" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P12" s="3">
         <v>46092.52502314815</v>
@@ -1558,7 +1540,7 @@
         <v>5.69</v>
       </c>
       <c r="S12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1566,16 +1548,16 @@
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="M13">
         <v>2</v>
       </c>
       <c r="N13" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="O13" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="P13" s="3">
         <v>46296.61392361111</v>
@@ -1587,7 +1569,7 @@
         <v>26.83</v>
       </c>
       <c r="S13" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="T13">
         <v>4</v>
@@ -1599,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="W13">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="X13" s="3">
         <v>46303</v>
@@ -1613,16 +1595,16 @@
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M14">
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O14" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P14" s="3">
         <v>46196.83574074074</v>
@@ -1634,7 +1616,7 @@
         <v>5.69</v>
       </c>
       <c r="S14" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1642,19 +1624,19 @@
         <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I15" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M15">
         <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O15" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P15" s="3">
         <v>46198.6271412037</v>
@@ -1666,7 +1648,7 @@
         <v>5.69</v>
       </c>
       <c r="S15" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1674,19 +1656,19 @@
         <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I16" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M16">
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="O16" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="P16" s="3">
         <v>45840.45584490741</v>
@@ -1698,7 +1680,7 @@
         <v>17.02</v>
       </c>
       <c r="S16" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1706,19 +1688,19 @@
         <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I17" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O17" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P17" s="3">
         <v>46198.6271412037</v>
@@ -1730,7 +1712,7 @@
         <v>5.69</v>
       </c>
       <c r="S17" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1738,16 +1720,16 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O18" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P18" s="3">
         <v>46309.55629629629</v>
@@ -1759,7 +1741,7 @@
         <v>5.69</v>
       </c>
       <c r="S18" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="T18">
         <v>1</v>
@@ -1785,16 +1767,16 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O19" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P19" s="3">
         <v>46252.93552083334</v>
@@ -1806,7 +1788,7 @@
         <v>5.69</v>
       </c>
       <c r="S19" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1814,19 +1796,19 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I20" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M20">
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O20" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P20" s="3">
         <v>46062.02391203704</v>
@@ -1838,7 +1820,7 @@
         <v>12.46</v>
       </c>
       <c r="S20" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -1846,19 +1828,19 @@
         <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I21" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M21">
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O21" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P21" s="3">
         <v>45903.0252662037</v>
@@ -1870,7 +1852,7 @@
         <v>9.31</v>
       </c>
       <c r="S21" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -1878,19 +1860,19 @@
         <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I22" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O22" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P22" s="3">
         <v>46178.95283564815</v>
@@ -1902,7 +1884,7 @@
         <v>5.69</v>
       </c>
       <c r="S22" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -1910,19 +1892,19 @@
         <v>46</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I23" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M23">
         <v>7</v>
       </c>
       <c r="N23" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="O23" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="P23" s="3">
         <v>46181.5243287037</v>
@@ -1934,7 +1916,7 @@
         <v>60.34</v>
       </c>
       <c r="S23" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -1942,16 +1924,16 @@
         <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="M24">
         <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O24" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P24" s="3">
         <v>46053.63612268519</v>
@@ -1963,7 +1945,7 @@
         <v>5.69</v>
       </c>
       <c r="S24" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -1971,19 +1953,19 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I25" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M25">
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O25" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P25" s="3">
         <v>46008.62306712963</v>
@@ -1995,7 +1977,7 @@
         <v>5.69</v>
       </c>
       <c r="S25" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2003,19 +1985,19 @@
         <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I26" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O26" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P26" s="3">
         <v>46152.90292824074</v>
@@ -2027,7 +2009,7 @@
         <v>5.69</v>
       </c>
       <c r="S26" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2035,19 +2017,19 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I27" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O27" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P27" s="3">
         <v>45953.84554398148</v>
@@ -2059,7 +2041,7 @@
         <v>12.46</v>
       </c>
       <c r="S27" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2067,16 +2049,16 @@
         <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="M28">
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O28" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P28" s="3">
         <v>46310.5215625</v>
@@ -2088,10 +2070,10 @@
         <v>5.69</v>
       </c>
       <c r="S28" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -2100,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="W28">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="X28" s="3">
         <v>46313</v>
@@ -2114,19 +2096,19 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I29" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M29">
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O29" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P29" s="3">
         <v>46111.64181712963</v>
@@ -2138,7 +2120,7 @@
         <v>12.46</v>
       </c>
       <c r="S29" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2146,16 +2128,16 @@
         <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M30">
         <v>1</v>
       </c>
       <c r="N30" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="O30" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P30" s="3">
         <v>46296.45141203704</v>
@@ -2167,7 +2149,7 @@
         <v>5.64</v>
       </c>
       <c r="S30" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="T30">
         <v>1</v>
@@ -2193,19 +2175,19 @@
         <v>54</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I31" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O31" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P31" s="3">
         <v>46210.48171296297</v>
@@ -2217,7 +2199,7 @@
         <v>5.69</v>
       </c>
       <c r="S31" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2225,16 +2207,16 @@
         <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M32">
         <v>2</v>
       </c>
       <c r="N32" t="s">
+        <v>224</v>
+      </c>
+      <c r="O32" t="s">
         <v>230</v>
-      </c>
-      <c r="O32" t="s">
-        <v>236</v>
       </c>
       <c r="P32" s="3">
         <v>46280.49378472222</v>
@@ -2246,7 +2228,7 @@
         <v>10.55</v>
       </c>
       <c r="S32" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="T32">
         <v>4</v>
@@ -2272,19 +2254,19 @@
         <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I33" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
       <c r="N33" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O33" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P33" s="3">
         <v>46225.98408564815</v>
@@ -2296,7 +2278,7 @@
         <v>5.69</v>
       </c>
       <c r="S33" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -2304,19 +2286,19 @@
         <v>57</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I34" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O34" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P34" s="3">
         <v>46106.56184027778</v>
@@ -2328,7 +2310,7 @@
         <v>5.69</v>
       </c>
       <c r="S34" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -2336,16 +2318,16 @@
         <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="M35">
         <v>1</v>
       </c>
       <c r="N35" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O35" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="P35" s="3">
         <v>46313.79324074074</v>
@@ -2357,7 +2339,7 @@
         <v>8.58</v>
       </c>
       <c r="S35" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -2365,19 +2347,19 @@
         <v>59</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I36" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M36">
         <v>1</v>
       </c>
       <c r="N36" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O36" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P36" s="3">
         <v>46196.84141203704</v>
@@ -2389,7 +2371,7 @@
         <v>5.69</v>
       </c>
       <c r="S36" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -2397,16 +2379,16 @@
         <v>60</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="M37">
         <v>2</v>
       </c>
       <c r="N37" t="s">
+        <v>225</v>
+      </c>
+      <c r="O37" t="s">
         <v>231</v>
-      </c>
-      <c r="O37" t="s">
-        <v>237</v>
       </c>
       <c r="P37" s="3">
         <v>46312.81608796296</v>
@@ -2418,7 +2400,7 @@
         <v>14.62</v>
       </c>
       <c r="S37" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -2426,19 +2408,19 @@
         <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I38" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M38">
         <v>1</v>
       </c>
       <c r="N38" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O38" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P38" s="3">
         <v>46073.66815972222</v>
@@ -2450,7 +2432,7 @@
         <v>12.46</v>
       </c>
       <c r="S38" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -2458,19 +2440,19 @@
         <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I39" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O39" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P39" s="3">
         <v>46245.82854166667</v>
@@ -2482,7 +2464,7 @@
         <v>5.69</v>
       </c>
       <c r="S39" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="T39">
         <v>1</v>
@@ -2508,19 +2490,19 @@
         <v>63</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I40" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M40">
         <v>1</v>
       </c>
       <c r="N40" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O40" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P40" s="3">
         <v>46050.93159722222</v>
@@ -2532,7 +2514,7 @@
         <v>12.46</v>
       </c>
       <c r="S40" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -2540,19 +2522,19 @@
         <v>64</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I41" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M41">
         <v>1</v>
       </c>
       <c r="N41" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O41" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P41" s="3">
         <v>45965.93854166667</v>
@@ -2564,7 +2546,7 @@
         <v>5.69</v>
       </c>
       <c r="S41" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -2572,19 +2554,19 @@
         <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I42" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M42">
         <v>1</v>
       </c>
       <c r="N42" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O42" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P42" s="3">
         <v>45992.89240740741</v>
@@ -2596,7 +2578,7 @@
         <v>5.69</v>
       </c>
       <c r="S42" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -2604,19 +2586,19 @@
         <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I43" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O43" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P43" s="3">
         <v>45944.90217592593</v>
@@ -2628,7 +2610,7 @@
         <v>9.31</v>
       </c>
       <c r="S43" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -2636,19 +2618,19 @@
         <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I44" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M44">
         <v>1</v>
       </c>
       <c r="N44" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O44" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P44" s="3">
         <v>46105.47987268519</v>
@@ -2660,7 +2642,7 @@
         <v>5.69</v>
       </c>
       <c r="S44" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -2668,19 +2650,19 @@
         <v>68</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I45" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M45">
         <v>1</v>
       </c>
       <c r="N45" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O45" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P45" s="3">
         <v>46210.50420138889</v>
@@ -2692,7 +2674,7 @@
         <v>5.69</v>
       </c>
       <c r="S45" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -2700,16 +2682,16 @@
         <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
       <c r="N46" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O46" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P46" s="3">
         <v>46052.56390046296</v>
@@ -2721,7 +2703,7 @@
         <v>5.69</v>
       </c>
       <c r="S46" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -2729,19 +2711,19 @@
         <v>70</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I47" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O47" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P47" s="3">
         <v>46091.88748842593</v>
@@ -2753,7 +2735,7 @@
         <v>9.31</v>
       </c>
       <c r="S47" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:25">
@@ -2761,19 +2743,19 @@
         <v>71</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I48" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M48">
         <v>1</v>
       </c>
       <c r="N48" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O48" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P48" s="3">
         <v>45978.69265046297</v>
@@ -2785,7 +2767,7 @@
         <v>12.46</v>
       </c>
       <c r="S48" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:25">
@@ -2793,19 +2775,19 @@
         <v>72</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I49" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M49">
         <v>1</v>
       </c>
       <c r="N49" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O49" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P49" s="3">
         <v>45919.81163194445</v>
@@ -2817,7 +2799,7 @@
         <v>5.69</v>
       </c>
       <c r="S49" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:25">
@@ -2825,16 +2807,16 @@
         <v>73</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="M50">
         <v>3</v>
       </c>
       <c r="N50" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="O50" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="P50" s="3">
         <v>46313.77442129629</v>
@@ -2846,7 +2828,25 @@
         <v>30.1</v>
       </c>
       <c r="S50" t="s">
-        <v>238</v>
+        <v>233</v>
+      </c>
+      <c r="T50">
+        <v>1</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>5</v>
+      </c>
+      <c r="X50" s="3">
+        <v>46320</v>
+      </c>
+      <c r="Y50">
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:25">
@@ -2854,16 +2854,16 @@
         <v>74</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="M51">
         <v>1</v>
       </c>
       <c r="N51" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="O51" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="P51" s="3">
         <v>46314.50759259259</v>
@@ -2875,7 +2875,7 @@
         <v>6.04</v>
       </c>
       <c r="S51" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="T51">
         <v>3</v>
@@ -2887,7 +2887,7 @@
         <v>2</v>
       </c>
       <c r="W51">
-        <v>491</v>
+        <v>537</v>
       </c>
       <c r="X51" s="3">
         <v>46313</v>
@@ -2901,19 +2901,19 @@
         <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I52" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M52">
         <v>1</v>
       </c>
       <c r="N52" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O52" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P52" s="3">
         <v>46051.04447916667</v>
@@ -2925,7 +2925,7 @@
         <v>5.69</v>
       </c>
       <c r="S52" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:25">
@@ -2933,19 +2933,19 @@
         <v>76</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I53" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O53" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P53" s="3">
         <v>45891.71650462963</v>
@@ -2957,7 +2957,7 @@
         <v>9.31</v>
       </c>
       <c r="S53" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:25">
@@ -2965,19 +2965,19 @@
         <v>77</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I54" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M54">
         <v>1</v>
       </c>
       <c r="N54" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O54" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P54" s="3">
         <v>46211.60210648148</v>
@@ -2989,7 +2989,7 @@
         <v>5.69</v>
       </c>
       <c r="S54" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:25">
@@ -2997,19 +2997,19 @@
         <v>78</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I55" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O55" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P55" s="3">
         <v>46167.36722222222</v>
@@ -3021,7 +3021,7 @@
         <v>5.69</v>
       </c>
       <c r="S55" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:25">
@@ -3029,19 +3029,19 @@
         <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I56" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M56">
         <v>1</v>
       </c>
       <c r="N56" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O56" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P56" s="3">
         <v>46050.54237268519</v>
@@ -3053,7 +3053,7 @@
         <v>5.69</v>
       </c>
       <c r="S56" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" spans="1:25">
@@ -3061,19 +3061,19 @@
         <v>80</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I57" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M57">
         <v>1</v>
       </c>
       <c r="N57" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O57" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P57" s="3">
         <v>45957.49894675926</v>
@@ -3085,7 +3085,7 @@
         <v>5.69</v>
       </c>
       <c r="S57" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:25">
@@ -3093,19 +3093,19 @@
         <v>81</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I58" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M58">
         <v>1</v>
       </c>
       <c r="N58" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O58" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P58" s="3">
         <v>46196.62574074074</v>
@@ -3117,7 +3117,7 @@
         <v>5.69</v>
       </c>
       <c r="S58" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:25">
@@ -3125,19 +3125,19 @@
         <v>82</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I59" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M59">
         <v>1</v>
       </c>
       <c r="N59" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O59" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P59" s="3">
         <v>45959.6512037037</v>
@@ -3149,7 +3149,7 @@
         <v>9.31</v>
       </c>
       <c r="S59" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="60" spans="1:25">
@@ -3157,19 +3157,19 @@
         <v>83</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I60" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M60">
         <v>1</v>
       </c>
       <c r="N60" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O60" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P60" s="3">
         <v>45973.56506944444</v>
@@ -3181,7 +3181,7 @@
         <v>9.31</v>
       </c>
       <c r="S60" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="61" spans="1:25">
@@ -3189,16 +3189,16 @@
         <v>84</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M61">
         <v>1</v>
       </c>
       <c r="N61" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="O61" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="P61" s="3">
         <v>46313.49944444445</v>
@@ -3210,7 +3210,7 @@
         <v>6.04</v>
       </c>
       <c r="S61" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="62" spans="1:25">
@@ -3218,19 +3218,19 @@
         <v>85</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I62" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M62">
         <v>1</v>
       </c>
       <c r="N62" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O62" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P62" s="3">
         <v>46191.82362268519</v>
@@ -3242,7 +3242,7 @@
         <v>5.69</v>
       </c>
       <c r="S62" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63" spans="1:25">
@@ -3250,16 +3250,16 @@
         <v>86</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M63">
         <v>2</v>
       </c>
       <c r="N63" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="O63" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="P63" s="3">
         <v>46286.62572916667</v>
@@ -3271,7 +3271,7 @@
         <v>14.22</v>
       </c>
       <c r="S63" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="T63">
         <v>2</v>
@@ -3297,16 +3297,16 @@
         <v>87</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M64">
         <v>1</v>
       </c>
       <c r="N64" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O64" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P64" s="3">
         <v>46304.50560185185</v>
@@ -3318,7 +3318,7 @@
         <v>5.69</v>
       </c>
       <c r="S64" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:25">
@@ -3326,16 +3326,16 @@
         <v>88</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="M65">
         <v>1</v>
       </c>
       <c r="N65" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O65" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P65" s="3">
         <v>46027.60903935185</v>
@@ -3347,7 +3347,7 @@
         <v>5.69</v>
       </c>
       <c r="S65" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66" spans="1:25">
@@ -3355,16 +3355,16 @@
         <v>89</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M66">
         <v>1</v>
       </c>
       <c r="N66" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O66" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P66" s="3">
         <v>46280.49518518519</v>
@@ -3376,7 +3376,7 @@
         <v>5.69</v>
       </c>
       <c r="S66" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="T66">
         <v>1</v>
@@ -3402,16 +3402,16 @@
         <v>90</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M67">
         <v>1</v>
       </c>
       <c r="N67" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O67" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P67" s="3">
         <v>46311.94667824074</v>
@@ -3423,7 +3423,7 @@
         <v>5.69</v>
       </c>
       <c r="S67" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="1:25">
@@ -3431,28 +3431,46 @@
         <v>91</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M68">
         <v>1</v>
       </c>
       <c r="N68" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="O68" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="P68" s="3">
-        <v>46318.90003472222</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="Q68" s="3">
-        <v>46318.90003472222</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="R68">
-        <v>6.53</v>
+        <v>8.58</v>
       </c>
       <c r="S68" t="s">
-        <v>238</v>
+        <v>233</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>8</v>
+      </c>
+      <c r="X68" s="3">
+        <v>46317</v>
+      </c>
+      <c r="Y68">
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:25">
@@ -3460,46 +3478,31 @@
         <v>92</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
+      </c>
+      <c r="I69" t="s">
+        <v>216</v>
       </c>
       <c r="M69">
         <v>1</v>
       </c>
       <c r="N69" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O69" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="P69" s="3">
-        <v>46313.79785879629</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q69" s="3">
-        <v>46313.79785879629</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R69">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S69" t="s">
-        <v>239</v>
-      </c>
-      <c r="T69">
-        <v>1</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>8</v>
-      </c>
-      <c r="X69" s="3">
-        <v>46317</v>
-      </c>
-      <c r="Y69">
-        <v>3</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:25">
@@ -3507,31 +3510,31 @@
         <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I70" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="M70">
         <v>1</v>
       </c>
       <c r="N70" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O70" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P70" s="3">
-        <v>46198.62712962963</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="Q70" s="3">
-        <v>46198.62712962963</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="R70">
         <v>5.69</v>
       </c>
       <c r="S70" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:25">
@@ -3539,31 +3542,28 @@
         <v>94</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I71" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O71" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P71" s="3">
-        <v>46212.55766203703</v>
+        <v>46199.43622685185</v>
       </c>
       <c r="Q71" s="3">
-        <v>46212.55766203703</v>
+        <v>46199.43622685185</v>
       </c>
       <c r="R71">
         <v>5.69</v>
       </c>
       <c r="S71" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="72" spans="1:25">
@@ -3571,28 +3571,31 @@
         <v>95</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
+      </c>
+      <c r="I72" t="s">
+        <v>209</v>
       </c>
       <c r="M72">
         <v>1</v>
       </c>
       <c r="N72" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O72" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P72" s="3">
-        <v>46199.43622685185</v>
+        <v>46211.60422453703</v>
       </c>
       <c r="Q72" s="3">
-        <v>46199.43622685185</v>
+        <v>46211.60422453703</v>
       </c>
       <c r="R72">
         <v>5.69</v>
       </c>
       <c r="S72" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="73" spans="1:25">
@@ -3600,31 +3603,31 @@
         <v>96</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I73" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M73">
         <v>1</v>
       </c>
       <c r="N73" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O73" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P73" s="3">
-        <v>46211.60422453703</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="Q73" s="3">
-        <v>46211.60422453703</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="R73">
         <v>5.69</v>
       </c>
       <c r="S73" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="74" spans="1:25">
@@ -3632,28 +3635,31 @@
         <v>97</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
+      </c>
+      <c r="I74" t="s">
+        <v>210</v>
       </c>
       <c r="M74">
         <v>1</v>
       </c>
       <c r="N74" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="O74" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="P74" s="3">
-        <v>46320.39783564815</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="Q74" s="3">
-        <v>46320.39783564815</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="R74">
-        <v>6.04</v>
+        <v>5.69</v>
       </c>
       <c r="S74" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="75" spans="1:25">
@@ -3661,31 +3667,31 @@
         <v>98</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I75" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="M75">
         <v>1</v>
       </c>
       <c r="N75" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O75" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P75" s="3">
-        <v>46196.76916666667</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="Q75" s="3">
-        <v>46196.76916666667</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="R75">
         <v>5.69</v>
       </c>
       <c r="S75" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="76" spans="1:25">
@@ -3693,31 +3699,28 @@
         <v>99</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="I76" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="M76">
         <v>1</v>
       </c>
       <c r="N76" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O76" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P76" s="3">
-        <v>46198.62644675926</v>
+        <v>46301.52780092593</v>
       </c>
       <c r="Q76" s="3">
-        <v>46198.62644675926</v>
+        <v>46301.52780092593</v>
       </c>
       <c r="R76">
-        <v>5.69</v>
+        <v>6.53</v>
       </c>
       <c r="S76" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77" spans="1:25">
@@ -3725,31 +3728,31 @@
         <v>100</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I77" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="M77">
         <v>1</v>
       </c>
       <c r="N77" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O77" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P77" s="3">
-        <v>46220.44594907408</v>
+        <v>46221.54171296296</v>
       </c>
       <c r="Q77" s="3">
-        <v>46220.44594907408</v>
+        <v>46221.54171296296</v>
       </c>
       <c r="R77">
         <v>5.69</v>
       </c>
       <c r="S77" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="78" spans="1:25">
@@ -3757,28 +3760,31 @@
         <v>101</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
+      </c>
+      <c r="I78" t="s">
+        <v>214</v>
       </c>
       <c r="M78">
         <v>1</v>
       </c>
       <c r="N78" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="O78" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="P78" s="3">
-        <v>46301.52780092593</v>
+        <v>45993.6759375</v>
       </c>
       <c r="Q78" s="3">
-        <v>46301.52780092593</v>
+        <v>45993.6759375</v>
       </c>
       <c r="R78">
-        <v>6.53</v>
+        <v>9.31</v>
       </c>
       <c r="S78" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79" spans="1:25">
@@ -3786,31 +3792,31 @@
         <v>102</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I79" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M79">
         <v>1</v>
       </c>
       <c r="N79" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="O79" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P79" s="3">
-        <v>46221.54171296296</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="Q79" s="3">
-        <v>46221.54171296296</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="R79">
-        <v>5.69</v>
+        <v>12.41</v>
       </c>
       <c r="S79" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:25">
@@ -3818,31 +3824,31 @@
         <v>103</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I80" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="M80">
         <v>1</v>
       </c>
       <c r="N80" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O80" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P80" s="3">
-        <v>45993.6759375</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="Q80" s="3">
-        <v>45993.6759375</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="R80">
         <v>9.31</v>
       </c>
       <c r="S80" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="81" spans="1:25">
@@ -3850,31 +3856,31 @@
         <v>104</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I81" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="M81">
         <v>1</v>
       </c>
       <c r="N81" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="O81" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="P81" s="3">
-        <v>46178.61515046296</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="Q81" s="3">
-        <v>46178.61515046296</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="R81">
-        <v>12.41</v>
+        <v>5.69</v>
       </c>
       <c r="S81" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="82" spans="1:25">
@@ -3882,31 +3888,31 @@
         <v>105</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I82" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M82">
         <v>1</v>
       </c>
       <c r="N82" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O82" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P82" s="3">
-        <v>45981.84152777777</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="Q82" s="3">
-        <v>45981.84152777777</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="R82">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S82" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" spans="1:25">
@@ -3914,31 +3920,31 @@
         <v>106</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I83" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M83">
         <v>1</v>
       </c>
       <c r="N83" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O83" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P83" s="3">
-        <v>45965.5908449074</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="Q83" s="3">
-        <v>45965.5908449074</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="R83">
         <v>5.69</v>
       </c>
       <c r="S83" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="84" spans="1:25">
@@ -3946,31 +3952,46 @@
         <v>107</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I84" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="M84">
         <v>1</v>
       </c>
       <c r="N84" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O84" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P84" s="3">
-        <v>46206.37778935185</v>
+        <v>46306.55003472222</v>
       </c>
       <c r="Q84" s="3">
-        <v>46206.37778935185</v>
+        <v>46306.55003472222</v>
       </c>
       <c r="R84">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S84" t="s">
-        <v>238</v>
+        <v>233</v>
+      </c>
+      <c r="T84">
+        <v>2</v>
+      </c>
+      <c r="U84">
+        <v>59.99</v>
+      </c>
+      <c r="V84">
+        <v>1</v>
+      </c>
+      <c r="W84">
+        <v>946</v>
+      </c>
+      <c r="X84" s="3">
+        <v>46294</v>
+      </c>
+      <c r="Y84">
+        <v>-13</v>
       </c>
     </row>
     <row r="85" spans="1:25">
@@ -3978,31 +3999,28 @@
         <v>108</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="I85" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="M85">
         <v>1</v>
       </c>
       <c r="N85" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O85" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P85" s="3">
-        <v>46220.91548611111</v>
+        <v>46312.95512731482</v>
       </c>
       <c r="Q85" s="3">
-        <v>46220.91548611111</v>
+        <v>46312.95512731482</v>
       </c>
       <c r="R85">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S85" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86" spans="1:25">
@@ -4010,46 +4028,31 @@
         <v>109</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
+      </c>
+      <c r="I86" t="s">
+        <v>209</v>
       </c>
       <c r="M86">
         <v>1</v>
       </c>
       <c r="N86" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O86" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="P86" s="3">
-        <v>46306.55003472222</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="Q86" s="3">
-        <v>46306.55003472222</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="R86">
-        <v>8.58</v>
+        <v>9.31</v>
       </c>
       <c r="S86" t="s">
-        <v>239</v>
-      </c>
-      <c r="T86">
-        <v>2</v>
-      </c>
-      <c r="U86">
-        <v>59.99</v>
-      </c>
-      <c r="V86">
-        <v>1</v>
-      </c>
-      <c r="W86">
-        <v>946</v>
-      </c>
-      <c r="X86" s="3">
-        <v>46294</v>
-      </c>
-      <c r="Y86">
-        <v>-13</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87" spans="1:25">
@@ -4057,28 +4060,31 @@
         <v>110</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
+      </c>
+      <c r="I87" t="s">
+        <v>210</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
       <c r="N87" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O87" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="P87" s="3">
-        <v>46312.95512731482</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q87" s="3">
-        <v>46312.95512731482</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R87">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S87" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="88" spans="1:25">
@@ -4086,31 +4092,31 @@
         <v>111</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M88">
         <v>1</v>
       </c>
       <c r="N88" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O88" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P88" s="3">
-        <v>45939.98240740741</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="Q88" s="3">
-        <v>45939.98240740741</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="R88">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S88" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89" spans="1:25">
@@ -4118,31 +4124,31 @@
         <v>112</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I89" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="M89">
         <v>1</v>
       </c>
       <c r="N89" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O89" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P89" s="3">
-        <v>46198.62712962963</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="Q89" s="3">
-        <v>46198.62712962963</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="R89">
         <v>5.69</v>
       </c>
       <c r="S89" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:25">
@@ -4150,31 +4156,31 @@
         <v>113</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I90" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="M90">
         <v>1</v>
       </c>
       <c r="N90" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O90" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P90" s="3">
-        <v>45990.94167824074</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="Q90" s="3">
-        <v>45990.94167824074</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="R90">
         <v>5.69</v>
       </c>
       <c r="S90" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="91" spans="1:25">
@@ -4182,124 +4188,31 @@
         <v>114</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I91" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N91" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O91" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P91" s="3">
-        <v>45913.74726851852</v>
+        <v>46196.65561342592</v>
       </c>
       <c r="Q91" s="3">
-        <v>45913.74726851852</v>
+        <v>46224.32857638889</v>
       </c>
       <c r="R91">
-        <v>5.69</v>
+        <v>11.38</v>
       </c>
       <c r="S91" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="92" spans="1:25">
-      <c r="A92" t="s">
-        <v>115</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="M92">
-        <v>1</v>
-      </c>
-      <c r="N92" t="s">
-        <v>226</v>
-      </c>
-      <c r="O92" t="s">
-        <v>235</v>
-      </c>
-      <c r="P92" s="3">
-        <v>46318.58416666667</v>
-      </c>
-      <c r="Q92" s="3">
-        <v>46318.58416666667</v>
-      </c>
-      <c r="R92">
-        <v>5.69</v>
-      </c>
-      <c r="S92" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="93" spans="1:25">
-      <c r="A93" t="s">
-        <v>116</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I93" t="s">
-        <v>217</v>
-      </c>
-      <c r="M93">
-        <v>1</v>
-      </c>
-      <c r="N93" t="s">
-        <v>226</v>
-      </c>
-      <c r="O93" t="s">
-        <v>235</v>
-      </c>
-      <c r="P93" s="3">
-        <v>46221.60350694445</v>
-      </c>
-      <c r="Q93" s="3">
-        <v>46221.60350694445</v>
-      </c>
-      <c r="R93">
-        <v>5.69</v>
-      </c>
-      <c r="S93" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="94" spans="1:25">
-      <c r="A94" t="s">
-        <v>117</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="I94" t="s">
-        <v>219</v>
-      </c>
-      <c r="M94">
-        <v>2</v>
-      </c>
-      <c r="N94" t="s">
-        <v>226</v>
-      </c>
-      <c r="O94" t="s">
-        <v>235</v>
-      </c>
-      <c r="P94" s="3">
-        <v>46196.65561342592</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>46224.32857638889</v>
-      </c>
-      <c r="R94">
-        <v>11.38</v>
-      </c>
-      <c r="S94" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -4394,9 +4307,6 @@
     <hyperlink ref="B89" r:id="rId88"/>
     <hyperlink ref="B90" r:id="rId89"/>
     <hyperlink ref="B91" r:id="rId90"/>
-    <hyperlink ref="B92" r:id="rId91"/>
-    <hyperlink ref="B93" r:id="rId92"/>
-    <hyperlink ref="B94" r:id="rId93"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="241">
   <si>
     <t>handle</t>
   </si>
@@ -100,9 +100,6 @@
     <t>annredfearn1</t>
   </si>
   <si>
-    <t>atoyese1</t>
-  </si>
-  <si>
     <t>beauty.baddie.444</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
     <t>godisgoodoooo</t>
   </si>
   <si>
-    <t>gone121256</t>
-  </si>
-  <si>
     <t>gull222020</t>
   </si>
   <si>
@@ -214,9 +208,6 @@
     <t>kingmxn</t>
   </si>
   <si>
-    <t>lezleeacko.tiktok2</t>
-  </si>
-  <si>
     <t>lindastubbs88</t>
   </si>
   <si>
@@ -238,9 +229,6 @@
     <t>mssushi26</t>
   </si>
   <si>
-    <t>myselfcareshelf</t>
-  </si>
-  <si>
     <t>mysterytiktok52</t>
   </si>
   <si>
@@ -289,9 +277,6 @@
     <t>sarahs.daily.deal</t>
   </si>
   <si>
-    <t>shafqatali0786</t>
-  </si>
-  <si>
     <t>sheluvslivx</t>
   </si>
   <si>
@@ -316,15 +301,9 @@
     <t>styled388</t>
   </si>
   <si>
-    <t>sunnah_fertilitycoach</t>
-  </si>
-  <si>
     <t>sylhetimumukworld</t>
   </si>
   <si>
-    <t>tabstoyou</t>
-  </si>
-  <si>
     <t>tanjinaunfiltered</t>
   </si>
   <si>
@@ -334,9 +313,6 @@
     <t>the.witchy.wander</t>
   </si>
   <si>
-    <t>theglam_lifter</t>
-  </si>
-  <si>
     <t>thetripleteez</t>
   </si>
   <si>
@@ -403,9 +379,6 @@
     <t>https://www.tiktok.com/@annredfearn1</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@atoyese1</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@beauty.baddie.444</t>
   </si>
   <si>
@@ -472,9 +445,6 @@
     <t>https://www.tiktok.com/@godisgoodoooo</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@gone121256</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@gull222020</t>
   </si>
   <si>
@@ -517,9 +487,6 @@
     <t>https://www.tiktok.com/@kingmxn</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@lezleeacko.tiktok2</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@lindastubbs88</t>
   </si>
   <si>
@@ -541,9 +508,6 @@
     <t>https://www.tiktok.com/@mssushi26</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@myselfcareshelf</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@mysterytiktok52</t>
   </si>
   <si>
@@ -592,9 +556,6 @@
     <t>https://www.tiktok.com/@sarahs.daily.deal</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@shafqatali0786</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@sheluvslivx</t>
   </si>
   <si>
@@ -619,15 +580,9 @@
     <t>https://www.tiktok.com/@styled388</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@sunnah_fertilitycoach</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@sylhetimumukworld</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@tabstoyou</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@tanjinaunfiltered</t>
   </si>
   <si>
@@ -637,9 +592,6 @@
     <t>https://www.tiktok.com/@the.witchy.wander</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@theglam_lifter</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@thetripleteez</t>
   </si>
   <si>
@@ -757,9 +709,6 @@
     <t>Ashwagandha Capsules, Ashwagandha Coffee, Green Burner, Gut Shift, Hibiscus, Spearmint, Turmeric Curcumin</t>
   </si>
   <si>
-    <t>Green Burner, Gut Shift, Skin Radiance, Turmeric Curcumin</t>
-  </si>
-  <si>
     <t>Ashwagandha Coffee, Spearmint</t>
   </si>
   <si>
@@ -770,9 +719,6 @@
   </si>
   <si>
     <t>Advent Teas of Joy</t>
-  </si>
-  <si>
-    <t>Skin Radiance</t>
   </si>
   <si>
     <t>Turmeric Curcumin</t>
@@ -1165,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y102"/>
+  <dimension ref="A1:Y94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1250,19 +1196,19 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I2" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="O2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P2" s="3">
         <v>46028.62637731482</v>
@@ -1274,7 +1220,7 @@
         <v>5.64</v>
       </c>
       <c r="S2" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1282,19 +1228,19 @@
         <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="I3" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O3" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P3" s="3">
         <v>45998.88378472222</v>
@@ -1306,7 +1252,7 @@
         <v>9.31</v>
       </c>
       <c r="S3" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1314,19 +1260,19 @@
         <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I4" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O4" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P4" s="3">
         <v>45986.77690972222</v>
@@ -1338,7 +1284,7 @@
         <v>5.69</v>
       </c>
       <c r="S4" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1346,28 +1292,31 @@
         <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
+      </c>
+      <c r="I5" t="s">
+        <v>217</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O5" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P5" s="3">
-        <v>46321.68112268519</v>
+        <v>45911.17809027778</v>
       </c>
       <c r="Q5" s="3">
-        <v>46321.68112268519</v>
+        <v>45911.17809027778</v>
       </c>
       <c r="R5">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S5" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1375,31 +1324,28 @@
         <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I6" t="s">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="O6" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="P6" s="3">
-        <v>45911.17809027778</v>
+        <v>46306.55002314815</v>
       </c>
       <c r="Q6" s="3">
-        <v>45911.17809027778</v>
+        <v>46314.97372685185</v>
       </c>
       <c r="R6">
-        <v>9.31</v>
+        <v>14.62</v>
       </c>
       <c r="S6" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1407,28 +1353,52 @@
         <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
+      </c>
+      <c r="E7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F7" t="s">
+        <v>212</v>
+      </c>
+      <c r="G7" t="s">
+        <v>213</v>
+      </c>
+      <c r="H7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J7" t="s">
+        <v>223</v>
+      </c>
+      <c r="K7" t="s">
+        <v>224</v>
+      </c>
+      <c r="L7" t="s">
+        <v>223</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="O7" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="P7" s="3">
-        <v>46306.55002314815</v>
+        <v>45989.98658564815</v>
       </c>
       <c r="Q7" s="3">
-        <v>46314.97372685185</v>
+        <v>45989.98658564815</v>
       </c>
       <c r="R7">
-        <v>14.62</v>
+        <v>9.31</v>
       </c>
       <c r="S7" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1436,52 +1406,31 @@
         <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E8" t="s">
-        <v>227</v>
-      </c>
-      <c r="F8" t="s">
-        <v>228</v>
-      </c>
-      <c r="G8" t="s">
-        <v>229</v>
-      </c>
-      <c r="H8" t="s">
-        <v>230</v>
+        <v>124</v>
       </c>
       <c r="I8" t="s">
-        <v>233</v>
-      </c>
-      <c r="J8" t="s">
-        <v>239</v>
-      </c>
-      <c r="K8" t="s">
-        <v>240</v>
-      </c>
-      <c r="L8" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O8" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P8" s="3">
-        <v>45989.98658564815</v>
+        <v>45974.46635416667</v>
       </c>
       <c r="Q8" s="3">
-        <v>45989.98658564815</v>
+        <v>45974.46635416667</v>
       </c>
       <c r="R8">
         <v>9.31</v>
       </c>
       <c r="S8" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1489,31 +1438,31 @@
         <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I9" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O9" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P9" s="3">
-        <v>45974.46635416667</v>
+        <v>45967.48326388889</v>
       </c>
       <c r="Q9" s="3">
-        <v>45974.46635416667</v>
+        <v>45967.48326388889</v>
       </c>
       <c r="R9">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S9" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1521,31 +1470,31 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I10" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O10" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P10" s="3">
-        <v>45967.48326388889</v>
+        <v>46176.59099537037</v>
       </c>
       <c r="Q10" s="3">
-        <v>45967.48326388889</v>
+        <v>46176.59099537037</v>
       </c>
       <c r="R10">
         <v>5.69</v>
       </c>
       <c r="S10" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1553,31 +1502,31 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I11" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O11" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P11" s="3">
-        <v>46176.59099537037</v>
+        <v>45996.23743055556</v>
       </c>
       <c r="Q11" s="3">
-        <v>46176.59099537037</v>
+        <v>45996.23743055556</v>
       </c>
       <c r="R11">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S11" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1585,31 +1534,31 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="I12" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O12" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P12" s="3">
-        <v>45996.23743055556</v>
+        <v>46209.78530092593</v>
       </c>
       <c r="Q12" s="3">
-        <v>45996.23743055556</v>
+        <v>46209.78530092593</v>
       </c>
       <c r="R12">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S12" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1617,31 +1566,31 @@
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I13" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O13" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P13" s="3">
-        <v>46209.78530092593</v>
+        <v>46092.52502314815</v>
       </c>
       <c r="Q13" s="3">
-        <v>46209.78530092593</v>
+        <v>46092.52502314815</v>
       </c>
       <c r="R13">
         <v>5.69</v>
       </c>
       <c r="S13" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1649,31 +1598,46 @@
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I14" t="s">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="O14" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="P14" s="3">
-        <v>46092.52502314815</v>
+        <v>46296.61392361111</v>
       </c>
       <c r="Q14" s="3">
-        <v>46092.52502314815</v>
+        <v>46296.61392361111</v>
       </c>
       <c r="R14">
-        <v>5.69</v>
+        <v>26.83</v>
       </c>
       <c r="S14" t="s">
-        <v>257</v>
+        <v>240</v>
+      </c>
+      <c r="T14">
+        <v>4</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>227</v>
+      </c>
+      <c r="X14" s="3">
+        <v>46303</v>
+      </c>
+      <c r="Y14">
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1681,46 +1645,28 @@
         <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="O15" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="P15" s="3">
-        <v>46296.61392361111</v>
+        <v>46196.83574074074</v>
       </c>
       <c r="Q15" s="3">
-        <v>46296.61392361111</v>
+        <v>46196.83574074074</v>
       </c>
       <c r="R15">
-        <v>26.83</v>
+        <v>5.69</v>
       </c>
       <c r="S15" t="s">
-        <v>258</v>
-      </c>
-      <c r="T15">
-        <v>4</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>227</v>
-      </c>
-      <c r="X15" s="3">
-        <v>46303</v>
-      </c>
-      <c r="Y15">
-        <v>6</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1728,28 +1674,31 @@
         <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
+      </c>
+      <c r="I16" t="s">
+        <v>219</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O16" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P16" s="3">
-        <v>46196.83574074074</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="Q16" s="3">
-        <v>46196.83574074074</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="R16">
         <v>5.69</v>
       </c>
       <c r="S16" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1757,31 +1706,31 @@
         <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I17" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N17" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="O17" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="P17" s="3">
-        <v>46198.6271412037</v>
+        <v>45840.45584490741</v>
       </c>
       <c r="Q17" s="3">
-        <v>46198.6271412037</v>
+        <v>46170.61114583333</v>
       </c>
       <c r="R17">
-        <v>5.69</v>
+        <v>17.02</v>
       </c>
       <c r="S17" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1789,31 +1738,31 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I18" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="O18" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="P18" s="3">
-        <v>45840.45584490741</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="Q18" s="3">
-        <v>46170.61114583333</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="R18">
-        <v>17.02</v>
+        <v>5.69</v>
       </c>
       <c r="S18" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1821,31 +1770,46 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I19" t="s">
-        <v>233</v>
+        <v>135</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O19" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P19" s="3">
-        <v>46198.6271412037</v>
+        <v>46309.55629629629</v>
       </c>
       <c r="Q19" s="3">
-        <v>46198.6271412037</v>
+        <v>46309.55629629629</v>
       </c>
       <c r="R19">
         <v>5.69</v>
       </c>
       <c r="S19" t="s">
-        <v>257</v>
+        <v>240</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>10</v>
+      </c>
+      <c r="X19" s="3">
+        <v>46311</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1853,46 +1817,28 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="M20">
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O20" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P20" s="3">
-        <v>46309.55629629629</v>
+        <v>46252.93552083334</v>
       </c>
       <c r="Q20" s="3">
-        <v>46309.55629629629</v>
+        <v>46252.93552083334</v>
       </c>
       <c r="R20">
         <v>5.69</v>
       </c>
       <c r="S20" t="s">
-        <v>258</v>
-      </c>
-      <c r="T20">
-        <v>1</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>10</v>
-      </c>
-      <c r="X20" s="3">
-        <v>46311</v>
-      </c>
-      <c r="Y20">
-        <v>1</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -1900,28 +1846,31 @@
         <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
+      </c>
+      <c r="I21" t="s">
+        <v>220</v>
       </c>
       <c r="M21">
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O21" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P21" s="3">
-        <v>46252.93552083334</v>
+        <v>46062.02391203704</v>
       </c>
       <c r="Q21" s="3">
-        <v>46252.93552083334</v>
+        <v>46062.02391203704</v>
       </c>
       <c r="R21">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S21" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -1929,31 +1878,31 @@
         <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I22" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O22" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P22" s="3">
-        <v>46062.02391203704</v>
+        <v>45903.0252662037</v>
       </c>
       <c r="Q22" s="3">
-        <v>46062.02391203704</v>
+        <v>45903.0252662037</v>
       </c>
       <c r="R22">
-        <v>12.46</v>
+        <v>9.31</v>
       </c>
       <c r="S22" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -1961,31 +1910,31 @@
         <v>46</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I23" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="M23">
         <v>1</v>
       </c>
       <c r="N23" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O23" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P23" s="3">
-        <v>45903.0252662037</v>
+        <v>46178.95283564815</v>
       </c>
       <c r="Q23" s="3">
-        <v>45903.0252662037</v>
+        <v>46178.95283564815</v>
       </c>
       <c r="R23">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S23" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -1993,31 +1942,31 @@
         <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I24" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="M24">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N24" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="O24" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="P24" s="3">
-        <v>46178.95283564815</v>
+        <v>46181.5243287037</v>
       </c>
       <c r="Q24" s="3">
-        <v>46178.95283564815</v>
+        <v>46253.65496527778</v>
       </c>
       <c r="R24">
-        <v>5.69</v>
+        <v>60.34</v>
       </c>
       <c r="S24" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2025,31 +1974,28 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="I25" t="s">
-        <v>235</v>
+        <v>141</v>
       </c>
       <c r="M25">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="O25" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="P25" s="3">
-        <v>46181.5243287037</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="Q25" s="3">
-        <v>46253.65496527778</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="R25">
-        <v>60.34</v>
+        <v>5.69</v>
       </c>
       <c r="S25" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2057,28 +2003,31 @@
         <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
+      </c>
+      <c r="I26" t="s">
+        <v>215</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O26" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P26" s="3">
-        <v>46053.63612268519</v>
+        <v>46008.62306712963</v>
       </c>
       <c r="Q26" s="3">
-        <v>46053.63612268519</v>
+        <v>46008.62306712963</v>
       </c>
       <c r="R26">
         <v>5.69</v>
       </c>
       <c r="S26" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2086,31 +2035,31 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I27" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O27" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P27" s="3">
-        <v>46008.62306712963</v>
+        <v>46152.90292824074</v>
       </c>
       <c r="Q27" s="3">
-        <v>46008.62306712963</v>
+        <v>46152.90292824074</v>
       </c>
       <c r="R27">
         <v>5.69</v>
       </c>
       <c r="S27" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2118,28 +2067,31 @@
         <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
+      </c>
+      <c r="I28" t="s">
+        <v>216</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="O28" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="P28" s="3">
-        <v>46316.69532407408</v>
+        <v>45953.84554398148</v>
       </c>
       <c r="Q28" s="3">
-        <v>46316.6953587963</v>
+        <v>45953.84554398148</v>
       </c>
       <c r="R28">
-        <v>28.05</v>
+        <v>12.46</v>
       </c>
       <c r="S28" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2147,31 +2099,46 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I29" t="s">
-        <v>236</v>
+        <v>145</v>
       </c>
       <c r="M29">
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O29" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P29" s="3">
-        <v>46152.90292824074</v>
+        <v>46310.5215625</v>
       </c>
       <c r="Q29" s="3">
-        <v>46152.90292824074</v>
+        <v>46310.5215625</v>
       </c>
       <c r="R29">
         <v>5.69</v>
       </c>
       <c r="S29" t="s">
-        <v>257</v>
+        <v>240</v>
+      </c>
+      <c r="T29">
+        <v>7</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>206</v>
+      </c>
+      <c r="X29" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y29">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2179,31 +2146,31 @@
         <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I30" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="M30">
         <v>1</v>
       </c>
       <c r="N30" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O30" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P30" s="3">
-        <v>45953.84554398148</v>
+        <v>46111.64181712963</v>
       </c>
       <c r="Q30" s="3">
-        <v>45953.84554398148</v>
+        <v>46111.64181712963</v>
       </c>
       <c r="R30">
         <v>12.46</v>
       </c>
       <c r="S30" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2211,31 +2178,31 @@
         <v>54</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="O31" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P31" s="3">
-        <v>46310.5215625</v>
+        <v>46296.45141203704</v>
       </c>
       <c r="Q31" s="3">
-        <v>46310.5215625</v>
+        <v>46296.45141203704</v>
       </c>
       <c r="R31">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="S31" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U31">
         <v>0</v>
@@ -2244,13 +2211,13 @@
         <v>0</v>
       </c>
       <c r="W31">
-        <v>206</v>
+        <v>9</v>
       </c>
       <c r="X31" s="3">
-        <v>46313</v>
+        <v>46298</v>
       </c>
       <c r="Y31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2258,31 +2225,31 @@
         <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="I32" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="M32">
         <v>1</v>
       </c>
       <c r="N32" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O32" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P32" s="3">
-        <v>46111.64181712963</v>
+        <v>46210.48171296297</v>
       </c>
       <c r="Q32" s="3">
-        <v>46111.64181712963</v>
+        <v>46210.48171296297</v>
       </c>
       <c r="R32">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S32" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2290,46 +2257,46 @@
         <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N33" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="O33" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="P33" s="3">
-        <v>46296.45141203704</v>
+        <v>46280.49378472222</v>
       </c>
       <c r="Q33" s="3">
-        <v>46296.45141203704</v>
+        <v>46280.49379629629</v>
       </c>
       <c r="R33">
-        <v>5.64</v>
+        <v>10.55</v>
       </c>
       <c r="S33" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="T33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U33">
+        <v>19.91</v>
+      </c>
+      <c r="V33">
+        <v>2</v>
+      </c>
+      <c r="W33">
+        <v>689</v>
+      </c>
+      <c r="X33" s="3">
+        <v>46281</v>
+      </c>
+      <c r="Y33">
         <v>0</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>9</v>
-      </c>
-      <c r="X33" s="3">
-        <v>46298</v>
-      </c>
-      <c r="Y33">
-        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -2337,31 +2304,31 @@
         <v>57</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I34" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O34" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P34" s="3">
-        <v>46210.48171296297</v>
+        <v>46225.98408564815</v>
       </c>
       <c r="Q34" s="3">
-        <v>46210.48171296297</v>
+        <v>46225.98408564815</v>
       </c>
       <c r="R34">
         <v>5.69</v>
       </c>
       <c r="S34" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -2369,46 +2336,31 @@
         <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
+      </c>
+      <c r="I35" t="s">
+        <v>216</v>
       </c>
       <c r="M35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="O35" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="P35" s="3">
-        <v>46280.49378472222</v>
+        <v>46106.56184027778</v>
       </c>
       <c r="Q35" s="3">
-        <v>46280.49379629629</v>
+        <v>46106.56184027778</v>
       </c>
       <c r="R35">
-        <v>10.55</v>
+        <v>5.69</v>
       </c>
       <c r="S35" t="s">
-        <v>258</v>
-      </c>
-      <c r="T35">
-        <v>4</v>
-      </c>
-      <c r="U35">
-        <v>19.91</v>
-      </c>
-      <c r="V35">
-        <v>2</v>
-      </c>
-      <c r="W35">
-        <v>689</v>
-      </c>
-      <c r="X35" s="3">
-        <v>46281</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -2416,31 +2368,28 @@
         <v>59</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="I36" t="s">
+        <v>152</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36" t="s">
+        <v>226</v>
+      </c>
+      <c r="O36" t="s">
         <v>237</v>
       </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="N36" t="s">
-        <v>242</v>
-      </c>
-      <c r="O36" t="s">
-        <v>254</v>
-      </c>
       <c r="P36" s="3">
-        <v>46225.98408564815</v>
+        <v>46313.79324074074</v>
       </c>
       <c r="Q36" s="3">
-        <v>46225.98408564815</v>
+        <v>46313.79324074074</v>
       </c>
       <c r="R36">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S36" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -2448,31 +2397,31 @@
         <v>60</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="I37" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M37">
         <v>1</v>
       </c>
       <c r="N37" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O37" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P37" s="3">
-        <v>46106.56184027778</v>
+        <v>46196.84141203704</v>
       </c>
       <c r="Q37" s="3">
-        <v>46106.56184027778</v>
+        <v>46196.84141203704</v>
       </c>
       <c r="R37">
         <v>5.69</v>
       </c>
       <c r="S37" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -2480,28 +2429,28 @@
         <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="M38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N38" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="O38" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="P38" s="3">
-        <v>46313.79324074074</v>
+        <v>46312.81608796296</v>
       </c>
       <c r="Q38" s="3">
-        <v>46313.79324074074</v>
+        <v>46313.7452662037</v>
       </c>
       <c r="R38">
-        <v>8.58</v>
+        <v>14.62</v>
       </c>
       <c r="S38" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -2509,31 +2458,31 @@
         <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="I39" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O39" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P39" s="3">
-        <v>46196.84141203704</v>
+        <v>46073.66815972222</v>
       </c>
       <c r="Q39" s="3">
-        <v>46196.84141203704</v>
+        <v>46073.66815972222</v>
       </c>
       <c r="R39">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S39" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -2541,28 +2490,49 @@
         <v>63</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
+      </c>
+      <c r="I40" t="s">
+        <v>220</v>
       </c>
       <c r="M40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N40" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="O40" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="P40" s="3">
-        <v>46312.81608796296</v>
+        <v>46245.82854166667</v>
       </c>
       <c r="Q40" s="3">
-        <v>46313.7452662037</v>
+        <v>46245.82854166667</v>
       </c>
       <c r="R40">
-        <v>14.62</v>
+        <v>5.69</v>
       </c>
       <c r="S40" t="s">
-        <v>257</v>
+        <v>240</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>23</v>
+      </c>
+      <c r="X40" s="3">
+        <v>46261</v>
+      </c>
+      <c r="Y40">
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -2570,31 +2540,31 @@
         <v>64</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I41" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="M41">
         <v>1</v>
       </c>
       <c r="N41" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O41" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P41" s="3">
-        <v>46073.66815972222</v>
+        <v>46050.93159722222</v>
       </c>
       <c r="Q41" s="3">
-        <v>46073.66815972222</v>
+        <v>46050.93159722222</v>
       </c>
       <c r="R41">
         <v>12.46</v>
       </c>
       <c r="S41" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -2602,49 +2572,31 @@
         <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I42" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="M42">
         <v>1</v>
       </c>
       <c r="N42" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O42" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P42" s="3">
-        <v>46245.82854166667</v>
+        <v>45965.93854166667</v>
       </c>
       <c r="Q42" s="3">
-        <v>46245.82854166667</v>
+        <v>45965.93854166667</v>
       </c>
       <c r="R42">
         <v>5.69</v>
       </c>
       <c r="S42" t="s">
-        <v>258</v>
-      </c>
-      <c r="T42">
-        <v>1</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-      <c r="W42">
-        <v>23</v>
-      </c>
-      <c r="X42" s="3">
-        <v>46261</v>
-      </c>
-      <c r="Y42">
-        <v>15</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -2652,28 +2604,31 @@
         <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
+      </c>
+      <c r="I43" t="s">
+        <v>216</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O43" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P43" s="3">
-        <v>46321.68144675926</v>
+        <v>45992.89240740741</v>
       </c>
       <c r="Q43" s="3">
-        <v>46321.68144675926</v>
+        <v>45992.89240740741</v>
       </c>
       <c r="R43">
         <v>5.69</v>
       </c>
       <c r="S43" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -2681,31 +2636,31 @@
         <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="I44" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="M44">
         <v>1</v>
       </c>
       <c r="N44" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O44" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P44" s="3">
-        <v>46050.93159722222</v>
+        <v>45944.90217592593</v>
       </c>
       <c r="Q44" s="3">
-        <v>46050.93159722222</v>
+        <v>45944.90217592593</v>
       </c>
       <c r="R44">
-        <v>12.46</v>
+        <v>9.31</v>
       </c>
       <c r="S44" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -2713,31 +2668,31 @@
         <v>68</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="I45" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="M45">
         <v>1</v>
       </c>
       <c r="N45" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O45" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P45" s="3">
-        <v>45965.93854166667</v>
+        <v>46105.47987268519</v>
       </c>
       <c r="Q45" s="3">
-        <v>45965.93854166667</v>
+        <v>46105.47987268519</v>
       </c>
       <c r="R45">
         <v>5.69</v>
       </c>
       <c r="S45" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -2745,31 +2700,28 @@
         <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="I46" t="s">
+        <v>162</v>
+      </c>
+      <c r="M46">
+        <v>3</v>
+      </c>
+      <c r="N46" t="s">
         <v>232</v>
       </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
-      <c r="N46" t="s">
-        <v>242</v>
-      </c>
       <c r="O46" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="P46" s="3">
-        <v>45992.89240740741</v>
+        <v>46313.75844907408</v>
       </c>
       <c r="Q46" s="3">
-        <v>45992.89240740741</v>
+        <v>46316.43625</v>
       </c>
       <c r="R46">
-        <v>5.69</v>
+        <v>18.24</v>
       </c>
       <c r="S46" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -2777,31 +2729,31 @@
         <v>70</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="I47" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O47" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P47" s="3">
-        <v>45944.90217592593</v>
+        <v>46210.50420138889</v>
       </c>
       <c r="Q47" s="3">
-        <v>45944.90217592593</v>
+        <v>46210.50420138889</v>
       </c>
       <c r="R47">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S47" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48" spans="1:25">
@@ -2809,31 +2761,28 @@
         <v>71</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I48" t="s">
-        <v>232</v>
+        <v>164</v>
       </c>
       <c r="M48">
         <v>1</v>
       </c>
       <c r="N48" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O48" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P48" s="3">
-        <v>46105.47987268519</v>
+        <v>46052.56390046296</v>
       </c>
       <c r="Q48" s="3">
-        <v>46105.47987268519</v>
+        <v>46052.56390046296</v>
       </c>
       <c r="R48">
         <v>5.69</v>
       </c>
       <c r="S48" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="49" spans="1:25">
@@ -2841,28 +2790,31 @@
         <v>72</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
+      </c>
+      <c r="I49" t="s">
+        <v>217</v>
       </c>
       <c r="M49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N49" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="O49" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="P49" s="3">
-        <v>46313.75844907408</v>
+        <v>46091.88748842593</v>
       </c>
       <c r="Q49" s="3">
-        <v>46316.43625</v>
+        <v>46091.88748842593</v>
       </c>
       <c r="R49">
-        <v>18.24</v>
+        <v>9.31</v>
       </c>
       <c r="S49" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:25">
@@ -2870,31 +2822,31 @@
         <v>73</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="I50" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="M50">
         <v>1</v>
       </c>
       <c r="N50" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O50" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P50" s="3">
-        <v>46210.50420138889</v>
+        <v>45978.69265046297</v>
       </c>
       <c r="Q50" s="3">
-        <v>46210.50420138889</v>
+        <v>45978.69265046297</v>
       </c>
       <c r="R50">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S50" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="51" spans="1:25">
@@ -2902,28 +2854,31 @@
         <v>74</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
+      </c>
+      <c r="I51" t="s">
+        <v>216</v>
       </c>
       <c r="M51">
         <v>1</v>
       </c>
       <c r="N51" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O51" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P51" s="3">
-        <v>46321.68141203704</v>
+        <v>45919.81163194445</v>
       </c>
       <c r="Q51" s="3">
-        <v>46321.68141203704</v>
+        <v>45919.81163194445</v>
       </c>
       <c r="R51">
         <v>5.69</v>
       </c>
       <c r="S51" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" spans="1:25">
@@ -2931,28 +2886,46 @@
         <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="M52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N52" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="O52" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="P52" s="3">
-        <v>46052.56390046296</v>
+        <v>46313.77442129629</v>
       </c>
       <c r="Q52" s="3">
-        <v>46052.56390046296</v>
+        <v>46314.78831018518</v>
       </c>
       <c r="R52">
-        <v>5.69</v>
+        <v>30.1</v>
       </c>
       <c r="S52" t="s">
-        <v>257</v>
+        <v>240</v>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
+        <v>46320</v>
+      </c>
+      <c r="Y52">
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:25">
@@ -2960,31 +2933,46 @@
         <v>76</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I53" t="s">
-        <v>233</v>
+        <v>169</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="O53" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="P53" s="3">
-        <v>46091.88748842593</v>
+        <v>46314.50759259259</v>
       </c>
       <c r="Q53" s="3">
-        <v>46091.88748842593</v>
+        <v>46314.50759259259</v>
       </c>
       <c r="R53">
-        <v>9.31</v>
+        <v>6.04</v>
       </c>
       <c r="S53" t="s">
-        <v>257</v>
+        <v>240</v>
+      </c>
+      <c r="T53">
+        <v>3</v>
+      </c>
+      <c r="U53">
+        <v>20.03</v>
+      </c>
+      <c r="V53">
+        <v>2</v>
+      </c>
+      <c r="W53">
+        <v>537</v>
+      </c>
+      <c r="X53" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y53">
+        <v>-2</v>
       </c>
     </row>
     <row r="54" spans="1:25">
@@ -2992,31 +2980,31 @@
         <v>77</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I54" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="M54">
         <v>1</v>
       </c>
       <c r="N54" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O54" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P54" s="3">
-        <v>45978.69265046297</v>
+        <v>46051.04447916667</v>
       </c>
       <c r="Q54" s="3">
-        <v>45978.69265046297</v>
+        <v>46051.04447916667</v>
       </c>
       <c r="R54">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S54" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="55" spans="1:25">
@@ -3024,31 +3012,31 @@
         <v>78</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I55" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O55" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P55" s="3">
-        <v>45919.81163194445</v>
+        <v>45891.71650462963</v>
       </c>
       <c r="Q55" s="3">
-        <v>45919.81163194445</v>
+        <v>45891.71650462963</v>
       </c>
       <c r="R55">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S55" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:25">
@@ -3056,46 +3044,31 @@
         <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
+      </c>
+      <c r="I56" t="s">
+        <v>215</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N56" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="O56" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="P56" s="3">
-        <v>46313.77442129629</v>
+        <v>46211.60210648148</v>
       </c>
       <c r="Q56" s="3">
-        <v>46314.78831018518</v>
+        <v>46211.60210648148</v>
       </c>
       <c r="R56">
-        <v>30.1</v>
+        <v>5.69</v>
       </c>
       <c r="S56" t="s">
-        <v>258</v>
-      </c>
-      <c r="T56">
-        <v>1</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
-      </c>
-      <c r="V56">
-        <v>0</v>
-      </c>
-      <c r="W56">
-        <v>5</v>
-      </c>
-      <c r="X56" s="3">
-        <v>46320</v>
-      </c>
-      <c r="Y56">
-        <v>6</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:25">
@@ -3103,46 +3076,31 @@
         <v>80</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
+      </c>
+      <c r="I57" t="s">
+        <v>217</v>
       </c>
       <c r="M57">
         <v>1</v>
       </c>
       <c r="N57" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="O57" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="P57" s="3">
-        <v>46314.50759259259</v>
+        <v>46167.36722222222</v>
       </c>
       <c r="Q57" s="3">
-        <v>46314.50759259259</v>
+        <v>46167.36722222222</v>
       </c>
       <c r="R57">
-        <v>6.04</v>
+        <v>5.69</v>
       </c>
       <c r="S57" t="s">
-        <v>258</v>
-      </c>
-      <c r="T57">
-        <v>3</v>
-      </c>
-      <c r="U57">
-        <v>20.03</v>
-      </c>
-      <c r="V57">
-        <v>2</v>
-      </c>
-      <c r="W57">
-        <v>537</v>
-      </c>
-      <c r="X57" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y57">
-        <v>-2</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:25">
@@ -3150,31 +3108,31 @@
         <v>81</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="I58" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="M58">
         <v>1</v>
       </c>
       <c r="N58" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O58" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P58" s="3">
-        <v>46051.04447916667</v>
+        <v>46050.54237268519</v>
       </c>
       <c r="Q58" s="3">
-        <v>46051.04447916667</v>
+        <v>46050.54237268519</v>
       </c>
       <c r="R58">
         <v>5.69</v>
       </c>
       <c r="S58" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="59" spans="1:25">
@@ -3182,31 +3140,31 @@
         <v>82</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I59" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="M59">
         <v>1</v>
       </c>
       <c r="N59" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O59" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P59" s="3">
-        <v>45891.71650462963</v>
+        <v>45957.49894675926</v>
       </c>
       <c r="Q59" s="3">
-        <v>45891.71650462963</v>
+        <v>45957.49894675926</v>
       </c>
       <c r="R59">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S59" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:25">
@@ -3214,31 +3172,31 @@
         <v>83</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I60" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="M60">
         <v>1</v>
       </c>
       <c r="N60" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O60" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P60" s="3">
-        <v>46211.60210648148</v>
+        <v>46196.62574074074</v>
       </c>
       <c r="Q60" s="3">
-        <v>46211.60210648148</v>
+        <v>46196.62574074074</v>
       </c>
       <c r="R60">
         <v>5.69</v>
       </c>
       <c r="S60" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:25">
@@ -3246,31 +3204,31 @@
         <v>84</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I61" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="M61">
         <v>1</v>
       </c>
       <c r="N61" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O61" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P61" s="3">
-        <v>46167.36722222222</v>
+        <v>45959.6512037037</v>
       </c>
       <c r="Q61" s="3">
-        <v>46167.36722222222</v>
+        <v>45959.6512037037</v>
       </c>
       <c r="R61">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S61" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:25">
@@ -3278,31 +3236,31 @@
         <v>85</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I62" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="M62">
         <v>1</v>
       </c>
       <c r="N62" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O62" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P62" s="3">
-        <v>46050.54237268519</v>
+        <v>45973.56506944444</v>
       </c>
       <c r="Q62" s="3">
-        <v>46050.54237268519</v>
+        <v>45973.56506944444</v>
       </c>
       <c r="R62">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S62" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:25">
@@ -3310,31 +3268,28 @@
         <v>86</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I63" t="s">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="M63">
         <v>1</v>
       </c>
       <c r="N63" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="O63" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="P63" s="3">
-        <v>45957.49894675926</v>
+        <v>46313.49944444445</v>
       </c>
       <c r="Q63" s="3">
-        <v>45957.49894675926</v>
+        <v>46313.49944444445</v>
       </c>
       <c r="R63">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S63" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:25">
@@ -3342,31 +3297,31 @@
         <v>87</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I64" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="M64">
         <v>1</v>
       </c>
       <c r="N64" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O64" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P64" s="3">
-        <v>46196.62574074074</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="Q64" s="3">
-        <v>46196.62574074074</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="R64">
         <v>5.69</v>
       </c>
       <c r="S64" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:25">
@@ -3374,31 +3329,46 @@
         <v>88</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I65" t="s">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="M65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N65" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="O65" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="P65" s="3">
-        <v>45959.6512037037</v>
+        <v>46286.62572916667</v>
       </c>
       <c r="Q65" s="3">
-        <v>45959.6512037037</v>
+        <v>46306.5500462963</v>
       </c>
       <c r="R65">
-        <v>9.31</v>
+        <v>14.22</v>
       </c>
       <c r="S65" t="s">
-        <v>257</v>
+        <v>240</v>
+      </c>
+      <c r="T65">
+        <v>2</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>32</v>
+      </c>
+      <c r="X65" s="3">
+        <v>46297</v>
+      </c>
+      <c r="Y65">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:25">
@@ -3406,31 +3376,28 @@
         <v>89</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I66" t="s">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="M66">
         <v>1</v>
       </c>
       <c r="N66" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O66" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P66" s="3">
-        <v>45973.56506944444</v>
+        <v>46304.50560185185</v>
       </c>
       <c r="Q66" s="3">
-        <v>45973.56506944444</v>
+        <v>46304.50560185185</v>
       </c>
       <c r="R66">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S66" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:25">
@@ -3438,28 +3405,28 @@
         <v>90</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="M67">
         <v>1</v>
       </c>
       <c r="N67" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="O67" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="P67" s="3">
-        <v>46313.49944444445</v>
+        <v>46027.60903935185</v>
       </c>
       <c r="Q67" s="3">
-        <v>46313.49944444445</v>
+        <v>46027.60903935185</v>
       </c>
       <c r="R67">
-        <v>6.04</v>
+        <v>5.69</v>
       </c>
       <c r="S67" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:25">
@@ -3467,28 +3434,46 @@
         <v>91</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="M68">
         <v>1</v>
       </c>
       <c r="N68" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O68" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P68" s="3">
-        <v>46321.63788194444</v>
+        <v>46280.49518518519</v>
       </c>
       <c r="Q68" s="3">
-        <v>46321.63788194444</v>
+        <v>46280.49518518519</v>
       </c>
       <c r="R68">
         <v>5.69</v>
       </c>
       <c r="S68" t="s">
-        <v>257</v>
+        <v>240</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>17</v>
+      </c>
+      <c r="X68" s="3">
+        <v>46283</v>
+      </c>
+      <c r="Y68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:25">
@@ -3496,31 +3481,28 @@
         <v>92</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I69" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="M69">
         <v>1</v>
       </c>
       <c r="N69" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O69" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P69" s="3">
-        <v>46191.82362268519</v>
+        <v>46311.94667824074</v>
       </c>
       <c r="Q69" s="3">
-        <v>46191.82362268519</v>
+        <v>46311.94667824074</v>
       </c>
       <c r="R69">
         <v>5.69</v>
       </c>
       <c r="S69" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" spans="1:25">
@@ -3528,31 +3510,31 @@
         <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="M70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="O70" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="P70" s="3">
-        <v>46286.62572916667</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="Q70" s="3">
-        <v>46306.5500462963</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="R70">
-        <v>14.22</v>
+        <v>8.58</v>
       </c>
       <c r="S70" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="T70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -3561,13 +3543,13 @@
         <v>0</v>
       </c>
       <c r="W70">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="X70" s="3">
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="Y70">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:25">
@@ -3575,28 +3557,31 @@
         <v>94</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
+      </c>
+      <c r="I71" t="s">
+        <v>222</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O71" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P71" s="3">
-        <v>46304.50560185185</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q71" s="3">
-        <v>46304.50560185185</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R71">
         <v>5.69</v>
       </c>
       <c r="S71" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="72" spans="1:25">
@@ -3604,28 +3589,31 @@
         <v>95</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
+      </c>
+      <c r="I72" t="s">
+        <v>219</v>
       </c>
       <c r="M72">
         <v>1</v>
       </c>
       <c r="N72" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O72" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P72" s="3">
-        <v>46027.60903935185</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="Q72" s="3">
-        <v>46027.60903935185</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="R72">
         <v>5.69</v>
       </c>
       <c r="S72" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="73" spans="1:25">
@@ -3633,46 +3621,28 @@
         <v>96</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="M73">
         <v>1</v>
       </c>
       <c r="N73" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O73" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P73" s="3">
-        <v>46280.49518518519</v>
+        <v>46199.43622685185</v>
       </c>
       <c r="Q73" s="3">
-        <v>46280.49518518519</v>
+        <v>46199.43622685185</v>
       </c>
       <c r="R73">
         <v>5.69</v>
       </c>
       <c r="S73" t="s">
-        <v>258</v>
-      </c>
-      <c r="T73">
-        <v>1</v>
-      </c>
-      <c r="U73">
-        <v>0</v>
-      </c>
-      <c r="V73">
-        <v>0</v>
-      </c>
-      <c r="W73">
-        <v>17</v>
-      </c>
-      <c r="X73" s="3">
-        <v>46283</v>
-      </c>
-      <c r="Y73">
-        <v>2</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:25">
@@ -3680,28 +3650,31 @@
         <v>97</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
+      </c>
+      <c r="I74" t="s">
+        <v>215</v>
       </c>
       <c r="M74">
         <v>1</v>
       </c>
       <c r="N74" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O74" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P74" s="3">
-        <v>46311.94667824074</v>
+        <v>46211.60422453703</v>
       </c>
       <c r="Q74" s="3">
-        <v>46311.94667824074</v>
+        <v>46211.60422453703</v>
       </c>
       <c r="R74">
         <v>5.69</v>
       </c>
       <c r="S74" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="75" spans="1:25">
@@ -3709,46 +3682,31 @@
         <v>98</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
+      </c>
+      <c r="I75" t="s">
+        <v>215</v>
       </c>
       <c r="M75">
         <v>1</v>
       </c>
       <c r="N75" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O75" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="P75" s="3">
-        <v>46313.79785879629</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="Q75" s="3">
-        <v>46313.79785879629</v>
+        <v>46196.76916666667</v>
       </c>
       <c r="R75">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S75" t="s">
-        <v>258</v>
-      </c>
-      <c r="T75">
-        <v>1</v>
-      </c>
-      <c r="U75">
-        <v>0</v>
-      </c>
-      <c r="V75">
-        <v>0</v>
-      </c>
-      <c r="W75">
-        <v>8</v>
-      </c>
-      <c r="X75" s="3">
-        <v>46317</v>
-      </c>
-      <c r="Y75">
-        <v>3</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:25">
@@ -3756,31 +3714,31 @@
         <v>99</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="I76" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="M76">
         <v>1</v>
       </c>
       <c r="N76" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O76" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P76" s="3">
-        <v>46198.62712962963</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="Q76" s="3">
-        <v>46198.62712962963</v>
+        <v>46198.62644675926</v>
       </c>
       <c r="R76">
         <v>5.69</v>
       </c>
       <c r="S76" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:25">
@@ -3788,28 +3746,31 @@
         <v>100</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
+      </c>
+      <c r="I77" t="s">
+        <v>217</v>
       </c>
       <c r="M77">
         <v>1</v>
       </c>
       <c r="N77" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O77" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P77" s="3">
-        <v>46321.44611111111</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="Q77" s="3">
-        <v>46321.44611111111</v>
+        <v>46220.44594907408</v>
       </c>
       <c r="R77">
         <v>5.69</v>
       </c>
       <c r="S77" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:25">
@@ -3817,31 +3778,28 @@
         <v>101</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I78" t="s">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="M78">
         <v>1</v>
       </c>
       <c r="N78" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O78" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="P78" s="3">
-        <v>46212.55766203703</v>
+        <v>46313.73416666667</v>
       </c>
       <c r="Q78" s="3">
-        <v>46212.55766203703</v>
+        <v>46313.73416666667</v>
       </c>
       <c r="R78">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S78" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:25">
@@ -3849,28 +3807,28 @@
         <v>102</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="M79">
         <v>1</v>
       </c>
       <c r="N79" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="O79" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="P79" s="3">
-        <v>46321.68106481482</v>
+        <v>46301.52780092593</v>
       </c>
       <c r="Q79" s="3">
-        <v>46321.68106481482</v>
+        <v>46301.52780092593</v>
       </c>
       <c r="R79">
-        <v>5.69</v>
+        <v>6.53</v>
       </c>
       <c r="S79" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:25">
@@ -3878,28 +3836,31 @@
         <v>103</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
+      </c>
+      <c r="I80" t="s">
+        <v>216</v>
       </c>
       <c r="M80">
         <v>1</v>
       </c>
       <c r="N80" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O80" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P80" s="3">
-        <v>46199.43622685185</v>
+        <v>46221.54171296296</v>
       </c>
       <c r="Q80" s="3">
-        <v>46199.43622685185</v>
+        <v>46221.54171296296</v>
       </c>
       <c r="R80">
         <v>5.69</v>
       </c>
       <c r="S80" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:25">
@@ -3907,31 +3868,31 @@
         <v>104</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="I81" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="M81">
         <v>1</v>
       </c>
       <c r="N81" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O81" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P81" s="3">
-        <v>46211.60422453703</v>
+        <v>45993.6759375</v>
       </c>
       <c r="Q81" s="3">
-        <v>46211.60422453703</v>
+        <v>45993.6759375</v>
       </c>
       <c r="R81">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S81" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:25">
@@ -3939,31 +3900,31 @@
         <v>105</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="I82" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="M82">
         <v>1</v>
       </c>
       <c r="N82" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="O82" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="P82" s="3">
-        <v>46196.76916666667</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="Q82" s="3">
-        <v>46196.76916666667</v>
+        <v>46178.61515046296</v>
       </c>
       <c r="R82">
-        <v>5.69</v>
+        <v>12.41</v>
       </c>
       <c r="S82" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:25">
@@ -3971,28 +3932,31 @@
         <v>106</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
+      </c>
+      <c r="I83" t="s">
+        <v>215</v>
       </c>
       <c r="M83">
         <v>1</v>
       </c>
       <c r="N83" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="O83" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="P83" s="3">
-        <v>46299.7694675926</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="Q83" s="3">
-        <v>46299.7694675926</v>
+        <v>45981.84152777777</v>
       </c>
       <c r="R83">
-        <v>5.11</v>
+        <v>9.31</v>
       </c>
       <c r="S83" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:25">
@@ -4000,31 +3964,31 @@
         <v>107</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="I84" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="M84">
         <v>1</v>
       </c>
       <c r="N84" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O84" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P84" s="3">
-        <v>46198.62644675926</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="Q84" s="3">
-        <v>46198.62644675926</v>
+        <v>45965.5908449074</v>
       </c>
       <c r="R84">
         <v>5.69</v>
       </c>
       <c r="S84" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:25">
@@ -4032,31 +3996,31 @@
         <v>108</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="I85" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="M85">
         <v>1</v>
       </c>
       <c r="N85" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O85" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P85" s="3">
-        <v>46220.44594907408</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="Q85" s="3">
-        <v>46220.44594907408</v>
+        <v>46206.37778935185</v>
       </c>
       <c r="R85">
         <v>5.69</v>
       </c>
       <c r="S85" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:25">
@@ -4064,28 +4028,31 @@
         <v>109</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
+      </c>
+      <c r="I86" t="s">
+        <v>219</v>
       </c>
       <c r="M86">
         <v>1</v>
       </c>
       <c r="N86" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O86" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="P86" s="3">
-        <v>46313.73416666667</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="Q86" s="3">
-        <v>46313.73416666667</v>
+        <v>46220.91548611111</v>
       </c>
       <c r="R86">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S86" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:25">
@@ -4093,28 +4060,46 @@
         <v>110</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
       <c r="N87" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="O87" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="P87" s="3">
-        <v>46301.52780092593</v>
+        <v>46306.55003472222</v>
       </c>
       <c r="Q87" s="3">
-        <v>46301.52780092593</v>
+        <v>46306.55003472222</v>
       </c>
       <c r="R87">
-        <v>6.53</v>
+        <v>8.58</v>
       </c>
       <c r="S87" t="s">
-        <v>257</v>
+        <v>240</v>
+      </c>
+      <c r="T87">
+        <v>2</v>
+      </c>
+      <c r="U87">
+        <v>59.99</v>
+      </c>
+      <c r="V87">
+        <v>1</v>
+      </c>
+      <c r="W87">
+        <v>946</v>
+      </c>
+      <c r="X87" s="3">
+        <v>46294</v>
+      </c>
+      <c r="Y87">
+        <v>-13</v>
       </c>
     </row>
     <row r="88" spans="1:25">
@@ -4122,31 +4107,28 @@
         <v>111</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I88" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="M88">
         <v>1</v>
       </c>
       <c r="N88" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O88" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="P88" s="3">
-        <v>46221.54171296296</v>
+        <v>46312.95512731482</v>
       </c>
       <c r="Q88" s="3">
-        <v>46221.54171296296</v>
+        <v>46312.95512731482</v>
       </c>
       <c r="R88">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S88" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:25">
@@ -4154,31 +4136,31 @@
         <v>112</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="I89" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="M89">
         <v>1</v>
       </c>
       <c r="N89" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O89" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P89" s="3">
-        <v>45993.6759375</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="Q89" s="3">
-        <v>45993.6759375</v>
+        <v>45939.98240740741</v>
       </c>
       <c r="R89">
         <v>9.31</v>
       </c>
       <c r="S89" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:25">
@@ -4186,31 +4168,31 @@
         <v>113</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="I90" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="M90">
         <v>1</v>
       </c>
       <c r="N90" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="O90" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="P90" s="3">
-        <v>46178.61515046296</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q90" s="3">
-        <v>46178.61515046296</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R90">
-        <v>12.41</v>
+        <v>5.69</v>
       </c>
       <c r="S90" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:25">
@@ -4218,31 +4200,31 @@
         <v>114</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="I91" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="M91">
         <v>1</v>
       </c>
       <c r="N91" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O91" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P91" s="3">
-        <v>45981.84152777777</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="Q91" s="3">
-        <v>45981.84152777777</v>
+        <v>45990.94167824074</v>
       </c>
       <c r="R91">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S91" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:25">
@@ -4250,31 +4232,31 @@
         <v>115</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="I92" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="M92">
         <v>1</v>
       </c>
       <c r="N92" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O92" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P92" s="3">
-        <v>45965.5908449074</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="Q92" s="3">
-        <v>45965.5908449074</v>
+        <v>45913.74726851852</v>
       </c>
       <c r="R92">
         <v>5.69</v>
       </c>
       <c r="S92" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:25">
@@ -4282,31 +4264,31 @@
         <v>116</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I93" t="s">
         <v>217</v>
       </c>
-      <c r="I93" t="s">
-        <v>236</v>
-      </c>
       <c r="M93">
         <v>1</v>
       </c>
       <c r="N93" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O93" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P93" s="3">
-        <v>46206.37778935185</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="Q93" s="3">
-        <v>46206.37778935185</v>
+        <v>46221.60350694445</v>
       </c>
       <c r="R93">
         <v>5.69</v>
       </c>
       <c r="S93" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:25">
@@ -4314,299 +4296,31 @@
         <v>117</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="I94" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="M94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N94" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O94" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P94" s="3">
-        <v>46220.91548611111</v>
+        <v>46196.65561342592</v>
       </c>
       <c r="Q94" s="3">
-        <v>46220.91548611111</v>
+        <v>46224.32857638889</v>
       </c>
       <c r="R94">
-        <v>5.69</v>
+        <v>11.38</v>
       </c>
       <c r="S94" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="95" spans="1:25">
-      <c r="A95" t="s">
-        <v>118</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="M95">
-        <v>1</v>
-      </c>
-      <c r="N95" t="s">
-        <v>242</v>
-      </c>
-      <c r="O95" t="s">
-        <v>255</v>
-      </c>
-      <c r="P95" s="3">
-        <v>46306.55003472222</v>
-      </c>
-      <c r="Q95" s="3">
-        <v>46306.55003472222</v>
-      </c>
-      <c r="R95">
-        <v>8.58</v>
-      </c>
-      <c r="S95" t="s">
-        <v>258</v>
-      </c>
-      <c r="T95">
-        <v>2</v>
-      </c>
-      <c r="U95">
-        <v>59.99</v>
-      </c>
-      <c r="V95">
-        <v>1</v>
-      </c>
-      <c r="W95">
-        <v>946</v>
-      </c>
-      <c r="X95" s="3">
-        <v>46294</v>
-      </c>
-      <c r="Y95">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="96" spans="1:25">
-      <c r="A96" t="s">
-        <v>119</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="M96">
-        <v>1</v>
-      </c>
-      <c r="N96" t="s">
-        <v>242</v>
-      </c>
-      <c r="O96" t="s">
-        <v>255</v>
-      </c>
-      <c r="P96" s="3">
-        <v>46312.95512731482</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>46312.95512731482</v>
-      </c>
-      <c r="R96">
-        <v>8.58</v>
-      </c>
-      <c r="S96" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19">
-      <c r="A97" t="s">
-        <v>120</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="I97" t="s">
-        <v>231</v>
-      </c>
-      <c r="M97">
-        <v>1</v>
-      </c>
-      <c r="N97" t="s">
-        <v>242</v>
-      </c>
-      <c r="O97" t="s">
-        <v>254</v>
-      </c>
-      <c r="P97" s="3">
-        <v>45939.98240740741</v>
-      </c>
-      <c r="Q97" s="3">
-        <v>45939.98240740741</v>
-      </c>
-      <c r="R97">
-        <v>9.31</v>
-      </c>
-      <c r="S97" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19">
-      <c r="A98" t="s">
-        <v>121</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I98" t="s">
-        <v>232</v>
-      </c>
-      <c r="M98">
-        <v>1</v>
-      </c>
-      <c r="N98" t="s">
-        <v>242</v>
-      </c>
-      <c r="O98" t="s">
-        <v>254</v>
-      </c>
-      <c r="P98" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="Q98" s="3">
-        <v>46198.62712962963</v>
-      </c>
-      <c r="R98">
-        <v>5.69</v>
-      </c>
-      <c r="S98" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19">
-      <c r="A99" t="s">
-        <v>122</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="I99" t="s">
-        <v>236</v>
-      </c>
-      <c r="M99">
-        <v>1</v>
-      </c>
-      <c r="N99" t="s">
-        <v>242</v>
-      </c>
-      <c r="O99" t="s">
-        <v>254</v>
-      </c>
-      <c r="P99" s="3">
-        <v>45990.94167824074</v>
-      </c>
-      <c r="Q99" s="3">
-        <v>45990.94167824074</v>
-      </c>
-      <c r="R99">
-        <v>5.69</v>
-      </c>
-      <c r="S99" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="100" spans="1:19">
-      <c r="A100" t="s">
-        <v>123</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="I100" t="s">
-        <v>235</v>
-      </c>
-      <c r="M100">
-        <v>1</v>
-      </c>
-      <c r="N100" t="s">
-        <v>242</v>
-      </c>
-      <c r="O100" t="s">
-        <v>254</v>
-      </c>
-      <c r="P100" s="3">
-        <v>45913.74726851852</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>45913.74726851852</v>
-      </c>
-      <c r="R100">
-        <v>5.69</v>
-      </c>
-      <c r="S100" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="101" spans="1:19">
-      <c r="A101" t="s">
-        <v>124</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="I101" t="s">
-        <v>233</v>
-      </c>
-      <c r="M101">
-        <v>1</v>
-      </c>
-      <c r="N101" t="s">
-        <v>242</v>
-      </c>
-      <c r="O101" t="s">
-        <v>254</v>
-      </c>
-      <c r="P101" s="3">
-        <v>46221.60350694445</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>46221.60350694445</v>
-      </c>
-      <c r="R101">
-        <v>5.69</v>
-      </c>
-      <c r="S101" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="102" spans="1:19">
-      <c r="A102" t="s">
-        <v>125</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I102" t="s">
-        <v>235</v>
-      </c>
-      <c r="M102">
-        <v>2</v>
-      </c>
-      <c r="N102" t="s">
-        <v>242</v>
-      </c>
-      <c r="O102" t="s">
-        <v>254</v>
-      </c>
-      <c r="P102" s="3">
-        <v>46196.65561342592</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>46224.32857638889</v>
-      </c>
-      <c r="R102">
-        <v>11.38</v>
-      </c>
-      <c r="S102" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -4704,14 +4418,6 @@
     <hyperlink ref="B92" r:id="rId91"/>
     <hyperlink ref="B93" r:id="rId92"/>
     <hyperlink ref="B94" r:id="rId93"/>
-    <hyperlink ref="B95" r:id="rId94"/>
-    <hyperlink ref="B96" r:id="rId95"/>
-    <hyperlink ref="B97" r:id="rId96"/>
-    <hyperlink ref="B98" r:id="rId97"/>
-    <hyperlink ref="B99" r:id="rId98"/>
-    <hyperlink ref="B100" r:id="rId99"/>
-    <hyperlink ref="B101" r:id="rId100"/>
-    <hyperlink ref="B102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/no_gmv_data.xlsx
+++ b/no_gmv_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="299">
   <si>
     <t>handle</t>
   </si>
@@ -91,30 +91,45 @@
     <t>days_to_first_video</t>
   </si>
   <si>
+    <t>a.g23467</t>
+  </si>
+  <si>
     <t>adwoafrimpong7</t>
   </si>
   <si>
     <t>ak786786786786786fk</t>
   </si>
   <si>
+    <t>andrealever0</t>
+  </si>
+  <si>
     <t>annredfearn1</t>
   </si>
   <si>
-    <t>baheerzwak2</t>
+    <t>at.tiktok.finds</t>
   </si>
   <si>
     <t>beauty.baddie.444</t>
   </si>
   <si>
+    <t>beckyedwards12</t>
+  </si>
+  <si>
     <t>celaniklozet</t>
   </si>
   <si>
     <t>christopherreidy7</t>
   </si>
   <si>
+    <t>courtsworld97</t>
+  </si>
+  <si>
     <t>craigkennethmccal</t>
   </si>
   <si>
+    <t>dailyshop47</t>
+  </si>
+  <si>
     <t>debsline.co</t>
   </si>
   <si>
@@ -124,6 +139,9 @@
     <t>emandpete_vanlife</t>
   </si>
   <si>
+    <t>emily_clarkbackup</t>
+  </si>
+  <si>
     <t>exclusive_shop5</t>
   </si>
   <si>
@@ -154,9 +172,15 @@
     <t>fxtimx20</t>
   </si>
   <si>
+    <t>garyjezzwhackerge</t>
+  </si>
+  <si>
     <t>gergaduud</t>
   </si>
   <si>
+    <t>gifts563</t>
+  </si>
+  <si>
     <t>globe_trot_with_neelam</t>
   </si>
   <si>
@@ -166,6 +190,9 @@
     <t>godisgoodoooo</t>
   </si>
   <si>
+    <t>goldenwillow406</t>
+  </si>
+  <si>
     <t>gull222020</t>
   </si>
   <si>
@@ -190,12 +217,12 @@
     <t>jemimapuddleduck67</t>
   </si>
   <si>
-    <t>jenny.ijita</t>
-  </si>
-  <si>
     <t>jesesworld</t>
   </si>
   <si>
+    <t>journeytobabylemon</t>
+  </si>
+  <si>
     <t>judef247</t>
   </si>
   <si>
@@ -205,15 +232,27 @@
     <t>katie.the.reader</t>
   </si>
   <si>
+    <t>kellylou721</t>
+  </si>
+  <si>
     <t>khadeeja088</t>
   </si>
   <si>
     <t>kingmxn</t>
   </si>
   <si>
+    <t>lilkie79</t>
+  </si>
+  <si>
     <t>lindastubbs88</t>
   </si>
   <si>
+    <t>luna.shops3</t>
+  </si>
+  <si>
+    <t>mags_tatum_49</t>
+  </si>
+  <si>
     <t>marjorie.binks</t>
   </si>
   <si>
@@ -226,6 +265,9 @@
     <t>melissavanzan236</t>
   </si>
   <si>
+    <t>motherhood274</t>
+  </si>
+  <si>
     <t>mssushi26</t>
   </si>
   <si>
@@ -241,6 +283,9 @@
     <t>nicki.sayce</t>
   </si>
   <si>
+    <t>nim_in_uk</t>
+  </si>
+  <si>
     <t>nitaz10</t>
   </si>
   <si>
@@ -268,12 +313,18 @@
     <t>s.asif11</t>
   </si>
   <si>
+    <t>sabysams</t>
+  </si>
+  <si>
     <t>sadiyomuqtaralbak</t>
   </si>
   <si>
     <t>sam.tuga156</t>
   </si>
   <si>
+    <t>samfinds2</t>
+  </si>
+  <si>
     <t>sarahs.daily.deal</t>
   </si>
   <si>
@@ -283,9 +334,15 @@
     <t>shopforfiver</t>
   </si>
   <si>
+    <t>shopwith.ami</t>
+  </si>
+  <si>
     <t>shopwithme082</t>
   </si>
   <si>
+    <t>shopwithmee_xx</t>
+  </si>
+  <si>
     <t>silentforever92</t>
   </si>
   <si>
@@ -301,6 +358,9 @@
     <t>styled388</t>
   </si>
   <si>
+    <t>supersparklyunicorn67</t>
+  </si>
+  <si>
     <t>sylhetimumukworld</t>
   </si>
   <si>
@@ -322,18 +382,33 @@
     <t>tinae38</t>
   </si>
   <si>
+    <t>tink4526</t>
+  </si>
+  <si>
     <t>todobablog</t>
   </si>
   <si>
     <t>tony03672</t>
   </si>
   <si>
+    <t>train_post</t>
+  </si>
+  <si>
+    <t>trendorav7</t>
+  </si>
+  <si>
+    <t>trip.tailors</t>
+  </si>
+  <si>
     <t>user24484259047033</t>
   </si>
   <si>
     <t>user8008669545474</t>
   </si>
   <si>
+    <t>usernamexxxxxxx04</t>
+  </si>
+  <si>
     <t>vision.rift</t>
   </si>
   <si>
@@ -343,9 +418,18 @@
     <t>waq78690</t>
   </si>
   <si>
+    <t>weinidigital</t>
+  </si>
+  <si>
     <t>whitneyrianebeautycare</t>
   </si>
   <si>
+    <t>whittlos</t>
+  </si>
+  <si>
+    <t>wideawakebookclub</t>
+  </si>
+  <si>
     <t>winniesnwoofs</t>
   </si>
   <si>
@@ -361,36 +445,54 @@
     <t>zaheersheikh786</t>
   </si>
   <si>
+    <t>zainayaa_</t>
+  </si>
+  <si>
     <t>zembii</t>
   </si>
   <si>
     <t>zynislam2</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@a.g23467</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@adwoafrimpong7</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@ak786786786786786fk</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@andrealever0</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@annredfearn1</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@baheerzwak2</t>
+    <t>https://www.tiktok.com/@at.tiktok.finds</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@beauty.baddie.444</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@beckyedwards12</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@celaniklozet</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@christopherreidy7</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@courtsworld97</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@craigkennethmccal</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@dailyshop47</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@debsline.co</t>
   </si>
   <si>
@@ -400,6 +502,9 @@
     <t>https://www.tiktok.com/@emandpete_vanlife</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@emily_clarkbackup</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@exclusive_shop5</t>
   </si>
   <si>
@@ -430,9 +535,15 @@
     <t>https://www.tiktok.com/@fxtimx20</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@garyjezzwhackerge</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@gergaduud</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@gifts563</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@globe_trot_with_neelam</t>
   </si>
   <si>
@@ -442,6 +553,9 @@
     <t>https://www.tiktok.com/@godisgoodoooo</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@goldenwillow406</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@gull222020</t>
   </si>
   <si>
@@ -466,12 +580,12 @@
     <t>https://www.tiktok.com/@jemimapuddleduck67</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@jenny.ijita</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@jesesworld</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@journeytobabylemon</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@judef247</t>
   </si>
   <si>
@@ -481,15 +595,27 @@
     <t>https://www.tiktok.com/@katie.the.reader</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@kellylou721</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@khadeeja088</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@kingmxn</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@lilkie79</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@lindastubbs88</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@luna.shops3</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@mags_tatum_49</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@marjorie.binks</t>
   </si>
   <si>
@@ -502,6 +628,9 @@
     <t>https://www.tiktok.com/@melissavanzan236</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@motherhood274</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@mssushi26</t>
   </si>
   <si>
@@ -517,6 +646,9 @@
     <t>https://www.tiktok.com/@nicki.sayce</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@nim_in_uk</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@nitaz10</t>
   </si>
   <si>
@@ -544,12 +676,18 @@
     <t>https://www.tiktok.com/@s.asif11</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@sabysams</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@sadiyomuqtaralbak</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@sam.tuga156</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@samfinds2</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@sarahs.daily.deal</t>
   </si>
   <si>
@@ -559,9 +697,15 @@
     <t>https://www.tiktok.com/@shopforfiver</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@shopwith.ami</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@shopwithme082</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@shopwithmee_xx</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@silentforever92</t>
   </si>
   <si>
@@ -577,6 +721,9 @@
     <t>https://www.tiktok.com/@styled388</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@supersparklyunicorn67</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@sylhetimumukworld</t>
   </si>
   <si>
@@ -598,18 +745,33 @@
     <t>https://www.tiktok.com/@tinae38</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@tink4526</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@todobablog</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@tony03672</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@train_post</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@trendorav7</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@trip.tailors</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@user24484259047033</t>
   </si>
   <si>
     <t>https://www.tiktok.com/@user8008669545474</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@usernamexxxxxxx04</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@vision.rift</t>
   </si>
   <si>
@@ -619,9 +781,18 @@
     <t>https://www.tiktok.com/@waq78690</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@weinidigital</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@whitneyrianebeautycare</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@whittlos</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@wideawakebookclub</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@winniesnwoofs</t>
   </si>
   <si>
@@ -637,6 +808,9 @@
     <t>https://www.tiktok.com/@zaheersheikh786</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@zainayaa_</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@zembii</t>
   </si>
   <si>
@@ -685,18 +859,27 @@
     <t>Household Appliances, Kitchenware, Toys &amp; Hobbies</t>
   </si>
   <si>
+    <t>Advent Teas of Joy</t>
+  </si>
+  <si>
     <t>Green Burner</t>
   </si>
   <si>
     <t>Ashwagandha Coffee</t>
   </si>
   <si>
+    <t>Hibiscus, Spearmint</t>
+  </si>
+  <si>
     <t>Ashwagandha Coffee, Green Burner, Gut Shift, Turmeric Curcumin</t>
   </si>
   <si>
     <t>Ashwagandha Coffee, Green Burner</t>
   </si>
   <si>
+    <t>Green Burner, Gut Shift, Skin Radiance, Turmeric Curcumin</t>
+  </si>
+  <si>
     <t>Ashwagandha Capsules, Ashwagandha Coffee, Green Burner, Gut Shift, Hibiscus, Spearmint, Turmeric Curcumin</t>
   </si>
   <si>
@@ -709,19 +892,19 @@
     <t>Ashwagandha Coffee, Green Burner, Gut Shift, Skin Radiance</t>
   </si>
   <si>
-    <t>Advent Teas of Joy</t>
-  </si>
-  <si>
     <t>Turmeric Curcumin</t>
   </si>
   <si>
+    <t>Spearmint</t>
+  </si>
+  <si>
+    <t>seller</t>
+  </si>
+  <si>
     <t>TikTok Shop (FBT)</t>
   </si>
   <si>
     <t>TikTok Shop (FBT), seller</t>
-  </si>
-  <si>
-    <t>seller</t>
   </si>
   <si>
     <t>No</t>
@@ -1102,7 +1285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y93"/>
+  <dimension ref="A1:Y122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1187,31 +1370,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I2" t="s">
-        <v>213</v>
+        <v>146</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>223</v>
+        <v>281</v>
       </c>
       <c r="O2" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P2" s="3">
-        <v>46028.62637731482</v>
+        <v>46323.76717592592</v>
       </c>
       <c r="Q2" s="3">
-        <v>46028.62637731482</v>
+        <v>46323.76717592592</v>
       </c>
       <c r="R2">
-        <v>5.64</v>
+        <v>6.04</v>
       </c>
       <c r="S2" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1219,31 +1399,31 @@
         <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="I3" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="O3" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P3" s="3">
-        <v>45998.88378472222</v>
+        <v>46028.62637731482</v>
       </c>
       <c r="Q3" s="3">
-        <v>45998.88378472222</v>
+        <v>46028.62637731482</v>
       </c>
       <c r="R3">
-        <v>9.31</v>
+        <v>5.64</v>
       </c>
       <c r="S3" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1251,31 +1431,31 @@
         <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="I4" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O4" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P4" s="3">
-        <v>45986.77690972222</v>
+        <v>45998.88378472222</v>
       </c>
       <c r="Q4" s="3">
-        <v>45986.77690972222</v>
+        <v>45998.88378472222</v>
       </c>
       <c r="R4">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S4" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1283,28 +1463,28 @@
         <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O5" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P5" s="3">
-        <v>46322.69690972222</v>
+        <v>46324.30358796296</v>
       </c>
       <c r="Q5" s="3">
-        <v>46322.69690972222</v>
+        <v>46324.30358796296</v>
       </c>
       <c r="R5">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S5" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1312,31 +1492,31 @@
         <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="I6" t="s">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="M6">
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O6" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P6" s="3">
-        <v>45911.17809027778</v>
+        <v>45986.77690972222</v>
       </c>
       <c r="Q6" s="3">
-        <v>45911.17809027778</v>
+        <v>45986.77690972222</v>
       </c>
       <c r="R6">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S6" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1344,52 +1524,28 @@
         <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" t="s">
-        <v>209</v>
-      </c>
-      <c r="F7" t="s">
-        <v>210</v>
-      </c>
-      <c r="G7" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" t="s">
-        <v>212</v>
-      </c>
-      <c r="I7" t="s">
-        <v>215</v>
-      </c>
-      <c r="J7" t="s">
-        <v>221</v>
-      </c>
-      <c r="K7" t="s">
-        <v>222</v>
-      </c>
-      <c r="L7" t="s">
-        <v>221</v>
+        <v>151</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O7" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P7" s="3">
-        <v>45989.98658564815</v>
+        <v>46323.27328703704</v>
       </c>
       <c r="Q7" s="3">
-        <v>45989.98658564815</v>
+        <v>46323.27328703704</v>
       </c>
       <c r="R7">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S7" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1397,31 +1553,31 @@
         <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="I8" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O8" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P8" s="3">
-        <v>45974.46635416667</v>
+        <v>45911.17809027778</v>
       </c>
       <c r="Q8" s="3">
-        <v>45974.46635416667</v>
+        <v>45911.17809027778</v>
       </c>
       <c r="R8">
         <v>9.31</v>
       </c>
       <c r="S8" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1429,31 +1585,28 @@
         <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I9" t="s">
-        <v>214</v>
+        <v>153</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O9" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P9" s="3">
-        <v>45967.48326388889</v>
+        <v>46324.30358796296</v>
       </c>
       <c r="Q9" s="3">
-        <v>45967.48326388889</v>
+        <v>46324.30358796296</v>
       </c>
       <c r="R9">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S9" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1461,31 +1614,52 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>125</v>
+        <v>154</v>
+      </c>
+      <c r="E10" t="s">
+        <v>267</v>
+      </c>
+      <c r="F10" t="s">
+        <v>268</v>
+      </c>
+      <c r="G10" t="s">
+        <v>269</v>
+      </c>
+      <c r="H10" t="s">
+        <v>270</v>
       </c>
       <c r="I10" t="s">
-        <v>216</v>
+        <v>273</v>
+      </c>
+      <c r="J10" t="s">
+        <v>279</v>
+      </c>
+      <c r="K10" t="s">
+        <v>280</v>
+      </c>
+      <c r="L10" t="s">
+        <v>279</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O10" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P10" s="3">
-        <v>46176.59099537037</v>
+        <v>45989.98658564815</v>
       </c>
       <c r="Q10" s="3">
-        <v>46176.59099537037</v>
+        <v>45989.98658564815</v>
       </c>
       <c r="R10">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S10" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1493,31 +1667,31 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="I11" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="M11">
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O11" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P11" s="3">
-        <v>45996.23743055556</v>
+        <v>45974.46635416667</v>
       </c>
       <c r="Q11" s="3">
-        <v>45996.23743055556</v>
+        <v>45974.46635416667</v>
       </c>
       <c r="R11">
-        <v>12.46</v>
+        <v>9.31</v>
       </c>
       <c r="S11" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1525,31 +1699,28 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I12" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O12" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P12" s="3">
-        <v>46209.78530092593</v>
+        <v>46324.30358796296</v>
       </c>
       <c r="Q12" s="3">
-        <v>46209.78530092593</v>
+        <v>46324.30358796296</v>
       </c>
       <c r="R12">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S12" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1557,31 +1728,31 @@
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="I13" t="s">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O13" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P13" s="3">
-        <v>46092.52502314815</v>
+        <v>45967.48326388889</v>
       </c>
       <c r="Q13" s="3">
-        <v>46092.52502314815</v>
+        <v>45967.48326388889</v>
       </c>
       <c r="R13">
         <v>5.69</v>
       </c>
       <c r="S13" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1589,46 +1760,46 @@
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="M14">
         <v>2</v>
       </c>
       <c r="N14" t="s">
-        <v>225</v>
+        <v>284</v>
       </c>
       <c r="O14" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="P14" s="3">
-        <v>46296.61392361111</v>
+        <v>46324.35034722222</v>
       </c>
       <c r="Q14" s="3">
-        <v>46296.61392361111</v>
+        <v>46324.3503587963</v>
       </c>
       <c r="R14">
-        <v>26.83</v>
+        <v>9.59</v>
       </c>
       <c r="S14" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>172.23</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>227</v>
+        <v>3683</v>
       </c>
       <c r="X14" s="3">
-        <v>46303</v>
+        <v>46314</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1636,28 +1807,31 @@
         <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>130</v>
+        <v>159</v>
+      </c>
+      <c r="I15" t="s">
+        <v>274</v>
       </c>
       <c r="M15">
         <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O15" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P15" s="3">
-        <v>46196.83574074074</v>
+        <v>46176.59099537037</v>
       </c>
       <c r="Q15" s="3">
-        <v>46196.83574074074</v>
+        <v>46176.59099537037</v>
       </c>
       <c r="R15">
         <v>5.69</v>
       </c>
       <c r="S15" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1665,31 +1839,31 @@
         <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="I16" t="s">
-        <v>217</v>
+        <v>271</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O16" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P16" s="3">
-        <v>46198.6271412037</v>
+        <v>45996.23743055556</v>
       </c>
       <c r="Q16" s="3">
-        <v>46198.6271412037</v>
+        <v>45996.23743055556</v>
       </c>
       <c r="R16">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S16" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1697,31 +1871,31 @@
         <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="I17" t="s">
-        <v>214</v>
+        <v>272</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
       <c r="O17" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="P17" s="3">
-        <v>45840.45584490741</v>
+        <v>46209.78530092593</v>
       </c>
       <c r="Q17" s="3">
-        <v>46170.61114583333</v>
+        <v>46209.78530092593</v>
       </c>
       <c r="R17">
-        <v>17.02</v>
+        <v>5.69</v>
       </c>
       <c r="S17" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1729,31 +1903,28 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I18" t="s">
-        <v>215</v>
+        <v>162</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O18" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P18" s="3">
-        <v>46198.6271412037</v>
+        <v>46324.49521990741</v>
       </c>
       <c r="Q18" s="3">
-        <v>46198.6271412037</v>
+        <v>46324.49521990741</v>
       </c>
       <c r="R18">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S18" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1761,46 +1932,31 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>134</v>
+        <v>163</v>
+      </c>
+      <c r="I19" t="s">
+        <v>273</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O19" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P19" s="3">
-        <v>46309.55629629629</v>
+        <v>46092.52502314815</v>
       </c>
       <c r="Q19" s="3">
-        <v>46309.55629629629</v>
+        <v>46092.52502314815</v>
       </c>
       <c r="R19">
         <v>5.69</v>
       </c>
       <c r="S19" t="s">
-        <v>237</v>
-      </c>
-      <c r="T19">
-        <v>1</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>10</v>
-      </c>
-      <c r="X19" s="3">
-        <v>46311</v>
-      </c>
-      <c r="Y19">
-        <v>1</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1808,28 +1964,46 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="O20" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="P20" s="3">
-        <v>46252.93552083334</v>
+        <v>46296.61392361111</v>
       </c>
       <c r="Q20" s="3">
-        <v>46252.93552083334</v>
+        <v>46296.61392361111</v>
       </c>
       <c r="R20">
-        <v>5.69</v>
+        <v>26.83</v>
       </c>
       <c r="S20" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T20">
+        <v>4</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>227</v>
+      </c>
+      <c r="X20" s="3">
+        <v>46303</v>
+      </c>
+      <c r="Y20">
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -1837,31 +2011,28 @@
         <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I21" t="s">
-        <v>218</v>
+        <v>165</v>
       </c>
       <c r="M21">
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O21" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P21" s="3">
-        <v>46062.02391203704</v>
+        <v>46196.83574074074</v>
       </c>
       <c r="Q21" s="3">
-        <v>46062.02391203704</v>
+        <v>46196.83574074074</v>
       </c>
       <c r="R21">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S21" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -1869,31 +2040,31 @@
         <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="I22" t="s">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O22" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P22" s="3">
-        <v>45903.0252662037</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="Q22" s="3">
-        <v>45903.0252662037</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="R22">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S22" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -1901,31 +2072,31 @@
         <v>46</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="I23" t="s">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N23" t="s">
-        <v>224</v>
+        <v>286</v>
       </c>
       <c r="O23" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="P23" s="3">
-        <v>46178.95283564815</v>
+        <v>45840.45584490741</v>
       </c>
       <c r="Q23" s="3">
-        <v>46178.95283564815</v>
+        <v>46170.61114583333</v>
       </c>
       <c r="R23">
-        <v>5.69</v>
+        <v>17.02</v>
       </c>
       <c r="S23" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -1933,31 +2104,31 @@
         <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="I24" t="s">
-        <v>217</v>
+        <v>273</v>
       </c>
       <c r="M24">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="O24" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="P24" s="3">
-        <v>46181.5243287037</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="Q24" s="3">
-        <v>46253.65496527778</v>
+        <v>46198.6271412037</v>
       </c>
       <c r="R24">
-        <v>60.34</v>
+        <v>5.69</v>
       </c>
       <c r="S24" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -1965,28 +2136,46 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="M25">
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O25" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P25" s="3">
-        <v>46053.63612268519</v>
+        <v>46309.55629629629</v>
       </c>
       <c r="Q25" s="3">
-        <v>46053.63612268519</v>
+        <v>46309.55629629629</v>
       </c>
       <c r="R25">
         <v>5.69</v>
       </c>
       <c r="S25" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>10</v>
+      </c>
+      <c r="X25" s="3">
+        <v>46311</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -1994,31 +2183,28 @@
         <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="I26" t="s">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O26" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P26" s="3">
-        <v>46008.62306712963</v>
+        <v>46252.93552083334</v>
       </c>
       <c r="Q26" s="3">
-        <v>46008.62306712963</v>
+        <v>46252.93552083334</v>
       </c>
       <c r="R26">
         <v>5.69</v>
       </c>
       <c r="S26" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2026,31 +2212,31 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="I27" t="s">
-        <v>218</v>
+        <v>276</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O27" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P27" s="3">
-        <v>46152.90292824074</v>
+        <v>46062.02391203704</v>
       </c>
       <c r="Q27" s="3">
-        <v>46152.90292824074</v>
+        <v>46062.02391203704</v>
       </c>
       <c r="R27">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S27" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2058,31 +2244,31 @@
         <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="I28" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="M28">
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O28" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P28" s="3">
-        <v>45953.84554398148</v>
+        <v>45903.0252662037</v>
       </c>
       <c r="Q28" s="3">
-        <v>45953.84554398148</v>
+        <v>45903.0252662037</v>
       </c>
       <c r="R28">
-        <v>12.46</v>
+        <v>9.31</v>
       </c>
       <c r="S28" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2090,46 +2276,28 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="M29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N29" t="s">
-        <v>224</v>
+        <v>287</v>
       </c>
       <c r="O29" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="P29" s="3">
-        <v>46310.5215625</v>
+        <v>46323.27358796296</v>
       </c>
       <c r="Q29" s="3">
-        <v>46310.5215625</v>
+        <v>46323.27359953704</v>
       </c>
       <c r="R29">
-        <v>5.69</v>
+        <v>28.05</v>
       </c>
       <c r="S29" t="s">
-        <v>237</v>
-      </c>
-      <c r="T29">
-        <v>7</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>207</v>
-      </c>
-      <c r="X29" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y29">
-        <v>2</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2137,31 +2305,31 @@
         <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I30" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="M30">
         <v>1</v>
       </c>
       <c r="N30" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O30" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P30" s="3">
-        <v>46111.64181712963</v>
+        <v>46178.95283564815</v>
       </c>
       <c r="Q30" s="3">
-        <v>46111.64181712963</v>
+        <v>46178.95283564815</v>
       </c>
       <c r="R30">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="S30" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2169,46 +2337,28 @@
         <v>54</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>223</v>
+        <v>283</v>
       </c>
       <c r="O31" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P31" s="3">
-        <v>46296.45141203704</v>
+        <v>46323.70123842593</v>
       </c>
       <c r="Q31" s="3">
-        <v>46296.45141203704</v>
+        <v>46323.70123842593</v>
       </c>
       <c r="R31">
-        <v>5.64</v>
+        <v>9.31</v>
       </c>
       <c r="S31" t="s">
-        <v>237</v>
-      </c>
-      <c r="T31">
-        <v>1</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>9</v>
-      </c>
-      <c r="X31" s="3">
-        <v>46298</v>
-      </c>
-      <c r="Y31">
-        <v>1</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2216,31 +2366,31 @@
         <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="I32" t="s">
-        <v>214</v>
+        <v>275</v>
       </c>
       <c r="M32">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N32" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="O32" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="P32" s="3">
-        <v>46210.48171296297</v>
+        <v>46181.5243287037</v>
       </c>
       <c r="Q32" s="3">
-        <v>46210.48171296297</v>
+        <v>46253.65496527778</v>
       </c>
       <c r="R32">
-        <v>5.69</v>
+        <v>60.34</v>
       </c>
       <c r="S32" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2248,46 +2398,28 @@
         <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="M33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="O33" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="P33" s="3">
-        <v>46280.49378472222</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="Q33" s="3">
-        <v>46280.49379629629</v>
+        <v>46053.63612268519</v>
       </c>
       <c r="R33">
-        <v>10.55</v>
+        <v>5.69</v>
       </c>
       <c r="S33" t="s">
-        <v>237</v>
-      </c>
-      <c r="T33">
-        <v>4</v>
-      </c>
-      <c r="U33">
-        <v>19.91</v>
-      </c>
-      <c r="V33">
-        <v>2</v>
-      </c>
-      <c r="W33">
-        <v>689</v>
-      </c>
-      <c r="X33" s="3">
-        <v>46281</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -2295,31 +2427,31 @@
         <v>57</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="I34" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O34" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P34" s="3">
-        <v>46225.98408564815</v>
+        <v>46008.62306712963</v>
       </c>
       <c r="Q34" s="3">
-        <v>46225.98408564815</v>
+        <v>46008.62306712963</v>
       </c>
       <c r="R34">
         <v>5.69</v>
       </c>
       <c r="S34" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -2327,28 +2459,28 @@
         <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="M35">
         <v>1</v>
       </c>
       <c r="N35" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O35" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="P35" s="3">
-        <v>46322.49665509259</v>
+        <v>46323.58881944444</v>
       </c>
       <c r="Q35" s="3">
-        <v>46322.49665509259</v>
+        <v>46323.58881944444</v>
       </c>
       <c r="R35">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S35" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -2356,31 +2488,31 @@
         <v>59</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="I36" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="M36">
         <v>1</v>
       </c>
       <c r="N36" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O36" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P36" s="3">
-        <v>46106.56184027778</v>
+        <v>46152.90292824074</v>
       </c>
       <c r="Q36" s="3">
-        <v>46106.56184027778</v>
+        <v>46152.90292824074</v>
       </c>
       <c r="R36">
         <v>5.69</v>
       </c>
       <c r="S36" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -2388,28 +2520,31 @@
         <v>60</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>152</v>
+        <v>181</v>
+      </c>
+      <c r="I37" t="s">
+        <v>272</v>
       </c>
       <c r="M37">
         <v>1</v>
       </c>
       <c r="N37" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O37" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="P37" s="3">
-        <v>46313.79324074074</v>
+        <v>45953.84554398148</v>
       </c>
       <c r="Q37" s="3">
-        <v>46313.79324074074</v>
+        <v>45953.84554398148</v>
       </c>
       <c r="R37">
-        <v>8.58</v>
+        <v>12.46</v>
       </c>
       <c r="S37" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -2417,31 +2552,46 @@
         <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I38" t="s">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="M38">
         <v>1</v>
       </c>
       <c r="N38" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O38" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P38" s="3">
-        <v>46196.84141203704</v>
+        <v>46310.5215625</v>
       </c>
       <c r="Q38" s="3">
-        <v>46196.84141203704</v>
+        <v>46310.5215625</v>
       </c>
       <c r="R38">
         <v>5.69</v>
       </c>
       <c r="S38" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T38">
+        <v>7</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>206</v>
+      </c>
+      <c r="X38" s="3">
+        <v>46313</v>
+      </c>
+      <c r="Y38">
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -2449,28 +2599,31 @@
         <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>154</v>
+        <v>183</v>
+      </c>
+      <c r="I39" t="s">
+        <v>271</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39" t="s">
-        <v>229</v>
+        <v>283</v>
       </c>
       <c r="O39" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="P39" s="3">
-        <v>46312.81608796296</v>
+        <v>46111.64181712963</v>
       </c>
       <c r="Q39" s="3">
-        <v>46313.7452662037</v>
+        <v>46111.64181712963</v>
       </c>
       <c r="R39">
-        <v>14.62</v>
+        <v>12.46</v>
       </c>
       <c r="S39" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -2478,31 +2631,46 @@
         <v>63</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I40" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="M40">
         <v>1</v>
       </c>
       <c r="N40" t="s">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="O40" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P40" s="3">
-        <v>46073.66815972222</v>
+        <v>46296.45141203704</v>
       </c>
       <c r="Q40" s="3">
-        <v>46073.66815972222</v>
+        <v>46296.45141203704</v>
       </c>
       <c r="R40">
-        <v>12.46</v>
+        <v>5.64</v>
       </c>
       <c r="S40" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>9</v>
+      </c>
+      <c r="X40" s="3">
+        <v>46298</v>
+      </c>
+      <c r="Y40">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -2510,49 +2678,31 @@
         <v>64</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="I41" t="s">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="M41">
         <v>1</v>
       </c>
       <c r="N41" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O41" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P41" s="3">
-        <v>46245.82854166667</v>
+        <v>46210.48171296297</v>
       </c>
       <c r="Q41" s="3">
-        <v>46245.82854166667</v>
+        <v>46210.48171296297</v>
       </c>
       <c r="R41">
         <v>5.69</v>
       </c>
       <c r="S41" t="s">
-        <v>237</v>
-      </c>
-      <c r="T41">
-        <v>1</v>
-      </c>
-      <c r="U41">
-        <v>0</v>
-      </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <v>18</v>
-      </c>
-      <c r="X41" s="3">
-        <v>46262</v>
-      </c>
-      <c r="Y41">
-        <v>16</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -2560,31 +2710,46 @@
         <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I42" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="M42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" t="s">
-        <v>224</v>
+        <v>289</v>
       </c>
       <c r="O42" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="P42" s="3">
-        <v>46050.93159722222</v>
+        <v>46280.49378472222</v>
       </c>
       <c r="Q42" s="3">
-        <v>46050.93159722222</v>
+        <v>46280.49379629629</v>
       </c>
       <c r="R42">
-        <v>12.46</v>
+        <v>10.55</v>
       </c>
       <c r="S42" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T42">
+        <v>4</v>
+      </c>
+      <c r="U42">
+        <v>19.91</v>
+      </c>
+      <c r="V42">
+        <v>2</v>
+      </c>
+      <c r="W42">
+        <v>689</v>
+      </c>
+      <c r="X42" s="3">
+        <v>46281</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -2592,31 +2757,31 @@
         <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="I43" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O43" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P43" s="3">
-        <v>45965.93854166667</v>
+        <v>46225.98408564815</v>
       </c>
       <c r="Q43" s="3">
-        <v>45965.93854166667</v>
+        <v>46225.98408564815</v>
       </c>
       <c r="R43">
         <v>5.69</v>
       </c>
       <c r="S43" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -2624,31 +2789,31 @@
         <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="I44" t="s">
-        <v>214</v>
+        <v>272</v>
       </c>
       <c r="M44">
         <v>1</v>
       </c>
       <c r="N44" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O44" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P44" s="3">
-        <v>45992.89240740741</v>
+        <v>46106.56184027778</v>
       </c>
       <c r="Q44" s="3">
-        <v>45992.89240740741</v>
+        <v>46106.56184027778</v>
       </c>
       <c r="R44">
         <v>5.69</v>
       </c>
       <c r="S44" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -2656,31 +2821,28 @@
         <v>68</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="I45" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="M45">
         <v>1</v>
       </c>
       <c r="N45" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O45" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P45" s="3">
-        <v>45944.90217592593</v>
+        <v>46324.02732638889</v>
       </c>
       <c r="Q45" s="3">
-        <v>45944.90217592593</v>
+        <v>46324.02732638889</v>
       </c>
       <c r="R45">
-        <v>9.31</v>
+        <v>6.04</v>
       </c>
       <c r="S45" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -2688,31 +2850,28 @@
         <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I46" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
       <c r="N46" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O46" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P46" s="3">
-        <v>46105.47987268519</v>
+        <v>46313.79324074074</v>
       </c>
       <c r="Q46" s="3">
-        <v>46105.47987268519</v>
+        <v>46313.79324074074</v>
       </c>
       <c r="R46">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S46" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -2720,31 +2879,31 @@
         <v>70</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="I47" t="s">
-        <v>218</v>
+        <v>276</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O47" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P47" s="3">
-        <v>46210.50420138889</v>
+        <v>46196.84141203704</v>
       </c>
       <c r="Q47" s="3">
-        <v>46210.50420138889</v>
+        <v>46196.84141203704</v>
       </c>
       <c r="R47">
         <v>5.69</v>
       </c>
       <c r="S47" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="48" spans="1:25">
@@ -2752,28 +2911,28 @@
         <v>71</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="M48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N48" t="s">
-        <v>224</v>
+        <v>290</v>
       </c>
       <c r="O48" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P48" s="3">
-        <v>46052.56390046296</v>
+        <v>46312.81608796296</v>
       </c>
       <c r="Q48" s="3">
-        <v>46052.56390046296</v>
+        <v>46313.7452662037</v>
       </c>
       <c r="R48">
-        <v>5.69</v>
+        <v>14.62</v>
       </c>
       <c r="S48" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="49" spans="1:25">
@@ -2781,31 +2940,28 @@
         <v>72</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I49" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="M49">
         <v>1</v>
       </c>
       <c r="N49" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O49" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P49" s="3">
-        <v>46091.88748842593</v>
+        <v>46324.30361111111</v>
       </c>
       <c r="Q49" s="3">
-        <v>46091.88748842593</v>
+        <v>46324.30361111111</v>
       </c>
       <c r="R49">
-        <v>9.31</v>
+        <v>6.04</v>
       </c>
       <c r="S49" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="50" spans="1:25">
@@ -2813,31 +2969,31 @@
         <v>73</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="I50" t="s">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="M50">
         <v>1</v>
       </c>
       <c r="N50" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O50" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P50" s="3">
-        <v>45978.69265046297</v>
+        <v>46073.66815972222</v>
       </c>
       <c r="Q50" s="3">
-        <v>45978.69265046297</v>
+        <v>46073.66815972222</v>
       </c>
       <c r="R50">
         <v>12.46</v>
       </c>
       <c r="S50" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="51" spans="1:25">
@@ -2845,31 +3001,49 @@
         <v>74</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="I51" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="M51">
         <v>1</v>
       </c>
       <c r="N51" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O51" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P51" s="3">
-        <v>45919.81163194445</v>
+        <v>46245.82854166667</v>
       </c>
       <c r="Q51" s="3">
-        <v>45919.81163194445</v>
+        <v>46245.82854166667</v>
       </c>
       <c r="R51">
         <v>5.69</v>
       </c>
       <c r="S51" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T51">
+        <v>1</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>6</v>
+      </c>
+      <c r="X51" s="3">
+        <v>46263</v>
+      </c>
+      <c r="Y51">
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:25">
@@ -2877,46 +3051,28 @@
         <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="M52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N52" t="s">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="O52" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="P52" s="3">
-        <v>46313.77442129629</v>
+        <v>46324.34166666667</v>
       </c>
       <c r="Q52" s="3">
-        <v>46314.78831018518</v>
+        <v>46324.34166666667</v>
       </c>
       <c r="R52">
-        <v>30.1</v>
+        <v>6.04</v>
       </c>
       <c r="S52" t="s">
-        <v>237</v>
-      </c>
-      <c r="T52">
-        <v>1</v>
-      </c>
-      <c r="U52">
-        <v>0</v>
-      </c>
-      <c r="V52">
-        <v>0</v>
-      </c>
-      <c r="W52">
-        <v>11</v>
-      </c>
-      <c r="X52" s="3">
-        <v>46320</v>
-      </c>
-      <c r="Y52">
-        <v>6</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:25">
@@ -2924,46 +3080,31 @@
         <v>76</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>168</v>
+        <v>197</v>
+      </c>
+      <c r="I53" t="s">
+        <v>272</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53" t="s">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="O53" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="P53" s="3">
-        <v>46314.50759259259</v>
+        <v>46050.93159722222</v>
       </c>
       <c r="Q53" s="3">
-        <v>46314.50759259259</v>
+        <v>46050.93159722222</v>
       </c>
       <c r="R53">
-        <v>6.04</v>
+        <v>12.46</v>
       </c>
       <c r="S53" t="s">
-        <v>237</v>
-      </c>
-      <c r="T53">
-        <v>3</v>
-      </c>
-      <c r="U53">
-        <v>20.03</v>
-      </c>
-      <c r="V53">
-        <v>2</v>
-      </c>
-      <c r="W53">
-        <v>537</v>
-      </c>
-      <c r="X53" s="3">
-        <v>46313</v>
-      </c>
-      <c r="Y53">
-        <v>-2</v>
+        <v>297</v>
       </c>
     </row>
     <row r="54" spans="1:25">
@@ -2971,31 +3112,28 @@
         <v>77</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I54" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="M54">
         <v>1</v>
       </c>
       <c r="N54" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O54" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P54" s="3">
-        <v>46051.04447916667</v>
+        <v>46324.02732638889</v>
       </c>
       <c r="Q54" s="3">
-        <v>46051.04447916667</v>
+        <v>46324.02732638889</v>
       </c>
       <c r="R54">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S54" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" spans="1:25">
@@ -3003,31 +3141,28 @@
         <v>78</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="I55" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O55" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P55" s="3">
-        <v>45891.71650462963</v>
+        <v>46324.30662037037</v>
       </c>
       <c r="Q55" s="3">
-        <v>45891.71650462963</v>
+        <v>46324.30662037037</v>
       </c>
       <c r="R55">
-        <v>9.31</v>
+        <v>6.04</v>
       </c>
       <c r="S55" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="1:25">
@@ -3035,31 +3170,31 @@
         <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="I56" t="s">
-        <v>213</v>
+        <v>276</v>
       </c>
       <c r="M56">
         <v>1</v>
       </c>
       <c r="N56" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O56" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P56" s="3">
-        <v>46211.60210648148</v>
+        <v>45965.93854166667</v>
       </c>
       <c r="Q56" s="3">
-        <v>46211.60210648148</v>
+        <v>45965.93854166667</v>
       </c>
       <c r="R56">
         <v>5.69</v>
       </c>
       <c r="S56" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:25">
@@ -3067,31 +3202,31 @@
         <v>80</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="I57" t="s">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="M57">
         <v>1</v>
       </c>
       <c r="N57" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O57" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P57" s="3">
-        <v>46167.36722222222</v>
+        <v>45992.89240740741</v>
       </c>
       <c r="Q57" s="3">
-        <v>46167.36722222222</v>
+        <v>45992.89240740741</v>
       </c>
       <c r="R57">
         <v>5.69</v>
       </c>
       <c r="S57" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" spans="1:25">
@@ -3099,31 +3234,31 @@
         <v>81</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="I58" t="s">
-        <v>218</v>
+        <v>278</v>
       </c>
       <c r="M58">
         <v>1</v>
       </c>
       <c r="N58" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O58" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P58" s="3">
-        <v>46050.54237268519</v>
+        <v>45944.90217592593</v>
       </c>
       <c r="Q58" s="3">
-        <v>46050.54237268519</v>
+        <v>45944.90217592593</v>
       </c>
       <c r="R58">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S58" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" spans="1:25">
@@ -3131,31 +3266,31 @@
         <v>82</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="I59" t="s">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="M59">
         <v>1</v>
       </c>
       <c r="N59" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O59" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P59" s="3">
-        <v>45957.49894675926</v>
+        <v>46105.47987268519</v>
       </c>
       <c r="Q59" s="3">
-        <v>45957.49894675926</v>
+        <v>46105.47987268519</v>
       </c>
       <c r="R59">
         <v>5.69</v>
       </c>
       <c r="S59" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="1:25">
@@ -3163,31 +3298,28 @@
         <v>83</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I60" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="M60">
         <v>1</v>
       </c>
       <c r="N60" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O60" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P60" s="3">
-        <v>46196.62574074074</v>
+        <v>46323.41782407407</v>
       </c>
       <c r="Q60" s="3">
-        <v>46196.62574074074</v>
+        <v>46323.41782407407</v>
       </c>
       <c r="R60">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S60" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="61" spans="1:25">
@@ -3195,31 +3327,31 @@
         <v>84</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="I61" t="s">
-        <v>215</v>
+        <v>276</v>
       </c>
       <c r="M61">
         <v>1</v>
       </c>
       <c r="N61" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O61" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P61" s="3">
-        <v>45959.6512037037</v>
+        <v>46210.50420138889</v>
       </c>
       <c r="Q61" s="3">
-        <v>45959.6512037037</v>
+        <v>46210.50420138889</v>
       </c>
       <c r="R61">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S61" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="62" spans="1:25">
@@ -3227,31 +3359,28 @@
         <v>85</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I62" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="M62">
         <v>1</v>
       </c>
       <c r="N62" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O62" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P62" s="3">
-        <v>45973.56506944444</v>
+        <v>46052.56390046296</v>
       </c>
       <c r="Q62" s="3">
-        <v>45973.56506944444</v>
+        <v>46052.56390046296</v>
       </c>
       <c r="R62">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S62" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:25">
@@ -3259,46 +3388,31 @@
         <v>86</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>178</v>
+        <v>207</v>
+      </c>
+      <c r="I63" t="s">
+        <v>273</v>
       </c>
       <c r="M63">
         <v>1</v>
       </c>
       <c r="N63" t="s">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="O63" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="P63" s="3">
-        <v>46313.49944444445</v>
+        <v>46091.88748842593</v>
       </c>
       <c r="Q63" s="3">
-        <v>46313.49944444445</v>
+        <v>46091.88748842593</v>
       </c>
       <c r="R63">
-        <v>6.04</v>
+        <v>9.31</v>
       </c>
       <c r="S63" t="s">
-        <v>237</v>
-      </c>
-      <c r="T63">
-        <v>1</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
-        <v>19</v>
-      </c>
-      <c r="X63" s="3">
-        <v>46321</v>
-      </c>
-      <c r="Y63">
-        <v>7</v>
+        <v>297</v>
       </c>
     </row>
     <row r="64" spans="1:25">
@@ -3306,31 +3420,31 @@
         <v>87</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="I64" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="M64">
         <v>1</v>
       </c>
       <c r="N64" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O64" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P64" s="3">
-        <v>46191.82362268519</v>
+        <v>45978.69265046297</v>
       </c>
       <c r="Q64" s="3">
-        <v>46191.82362268519</v>
+        <v>45978.69265046297</v>
       </c>
       <c r="R64">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="S64" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:25">
@@ -3338,46 +3452,31 @@
         <v>88</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>180</v>
+        <v>209</v>
+      </c>
+      <c r="I65" t="s">
+        <v>272</v>
       </c>
       <c r="M65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N65" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
       <c r="O65" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="P65" s="3">
-        <v>46286.62572916667</v>
+        <v>45919.81163194445</v>
       </c>
       <c r="Q65" s="3">
-        <v>46306.5500462963</v>
+        <v>45919.81163194445</v>
       </c>
       <c r="R65">
-        <v>14.22</v>
+        <v>5.69</v>
       </c>
       <c r="S65" t="s">
-        <v>237</v>
-      </c>
-      <c r="T65">
-        <v>2</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>32</v>
-      </c>
-      <c r="X65" s="3">
-        <v>46297</v>
-      </c>
-      <c r="Y65">
-        <v>10</v>
+        <v>297</v>
       </c>
     </row>
     <row r="66" spans="1:25">
@@ -3385,28 +3484,28 @@
         <v>89</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="M66">
         <v>1</v>
       </c>
       <c r="N66" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O66" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P66" s="3">
-        <v>46304.50560185185</v>
+        <v>46323.27350694445</v>
       </c>
       <c r="Q66" s="3">
-        <v>46304.50560185185</v>
+        <v>46323.27350694445</v>
       </c>
       <c r="R66">
         <v>5.69</v>
       </c>
       <c r="S66" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="67" spans="1:25">
@@ -3414,28 +3513,46 @@
         <v>90</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="M67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N67" t="s">
-        <v>224</v>
+        <v>291</v>
       </c>
       <c r="O67" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="P67" s="3">
-        <v>46027.60903935185</v>
+        <v>46313.77442129629</v>
       </c>
       <c r="Q67" s="3">
-        <v>46027.60903935185</v>
+        <v>46314.78831018518</v>
       </c>
       <c r="R67">
-        <v>5.69</v>
+        <v>30.1</v>
       </c>
       <c r="S67" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T67">
+        <v>2</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>46</v>
+      </c>
+      <c r="X67" s="3">
+        <v>46320</v>
+      </c>
+      <c r="Y67">
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:25">
@@ -3443,46 +3560,46 @@
         <v>91</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="M68">
         <v>1</v>
       </c>
       <c r="N68" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O68" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P68" s="3">
-        <v>46280.49518518519</v>
+        <v>46314.50759259259</v>
       </c>
       <c r="Q68" s="3">
-        <v>46280.49518518519</v>
+        <v>46314.50759259259</v>
       </c>
       <c r="R68">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S68" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="T68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>20.03</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W68">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="X68" s="3">
-        <v>46283</v>
+        <v>46313</v>
       </c>
       <c r="Y68">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="69" spans="1:25">
@@ -3490,28 +3607,31 @@
         <v>92</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>184</v>
+        <v>213</v>
+      </c>
+      <c r="I69" t="s">
+        <v>271</v>
       </c>
       <c r="M69">
         <v>1</v>
       </c>
       <c r="N69" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O69" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P69" s="3">
-        <v>46311.94667824074</v>
+        <v>46051.04447916667</v>
       </c>
       <c r="Q69" s="3">
-        <v>46311.94667824074</v>
+        <v>46051.04447916667</v>
       </c>
       <c r="R69">
         <v>5.69</v>
       </c>
       <c r="S69" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="70" spans="1:25">
@@ -3519,46 +3639,31 @@
         <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>185</v>
+        <v>214</v>
+      </c>
+      <c r="I70" t="s">
+        <v>271</v>
       </c>
       <c r="M70">
         <v>1</v>
       </c>
       <c r="N70" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O70" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="P70" s="3">
-        <v>46313.79785879629</v>
+        <v>45891.71650462963</v>
       </c>
       <c r="Q70" s="3">
-        <v>46313.79785879629</v>
+        <v>45891.71650462963</v>
       </c>
       <c r="R70">
-        <v>8.58</v>
+        <v>9.31</v>
       </c>
       <c r="S70" t="s">
-        <v>237</v>
-      </c>
-      <c r="T70">
-        <v>1</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-      <c r="V70">
-        <v>0</v>
-      </c>
-      <c r="W70">
-        <v>9</v>
-      </c>
-      <c r="X70" s="3">
-        <v>46317</v>
-      </c>
-      <c r="Y70">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="1:25">
@@ -3566,31 +3671,31 @@
         <v>94</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="I71" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O71" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P71" s="3">
-        <v>46198.62712962963</v>
+        <v>46211.60210648148</v>
       </c>
       <c r="Q71" s="3">
-        <v>46198.62712962963</v>
+        <v>46211.60210648148</v>
       </c>
       <c r="R71">
         <v>5.69</v>
       </c>
       <c r="S71" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="72" spans="1:25">
@@ -3598,31 +3703,31 @@
         <v>95</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="I72" t="s">
-        <v>217</v>
+        <v>273</v>
       </c>
       <c r="M72">
         <v>1</v>
       </c>
       <c r="N72" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O72" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P72" s="3">
-        <v>46212.55766203703</v>
+        <v>46167.36722222222</v>
       </c>
       <c r="Q72" s="3">
-        <v>46212.55766203703</v>
+        <v>46167.36722222222</v>
       </c>
       <c r="R72">
         <v>5.69</v>
       </c>
       <c r="S72" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="73" spans="1:25">
@@ -3630,28 +3735,31 @@
         <v>96</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>188</v>
+        <v>217</v>
+      </c>
+      <c r="I73" t="s">
+        <v>276</v>
       </c>
       <c r="M73">
         <v>1</v>
       </c>
       <c r="N73" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O73" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P73" s="3">
-        <v>46199.43622685185</v>
+        <v>46050.54237268519</v>
       </c>
       <c r="Q73" s="3">
-        <v>46199.43622685185</v>
+        <v>46050.54237268519</v>
       </c>
       <c r="R73">
         <v>5.69</v>
       </c>
       <c r="S73" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="74" spans="1:25">
@@ -3659,31 +3767,31 @@
         <v>97</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="I74" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="M74">
         <v>1</v>
       </c>
       <c r="N74" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O74" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P74" s="3">
-        <v>46211.60422453703</v>
+        <v>45957.49894675926</v>
       </c>
       <c r="Q74" s="3">
-        <v>46211.60422453703</v>
+        <v>45957.49894675926</v>
       </c>
       <c r="R74">
         <v>5.69</v>
       </c>
       <c r="S74" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="1:25">
@@ -3691,31 +3799,31 @@
         <v>98</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="I75" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="M75">
         <v>1</v>
       </c>
       <c r="N75" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O75" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P75" s="3">
-        <v>46196.76916666667</v>
+        <v>46196.62574074074</v>
       </c>
       <c r="Q75" s="3">
-        <v>46196.76916666667</v>
+        <v>46196.62574074074</v>
       </c>
       <c r="R75">
         <v>5.69</v>
       </c>
       <c r="S75" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="76" spans="1:25">
@@ -3723,31 +3831,28 @@
         <v>99</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I76" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="M76">
         <v>1</v>
       </c>
       <c r="N76" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O76" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P76" s="3">
-        <v>46198.62644675926</v>
+        <v>46324.02733796297</v>
       </c>
       <c r="Q76" s="3">
-        <v>46198.62644675926</v>
+        <v>46324.02733796297</v>
       </c>
       <c r="R76">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S76" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="77" spans="1:25">
@@ -3755,31 +3860,31 @@
         <v>100</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="I77" t="s">
-        <v>215</v>
+        <v>273</v>
       </c>
       <c r="M77">
         <v>1</v>
       </c>
       <c r="N77" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O77" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P77" s="3">
-        <v>46220.44594907408</v>
+        <v>45959.6512037037</v>
       </c>
       <c r="Q77" s="3">
-        <v>46220.44594907408</v>
+        <v>45959.6512037037</v>
       </c>
       <c r="R77">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="S77" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="78" spans="1:25">
@@ -3787,28 +3892,31 @@
         <v>101</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>193</v>
+        <v>222</v>
+      </c>
+      <c r="I78" t="s">
+        <v>271</v>
       </c>
       <c r="M78">
         <v>1</v>
       </c>
       <c r="N78" t="s">
-        <v>232</v>
+        <v>283</v>
       </c>
       <c r="O78" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="P78" s="3">
-        <v>46301.52780092593</v>
+        <v>45973.56506944444</v>
       </c>
       <c r="Q78" s="3">
-        <v>46301.52780092593</v>
+        <v>45973.56506944444</v>
       </c>
       <c r="R78">
-        <v>6.53</v>
+        <v>9.31</v>
       </c>
       <c r="S78" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="79" spans="1:25">
@@ -3816,31 +3924,28 @@
         <v>102</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I79" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="M79">
         <v>1</v>
       </c>
       <c r="N79" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O79" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P79" s="3">
-        <v>46221.54171296296</v>
+        <v>46324.30361111111</v>
       </c>
       <c r="Q79" s="3">
-        <v>46221.54171296296</v>
+        <v>46324.30361111111</v>
       </c>
       <c r="R79">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S79" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="80" spans="1:25">
@@ -3848,31 +3953,46 @@
         <v>103</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I80" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="M80">
         <v>1</v>
       </c>
       <c r="N80" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O80" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P80" s="3">
-        <v>45993.6759375</v>
+        <v>46313.49944444445</v>
       </c>
       <c r="Q80" s="3">
-        <v>45993.6759375</v>
+        <v>46313.49944444445</v>
       </c>
       <c r="R80">
-        <v>9.31</v>
+        <v>6.04</v>
       </c>
       <c r="S80" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T80">
+        <v>1</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>23</v>
+      </c>
+      <c r="X80" s="3">
+        <v>46321</v>
+      </c>
+      <c r="Y80">
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:25">
@@ -3880,31 +4000,31 @@
         <v>104</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="I81" t="s">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="M81">
         <v>1</v>
       </c>
       <c r="N81" t="s">
-        <v>223</v>
+        <v>283</v>
       </c>
       <c r="O81" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="P81" s="3">
-        <v>46178.61515046296</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="Q81" s="3">
-        <v>46178.61515046296</v>
+        <v>46191.82362268519</v>
       </c>
       <c r="R81">
-        <v>12.41</v>
+        <v>5.69</v>
       </c>
       <c r="S81" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" spans="1:25">
@@ -3912,31 +4032,46 @@
         <v>105</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I82" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="M82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N82" t="s">
-        <v>224</v>
+        <v>286</v>
       </c>
       <c r="O82" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="P82" s="3">
-        <v>45981.84152777777</v>
+        <v>46286.62572916667</v>
       </c>
       <c r="Q82" s="3">
-        <v>45981.84152777777</v>
+        <v>46306.5500462963</v>
       </c>
       <c r="R82">
-        <v>9.31</v>
+        <v>14.22</v>
       </c>
       <c r="S82" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T82">
+        <v>2</v>
+      </c>
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>32</v>
+      </c>
+      <c r="X82" s="3">
+        <v>46297</v>
+      </c>
+      <c r="Y82">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:25">
@@ -3944,31 +4079,28 @@
         <v>106</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I83" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="M83">
         <v>1</v>
       </c>
       <c r="N83" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O83" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P83" s="3">
-        <v>45965.5908449074</v>
+        <v>46323.27322916667</v>
       </c>
       <c r="Q83" s="3">
-        <v>45965.5908449074</v>
+        <v>46323.27322916667</v>
       </c>
       <c r="R83">
         <v>5.69</v>
       </c>
       <c r="S83" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="84" spans="1:25">
@@ -3976,31 +4108,28 @@
         <v>107</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="I84" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="M84">
         <v>1</v>
       </c>
       <c r="N84" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O84" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P84" s="3">
-        <v>46206.37778935185</v>
+        <v>46304.50560185185</v>
       </c>
       <c r="Q84" s="3">
-        <v>46206.37778935185</v>
+        <v>46304.50560185185</v>
       </c>
       <c r="R84">
         <v>5.69</v>
       </c>
       <c r="S84" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="85" spans="1:25">
@@ -4008,31 +4137,28 @@
         <v>108</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I85" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="M85">
         <v>1</v>
       </c>
       <c r="N85" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O85" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P85" s="3">
-        <v>46220.91548611111</v>
+        <v>46324.30361111111</v>
       </c>
       <c r="Q85" s="3">
-        <v>46220.91548611111</v>
+        <v>46324.30361111111</v>
       </c>
       <c r="R85">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S85" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="1:25">
@@ -4040,46 +4166,28 @@
         <v>109</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="M86">
         <v>1</v>
       </c>
       <c r="N86" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O86" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="P86" s="3">
-        <v>46306.55003472222</v>
+        <v>46027.60903935185</v>
       </c>
       <c r="Q86" s="3">
-        <v>46306.55003472222</v>
+        <v>46027.60903935185</v>
       </c>
       <c r="R86">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S86" t="s">
-        <v>237</v>
-      </c>
-      <c r="T86">
-        <v>2</v>
-      </c>
-      <c r="U86">
-        <v>59.99</v>
-      </c>
-      <c r="V86">
-        <v>1</v>
-      </c>
-      <c r="W86">
-        <v>946</v>
-      </c>
-      <c r="X86" s="3">
-        <v>46294</v>
-      </c>
-      <c r="Y86">
-        <v>-13</v>
+        <v>297</v>
       </c>
     </row>
     <row r="87" spans="1:25">
@@ -4087,28 +4195,46 @@
         <v>110</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
       <c r="N87" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O87" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="P87" s="3">
-        <v>46312.95512731482</v>
+        <v>46280.49518518519</v>
       </c>
       <c r="Q87" s="3">
-        <v>46312.95512731482</v>
+        <v>46280.49518518519</v>
       </c>
       <c r="R87">
-        <v>8.58</v>
+        <v>5.69</v>
       </c>
       <c r="S87" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T87">
+        <v>1</v>
+      </c>
+      <c r="U87">
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>17</v>
+      </c>
+      <c r="X87" s="3">
+        <v>46283</v>
+      </c>
+      <c r="Y87">
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:25">
@@ -4116,31 +4242,28 @@
         <v>111</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I88" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="M88">
         <v>1</v>
       </c>
       <c r="N88" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O88" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P88" s="3">
-        <v>45939.98240740741</v>
+        <v>46311.94667824074</v>
       </c>
       <c r="Q88" s="3">
-        <v>45939.98240740741</v>
+        <v>46311.94667824074</v>
       </c>
       <c r="R88">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="S88" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="89" spans="1:25">
@@ -4148,31 +4271,46 @@
         <v>112</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="I89" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="M89">
         <v>1</v>
       </c>
       <c r="N89" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O89" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P89" s="3">
-        <v>46198.62712962963</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="Q89" s="3">
-        <v>46198.62712962963</v>
+        <v>46313.79785879629</v>
       </c>
       <c r="R89">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="S89" t="s">
-        <v>236</v>
+        <v>298</v>
+      </c>
+      <c r="T89">
+        <v>1</v>
+      </c>
+      <c r="U89">
+        <v>0</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>9</v>
+      </c>
+      <c r="X89" s="3">
+        <v>46317</v>
+      </c>
+      <c r="Y89">
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:25">
@@ -4180,31 +4318,31 @@
         <v>113</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="I90" t="s">
-        <v>218</v>
+        <v>278</v>
       </c>
       <c r="M90">
         <v>1</v>
       </c>
       <c r="N90" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O90" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P90" s="3">
-        <v>45990.94167824074</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="Q90" s="3">
-        <v>45990.94167824074</v>
+        <v>46198.62712962963</v>
       </c>
       <c r="R90">
         <v>5.69</v>
       </c>
       <c r="S90" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="91" spans="1:25">
@@ -4212,31 +4350,28 @@
         <v>114</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="I91" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="M91">
         <v>1</v>
       </c>
       <c r="N91" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="O91" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P91" s="3">
-        <v>45913.74726851852</v>
+        <v>46323.33027777778</v>
       </c>
       <c r="Q91" s="3">
-        <v>45913.74726851852</v>
+        <v>46323.33027777778</v>
       </c>
       <c r="R91">
-        <v>5.69</v>
+        <v>6.04</v>
       </c>
       <c r="S91" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="92" spans="1:25">
@@ -4244,31 +4379,31 @@
         <v>115</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="I92" t="s">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="M92">
         <v>1</v>
       </c>
       <c r="N92" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="O92" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P92" s="3">
-        <v>46221.60350694445</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="Q92" s="3">
-        <v>46221.60350694445</v>
+        <v>46212.55766203703</v>
       </c>
       <c r="R92">
         <v>5.69</v>
       </c>
       <c r="S92" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="93" spans="1:25">
@@ -4276,31 +4411,938 @@
         <v>116</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="I93" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93" t="s">
+        <v>283</v>
+      </c>
+      <c r="O93" t="s">
+        <v>295</v>
+      </c>
+      <c r="P93" s="3">
+        <v>46199.43622685185</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>46199.43622685185</v>
+      </c>
+      <c r="R93">
+        <v>5.69</v>
+      </c>
+      <c r="S93" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25">
+      <c r="A94" t="s">
+        <v>117</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I94" t="s">
+        <v>271</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94" t="s">
+        <v>283</v>
+      </c>
+      <c r="O94" t="s">
+        <v>295</v>
+      </c>
+      <c r="P94" s="3">
+        <v>46211.60422453703</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>46211.60422453703</v>
+      </c>
+      <c r="R94">
+        <v>5.69</v>
+      </c>
+      <c r="S94" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25">
+      <c r="A95" t="s">
+        <v>118</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I95" t="s">
+        <v>271</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95" t="s">
+        <v>283</v>
+      </c>
+      <c r="O95" t="s">
+        <v>295</v>
+      </c>
+      <c r="P95" s="3">
+        <v>46196.76916666667</v>
+      </c>
+      <c r="Q95" s="3">
+        <v>46196.76916666667</v>
+      </c>
+      <c r="R95">
+        <v>5.69</v>
+      </c>
+      <c r="S95" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25">
+      <c r="A96" t="s">
+        <v>119</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I96" t="s">
+        <v>272</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96" t="s">
+        <v>283</v>
+      </c>
+      <c r="O96" t="s">
+        <v>295</v>
+      </c>
+      <c r="P96" s="3">
+        <v>46198.62644675926</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>46198.62644675926</v>
+      </c>
+      <c r="R96">
+        <v>5.69</v>
+      </c>
+      <c r="S96" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25">
+      <c r="A97" t="s">
+        <v>120</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I97" t="s">
+        <v>273</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97" t="s">
+        <v>283</v>
+      </c>
+      <c r="O97" t="s">
+        <v>295</v>
+      </c>
+      <c r="P97" s="3">
+        <v>46220.44594907408</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>46220.44594907408</v>
+      </c>
+      <c r="R97">
+        <v>5.69</v>
+      </c>
+      <c r="S97" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25">
+      <c r="A98" t="s">
+        <v>121</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98" t="s">
+        <v>292</v>
+      </c>
+      <c r="O98" t="s">
+        <v>294</v>
+      </c>
+      <c r="P98" s="3">
+        <v>46301.52780092593</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>46301.52780092593</v>
+      </c>
+      <c r="R98">
+        <v>6.53</v>
+      </c>
+      <c r="S98" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25">
+      <c r="A99" t="s">
+        <v>122</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99" t="s">
+        <v>281</v>
+      </c>
+      <c r="O99" t="s">
+        <v>294</v>
+      </c>
+      <c r="P99" s="3">
+        <v>46323.29621527778</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>46323.29621527778</v>
+      </c>
+      <c r="R99">
+        <v>6.04</v>
+      </c>
+      <c r="S99" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25">
+      <c r="A100" t="s">
+        <v>123</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I100" t="s">
+        <v>272</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100" t="s">
+        <v>283</v>
+      </c>
+      <c r="O100" t="s">
+        <v>295</v>
+      </c>
+      <c r="P100" s="3">
+        <v>46221.54171296296</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>46221.54171296296</v>
+      </c>
+      <c r="R100">
+        <v>5.69</v>
+      </c>
+      <c r="S100" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25">
+      <c r="A101" t="s">
+        <v>124</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I101" t="s">
+        <v>276</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101" t="s">
+        <v>283</v>
+      </c>
+      <c r="O101" t="s">
+        <v>295</v>
+      </c>
+      <c r="P101" s="3">
+        <v>45993.6759375</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>45993.6759375</v>
+      </c>
+      <c r="R101">
+        <v>9.31</v>
+      </c>
+      <c r="S101" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25">
+      <c r="A102" t="s">
+        <v>125</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="M102">
+        <v>1</v>
+      </c>
+      <c r="N102" t="s">
+        <v>281</v>
+      </c>
+      <c r="O102" t="s">
+        <v>294</v>
+      </c>
+      <c r="P102" s="3">
+        <v>46324.02732638889</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>46324.02732638889</v>
+      </c>
+      <c r="R102">
+        <v>6.04</v>
+      </c>
+      <c r="S102" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25">
+      <c r="A103" t="s">
+        <v>126</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103" t="s">
+        <v>293</v>
+      </c>
+      <c r="O103" t="s">
+        <v>294</v>
+      </c>
+      <c r="P103" s="3">
+        <v>46324.31054398148</v>
+      </c>
+      <c r="Q103" s="3">
+        <v>46324.31054398148</v>
+      </c>
+      <c r="R103">
+        <v>4.86</v>
+      </c>
+      <c r="S103" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25">
+      <c r="A104" t="s">
+        <v>127</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104" t="s">
+        <v>281</v>
+      </c>
+      <c r="O104" t="s">
+        <v>294</v>
+      </c>
+      <c r="P104" s="3">
+        <v>46324.07296296296</v>
+      </c>
+      <c r="Q104" s="3">
+        <v>46324.07296296296</v>
+      </c>
+      <c r="R104">
+        <v>6.04</v>
+      </c>
+      <c r="S104" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25">
+      <c r="A105" t="s">
+        <v>128</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="I105" t="s">
+        <v>276</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105" t="s">
+        <v>282</v>
+      </c>
+      <c r="O105" t="s">
+        <v>294</v>
+      </c>
+      <c r="P105" s="3">
+        <v>46178.61515046296</v>
+      </c>
+      <c r="Q105" s="3">
+        <v>46178.61515046296</v>
+      </c>
+      <c r="R105">
+        <v>12.41</v>
+      </c>
+      <c r="S105" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25">
+      <c r="A106" t="s">
+        <v>129</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I106" t="s">
+        <v>271</v>
+      </c>
+      <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="N106" t="s">
+        <v>283</v>
+      </c>
+      <c r="O106" t="s">
+        <v>295</v>
+      </c>
+      <c r="P106" s="3">
+        <v>45981.84152777777</v>
+      </c>
+      <c r="Q106" s="3">
+        <v>45981.84152777777</v>
+      </c>
+      <c r="R106">
+        <v>9.31</v>
+      </c>
+      <c r="S106" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25">
+      <c r="A107" t="s">
+        <v>130</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107" t="s">
+        <v>281</v>
+      </c>
+      <c r="O107" t="s">
+        <v>294</v>
+      </c>
+      <c r="P107" s="3">
+        <v>46323.57241898148</v>
+      </c>
+      <c r="Q107" s="3">
+        <v>46323.57241898148</v>
+      </c>
+      <c r="R107">
+        <v>6.04</v>
+      </c>
+      <c r="S107" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25">
+      <c r="A108" t="s">
+        <v>131</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I108" t="s">
+        <v>273</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108" t="s">
+        <v>283</v>
+      </c>
+      <c r="O108" t="s">
+        <v>295</v>
+      </c>
+      <c r="P108" s="3">
+        <v>45965.5908449074</v>
+      </c>
+      <c r="Q108" s="3">
+        <v>45965.5908449074</v>
+      </c>
+      <c r="R108">
+        <v>5.69</v>
+      </c>
+      <c r="S108" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25">
+      <c r="A109" t="s">
+        <v>132</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I109" t="s">
+        <v>276</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109" t="s">
+        <v>283</v>
+      </c>
+      <c r="O109" t="s">
+        <v>295</v>
+      </c>
+      <c r="P109" s="3">
+        <v>46206.37778935185</v>
+      </c>
+      <c r="Q109" s="3">
+        <v>46206.37778935185</v>
+      </c>
+      <c r="R109">
+        <v>5.69</v>
+      </c>
+      <c r="S109" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25">
+      <c r="A110" t="s">
+        <v>133</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I110" t="s">
+        <v>275</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110" t="s">
+        <v>283</v>
+      </c>
+      <c r="O110" t="s">
+        <v>295</v>
+      </c>
+      <c r="P110" s="3">
+        <v>46220.91548611111</v>
+      </c>
+      <c r="Q110" s="3">
+        <v>46220.91548611111</v>
+      </c>
+      <c r="R110">
+        <v>5.69</v>
+      </c>
+      <c r="S110" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25">
+      <c r="A111" t="s">
+        <v>134</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111" t="s">
+        <v>292</v>
+      </c>
+      <c r="O111" t="s">
+        <v>294</v>
+      </c>
+      <c r="P111" s="3">
+        <v>46323.27356481482</v>
+      </c>
+      <c r="Q111" s="3">
+        <v>46323.27356481482</v>
+      </c>
+      <c r="R111">
+        <v>6.53</v>
+      </c>
+      <c r="S111" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25">
+      <c r="A112" t="s">
+        <v>135</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="M112">
+        <v>1</v>
+      </c>
+      <c r="N112" t="s">
+        <v>283</v>
+      </c>
+      <c r="O112" t="s">
+        <v>294</v>
+      </c>
+      <c r="P112" s="3">
+        <v>46306.55003472222</v>
+      </c>
+      <c r="Q112" s="3">
+        <v>46306.55003472222</v>
+      </c>
+      <c r="R112">
+        <v>8.58</v>
+      </c>
+      <c r="S112" t="s">
+        <v>298</v>
+      </c>
+      <c r="T112">
         <v>2</v>
       </c>
-      <c r="N93" t="s">
-        <v>224</v>
-      </c>
-      <c r="O93" t="s">
-        <v>233</v>
-      </c>
-      <c r="P93" s="3">
+      <c r="U112">
+        <v>59.99</v>
+      </c>
+      <c r="V112">
+        <v>1</v>
+      </c>
+      <c r="W112">
+        <v>946</v>
+      </c>
+      <c r="X112" s="3">
+        <v>46294</v>
+      </c>
+      <c r="Y112">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19">
+      <c r="A113" t="s">
+        <v>136</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="M113">
+        <v>1</v>
+      </c>
+      <c r="N113" t="s">
+        <v>281</v>
+      </c>
+      <c r="O113" t="s">
+        <v>294</v>
+      </c>
+      <c r="P113" s="3">
+        <v>46323.6288425926</v>
+      </c>
+      <c r="Q113" s="3">
+        <v>46323.6288425926</v>
+      </c>
+      <c r="R113">
+        <v>6.04</v>
+      </c>
+      <c r="S113" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19">
+      <c r="A114" t="s">
+        <v>137</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="M114">
+        <v>1</v>
+      </c>
+      <c r="N114" t="s">
+        <v>281</v>
+      </c>
+      <c r="O114" t="s">
+        <v>294</v>
+      </c>
+      <c r="P114" s="3">
+        <v>46324.30362268518</v>
+      </c>
+      <c r="Q114" s="3">
+        <v>46324.30362268518</v>
+      </c>
+      <c r="R114">
+        <v>6.04</v>
+      </c>
+      <c r="S114" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19">
+      <c r="A115" t="s">
+        <v>138</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115" t="s">
+        <v>283</v>
+      </c>
+      <c r="O115" t="s">
+        <v>294</v>
+      </c>
+      <c r="P115" s="3">
+        <v>46312.95512731482</v>
+      </c>
+      <c r="Q115" s="3">
+        <v>46312.95512731482</v>
+      </c>
+      <c r="R115">
+        <v>8.58</v>
+      </c>
+      <c r="S115" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19">
+      <c r="A116" t="s">
+        <v>139</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I116" t="s">
+        <v>271</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116" t="s">
+        <v>283</v>
+      </c>
+      <c r="O116" t="s">
+        <v>295</v>
+      </c>
+      <c r="P116" s="3">
+        <v>45939.98240740741</v>
+      </c>
+      <c r="Q116" s="3">
+        <v>45939.98240740741</v>
+      </c>
+      <c r="R116">
+        <v>9.31</v>
+      </c>
+      <c r="S116" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19">
+      <c r="A117" t="s">
+        <v>140</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I117" t="s">
+        <v>272</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117" t="s">
+        <v>283</v>
+      </c>
+      <c r="O117" t="s">
+        <v>295</v>
+      </c>
+      <c r="P117" s="3">
+        <v>46198.62712962963</v>
+      </c>
+      <c r="Q117" s="3">
+        <v>46198.62712962963</v>
+      </c>
+      <c r="R117">
+        <v>5.69</v>
+      </c>
+      <c r="S117" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19">
+      <c r="A118" t="s">
+        <v>141</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I118" t="s">
+        <v>276</v>
+      </c>
+      <c r="M118">
+        <v>1</v>
+      </c>
+      <c r="N118" t="s">
+        <v>283</v>
+      </c>
+      <c r="O118" t="s">
+        <v>295</v>
+      </c>
+      <c r="P118" s="3">
+        <v>45990.94167824074</v>
+      </c>
+      <c r="Q118" s="3">
+        <v>45990.94167824074</v>
+      </c>
+      <c r="R118">
+        <v>5.69</v>
+      </c>
+      <c r="S118" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19">
+      <c r="A119" t="s">
+        <v>142</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I119" t="s">
+        <v>275</v>
+      </c>
+      <c r="M119">
+        <v>1</v>
+      </c>
+      <c r="N119" t="s">
+        <v>283</v>
+      </c>
+      <c r="O119" t="s">
+        <v>295</v>
+      </c>
+      <c r="P119" s="3">
+        <v>45913.74726851852</v>
+      </c>
+      <c r="Q119" s="3">
+        <v>45913.74726851852</v>
+      </c>
+      <c r="R119">
+        <v>5.69</v>
+      </c>
+      <c r="S119" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19">
+      <c r="A120" t="s">
+        <v>143</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="M120">
+        <v>1</v>
+      </c>
+      <c r="N120" t="s">
+        <v>283</v>
+      </c>
+      <c r="O120" t="s">
+        <v>295</v>
+      </c>
+      <c r="P120" s="3">
+        <v>46323.27373842592</v>
+      </c>
+      <c r="Q120" s="3">
+        <v>46323.27373842592</v>
+      </c>
+      <c r="R120">
+        <v>5.69</v>
+      </c>
+      <c r="S120" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19">
+      <c r="A121" t="s">
+        <v>144</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I121" t="s">
+        <v>273</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121" t="s">
+        <v>283</v>
+      </c>
+      <c r="O121" t="s">
+        <v>295</v>
+      </c>
+      <c r="P121" s="3">
+        <v>46221.60350694445</v>
+      </c>
+      <c r="Q121" s="3">
+        <v>46221.60350694445</v>
+      </c>
+      <c r="R121">
+        <v>5.69</v>
+      </c>
+      <c r="S121" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19">
+      <c r="A122" t="s">
+        <v>145</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I122" t="s">
+        <v>275</v>
+      </c>
+      <c r="M122">
+        <v>2</v>
+      </c>
+      <c r="N122" t="s">
+        <v>283</v>
+      </c>
+      <c r="O122" t="s">
+        <v>295</v>
+      </c>
+      <c r="P122" s="3">
         <v>46196.65561342592</v>
       </c>
-      <c r="Q93" s="3">
+      <c r="Q122" s="3">
         <v>46224.32857638889</v>
       </c>
-      <c r="R93">
+      <c r="R122">
         <v>11.38</v>
       </c>
-      <c r="S93" t="s">
-        <v>236</v>
+      <c r="S122" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -4397,6 +5439,35 @@
     <hyperlink ref="B91" r:id="rId90"/>
     <hyperlink ref="B92" r:id="rId91"/>
     <hyperlink ref="B93" r:id="rId92"/>
+    <hyperlink ref="B94" r:id="rId93"/>
+    <hyperlink ref="B95" r:id="rId94"/>
+    <hyperlink ref="B96" r:id="rId95"/>
+    <hyperlink ref="B97" r:id="rId96"/>
+    <hyperlink ref="B98" r:id="rId97"/>
+    <hyperlink ref="B99" r:id="rId98"/>
+    <hyperlink ref="B100" r:id="rId99"/>
+    <hyperlink ref="B101" r:id="rId100"/>
+    <hyperlink ref="B102" r:id="rId101"/>
+    <hyperlink ref="B103" r:id="rId102"/>
+    <hyperlink ref="B104" r:id="rId103"/>
+    <hyperlink ref="B105" r:id="rId104"/>
+    <hyperlink ref="B106" r:id="rId105"/>
+    <hyperlink ref="B107" r:id="rId106"/>
+    <hyperlink ref="B108" r:id="rId107"/>
+    <hyperlink ref="B109" r:id="rId108"/>
+    <hyperlink ref="B110" r:id="rId109"/>
+    <hyperlink ref="B111" r:id="rId110"/>
+    <hyperlink ref="B112" r:id="rId111"/>
+    <hyperlink ref="B113" r:id="rId112"/>
+    <hyperlink ref="B114" r:id="rId113"/>
+    <hyperlink ref="B115" r:id="rId114"/>
+    <hyperlink ref="B116" r:id="rId115"/>
+    <hyperlink ref="B117" r:id="rId116"/>
+    <hyperlink ref="B118" r:id="rId117"/>
+    <hyperlink ref="B119" r:id="rId118"/>
+    <hyperlink ref="B120" r:id="rId119"/>
+    <hyperlink ref="B121" r:id="rId120"/>
+    <hyperlink ref="B122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
